--- a/data/noticias.xlsx
+++ b/data/noticias.xlsx
@@ -466,17 +466,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Impactante video de una joven que se lanzó por un tobogán en Cocorná, Antioquia: la adolescente quedó inconsciente en la piscina</t>
+          <t>Una empresa digital de aseo de hogares y oficinas le ha ido ganando terreno a la tradicional Casa Limpia</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Las2orillas</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -486,12 +486,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Empleo</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -501,12 +501,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/09/14/impactante-video-de-una-joven-que-se-lanzo-por-un-tobogan-en-cocorna-antioquia-la-adolescente-quedo-inconsciente-en-la-piscina/</t>
+          <t>https://www.las2orillas.co/una-empresa-digital-de-aseo-de-hogares-y-oficinas-le-ha-ido-ganando-terreno-a-la-tradicional-casa-limpia/</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Las imágenes difundidas en redes sociales muestran el instante en que la usuaria llegó al agua y la reacción de varias personas para socorrerla</t>
+          <t>Hogarú nació para responder a las necesidades de jóvenes que han cambiado la relación laboral directa con empleadas domésticasEl artículoUna empresa digital de aseo de hogares y oficinas le ha ido ganando terreno a la tradicional Casa Limpiafue...</t>
         </is>
       </c>
     </row>
@@ -518,12 +518,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Una empresa digital de aseo de hogares y oficinas le ha ido ganando terreno a la tradicional Casa Limpia</t>
+          <t>Impactante video de una joven que se lanzó por un tobogán en Cocorná, Antioquia: la adolescente quedó inconsciente en la piscina</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Las2orillas</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -533,12 +533,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Empleo</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Medellín</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -548,12 +548,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.las2orillas.co/una-empresa-digital-de-aseo-de-hogares-y-oficinas-le-ha-ido-ganando-terreno-a-la-tradicional-casa-limpia/</t>
+          <t>https://www.infobae.com/colombia/2026/09/14/impactante-video-de-una-joven-que-se-lanzo-por-un-tobogan-en-cocorna-antioquia-la-adolescente-quedo-inconsciente-en-la-piscina/</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Hogarú nació para responder a las necesidades de jóvenes que han cambiado la relación laboral directa con empleadas domésticasEl artículoUna empresa digital de aseo de hogares y oficinas le ha ido ganando terreno a la tradicional Casa Limpiafue...</t>
+          <t>Las imágenes difundidas en redes sociales muestran el instante en que la usuaria llegó al agua y la reacción de varias personas para socorrerla</t>
         </is>
       </c>
     </row>

--- a/data/noticias.xlsx
+++ b/data/noticias.xlsx
@@ -466,17 +466,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Una empresa digital de aseo de hogares y oficinas le ha ido ganando terreno a la tradicional Casa Limpia</t>
+          <t>Familia busca a Hever Stiven Muñoz Giraldo, joven desaparecido en la vereda Chembe de Ibagué desde el 8 de septiembre</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Las2orillas</t>
+          <t>Pulzo</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -486,12 +486,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Empleo</t>
+          <t>Protección</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Ibagué</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -501,14 +501,10 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.las2orillas.co/una-empresa-digital-de-aseo-de-hogares-y-oficinas-le-ha-ido-ganando-terreno-a-la-tradicional-casa-limpia/</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Hogarú nació para responder a las necesidades de jóvenes que han cambiado la relación laboral directa con empleadas domésticasEl artículoUna empresa digital de aseo de hogares y oficinas le ha ido ganando terreno a la tradicional Casa Limpiafue...</t>
-        </is>
-      </c>
+          <t>https://www.pulzo.com/nacion/desaparicion-de-hever-stiven-munoz-giraldo-en-ibague-datos-clave-y-como-ayudar-PP5304535A</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">

--- a/data/noticias.xlsx
+++ b/data/noticias.xlsx
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/data/noticias.xlsx
+++ b/data/noticias.xlsx
@@ -466,17 +466,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Joven de 20 años fue asesinado durante una riña cerca del estadio Armando Maestre en Valledupar</t>
+          <t>Un dirigente empresarial y político samario cuñado del influyente Joaquín Gutiérrez será el presidente de Coljuegos</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Pulzo</t>
+          <t>Las2orillas</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -486,12 +486,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Valledupar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -501,30 +501,34 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.pulzo.com/nacion/valledupar-detalles-del-asesinato-de-keiner-acuna-y-captura-de-gonzalo-palacio-cujia-PP5309154A</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>https://www.las2orillas.co/un-dirigente-empresarial-y-politico-samario-cunado-del-influyente-joaquin-gutierrez-sera-el-presidente-de-coljuegos/</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Jaime Vives Pinedo llega a uno de los cargos bien remunerados en un momento en que el sector está al alza y mueve un presupuesto anual de $ 1.5 billonesEl artículoUn dirigente empresarial y político samario cuñado del influyente Joaquín Gutiérrez...</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Jóvenes con machetes se subieron a una ‘chiva rumbera’ y generaron pánico en Ibagué: autoridades investigan lo ocurrido</t>
+          <t>Prosperidad Social entregará transferencias a beneficiarios afectados por el terremoto sin verificación de condicionalidades y corresponsabilidades</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Prosperidad Social</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -534,22 +538,22 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ibagué</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/09/21/jovenes-con-machetes-se-subieron-a-una-chiva-rumbera-y-generaron-panico-en-ibague-autoridades-investigan-lo-ocurrido/</t>
+          <t>https://prosperidadsocial.gov.co/Noticias/prosperidad-social-entregara-transferencias-a-beneficiarios-afectados-por-el-terremoto-sin-verificacion-de-condicionalidades-y-corresponsabilidades/</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>La hipótesis preliminar apunta a un conflicto entre jóvenes de distintas comunas, algunos posiblemente menores de edad</t>
+          <t>El Gobierno nacional autorizó a Prosperidad Social a suspender temporalmente las verificaciones de corresponsabilidades que no puedan realizarse por las afectaciones del terremoto. La medida busca evitar que beneficiarios pierdan o retrasen sus...</t>
         </is>
       </c>
     </row>
@@ -561,12 +565,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Un dirigente empresarial y político samario cuñado del influyente Joaquín Gutiérrez será el presidente de Coljuegos</t>
+          <t>Joven de 20 años fue asesinado durante una riña cerca del estadio Armando Maestre en Valledupar</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Las2orillas</t>
+          <t>Pulzo</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -576,12 +580,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Valledupar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -591,14 +595,10 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.las2orillas.co/un-dirigente-empresarial-y-politico-samario-cunado-del-influyente-joaquin-gutierrez-sera-el-presidente-de-coljuegos/</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Jaime Vives Pinedo llega a uno de los cargos bien remunerados en un momento en que el sector está al alza y mueve un presupuesto anual de $ 1.5 billonesEl artículoUn dirigente empresarial y político samario cuñado del influyente Joaquín Gutiérrez...</t>
-        </is>
-      </c>
+          <t>https://www.pulzo.com/nacion/valledupar-detalles-del-asesinato-de-keiner-acuna-y-captura-de-gonzalo-palacio-cujia-PP5309154A</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -608,17 +608,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Prosperidad Social entregará transferencias a beneficiarios afectados por el terremoto sin verificación de condicionalidades y corresponsabilidades</t>
+          <t>Jóvenes con machetes se subieron a una ‘chiva rumbera’ y generaron pánico en Ibagué: autoridades investigan lo ocurrido</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Prosperidad Social</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -628,22 +628,22 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Ibagué</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://prosperidadsocial.gov.co/Noticias/prosperidad-social-entregara-transferencias-a-beneficiarios-afectados-por-el-terremoto-sin-verificacion-de-condicionalidades-y-corresponsabilidades/</t>
+          <t>https://www.infobae.com/colombia/2026/09/21/jovenes-con-machetes-se-subieron-a-una-chiva-rumbera-y-generaron-panico-en-ibague-autoridades-investigan-lo-ocurrido/</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>El Gobierno nacional autorizó a Prosperidad Social a suspender temporalmente las verificaciones de corresponsabilidades que no puedan realizarse por las afectaciones del terremoto. La medida busca evitar que beneficiarios pierdan o retrasen sus...</t>
+          <t>La hipótesis preliminar apunta a un conflicto entre jóvenes de distintas comunas, algunos posiblemente menores de edad</t>
         </is>
       </c>
     </row>

--- a/data/noticias.xlsx
+++ b/data/noticias.xlsx
@@ -466,27 +466,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Por muerte de Donovan Balanta Paz en Ciudad Bolívar, Policía anunció investigación disciplinaria y suspendió a siete uniformados</t>
+          <t>Prosperidad Social entregará transferencias a beneficiarios afectados por el terremoto sin verificación de condicionalidades y corresponsabilidades</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Prosperidad Social</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -501,12 +501,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/deportes/2026/09/23/por-muerte-de-donovan-balanta-paz-en-ciudad-bolivar-policia-anuncio-investigacion-disciplinaria-y-suspendio-a-siete-uniformados/</t>
+          <t>https://prosperidadsocial.gov.co/Noticias/prosperidad-social-entregara-transferencias-a-beneficiarios-afectados-por-el-terremoto-sin-verificacion-de-condicionalidades-y-corresponsabilidades/</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>El caso se presentó en el sector de Caracolí, un punto limítrofe entre el sur de Bogotá y el vecino municipio de Soacha, en Cundinamarca. La familia del joven de 34 años pide justicia</t>
+          <t>El Gobierno nacional autorizó a Prosperidad Social a suspender temporalmente las verificaciones de corresponsabilidades que no puedan realizarse por las afectaciones del terremoto. La medida busca evitar que beneficiarios pierdan o retrasen sus...</t>
         </is>
       </c>
     </row>
@@ -518,22 +518,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Prosperidad Social entregará transferencias a beneficiarios afectados por el terremoto sin verificación de condicionalidades y corresponsabilidades</t>
+          <t>Por muerte de Donovan Balanta Paz en Ciudad Bolívar, Policía anunció investigación disciplinaria y suspendió a siete uniformados</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Prosperidad Social</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -548,12 +548,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://prosperidadsocial.gov.co/Noticias/prosperidad-social-entregara-transferencias-a-beneficiarios-afectados-por-el-terremoto-sin-verificacion-de-condicionalidades-y-corresponsabilidades/</t>
+          <t>https://www.infobae.com/colombia/deportes/2026/09/23/por-muerte-de-donovan-balanta-paz-en-ciudad-bolivar-policia-anuncio-investigacion-disciplinaria-y-suspendio-a-siete-uniformados/</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>El Gobierno nacional autorizó a Prosperidad Social a suspender temporalmente las verificaciones de corresponsabilidades que no puedan realizarse por las afectaciones del terremoto. La medida busca evitar que beneficiarios pierdan o retrasen sus...</t>
+          <t>El caso se presentó en el sector de Caracolí, un punto limítrofe entre el sur de Bogotá y el vecino municipio de Soacha, en Cundinamarca. La familia del joven de 34 años pide justicia</t>
         </is>
       </c>
     </row>

--- a/data/noticias.xlsx
+++ b/data/noticias.xlsx
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/data/noticias.xlsx
+++ b/data/noticias.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I231"/>
+  <dimension ref="A1:I229"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,74 +466,70 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Prosperidad Social entregará transferencias a beneficiarios afectados por el terremoto sin verificación de condicionalidades y corresponsabilidades</t>
+          <t>Los jovenes en colombia estan leyendo peor: lo que dicen las pruebas pisa 2025 sobre los trabajadores del futuro</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Prosperidad Social</t>
+          <t>Portafolio</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Política pública</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://prosperidadsocial.gov.co/Noticias/prosperidad-social-entregara-transferencias-a-beneficiarios-afectados-por-el-terremoto-sin-verificacion-de-condicionalidades-y-corresponsabilidades/</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>El Gobierno nacional autorizó a Prosperidad Social a suspender temporalmente las verificaciones de corresponsabilidades que no puedan realizarse por las afectaciones del terremoto. La medida busca evitar que beneficiarios pierdan o retrasen sus...</t>
-        </is>
-      </c>
+          <t>https://www.portafolio.co/economia/los-jovenes-en-colombia-estan-leyendo-peor-lo-que-dicen-las-pruebas-pisa-2025-sobre-los-trabajadores-del-futuro-503346</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Por muerte de Donovan Balanta Paz en Ciudad Bolívar, Policía anunció investigación disciplinaria y suspendió a siete uniformados</t>
+          <t>Prosperidad Social entregará transferencias a beneficiarios afectados por el terremoto sin verificación de condicionalidades y corresponsabilidades</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Prosperidad Social</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -548,29 +544,29 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/deportes/2026/09/23/por-muerte-de-donovan-balanta-paz-en-ciudad-bolivar-policia-anuncio-investigacion-disciplinaria-y-suspendio-a-siete-uniformados/</t>
+          <t>https://prosperidadsocial.gov.co/Noticias/prosperidad-social-entregara-transferencias-a-beneficiarios-afectados-por-el-terremoto-sin-verificacion-de-condicionalidades-y-corresponsabilidades/</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>El caso se presentó en el sector de Caracolí, un punto limítrofe entre el sur de Bogotá y el vecino municipio de Soacha, en Cundinamarca. La familia del joven de 34 años pide justicia</t>
+          <t>El Gobierno nacional autorizó a Prosperidad Social a suspender temporalmente las verificaciones de corresponsabilidades que no puedan realizarse por las afectaciones del terremoto. La medida busca evitar que beneficiarios pierdan o retrasen sus...</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Joven de 20 años fue asesinado durante una riña cerca del estadio Armando Maestre en Valledupar</t>
+          <t>Por muerte de Donovan Balanta Paz en Ciudad Bolívar, Policía anunció investigación disciplinaria y suspendió a siete uniformados</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Pulzo</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -585,20 +581,24 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Valledupar</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.pulzo.com/nacion/valledupar-detalles-del-asesinato-de-keiner-acuna-y-captura-de-gonzalo-palacio-cujia-PP5309154A</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>https://www.infobae.com/colombia/deportes/2026/09/23/por-muerte-de-donovan-balanta-paz-en-ciudad-bolivar-policia-anuncio-investigacion-disciplinaria-y-suspendio-a-siete-uniformados/</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>El caso se presentó en el sector de Caracolí, un punto limítrofe entre el sur de Bogotá y el vecino municipio de Soacha, en Cundinamarca. La familia del joven de 34 años pide justicia</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -608,12 +608,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Jóvenes con machetes se subieron a una ‘chiva rumbera’ y generaron pánico en Ibagué: autoridades investigan lo ocurrido</t>
+          <t>Joven de 20 años fue asesinado durante una riña cerca del estadio Armando Maestre en Valledupar</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Pulzo</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -623,12 +623,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ibagué</t>
+          <t>Valledupar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -638,24 +638,20 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/09/21/jovenes-con-machetes-se-subieron-a-una-chiva-rumbera-y-generaron-panico-en-ibague-autoridades-investigan-lo-ocurrido/</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>La hipótesis preliminar apunta a un conflicto entre jóvenes de distintas comunas, algunos posiblemente menores de edad</t>
-        </is>
-      </c>
+          <t>https://www.pulzo.com/nacion/valledupar-detalles-del-asesinato-de-keiner-acuna-y-captura-de-gonzalo-palacio-cujia-PP5309154A</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Un camión de basura chocó de atrás a un auto conducido por un joven alcoholizado: el impactante resultado del test</t>
+          <t>Jóvenes con machetes se subieron a una ‘chiva rumbera’ y generaron pánico en Ibagué: autoridades investigan lo ocurrido</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -675,7 +671,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Quibdó</t>
+          <t>Ibagué</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -685,29 +681,29 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/sociedad/2026/09/18/un-camion-de-basura-choco-de-atras-a-un-auto-conducido-por-un-joven-alcoholizado-el-impactante-resultado-del-test/</t>
+          <t>https://www.infobae.com/colombia/2026/09/21/jovenes-con-machetes-se-subieron-a-una-chiva-rumbera-y-generaron-panico-en-ibague-autoridades-investigan-lo-ocurrido/</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>El siniestro ocurrió esta mañana cerca de la Planetario, en el cruce de Belisario Roldán y Casares. El vehículo de mayor porte no llegó a maniobrar luego de una brusca frenada del coche a escasos metros</t>
+          <t>La hipótesis preliminar apunta a un conflicto entre jóvenes de distintas comunas, algunos posiblemente menores de edad</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Familia busca a Hever Stiven Muñoz Giraldo, joven desaparecido en la vereda Chembe de Ibagué desde el 8 de septiembre</t>
+          <t>Un camión de basura chocó de atrás a un auto conducido por un joven alcoholizado: el impactante resultado del test</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Pulzo</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -717,12 +713,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Protección</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ibagué</t>
+          <t>Quibdó</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -732,25 +728,29 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.pulzo.com/nacion/desaparicion-de-hever-stiven-munoz-giraldo-en-ibague-datos-clave-y-como-ayudar-PP5304535A</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>https://www.infobae.com/sociedad/2026/09/18/un-camion-de-basura-choco-de-atras-a-un-auto-conducido-por-un-joven-alcoholizado-el-impactante-resultado-del-test/</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>El siniestro ocurrió esta mañana cerca de la Planetario, en el cruce de Belisario Roldán y Casares. El vehículo de mayor porte no llegó a maniobrar luego de una brusca frenada del coche a escasos metros</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Impactante video de una joven que se lanzó por un tobogán en Cocorná, Antioquia: la adolescente quedó inconsciente en la piscina</t>
+          <t>Familia busca a Hever Stiven Muñoz Giraldo, joven desaparecido en la vereda Chembe de Ibagué desde el 8 de septiembre</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Pulzo</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -760,12 +760,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Protección</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Ibagué</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -775,29 +775,25 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/09/14/impactante-video-de-una-joven-que-se-lanzo-por-un-tobogan-en-cocorna-antioquia-la-adolescente-quedo-inconsciente-en-la-piscina/</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Las imágenes difundidas en redes sociales muestran el instante en que la usuaria llegó al agua y la reacción de varias personas para socorrerla</t>
-        </is>
-      </c>
+          <t>https://www.pulzo.com/nacion/desaparicion-de-hever-stiven-munoz-giraldo-en-ibague-datos-clave-y-como-ayudar-PP5304535A</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>De la Espriella le puso dura tarea a Restrepo: esto es lo que viene para 2,5 millones de jóvenes en Colombia</t>
+          <t>Impactante video de una joven que se lanzó por un tobogán en Cocorná, Antioquia: la adolescente quedó inconsciente en la piscina</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Pulzo</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -812,7 +808,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Medellín</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -822,20 +818,24 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.pulzo.com/nacion/5-misiones-vicepresidente-restrepo-para-impulsar-economia-colombia-PP5300986</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>https://www.infobae.com/colombia/2026/09/14/impactante-video-de-una-joven-que-se-lanzo-por-un-tobogan-en-cocorna-antioquia-la-adolescente-quedo-inconsciente-en-la-piscina/</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Las imágenes difundidas en redes sociales muestran el instante en que la usuaria llegó al agua y la reacción de varias personas para socorrerla</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Idartes organiza visita multisensorial inclusiva al XVI Salón Nacional de Arte Joven en la Galería Santa Fe de Bogotá</t>
+          <t>De la Espriella le puso dura tarea a Restrepo: esto es lo que viene para 2,5 millones de jóvenes en Colombia</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -850,22 +850,22 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Cultura y deporte</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.pulzo.com/nacion/bogota/visita-multisensorial-inclusiva-en-galeria-santa-fe-arte-accesible-para-todos-en-bogota-PP5299732A</t>
+          <t>https://www.pulzo.com/nacion/5-misiones-vicepresidente-restrepo-para-impulsar-economia-colombia-PP5300986</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -878,12 +878,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Venecia descubre 'Los poderes': una confesión colombiana de lo errático de la juventud</t>
+          <t>Idartes organiza visita multisensorial inclusiva al XVI Salón Nacional de Arte Joven en la Galería Santa Fe de Bogotá</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Pulzo</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -893,22 +893,22 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Cultura y deporte</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/america/agencias/2026/09/11/venecia-descubre-los-poderes-una-confesion-colombiana-de-lo-erratico-de-la-juventud/</t>
+          <t>https://www.pulzo.com/nacion/bogota/visita-multisensorial-inclusiva-en-galeria-santa-fe-arte-accesible-para-todos-en-bogota-PP5299732A</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -916,12 +916,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Quedan prohibidos los celulares en los colegios de Bogotá: el Distrito explicó los alcances de la medida para establecimientos públicos y privados</t>
+          <t>Venecia descubre 'Los poderes': una confesión colombiana de lo errático de la juventud</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -936,106 +936,102 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/09/07/quedan-prohibidos-los-celulares-en-los-colegios-de-bogota-el-distrito-explico-los-alcances-de-la-medida-para-establecimientos-publicos-y-privados/</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>La medida rige para instituciones públicas y privadas, y busca resguardar el tiempo de estudio de niñas, niños y jóvenes, con reglas durante clases y descansos y con excepciones por salud y emergencias</t>
-        </is>
-      </c>
+          <t>https://www.infobae.com/america/agencias/2026/09/11/venecia-descubre-los-poderes-una-confesion-colombiana-de-lo-erratico-de-la-juventud/</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Adulta mayor de 94 años habría sido víctima de abuso en hogar geriátrico de Antioquia</t>
+          <t>Quedan prohibidos los celulares en los colegios de Bogotá: el Distrito explicó los alcances de la medida para establecimientos públicos y privados</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Protección</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/mas-regiones/adulta-mayor-de-94-anos-habria-sido-victima-de-abuso-en-hogar-geriatrico-de-antioquia/</t>
+          <t>https://www.infobae.com/colombia/2026/09/07/quedan-prohibidos-los-celulares-en-los-colegios-de-bogota-el-distrito-explico-los-alcances-de-la-medida-para-establecimientos-publicos-y-privados/</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Tres jóvenes que realizaban prácticas en un hogar para adultos mayores sin investigados por presuntos abusos contra una mujer de 94 años.</t>
+          <t>La medida rige para instituciones públicas y privadas, y busca resguardar el tiempo de estudio de niñas, niños y jóvenes, con reglas durante clases y descansos y con excepciones por salud y emergencias</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cómo los jóvenes pueden sumar experiencia profesional antes de su primer empleo en Colombia, según expertos</t>
+          <t>Adulta mayor de 94 años habría sido víctima de abuso en hogar geriátrico de Antioquia</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Pulzo</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Empleo</t>
+          <t>Protección</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Medellín</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1045,25 +1041,29 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://www.pulzo.com/empleo/primer-empleo-en-colombia-como-construir-experiencia-profesional-antes-de-graduarse-PP5293106A</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>https://www.elespectador.com/colombia/mas-regiones/adulta-mayor-de-94-anos-habria-sido-victima-de-abuso-en-hogar-geriatrico-de-antioquia/</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Tres jóvenes que realizaban prácticas en un hogar para adultos mayores sin investigados por presuntos abusos contra una mujer de 94 años.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Niña de cinco años fue encontrada deambulando por las calles en Bogotá: estaba buscando a su mamá que habría salido con unos amigos</t>
+          <t>Cómo los jóvenes pueden sumar experiencia profesional antes de su primer empleo en Colombia, según expertos</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Pulzo</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1073,29 +1073,25 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Seguridad</t>
+          <t>Empleo</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/09/03/nina-de-cinco-anos-fue-encontrada-deambulando-por-las-calles-en-bogota-estaba-buscando-a-su-mama-que-habria-salido-con-unos-amigos/</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>La Policía de Infancia y Adolescencia llegó al lugar y adelantó las labores de revisión física y emocional de la pequeña que se encontraba llorando y en pijama en el momento del encuentro</t>
-        </is>
-      </c>
+          <t>https://www.pulzo.com/empleo/primer-empleo-en-colombia-como-construir-experiencia-profesional-antes-de-graduarse-PP5293106A</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1105,42 +1101,42 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Jineth Bedoya recibió el Premio Nacional de Periodismo Silvia Galvis 2026 a la Trayectoria</t>
+          <t>Niña de cinco años fue encontrada deambulando por las calles en Bogotá: estaba buscando a su mamá que habría salido con unos amigos</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Seguridad</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bucaramanga</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/el-magazin-cultural/jineth-bedoya-recibio-el-premio-nacional-de-periodismo-silvia-galvis-2026-a-la-trayectoria/</t>
+          <t>https://www.infobae.com/colombia/2026/09/03/nina-de-cinco-anos-fue-encontrada-deambulando-por-las-calles-en-bogota-estaba-buscando-a-su-mama-que-habria-salido-con-unos-amigos/</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>La Universidad Autónoma de Bucaramanga (UNAB) también entregó los galardones anuales al mejor periodismo de Opinión, Regional y de Jóvenes.</t>
+          <t>La Policía de Infancia y Adolescencia llegó al lugar y adelantó las labores de revisión física y emocional de la pequeña que se encontraba llorando y en pijama en el momento del encuentro</t>
         </is>
       </c>
     </row>
@@ -1152,7 +1148,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Los pueblos del Valle empiezan a reconstruirse tras el terremoto</t>
+          <t>Jineth Bedoya recibió el Premio Nacional de Periodismo Silvia Galvis 2026 a la Trayectoria</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1167,12 +1163,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Popayán</t>
+          <t>Bucaramanga</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1182,12 +1178,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/mas-regiones/los-pueblos-del-valle-empiezan-a-reconstruirse-tras-el-terremoto/</t>
+          <t>https://www.elespectador.com/el-magazin-cultural/jineth-bedoya-recibio-el-premio-nacional-de-periodismo-silvia-galvis-2026-a-la-trayectoria/</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Convites, mingas y con más de 80 jóvenes, así comenzó la reconstrucción desde las comunidades en el Valle del Cauca.</t>
+          <t>La Universidad Autónoma de Bucaramanga (UNAB) también entregó los galardones anuales al mejor periodismo de Opinión, Regional y de Jóvenes.</t>
         </is>
       </c>
     </row>
@@ -1199,27 +1195,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>El paisa que pasó de pintar vallas publicitarias a crear una colección de esculturas de Botero en icopor</t>
+          <t>Los pueblos del Valle empiezan a reconstruirse tras el terremoto</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Las2orillas</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Cultura y deporte</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Popayán</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1229,12 +1225,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://www.las2orillas.co/el-paisa-que-paso-de-pintar-vallas-publicitarias-a-crear-una-coleccion-de-esculturas-de-botero-en-icopor/</t>
+          <t>https://www.elespectador.com/colombia/mas-regiones/los-pueblos-del-valle-empiezan-a-reconstruirse-tras-el-terremoto/</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>José González, habitante de la Comuna 9, creó réplicas de Fernando Botero en icopor para acercar el arte a los jóvenes y rescatar la memoria del maestro en MedellínEl artículoEl paisa que pasó de pintar vallas publicitarias a crear una colección de...</t>
+          <t>Convites, mingas y con más de 80 jóvenes, así comenzó la reconstrucción desde las comunidades en el Valle del Cauca.</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1242,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Tres películas nacionales logran llegar al gran Festival de Cine de Venecia, pero aún los colombianos no las pueden ver</t>
+          <t>El paisa que pasó de pintar vallas publicitarias a crear una colección de esculturas de Botero en icopor</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1266,7 +1262,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Medellín</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1276,118 +1272,118 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.las2orillas.co/tres-peliculas-nacionales-logran-llegar-al-gran-festival-de-cine-de-venecia-pero-aun-los-colombianos-no-las-pueden-ver/</t>
+          <t>https://www.las2orillas.co/el-paisa-que-paso-de-pintar-vallas-publicitarias-a-crear-una-coleccion-de-esculturas-de-botero-en-icopor/</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Los directores son 4 jóvenes colombianos que se la jugaron con sus propios medios y se impusieron a miles de producciones para llegar a la codiciada competenciaEl artículoTres películas nacionales logran llegar al gran Festival de Cine de Venecia,...</t>
+          <t>José González, habitante de la Comuna 9, creó réplicas de Fernando Botero en icopor para acercar el arte a los jóvenes y rescatar la memoria del maestro en MedellínEl artículoEl paisa que pasó de pintar vallas publicitarias a crear una colección de...</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>¡Hay más tiempo! Bogotá amplía las inscripciones a los Concursos Juveniles 2026</t>
+          <t>Tres películas nacionales logran llegar al gran Festival de Cine de Venecia, pero aún los colombianos no las pueden ver</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>SDIS - Juventud</t>
+          <t>Las2orillas</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Cultura y deporte</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#12dfbb473d</t>
+          <t>https://www.las2orillas.co/tres-peliculas-nacionales-logran-llegar-al-gran-festival-de-cine-de-venecia-pero-aun-los-colombianos-no-las-pueden-ver/</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Bogotá, D.C., septiembre 2 de 2026.La Secretaría Distrital de Integración Social, a través de la Subdirección para la Juventud, amplió hasta el 8 de septiembre de 2026 el plazo de inscripción a los Concursos Juveniles que se desarrollan en el marco...</t>
+          <t>Los directores son 4 jóvenes colombianos que se la jugaron con sus propios medios y se impusieron a miles de producciones para llegar a la codiciada competenciaEl artículoTres películas nacionales logran llegar al gran Festival de Cine de Venecia,...</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Liberaron a tres jóvenes secuestrados en Anorí, Antioquia, luego de operativo militar</t>
+          <t>¡Hay más tiempo! Bogotá amplía las inscripciones a los Concursos Juveniles 2026</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>SDIS - Juventud</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Seguridad</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/mas-regiones/liberaron-a-tres-jovenes-secuestrados-en-anori-antioquia-luego-de-operativo-militar/</t>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#12dfbb473d</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Los jóvenes habían sido retenidos en el corregimiento Charcón de Liberia, en Anorí. El Ejército los liberó tras un operativo realizado.</t>
+          <t>Bogotá, D.C., septiembre 2 de 2026.La Secretaría Distrital de Integración Social, a través de la Subdirección para la Juventud, amplió hasta el 8 de septiembre de 2026 el plazo de inscripción a los Concursos Juveniles que se desarrollan en el marco...</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Investigan asesinato de adolescente LGBT hallado con presuntos signos de tortura en Medellín</t>
+          <t>Liberaron a tres jóvenes secuestrados en Anorí, Antioquia, luego de operativo militar</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1402,7 +1398,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Seguridad</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1417,12 +1413,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/medellin/investigan-asesinato-de-adolescente-lgbti-hallado-con-presuntos-signos-de-tortura-en-medellin/</t>
+          <t>https://www.elespectador.com/colombia/mas-regiones/liberaron-a-tres-jovenes-secuestrados-en-anori-antioquia-luego-de-operativo-militar/</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Johan Alexis Naranjo Cuesta, de 17 años, fue hallado con varias heridas en su cuerpo dentro de la casa de su mamá.</t>
+          <t>Los jóvenes habían sido retenidos en el corregimiento Charcón de Liberia, en Anorí. El Ejército los liberó tras un operativo realizado.</t>
         </is>
       </c>
     </row>
@@ -1434,27 +1430,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Prosperidad social anuncia entrega de renta joven y colombia mayor: vea como cobrar el septimo ciclo de septiembre</t>
+          <t>Investigan asesinato de adolescente LGBT hallado con presuntos signos de tortura en Medellín</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Portafolio</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Medellín</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1464,25 +1460,29 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://www.portafolio.co/economia/gobierno/prosperidad-social-anuncia-entrega-de-renta-joven-y-colombia-mayor-vea-como-cobrar-el-septimo-ciclo-de-septiembre-501487</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>https://www.elespectador.com/colombia/medellin/investigan-asesinato-de-adolescente-lgbti-hallado-con-presuntos-signos-de-tortura-en-medellin/</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Johan Alexis Naranjo Cuesta, de 17 años, fue hallado con varias heridas en su cuerpo dentro de la casa de su mamá.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>3 adolescentes fueron detenidos tras robar un vehículo en Bogotá: habían salido hace un mes del centro El Redentor</t>
+          <t>Prosperidad social anuncia entrega de renta joven y colombia mayor: vea como cobrar el septimo ciclo de septiembre</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Portafolio</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1492,29 +1492,25 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Seguridad</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/08/30/3-adolescentes-fueron-detenidos-tras-robar-un-vehiculo-en-bogota-habian-salido-hace-un-mes-del-centro-el-redentor/</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>La Policía Nacional reportó que los menores de 16 y 17 años intentaron huir en el carro sustraído, pero fueron interceptados en Santa Fe luego de que el GPS permitió ubicarlo</t>
-        </is>
-      </c>
+          <t>https://www.portafolio.co/economia/gobierno/prosperidad-social-anuncia-entrega-de-renta-joven-y-colombia-mayor-vea-como-cobrar-el-septimo-ciclo-de-septiembre-501487</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1524,54 +1520,54 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Dos muertos y 15 heridos dejó accidente de bus en Saldaña, Tolima</t>
+          <t>3 adolescentes fueron detenidos tras robar un vehículo en Bogotá: habían salido hace un mes del centro El Redentor</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Seguridad</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ibagué</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/mas-regiones/dos-muertos-y-15-heridos-dejo-accidente-de-bus-en-saldana-tolima/</t>
+          <t>https://www.infobae.com/colombia/2026/08/30/3-adolescentes-fueron-detenidos-tras-robar-un-vehiculo-en-bogota-habian-salido-hace-un-mes-del-centro-el-redentor/</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>El hecho se registró a un kilómetro del sector de Castilla. Entre los muertos hay un menor de edad.</t>
+          <t>La Policía Nacional reportó que los menores de 16 y 17 años intentaron huir en el carro sustraído, pero fueron interceptados en Santa Fe luego de que el GPS permitió ubicarlo</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Aerocivil investiga el video del hombre que voló montado sobre un dron en el Meta</t>
+          <t>Dos muertos y 15 heridos dejó accidente de bus en Saldaña, Tolima</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1586,12 +1582,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Villavicencio</t>
+          <t>Ibagué</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1601,44 +1597,44 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/mas-regiones/aerocivil-investigara-el-video-del-hombre-que-volo-montado-sobre-un-dron-en-el-meta/</t>
+          <t>https://www.elespectador.com/colombia/mas-regiones/dos-muertos-y-15-heridos-dejo-accidente-de-bus-en-saldana-tolima/</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Aerocivil anunció sanciones tras el video de un joven volando montado sobre un dron fumigador en Puerto Gaitán, Meta.</t>
+          <t>El hecho se registró a un kilómetro del sector de Castilla. Entre los muertos hay un menor de edad.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Detuvieron a un hombre por el ataque a tiros a tres adolescentes en José C. Paz</t>
+          <t>Aerocivil investiga el video del hombre que voló montado sobre un dron en el Meta</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Villavicencio</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1648,12 +1644,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/sociedad/policiales/2026/08/26/detuvieron-a-un-hombre-por-el-ataque-a-tiros-a-tres-adolescentes-en-jose-c-paz/</t>
+          <t>https://www.elespectador.com/colombia/mas-regiones/aerocivil-investigara-el-video-del-hombre-que-volo-montado-sobre-un-dron-en-el-meta/</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>La Policía bonaerense apresó al sospechoso de 40 años y le secuestró una pistola Beretta calibre 9 milímetros con municiones</t>
+          <t>Aerocivil anunció sanciones tras el video de un joven volando montado sobre un dron fumigador en Puerto Gaitán, Meta.</t>
         </is>
       </c>
     </row>
@@ -1665,7 +1661,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Astrónomos descubren un inesperado dato sobre la formación de planetas: los dos factores que influyen en su tamaño</t>
+          <t>Detuvieron a un hombre por el ataque a tiros a tres adolescentes en José C. Paz</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1680,12 +1676,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Valledupar</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1695,29 +1691,29 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/america/ciencia-america/2026/08/26/astronomos-descubren-un-inesperado-dato-sobre-la-formacion-de-planetas-los-dos-factores-que-influyen-en-su-tamano/</t>
+          <t>https://www.infobae.com/sociedad/policiales/2026/08/26/detuvieron-a-un-hombre-por-el-ataque-a-tiros-a-tres-adolescentes-en-jose-c-paz/</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Un equipo de astrónomos analizó 72 sistemas estelares jóvenes y descubrió que el gas necesario para crear gigantes como Júpiter desaparece en etapas predecibles</t>
+          <t>La Policía bonaerense apresó al sospechoso de 40 años y le secuestró una pistola Beretta calibre 9 milímetros con municiones</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Joven de 19 años asesinado en Flandes, Tolima: autoridades investigan ataque armado y posible vínculo familiar</t>
+          <t>Astrónomos descubren un inesperado dato sobre la formación de planetas: los dos factores que influyen en su tamaño</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Pulzo</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1727,12 +1723,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ibagué</t>
+          <t>Valledupar</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1742,40 +1738,44 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://www.pulzo.com/nacion/asesinato-de-juan-david-rojas-monzon-en-flandes-tolima-investigacion-y-contexto-PP5283828A</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>https://www.infobae.com/america/ciencia-america/2026/08/26/astronomos-descubren-un-inesperado-dato-sobre-la-formacion-de-planetas-los-dos-factores-que-influyen-en-su-tamano/</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Un equipo de astrónomos analizó 72 sistemas estelares jóvenes y descubrió que el gas necesario para crear gigantes como Júpiter desaparece en etapas predecibles</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Salwa Maloof Habib, la nueva reina del Carnaval de Barranquilla 2027: ¿quién es?</t>
+          <t>Joven de 19 años asesinado en Flandes, Tolima: autoridades investigan ataque armado y posible vínculo familiar</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Pulzo</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Barranquilla</t>
+          <t>Ibagué</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1785,14 +1785,10 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/barranquilla-ya-tiene-reina-salwa-maloof-habib-llevara-la-corona-del-carnaval-2027/</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Salwa Maloof Habib, fue elegida como reina del Carnaval de Barranquilla 2027. La joven es profesional en Relaciones Internacionales.</t>
-        </is>
-      </c>
+          <t>https://www.pulzo.com/nacion/asesinato-de-juan-david-rojas-monzon-en-flandes-tolima-investigacion-y-contexto-PP5283828A</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1802,7 +1798,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Salwa Maloof Habib es la nueva reina del Carnaval de Barranquilla</t>
+          <t>Salwa Maloof Habib, la nueva reina del Carnaval de Barranquilla 2027: ¿quién es?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1832,12 +1828,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/barranquilla/salwa-maloof-habib-es-la-nueva-reina-del-carnaval-de-barranquilla/</t>
+          <t>https://www.elespectador.com/colombia/barranquilla-ya-tiene-reina-salwa-maloof-habib-llevara-la-corona-del-carnaval-2027/</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>La Junta Directiva del Carnaval de Barranquilla designó a la joven de 24 años como embajadora de la fiesta Patrimonio de la Humanidad.</t>
+          <t>Salwa Maloof Habib, fue elegida como reina del Carnaval de Barranquilla 2027. La joven es profesional en Relaciones Internacionales.</t>
         </is>
       </c>
     </row>
@@ -1849,7 +1845,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Masacre en Barranquilla: asesinaron a tres personas en Las Nieves; dos eran menores de edad</t>
+          <t>Salwa Maloof Habib es la nueva reina del Carnaval de Barranquilla</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1864,7 +1860,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1879,12 +1875,12 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/barranquilla/masacre-en-barranquilla-asesinaron-a-tres-personas-en-las-nieves-dos-eran-menores-de-edad/</t>
+          <t>https://www.elespectador.com/colombia/barranquilla/salwa-maloof-habib-es-la-nueva-reina-del-carnaval-de-barranquilla/</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Las autoridades capturaron a dos adultos y un adolescente que habrían participado en masacre en Las Nieves, Barranquilla.</t>
+          <t>La Junta Directiva del Carnaval de Barranquilla designó a la joven de 24 años como embajadora de la fiesta Patrimonio de la Humanidad.</t>
         </is>
       </c>
     </row>
@@ -1896,27 +1892,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>El joven de Buga que quiere devolver a Colombia al gran ciclismo y sigue los pasos de Egan Bernal</t>
+          <t>Masacre en Barranquilla: asesinaron a tres personas en Las Nieves; dos eran menores de edad</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Las2orillas</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cultura y deporte</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Barranquilla</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1926,12 +1922,12 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://www.las2orillas.co/el-joven-de-buga-que-quiere-devolver-a-colombia-al-gran-ciclismo-y-sigue-los-pasos-de-egan-bernal/</t>
+          <t>https://www.elespectador.com/colombia/barranquilla/masacre-en-barranquilla-asesinaron-a-tres-personas-en-las-nieves-dos-eran-menores-de-edad/</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Juan David Quintero tiene 19 años y acaba de fichar por la academia del INEOS, donde buscará dar el salto al máximo nivel de su deporteEl artículoEl joven de Buga que quiere devolver a Colombia al gran ciclismo y sigue los pasos de Egan Bernalfue...</t>
+          <t>Las autoridades capturaron a dos adultos y un adolescente que habrían participado en masacre en Las Nieves, Barranquilla.</t>
         </is>
       </c>
     </row>
@@ -1943,7 +1939,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Lo que se sabe del joven que terminó muerto luego de atacar por el cuello a policía en un CAI de Bogotá</t>
+          <t>El joven de Buga que quiere devolver a Colombia al gran ciclismo y sigue los pasos de Egan Bernal</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1958,27 +1954,27 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Cultura y deporte</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://www.las2orillas.co/lo-que-se-sabe-del-joven-que-termino-muerto-luego-de-atacar-por-el-cuello-a-policia-en-un-cai-de-bogota/</t>
+          <t>https://www.las2orillas.co/el-joven-de-buga-que-quiere-devolver-a-colombia-al-gran-ciclismo-y-sigue-los-pasos-de-egan-bernal/</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Michael Santos agredió con un arma blanca al subintendente Rubén Ramírez en el CAI Galán, quien durante el forcejeo lo abatió con su arma de dotaciónEl artículoLo que se sabe del joven que terminó muerto luego de atacar por el cuello a policía en un...</t>
+          <t>Juan David Quintero tiene 19 años y acaba de fichar por la academia del INEOS, donde buscará dar el salto al máximo nivel de su deporteEl artículoEl joven de Buga que quiere devolver a Colombia al gran ciclismo y sigue los pasos de Egan Bernalfue...</t>
         </is>
       </c>
     </row>
@@ -1990,22 +1986,22 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Bogotá abre convocatoria con USD 40.000 para impulsar iniciativas de acción climática lideradas por jóvenes</t>
+          <t>Lo que se sabe del joven que terminó muerto luego de atacar por el cuello a policía en un CAI de Bogotá</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>SDIS - Juventud</t>
+          <t>Las2orillas</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2020,71 +2016,71 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#4d985ec1e7</t>
+          <t>https://www.las2orillas.co/lo-que-se-sabe-del-joven-que-termino-muerto-luego-de-atacar-por-el-cuello-a-policia-en-un-cai-de-bogota/</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Bogotá D. C., agosto 22 de 2026.Bogotá abre oficialmente la Convocatoria de Iniciativas Juveniles de Acción Climática, una oportunidad para identificar, acompañar e impulsar propuestas lideradas por jóvenes que estén aportando soluciones a los...</t>
+          <t>Michael Santos agredió con un arma blanca al subintendente Rubén Ramírez en el CAI Galán, quien durante el forcejeo lo abatió con su arma de dotaciónEl artículoLo que se sabe del joven que terminó muerto luego de atacar por el cuello a policía en un...</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Presuntos integrantes de las ACSN castigaron a jóvenes tras una riña en Santa Marta</t>
+          <t>Bogotá abre convocatoria con USD 40.000 para impulsar iniciativas de acción climática lideradas por jóvenes</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>SDIS - Juventud</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Santa Marta</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/mas-regiones/presuntos-integrantes-de-las-acsn-castigaron-a-jovenes-tras-una-rina-en-santa-marta/</t>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#4d985ec1e7</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Jóvenes fueron sometidos a un supuesto castigo tras una riña en Santa Marta. La ACSN niega haberlo ordenado.</t>
+          <t>Bogotá D. C., agosto 22 de 2026.Bogotá abre oficialmente la Convocatoria de Iniciativas Juveniles de Acción Climática, una oportunidad para identificar, acompañar e impulsar propuestas lideradas por jóvenes que estén aportando soluciones a los...</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Un hombre murió en medio de corralejas clandestinas de Caucasia, Antioquia</t>
+          <t>Presuntos integrantes de las ACSN castigaron a jóvenes tras una riña en Santa Marta</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2104,7 +2100,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Santa Marta</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2114,34 +2110,34 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/mas-regiones/un-hombre-murio-en-medio-de-corralejas-clandestinas-de-caucasia-antioquia/</t>
+          <t>https://www.elespectador.com/colombia/mas-regiones/presuntos-integrantes-de-las-acsn-castigaron-a-jovenes-tras-una-rina-en-santa-marta/</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Un joven de 27 años murió corneado por un toro durante unas corralejas ilegales en Caucasia. La Policía ordenó suspender el evento.</t>
+          <t>Jóvenes fueron sometidos a un supuesto castigo tras una riña en Santa Marta. La ACSN niega haberlo ordenado.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Masacre en Cali dejo tres jóvenes fallecidos: les dispararon en plena vía pública</t>
+          <t>Un hombre murió en medio de corralejas clandestinas de Caucasia, Antioquia</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2151,7 +2147,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Medellín</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2161,12 +2157,12 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/08/18/masacre-en-cali-dejo-tres-jovenes-fallecidos-les-dispararon-en-plena-via-publica/</t>
+          <t>https://www.elespectador.com/colombia/mas-regiones/un-hombre-murio-en-medio-de-corralejas-clandestinas-de-caucasia-antioquia/</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>La Defensoría del Pueblo señaló el uso de la ciudad como plataforma criminal y zona de refugio por parte de grupos armados</t>
+          <t>Un joven de 27 años murió corneado por un toro durante unas corralejas ilegales en Caucasia. La Policía ordenó suspender el evento.</t>
         </is>
       </c>
     </row>
@@ -2178,89 +2174,89 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Bogotá abre concursos juveniles con $100 millones en reconocimientos para el talento, las iniciativas y los emprendimientos de jóvenes</t>
+          <t>Masacre en Cali dejo tres jóvenes fallecidos: les dispararon en plena vía pública</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>SDIS - Juventud</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Cultura y deporte</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#7413dc43f2</t>
+          <t>https://www.infobae.com/colombia/2026/08/18/masacre-en-cali-dejo-tres-jovenes-fallecidos-les-dispararon-en-plena-via-publica/</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Bogotá, D. C., agosto 18 de 2026.Manteniendo una tradición que cada año abre escenarios para reconocer el talento, las ideas y los procesos liderados por las juventudes de la ciudad, la Secretaría Distrital de Integración Social, a través de la...</t>
+          <t>La Defensoría del Pueblo señaló el uso de la ciudad como plataforma criminal y zona de refugio por parte de grupos armados</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Murió Daniela Largo, la mujer que fue rescatada entre los escombros en Pereira</t>
+          <t>Bogotá abre concursos juveniles con $100 millones en reconocimientos para el talento, las iniciativas y los emprendimientos de jóvenes</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>SDIS - Juventud</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Cultura y deporte</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Pereira</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/mas-regiones/murio-daniela-largo-la-mujer-que-fue-rescatada-entre-los-escombros-en-pereira/</t>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#7413dc43f2</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Murió Daniela Largo, la joven que fue rescatada el pasado martes, luego de permanecer por más de 36 horas bajo los escombros, en Pereira.</t>
+          <t>Bogotá, D. C., agosto 18 de 2026.Manteniendo una tradición que cada año abre escenarios para reconocer el talento, las ideas y los procesos liderados por las juventudes de la ciudad, la Secretaría Distrital de Integración Social, a través de la...</t>
         </is>
       </c>
     </row>
@@ -2272,22 +2268,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>La historia de Juan Felipe Giraldo, el joven que se iba a casar y falleció tras el terremoto en Pereira</t>
+          <t>Murió Daniela Largo, la mujer que fue rescatada entre los escombros en Pereira</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Las2orillas</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2302,44 +2298,44 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://www.las2orillas.co/la-historia-de-juan-felipe-giraldo-el-joven-que-se-iba-a-casar-y-fallecio-tras-el-terremoto-en-pereira/</t>
+          <t>https://www.elespectador.com/colombia/mas-regiones/murio-daniela-largo-la-mujer-que-fue-rescatada-entre-los-escombros-en-pereira/</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>A días de casarse, el joven falleció tras el terremoto en Pereira. Su padre, Hernán Giraldo, lideró una incansable búsqueda en el Hotel DibeniEl artículoLa historia de Juan Felipe Giraldo, el joven que se iba a casar y falleció tras el terremoto en...</t>
+          <t>Murió Daniela Largo, la joven que fue rescatada el pasado martes, luego de permanecer por más de 36 horas bajo los escombros, en Pereira.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Terremoto en Cali: la historia de Lenny Fernández, la mujer que murió protegiendo a su perro</t>
+          <t>La historia de Juan Felipe Giraldo, el joven que se iba a casar y falleció tras el terremoto en Pereira</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Las2orillas</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Pereira</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2349,12 +2345,12 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/cali/terremoto-en-cali-la-historia-de-lenny-fernandez-la-abogada-que-murio-protegiendo-a-su-perro/</t>
+          <t>https://www.las2orillas.co/la-historia-de-juan-felipe-giraldo-el-joven-que-se-iba-a-casar-y-fallecio-tras-el-terremoto-en-pereira/</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Las autoridades encontraron a una joven bajo los escombros abrazada a su perro. El animal fue rescatado con vida.</t>
+          <t>A días de casarse, el joven falleció tras el terremoto en Pereira. Su padre, Hernán Giraldo, lideró una incansable búsqueda en el Hotel DibeniEl artículoLa historia de Juan Felipe Giraldo, el joven que se iba a casar y falleció tras el terremoto en...</t>
         </is>
       </c>
     </row>
@@ -2366,89 +2362,89 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>El Microcurso: Activa el Arte -Jóvenes que crean, gestionan y transforman llega a Bogotá</t>
+          <t>Terremoto en Cali: la historia de Lenny Fernández, la mujer que murió protegiendo a su perro</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>SDIS - Juventud</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Cultura y deporte</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#696c8328dd</t>
+          <t>https://www.elespectador.com/colombia/cali/terremoto-en-cali-la-historia-de-lenny-fernandez-la-abogada-que-murio-protegiendo-a-su-perro/</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>•Idartes y la Secretaría Distrital de Integración Social abren un programa de formación gratuita para fortalecer proyectos artísticos y culturales liderados por jóvenes en Bogotá. Bogotá, D.C., agosto 13 de 2026. El Instituto Distrital de las Artes...</t>
+          <t>Las autoridades encontraron a una joven bajo los escombros abrazada a su perro. El animal fue rescatado con vida.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Rescataron viva a Daniela, joven atrapada 36 horas bajo los escombros, en Pereira</t>
+          <t>El Microcurso: Activa el Arte -Jóvenes que crean, gestionan y transforman llega a Bogotá</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>SDIS - Juventud</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Cultura y deporte</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Pereira</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/mas-regiones/rescataron-viva-a-daniela-joven-atrapada-36-horas-bajo-los-escombros-en-pereira/</t>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#696c8328dd</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Así fue el rescate de Daniela, la mujer de 32 años que sobrevivió por 36 horas bajo los escombros, en Pereira.</t>
+          <t>•Idartes y la Secretaría Distrital de Integración Social abren un programa de formación gratuita para fortalecer proyectos artísticos y culturales liderados por jóvenes en Bogotá. Bogotá, D.C., agosto 13 de 2026. El Instituto Distrital de las Artes...</t>
         </is>
       </c>
     </row>
@@ -2460,7 +2456,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Terremoto: confirman muerte de seis estudiantes en Yumbo y Calima El Darién, en Valle</t>
+          <t>Rescataron viva a Daniela, joven atrapada 36 horas bajo los escombros, en Pereira</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2475,12 +2471,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Pereira</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2490,24 +2486,24 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/cali/terremoto-confirman-muerte-de-seis-estudiantes-en-yumbo-y-calima-el-darien-en-valle/</t>
+          <t>https://www.elespectador.com/colombia/mas-regiones/rescataron-viva-a-daniela-joven-atrapada-36-horas-bajo-los-escombros-en-pereira/</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>El Ministerio de Educación confirmó el fallecimiento de seis menores de edad estudiantes de colegios en Yumbo y Calima El Darién.</t>
+          <t>Así fue el rescate de Daniela, la mujer de 32 años que sobrevivió por 36 horas bajo los escombros, en Pereira.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Ataque armado en Barranquilla dejó a joven de 20 años muerta; tenía tres hijos</t>
+          <t>Terremoto: confirman muerte de seis estudiantes en Yumbo y Calima El Darién, en Valle</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2527,7 +2523,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Barranquilla</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2537,12 +2533,12 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/barranquilla/joven-de-20-anos-murio-tras-ser-atacada-junto-a-su-pareja-en-barranquilla/</t>
+          <t>https://www.elespectador.com/colombia/cali/terremoto-confirman-muerte-de-seis-estudiantes-en-yumbo-y-calima-el-darien-en-valle/</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Una joven de 20 años murió luego de ser atacada a bala junto a su pareja en el barrio La Esmeralda, en Barranquilla.</t>
+          <t>El Ministerio de Educación confirmó el fallecimiento de seis menores de edad estudiantes de colegios en Yumbo y Calima El Darién.</t>
         </is>
       </c>
     </row>
@@ -2554,17 +2550,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Don Rey, el músico de Quibdó que cambió las armas por instrumentos a cientos de jóvenes del Chocó</t>
+          <t>Ataque armado en Barranquilla dejó a joven de 20 años muerta; tenía tres hijos</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Las2orillas</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2574,7 +2570,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Quibdó</t>
+          <t>Barranquilla</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2584,29 +2580,29 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://www.las2orillas.co/don-rey-el-musico-de-quibdo-que-cambio-las-armas-por-instrumentos-a-cientos-de-jovenes-del-choco/</t>
+          <t>https://www.elespectador.com/colombia/barranquilla/joven-de-20-anos-murio-tras-ser-atacada-junto-a-su-pareja-en-barranquilla/</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Con Somos Arte convirtió la música en un refugio que hoy encuentra en el arte una oportunidad para cambiar la historia de cientos de menores de edadEl artículoDon Rey, el músico de Quibdó que cambió las armas por instrumentos a cientos de jóvenes...</t>
+          <t>Una joven de 20 años murió luego de ser atacada a bala junto a su pareja en el barrio La Esmeralda, en Barranquilla.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Jóvenes vinculados a IDIPRON se gradúan como bachilleres académicos en ceremonia apoyada por la Alcaldía de Bogotá</t>
+          <t>Don Rey, el músico de Quibdó que cambió las armas por instrumentos a cientos de jóvenes del Chocó</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Pulzo</t>
+          <t>Las2orillas</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2616,72 +2612,72 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Quibdó</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://www.pulzo.com/nacion/bogota/jovenes-de-bogota-se-graduan-como-bachilleres-gracias-a-apoyo-educativo-de-idipron-PP5269385A</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>https://www.las2orillas.co/don-rey-el-musico-de-quibdo-que-cambio-las-armas-por-instrumentos-a-cientos-de-jovenes-del-choco/</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Con Somos Arte convirtió la música en un refugio que hoy encuentra en el arte una oportunidad para cambiar la historia de cientos de menores de edadEl artículoDon Rey, el músico de Quibdó que cambió las armas por instrumentos a cientos de jóvenes...</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Incendio en Buritaca dejó a tres menores de edad con graves quemaduras</t>
+          <t>Jóvenes vinculados a IDIPRON se gradúan como bachilleres académicos en ceremonia apoyada por la Alcaldía de Bogotá</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Pulzo</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Santa Marta</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/mas-regiones/incendio-en-buritaca-dejo-a-tres-menores-de-edad-con-graves-quemaduras/</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>Un incendio en una vivienda en Buritaca, zona rural de Santa Marta, dejó tres menores heridos. Padres exigen su traslado de hospital.</t>
-        </is>
-      </c>
+          <t>https://www.pulzo.com/nacion/bogota/jovenes-de-bogota-se-graduan-como-bachilleres-gracias-a-apoyo-educativo-de-idipron-PP5269385A</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2691,27 +2687,27 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>El colegio de sacerdotes que hace 32 años sacó bachiller a Abelardo De la Espriella</t>
+          <t>Incendio en Buritaca dejó a tres menores de edad con graves quemaduras</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Las2orillas</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Santa Marta</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2721,44 +2717,44 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://www.las2orillas.co/el-colegio-de-sacerdotes-que-hace-32-anos-saco-bachiller-a-abelardo-de-la-espriella/</t>
+          <t>https://www.elespectador.com/colombia/mas-regiones/incendio-en-buritaca-dejo-a-tres-menores-de-edad-con-graves-quemaduras/</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Se formó en el colegio La Salle de Montería, un colegio fundado hace 70años donde hizo grandes amigos que viajaron hasta Cali para acompañarlo en la posesiónEl artículoEl colegio de sacerdotes que hace 32 años sacó bachiller a Abelardo De la...</t>
+          <t>Un incendio en una vivienda en Buritaca, zona rural de Santa Marta, dejó tres menores heridos. Padres exigen su traslado de hospital.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Hallan muerto a joven silletero de Medellín</t>
+          <t>El colegio de sacerdotes que hace 32 años sacó bachiller a Abelardo De la Espriella</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Las2orillas</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2768,24 +2764,24 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/medellin/hallan-muerto-a-joven-silletero-de-medellin/</t>
+          <t>https://www.las2orillas.co/el-colegio-de-sacerdotes-que-hace-32-anos-saco-bachiller-a-abelardo-de-la-espriella/</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Un menor de edad silletero fue reportado como desaparecido en Santa Elena. Federico Gutiérrez confirmó su muerte.</t>
+          <t>Se formó en el colegio La Salle de Montería, un colegio fundado hace 70años donde hizo grandes amigos que viajaron hasta Cali para acompañarlo en la posesiónEl artículoEl colegio de sacerdotes que hace 32 años sacó bachiller a Abelardo De la...</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Mujer murió al caer al vacío tras intentar parquear su carro en parqueadero de Medellín</t>
+          <t>Hallan muerto a joven silletero de Medellín</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2815,118 +2811,118 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/medellin/mujer-murio-al-caer-al-vacio-al-intentar-parquear-su-carro-en-parqueadero-de-medellin/</t>
+          <t>https://www.elespectador.com/colombia/medellin/hallan-muerto-a-joven-silletero-de-medellin/</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Una joven murió en Medellín al intentar parquear su camioneta en un parqueadero en un tercer piso. El carro atravesó un muro.</t>
+          <t>Un menor de edad silletero fue reportado como desaparecido en Santa Elena. Federico Gutiérrez confirmó su muerte.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Bogotá supera los 24.500 jóvenes acompañados por Jóvenes con Oportunidades y le apunta a 40.000 en 2027</t>
+          <t>Mujer murió al caer al vacío tras intentar parquear su carro en parqueadero de Medellín</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>SDIS - Juventud</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Empleo</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Medellín</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#7505b85bbe</t>
+          <t>https://www.elespectador.com/colombia/medellin/mujer-murio-al-caer-al-vacio-al-intentar-parquear-su-carro-en-parqueadero-de-medellin/</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Bogotá D. C., agosto 4 de 2026.Cada oportunidad que recibe un joven puede convertirse en el comienzo de una nueva historia. Esa es la apuesta de Jóvenes con Oportunidades, el programa del Distrito que continúa ampliando el acceso de las juventudes...</t>
+          <t>Una joven murió en Medellín al intentar parquear su camioneta en un parqueadero en un tercer piso. El carro atravesó un muro.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Asesinaron a joven de 17 años en medio de ataque sicarial en Barranquilla: hay tres heridos</t>
+          <t>Bogotá supera los 24.500 jóvenes acompañados por Jóvenes con Oportunidades y le apunta a 40.000 en 2027</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>SDIS - Juventud</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Empleo</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Barranquilla</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/barranquilla/asesinaron-a-joven-de-17-anos-en-medio-de-ataque-sicarial-en-barranquilla-hay-tres-heridos/</t>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#7505b85bbe</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Las autoridades investigan el asesinato de una adolescente en el barrio El Rebolo de Barranquilla. Tres hombres fueron heridos en el ataque.</t>
+          <t>Bogotá D. C., agosto 4 de 2026.Cada oportunidad que recibe un joven puede convertirse en el comienzo de una nueva historia. Esa es la apuesta de Jóvenes con Oportunidades, el programa del Distrito que continúa ampliando el acceso de las juventudes...</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Capturan en Bucaramanga a mujer condenada por explotación sexual a una menor de edad</t>
+          <t>Asesinaron a joven de 17 años en medio de ataque sicarial en Barranquilla: hay tres heridos</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2941,12 +2937,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Seguridad</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Bucaramanga</t>
+          <t>Barranquilla</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2956,12 +2952,12 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/mas-regiones/capturan-en-bucaramanga-a-mujer-condenada-por-explotacion-sexual-a-una-menor-de-edad/</t>
+          <t>https://www.elespectador.com/colombia/barranquilla/asesinaron-a-joven-de-17-anos-en-medio-de-ataque-sicarial-en-barranquilla-hay-tres-heridos/</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Mujer condenada por un juzgado de Barrancabermeja fue capturada en Bucaramanga por explotación sexual a una niña.</t>
+          <t>Las autoridades investigan el asesinato de una adolescente en el barrio El Rebolo de Barranquilla. Tres hombres fueron heridos en el ataque.</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2969,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>En Puerto Colombia hallan restos de joven barranquillero desaparecido</t>
+          <t>Capturan en Bucaramanga a mujer condenada por explotación sexual a una menor de edad</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2988,12 +2984,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Protección</t>
+          <t>Seguridad</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bucaramanga</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3003,57 +2999,61 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/barranquilla/en-puerto-colombia-hallan-restos-de-joven-barranquillero-desaparecido/</t>
+          <t>https://www.elespectador.com/colombia/mas-regiones/capturan-en-bucaramanga-a-mujer-condenada-por-explotacion-sexual-a-una-menor-de-edad/</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Hallan restos desmembrados de joven de 19 años desaparecido en la vía a Sabanilla, Puerto Colombia.</t>
+          <t>Mujer condenada por un juzgado de Barrancabermeja fue capturada en Bucaramanga por explotación sexual a una niña.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Denuncian presunto abuso policial en Bogotá: menor de edad habría sido agredido en un CAI</t>
+          <t>En Puerto Colombia hallan restos de joven barranquillero desaparecido</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Pulzo</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Seguridad</t>
+          <t>Protección</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://www.pulzo.com/nacion/bogota/denuncian-presunto-abuso-policial-bogota-menor-edad-habria-sido-agredido-PP5259724A</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>https://www.elespectador.com/colombia/barranquilla/en-puerto-colombia-hallan-restos-de-joven-barranquillero-desaparecido/</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Hallan restos desmembrados de joven de 19 años desaparecido en la vía a Sabanilla, Puerto Colombia.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Fuerte riña entre jóvenes en Rionegro, Antioquia, terminó con un capturado y cuatro menores aprehendidos</t>
+          <t>Denuncian presunto abuso policial en Bogotá: menor de edad habría sido agredido en un CAI</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Pulzo</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3078,29 +3078,25 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Seguridad</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/07/30/fuerte-rina-entre-jovenes-en-rionegro-antioquia-termino-con-un-capturado-y-cuatro-menores-aprehendidos/</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>La Policía atendió un reporte ciudadano por un enfrentamiento en vía pública, donde resultaron lesionados cinco implicados y se abrió un proceso penal</t>
-        </is>
-      </c>
+          <t>https://www.pulzo.com/nacion/bogota/denuncian-presunto-abuso-policial-bogota-menor-edad-habria-sido-agredido-PP5259724A</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3110,17 +3106,17 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Capturaron a cinco personas implicadas en el asesinato de María Camila Potosí en Cali</t>
+          <t>Fuerte riña entre jóvenes en Rionegro, Antioquia, terminó con un capturado y cuatro menores aprehendidos</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3130,7 +3126,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Medellín</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3140,57 +3136,61 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/cali/capturaron-a-cinco-personas-implicadas-en-el-asesinato-de-maria-camila-potosi-en-cali/</t>
+          <t>https://www.infobae.com/colombia/2026/07/30/fuerte-rina-entre-jovenes-en-rionegro-antioquia-termino-con-un-capturado-y-cuatro-menores-aprehendidos/</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>La Fiscalía anunció que capturó a cinco personas que estarían relacionadas con la joven embarazada María Camila Potosí.</t>
+          <t>La Policía atendió un reporte ciudadano por un enfrentamiento en vía pública, donde resultaron lesionados cinco implicados y se abrió un proceso penal</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Niños y jóvenes de La Candelaria podrán inscribirse gratis al Centro Filarmónico Local de Bogotá</t>
+          <t>Capturaron a cinco personas implicadas en el asesinato de María Camila Potosí en Cali</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Pulzo</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://www.pulzo.com/nacion/www.pulzo.com/formacion-musical-gratuita-ninos-jovenes-la-candelaria-POST_TYPE=ALIADOS&amp;P=5257982</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>https://www.elespectador.com/colombia/cali/capturaron-a-cinco-personas-implicadas-en-el-asesinato-de-maria-camila-potosi-en-cali/</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>La Fiscalía anunció que capturó a cinco personas que estarían relacionadas con la joven embarazada María Camila Potosí.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Por qué Jennifer Pedraza celebró ‘a medias’ la renuncia de Juliana Guerrero del Consejo Superior de la Universidad del Cesar: “Feliz pero triste”</t>
+          <t>Niños y jóvenes de La Candelaria podrán inscribirse gratis al Centro Filarmónico Local de Bogotá</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Pulzo</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3215,29 +3215,25 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Valledupar</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/07/28/jennifer-pedraza-celebro-a-medias-la-renuncia-de-juliana-guerrero-del-consejo-superior-de-la-universidad-del-cesar-feliz-pero-triste/</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>La senadora de Dignidad y Compromiso reiteró sus críticas al presidente Gustavo Petro al defender las acciones de la joven cesarense en el Ejecutivo</t>
-        </is>
-      </c>
+          <t>https://www.pulzo.com/nacion/www.pulzo.com/formacion-musical-gratuita-ninos-jovenes-la-candelaria-POST_TYPE=ALIADOS&amp;P=5257982</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3247,12 +3243,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Dos abogados del Rosario defenderán a Juliana Guerrero y su hermana comprometidas en gran escándalo de corrupción</t>
+          <t>Por qué Jennifer Pedraza celebró ‘a medias’ la renuncia de Juliana Guerrero del Consejo Superior de la Universidad del Cesar: “Feliz pero triste”</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Las2orillas</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3262,7 +3258,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Protección</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3277,29 +3273,29 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://www.las2orillas.co/dos-abogados-del-rosario-defenderan-a-juliana-guerrero-y-su-hermana-comprometidas-en-gran-escandalo-de-corrupcion/</t>
+          <t>https://www.infobae.com/colombia/2026/07/28/jennifer-pedraza-celebro-a-medias-la-renuncia-de-juliana-guerrero-del-consejo-superior-de-la-universidad-del-cesar-feliz-pero-triste/</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Acorralada, la joven vallenata madrugó a renunciar a la representación del Presidente en la UPC del Cesar y a contratar al bufete Álzate Hernández para su defensaEl artículoDos abogados del Rosario defenderán a Juliana Guerrero y su hermana...</t>
+          <t>La senadora de Dignidad y Compromiso reiteró sus críticas al presidente Gustavo Petro al defender las acciones de la joven cesarense en el Ejecutivo</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Andrea Petro se apartó de su papá Gustavo Petro y pidió que se investigue a Juliana Guerrero por hechos de corrupción: “No puede haber privilegios”</t>
+          <t>Dos abogados del Rosario defenderán a Juliana Guerrero y su hermana comprometidas en gran escándalo de corrupción</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Las2orillas</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3309,12 +3305,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Protección</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Valledupar</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -3324,12 +3320,12 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/07/27/andrea-petro-se-aparto-de-su-papa-gustavo-petro-y-pidio-que-se-investigue-a-juliana-guerrero-por-hechos-de-corrupcion-no-puede-haber-privilegios/</t>
+          <t>https://www.las2orillas.co/dos-abogados-del-rosario-defenderan-a-juliana-guerrero-y-su-hermana-comprometidas-en-gran-escandalo-de-corrupcion/</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>La hija del presidente colombiano expresó en sus redes sociales su descontento a los hechos de corrupción que involucran a la joven exfuncionaria en el Ejecutivo</t>
+          <t>Acorralada, la joven vallenata madrugó a renunciar a la representación del Presidente en la UPC del Cesar y a contratar al bufete Álzate Hernández para su defensaEl artículoDos abogados del Rosario defenderán a Juliana Guerrero y su hermana...</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3337,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Angie Rodríguez se despachó contra Juliana Guerrero y recordó episodio de cuando le negaron la entrada a la Casa de Nariño: apuntó a las bodegas</t>
+          <t>Andrea Petro se apartó de su papá Gustavo Petro y pidió que se investigue a Juliana Guerrero por hechos de corrupción: “No puede haber privilegios”</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3361,7 +3357,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Pasto</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -3371,24 +3367,24 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/07/27/angie-rodriguez-se-despacho-contra-juliana-guerrero-y-recordo-episodio-de-cuando-le-negaron-la-entrada-a-la-casa-de-narino-apunto-a-las-bodegas/</t>
+          <t>https://www.infobae.com/colombia/2026/07/27/andrea-petro-se-aparto-de-su-papa-gustavo-petro-y-pidio-que-se-investigue-a-juliana-guerrero-por-hechos-de-corrupcion-no-puede-haber-privilegios/</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>La gerente del Fondo Adaptación denunció una serie de presuntos hechos de presión, exclusión y hostigamiento dentro del Gobierno, y señaló directamente a la joven y a otros altos cargos por su supuesta participación en redes de influencias</t>
+          <t>La hija del presidente colombiano expresó en sus redes sociales su descontento a los hechos de corrupción que involucran a la joven exfuncionaria en el Ejecutivo</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Alejandro Bermeo, senador involucrado en presunto caso de abuso sexual, propuso una “semana anticomunista” en los colegios de Colombia: la iniciativa ha generado polémica</t>
+          <t>Angie Rodríguez se despachó contra Juliana Guerrero y recordó episodio de cuando le negaron la entrada a la Casa de Nariño: apuntó a las bodegas</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3403,12 +3399,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Pasto</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -3418,24 +3414,24 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/07/26/alejandro-bermeo-senador-involucrado-en-presunto-caso-de-abuso-sexual-propuso-una-semana-anticomunista-en-los-colegios-de-colombia-la-iniciativa-ha-generado-polemica/</t>
+          <t>https://www.infobae.com/colombia/2026/07/27/angie-rodriguez-se-despacho-contra-juliana-guerrero-y-recordo-episodio-de-cuando-le-negaron-la-entrada-a-la-casa-de-narino-apunto-a-las-bodegas/</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>El congresista de Salvación Nacional señaló que la iniciativa plantea dedicar siete días al año en todo el bachillerato para abordar todo lo relacionado con dicho modelo político que, en su visión, podría afectar la democracia colombiana</t>
+          <t>La gerente del Fondo Adaptación denunció una serie de presuntos hechos de presión, exclusión y hostigamiento dentro del Gobierno, y señaló directamente a la joven y a otros altos cargos por su supuesta participación en redes de influencias</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Alcalde de Cali aumentó recompensa por información sobre el asesino de María Camila Potosí: ofreció $200 millones</t>
+          <t>Alejandro Bermeo, senador involucrado en presunto caso de abuso sexual, propuso una “semana anticomunista” en los colegios de Colombia: la iniciativa ha generado polémica</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3450,12 +3446,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -3465,12 +3461,12 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/07/24/alcalde-de-cali-aumento-recompensa-por-informacion-sobre-el-asesino-de-maria-camila-potosi-ofrecio-200-millones/</t>
+          <t>https://www.infobae.com/colombia/2026/07/26/alejandro-bermeo-senador-involucrado-en-presunto-caso-de-abuso-sexual-propuso-una-semana-anticomunista-en-los-colegios-de-colombia-la-iniciativa-ha-generado-polemica/</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>La joven de 21 años fue encontrada junto al caudal de un río, amarrada de pies y manos, con signos de tortura y con varias heridas con arma blanca</t>
+          <t>El congresista de Salvación Nacional señaló que la iniciativa plantea dedicar siete días al año en todo el bachillerato para abordar todo lo relacionado con dicho modelo político que, en su visión, podría afectar la democracia colombiana</t>
         </is>
       </c>
     </row>
@@ -3482,17 +3478,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Alcaldía de Cali ofreció recompensa por información sobre crimen de María Camila Potosí</t>
+          <t>Alcalde de Cali aumentó recompensa por información sobre el asesino de María Camila Potosí: ofreció $200 millones</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -3512,12 +3508,12 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/cali/alcaldia-de-cali-ofrecio-recompensa-por-informacion-sobre-crimen-de-maria-camila-potosi/</t>
+          <t>https://www.infobae.com/colombia/2026/07/24/alcalde-de-cali-aumento-recompensa-por-informacion-sobre-el-asesino-de-maria-camila-potosi-ofrecio-200-millones/</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Alejandro Eder, alcalde de Cali, ofreció una recompensa de COP 50 millones por información sobre el crimen de la joven María Camila Potosí.</t>
+          <t>La joven de 21 años fue encontrada junto al caudal de un río, amarrada de pies y manos, con signos de tortura y con varias heridas con arma blanca</t>
         </is>
       </c>
     </row>
@@ -3529,42 +3525,42 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>‘Comidas Compartidas’: cuando los alimentos conectan a las personas y derriban prejuicios</t>
+          <t>Alcaldía de Cali ofreció recompensa por información sobre crimen de María Camila Potosí</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>SDIS - Juventud</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Cultura y deporte</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#548ecae5f8</t>
+          <t>https://www.elespectador.com/colombia/cali/alcaldia-de-cali-ofrecio-recompensa-por-informacion-sobre-crimen-de-maria-camila-potosi/</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Bogotá, D.C, 24 de julio de 2026.Los alimentos, además de ser indispensables para los seres vivos, tienen el poder de conectar a las personas. Así lo demostró una nueva versión de ‘Comidas Compartidas’, una actividad en la que voluntarios de...</t>
+          <t>Alejandro Eder, alcalde de Cali, ofreció una recompensa de COP 50 millones por información sobre el crimen de la joven María Camila Potosí.</t>
         </is>
       </c>
     </row>
@@ -7420,12 +7416,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Voluntariado transformador: unidad de autocuidado para habitantes de calle en el Voto Nacional estrena ludoteca</t>
+          <t>Abierta convocatoria para la Escuela Distrital de Emprendimiento para jóvenes en Engativá</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -7440,7 +7436,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -7455,29 +7451,29 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#364408dd32</t>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#248fcdb8a0</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>• 40 personas, entre voluntarios de empresas y habitantes de calle, unieron esfuerzos para adecuar un espacio que estimula el conocimiento y pone a volar a la imaginación. • Esta acción se enmarca en la estrategia ‘Más manos por Bogotá’, programa de...</t>
+          <t>• El Distrito abre la convocatoria para 50 jóvenes entre 18 y 28 años, que cuentan con un emprendimiento en marcha y buscan fortalecer sus capacidades para hacerlo crecer y consolidarlo. • La formación se realizará de manera presencial en la Casa de...</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Abierta convocatoria para la Escuela Distrital de Emprendimiento para jóvenes en Engativá</t>
+          <t>Miles de jóvenes se toman Bogotá: Prosperidad Social acompaña el Festival Nacional de la Juventud</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>SDIS - Juventud</t>
+          <t>Prosperidad Social</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -7502,91 +7498,91 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#248fcdb8a0</t>
+          <t>https://prosperidadsocial.gov.co/Noticias/miles-de-jovenes-se-toman-bogota-prosperidad-social-acompana-el-festival-nacional-de-la-juventud/</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>• El Distrito abre la convocatoria para 50 jóvenes entre 18 y 28 años, que cuentan con un emprendimiento en marcha y buscan fortalecer sus capacidades para hacerlo crecer y consolidarlo. • La formación se realizará de manera presencial en la Casa de...</t>
+          <t>Más de 4.000 jóvenes de todo el país se reúnen del 24 al 26 de abril en la sede Aduanilla de Paiba de la Universidad Distrital</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Miles de jóvenes se toman Bogotá: Prosperidad Social acompaña el Festival Nacional de la Juventud</t>
+          <t>El tío comunista de Paloma Valencia, la oveja negra que incomodó a su familia conservadora</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Prosperidad Social</t>
+          <t>Las2orillas</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Popayán</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>https://prosperidadsocial.gov.co/Noticias/miles-de-jovenes-se-toman-bogota-prosperidad-social-acompana-el-festival-nacional-de-la-juventud/</t>
+          <t>https://www.las2orillas.co/el-tio-comunista-de-paloma-valencia-la-oveja-negra-que-incomodo-a-su-familia-conservadora/</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Más de 4.000 jóvenes de todo el país se reúnen del 24 al 26 de abril en la sede Aduanilla de Paiba de la Universidad Distrital</t>
+          <t>Álvaro Pío Valencia, hermano del expresidente Guillermo León, conoció de joven al papá de Iván Cepeda en Popayán e influyó para que él fuera un consagrado ComunistaEl artículoEl tío comunista de Paloma Valencia, la oveja negra que incomodó a su...</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>El tío comunista de Paloma Valencia, la oveja negra que incomodó a su familia conservadora</t>
+          <t>Masacre en Mocoa: asesinaron a cinco jóvenes en zona boscosa</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Las2orillas</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Popayán</t>
+          <t>Mocoa</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -7596,12 +7592,12 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>https://www.las2orillas.co/el-tio-comunista-de-paloma-valencia-la-oveja-negra-que-incomodo-a-su-familia-conservadora/</t>
+          <t>https://www.elespectador.com/colombia/mas-regiones/masacre-en-mocoa-asesinaron-a-cinco-jovenes-en-zona-boscosa/</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Álvaro Pío Valencia, hermano del expresidente Guillermo León, conoció de joven al papá de Iván Cepeda en Popayán e influyó para que él fuera un consagrado ComunistaEl artículoEl tío comunista de Paloma Valencia, la oveja negra que incomodó a su...</t>
+          <t>Cinco hombres fueron asesinados en Mocoa. El hecho se dio después de que se difundió un panfleto amenazante.</t>
         </is>
       </c>
     </row>
@@ -7613,7 +7609,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Masacre en Mocoa: asesinaron a cinco jóvenes en zona boscosa</t>
+          <t>Patinador de 14 años de la Liga Vallecaucana murió durante un entrenamiento: esto se sabe</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -7633,7 +7629,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Mocoa</t>
+          <t>Popayán</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -7643,24 +7639,24 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/mas-regiones/masacre-en-mocoa-asesinaron-a-cinco-jovenes-en-zona-boscosa/</t>
+          <t>https://www.elespectador.com/colombia/cali/muere-joven-patinador-en-cali-tras-accidente-durante-entrenamiento-en-patinodromo/</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>Cinco hombres fueron asesinados en Mocoa. El hecho se dio después de que se difundió un panfleto amenazante.</t>
+          <t>El joven hacía parte de la Liga Vallecaucana de Patinaje y del club Relámpago.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Patinador de 14 años de la Liga Vallecaucana murió durante un entrenamiento: esto se sabe</t>
+          <t>Capturan a hombre que se hizo pasar por mototaxista y abusó de una joven de 14 años en Cali</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -7680,7 +7676,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Popayán</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -7690,34 +7686,34 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/cali/muere-joven-patinador-en-cali-tras-accidente-durante-entrenamiento-en-patinodromo/</t>
+          <t>https://www.elespectador.com/colombia/cali/capturan-a-hombre-que-se-hizo-pasar-por-mototaxista-y-abuso-de-una-joven-de-14-anos-en-cali/</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>El joven hacía parte de la Liga Vallecaucana de Patinaje y del club Relámpago.</t>
+          <t>La víctima fue herida con arma cortopunzante y asfixiada hasta quedar inconsciente.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Capturan a hombre que se hizo pasar por mototaxista y abusó de una joven de 14 años en Cali</t>
+          <t>La jueza que investiga el colapso de una pasarela en Santander imputa a un tercer técnico de Costas y aprecia indicios de seis homicidios por imprudencia grave</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -7727,7 +7723,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Bucaramanga</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -7737,12 +7733,12 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/cali/capturan-a-hombre-que-se-hizo-pasar-por-mototaxista-y-abuso-de-una-joven-de-14-anos-en-cali/</t>
+          <t>https://www.infobae.com/espana/2026/04/21/la-jueza-que-investiga-el-colapso-de-una-pasarela-en-santander-imputa-a-un-tercer-tecnico-de-costas-y-aprecia-indicios-de-seis-homicidios-por-imprudencia-grave/</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>La víctima fue herida con arma cortopunzante y asfixiada hasta quedar inconsciente.</t>
+          <t>La instructora considera que la falta de inspección y mantenimiento durante años generó un riesgo no controlado que desembocó en el desplome de la estructura y en la muerte de seis jóvenes</t>
         </is>
       </c>
     </row>
@@ -7754,17 +7750,17 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>La jueza que investiga el colapso de una pasarela en Santander imputa a un tercer técnico de Costas y aprecia indicios de seis homicidios por imprudencia grave</t>
+          <t>Investigan el asesinato de adolescente de 15 años en campo de golf en Cartagena</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -7774,7 +7770,7 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Bucaramanga</t>
+          <t>Cartagena</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -7784,34 +7780,34 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/espana/2026/04/21/la-jueza-que-investiga-el-colapso-de-una-pasarela-en-santander-imputa-a-un-tercer-tecnico-de-costas-y-aprecia-indicios-de-seis-homicidios-por-imprudencia-grave/</t>
+          <t>https://www.elespectador.com/colombia/cartagena/investigan-el-asesinato-de-adolescente-de-17-anos-en-campo-de-golf-en-cartagena/</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>La instructora considera que la falta de inspección y mantenimiento durante años generó un riesgo no controlado que desembocó en el desplome de la estructura y en la muerte de seis jóvenes</t>
+          <t>Las autoridades buscan esclarecer por qué un empleado de seguridad de un club de golf de Cartagena disparó contra un adolescente.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Investigan el asesinato de adolescente de 15 años en campo de golf en Cartagena</t>
+          <t>Filtran las primeras imágenes del doble asesinato contra miembros de la producción de ‘Sin senos sí hay paraíso 4′ en Bogotá: el agresor atacó por la espalda</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -7821,34 +7817,34 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Cartagena</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/cartagena/investigan-el-asesinato-de-adolescente-de-17-anos-en-campo-de-golf-en-cartagena/</t>
+          <t>https://www.infobae.com/colombia/2026/04/20/filtran-las-primeras-imagenes-del-doble-asesinato-contra-miembros-de-la-produccion-de-sin-senos-si-hay-paraiso-4-en-bogota-el-agresor-ataco-por-la-espalda/</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>Las autoridades buscan esclarecer por qué un empleado de seguridad de un club de golf de Cartagena disparó contra un adolescente.</t>
+          <t>En el material fílmico se observa cuando el joven de 24 años diagnosticado con enfermedad mental se acercó al conductor de 45 años y, sin mediar palabra, lo tomó por el cuello y lo hirió mortalmente con arma blanca</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Filtran las primeras imágenes del doble asesinato contra miembros de la producción de ‘Sin senos sí hay paraíso 4′ en Bogotá: el agresor atacó por la espalda</t>
+          <t>Magnicidio Miguel Uribe Turbay: menor de edad que disparó al precandidato fue declarado como víctima en el proceso judicial</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -7868,39 +7864,39 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/04/20/filtran-las-primeras-imagenes-del-doble-asesinato-contra-miembros-de-la-produccion-de-sin-senos-si-hay-paraiso-4-en-bogota-el-agresor-ataco-por-la-espalda/</t>
+          <t>https://www.infobae.com/colombia/2026/04/18/magnicidio-miguel-uribe-turbay-menor-de-edad-que-disparo-al-precandidato-fue-declarado-como-victima-en-el-proceso-judicial/</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>En el material fílmico se observa cuando el joven de 24 años diagnosticado con enfermedad mental se acercó al conductor de 45 años y, sin mediar palabra, lo tomó por el cuello y lo hirió mortalmente con arma blanca</t>
+          <t>Alias Tianz confesó el crimen y cumple una sanción de siete años en un centro de atención especializada, bajo la custodia del Instituto Colombiano de Bienestar Familiar</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Magnicidio Miguel Uribe Turbay: menor de edad que disparó al precandidato fue declarado como víctima en el proceso judicial</t>
+          <t>Uno de cada cuatro jovenes en colombia no estudia ni trabaja y el mercado laboral da senales de debilidad</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Portafolio</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -7910,7 +7906,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Empleo</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -7925,14 +7921,10 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/04/18/magnicidio-miguel-uribe-turbay-menor-de-edad-que-disparo-al-precandidato-fue-declarado-como-victima-en-el-proceso-judicial/</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>Alias Tianz confesó el crimen y cumple una sanción de siete años en un centro de atención especializada, bajo la custodia del Instituto Colombiano de Bienestar Familiar</t>
-        </is>
-      </c>
+          <t>https://www.portafolio.co/economia/empleo/uno-de-cada-cuatro-jovenes-en-colombia-no-estudia-ni-trabaja-y-el-mercado-laboral-da-senales-de-debilidad-492018</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -7942,60 +7934,64 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Uno de cada cuatro jovenes en colombia no estudia ni trabaja y el mercado laboral da senales de debilidad</t>
+          <t>¡Atención, jóvenes! Bogotá abre formación gratuita para impulsar emprendimientos</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Portafolio</t>
+          <t>SDIS - Juventud</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Empleo</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>https://www.portafolio.co/economia/empleo/uno-de-cada-cuatro-jovenes-en-colombia-no-estudia-ni-trabaja-y-el-mercado-laboral-da-senales-de-debilidad-492018</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr"/>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#ee67a6f4f1</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>•Bogotá abre la convocatoria de Innovers 2026, un programa gratuito para fortalecer el emprendimiento juvenil. • Dirigido a jóvenes entre 18 y 28 años, desde quienes tienen una idea hasta emprendimientos en crecimiento.</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>¡Atención, jóvenes! Bogotá abre formación gratuita para impulsar emprendimientos</t>
+          <t>Asesinaron a dos jóvenes que habían sido secuestrados por la guerrilla hace un mes en Arauca</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>SDIS - Juventud</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -8005,44 +8001,40 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Arauca</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#ee67a6f4f1</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>•Bogotá abre la convocatoria de Innovers 2026, un programa gratuito para fortalecer el emprendimiento juvenil. • Dirigido a jóvenes entre 18 y 28 años, desde quienes tienen una idea hasta emprendimientos en crecimiento.</t>
-        </is>
-      </c>
+          <t>https://www.bluradio.com/nacion/asesinaron-a-dos-jovenes-que-habian-sido-secuestrados-por-la-guerrilla-hace-un-mes-en-arauca-rg10</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Asesinaron a dos jóvenes que habían sido secuestrados por la guerrilla hace un mes en Arauca</t>
+          <t>Bomberos rescataron a joven que le quedó atrapado el dedo en una banca del MIO en Cali</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -8052,7 +8044,7 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Arauca</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -8062,20 +8054,24 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/nacion/asesinaron-a-dos-jovenes-que-habian-sido-secuestrados-por-la-guerrilla-hace-un-mes-en-arauca-rg10</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr"/>
+          <t>https://www.elespectador.com/colombia/cali/bomberos-rescataron-a-joven-que-le-quedo-atrapado-el-dedo-en-una-banca-del-mio-en-cali/</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>El caso ocurrió en un paradero del sistema en el barrio Potrero Grande del MIO en Cali.</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Bomberos rescataron a joven que le quedó atrapado el dedo en una banca del MIO en Cali</t>
+          <t>Medellín abre convocatoria para impulsar emprendimientos rurales de jóvenes y mujeres</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -8095,7 +8091,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Medellín</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -8105,12 +8101,12 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/cali/bomberos-rescataron-a-joven-que-le-quedo-atrapado-el-dedo-en-una-banca-del-mio-en-cali/</t>
+          <t>https://www.elespectador.com/colombia/medellin/medellin-abre-convocatoria-para-impulsar-emprendimientos-rurales-de-jovenes-y-mujeres/</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>El caso ocurrió en un paradero del sistema en el barrio Potrero Grande del MIO en Cali.</t>
+          <t>Hasta 40 iniciativas podrán acceder a recursos y acompañamiento técnico. Las inscripciones estarán abiertas hasta el 10 de abril.</t>
         </is>
       </c>
     </row>
@@ -8122,27 +8118,27 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Medellín abre convocatoria para impulsar emprendimientos rurales de jóvenes y mujeres</t>
+          <t>MATAR MUJERES: LA VIOLENCIA INSTRUMENTAL COMO ESTRATEGIA DEL CONTROL ARMADO</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>La Silla Vacía</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -8152,34 +8148,34 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/medellin/medellin-abre-convocatoria-para-impulsar-emprendimientos-rurales-de-jovenes-y-mujeres/</t>
+          <t>https://www.lasillavacia.com/red-de-expertos/matar-mujeres-la-violencia-instrumental-como-estrategia-del-control-armado/</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>Hasta 40 iniciativas podrán acceder a recursos y acompañamiento técnico. Las inscripciones estarán abiertas hasta el 10 de abril.</t>
+          <t>El asesinato de dos adolescentes en Malambo, Atlántico, es un crimen atroz que evidencia una lógica que se repite en distintos territorios y que consiste en matar mujeres para castigar, advertir e imponer control. Mientras sus familias recibían...</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>MATAR MUJERES: LA VIOLENCIA INSTRUMENTAL COMO ESTRATEGIA DEL CONTROL ARMADO</t>
+          <t>Capturan a joven de 19 años por asesinato de mujer y su hijo en Villavicencio</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>La Silla Vacía</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -8189,7 +8185,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Villavicencio</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -8199,12 +8195,12 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>https://www.lasillavacia.com/red-de-expertos/matar-mujeres-la-violencia-instrumental-como-estrategia-del-control-armado/</t>
+          <t>https://www.elespectador.com/colombia/mas-regiones/capturan-a-joven-de-19-anos-por-asesinato-de-mujer-y-su-hijo-en-villavicencio/</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>El asesinato de dos adolescentes en Malambo, Atlántico, es un crimen atroz que evidencia una lógica que se repite en distintos territorios y que consiste en matar mujeres para castigar, advertir e imponer control. Mientras sus familias recibían...</t>
+          <t>Las autoridades capturaron a un joven de 19 años señalado del doble homicidio ocurrido en el barrio San Antonio de Villavicencio.</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8212,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Capturan a joven de 19 años por asesinato de mujer y su hijo en Villavicencio</t>
+          <t>Hallaron el cuerpo de una adolescente de 14 años que se ahogó en playa de Antioquia</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -8231,12 +8227,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Villavicencio</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -8246,24 +8242,24 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/mas-regiones/capturan-a-joven-de-19-anos-por-asesinato-de-mujer-y-su-hijo-en-villavicencio/</t>
+          <t>https://www.elespectador.com/colombia/mas-regiones/hallaron-el-cuerpo-de-una-adolescente-de-14-anos-que-se-ahogo-en-playa-de-san-juan-de-uraba-en-antioquia/</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>Las autoridades capturaron a un joven de 19 años señalado del doble homicidio ocurrido en el barrio San Antonio de Villavicencio.</t>
+          <t>La menor había ingresado al mar con una amiga en una zona con fuerte oleaje. Su cuerpo fue hallado horas después.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Hallaron el cuerpo de una adolescente de 14 años que se ahogó en playa de Antioquia</t>
+          <t>Ataque de pitbull que dejó a perro muerto y joven herido en Barranquilla</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -8278,12 +8274,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Barranquilla</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -8293,59 +8289,59 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/mas-regiones/hallaron-el-cuerpo-de-una-adolescente-de-14-anos-que-se-ahogo-en-playa-de-san-juan-de-uraba-en-antioquia/</t>
+          <t>https://www.elespectador.com/colombia/barranquilla/anuncian-acciones-tras-ataque-de-pitbull-que-dejo-a-perro-muerto-y-joven-herido-en-barranquilla/</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>La menor había ingresado al mar con una amiga en una zona con fuerte oleaje. Su cuerpo fue hallado horas después.</t>
+          <t>El hecho ocurrió en un conjunto residencial de Barranquilla y quedó registrado en cámaras de seguridad.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Ataque de pitbull que dejó a perro muerto y joven herido en Barranquilla</t>
+          <t>Prosperidad Social amplía el periodo de transferencias de Renta Joven en modalidad de giro</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Prosperidad Social</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Política pública</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Barranquilla</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/barranquilla/anuncian-acciones-tras-ataque-de-pitbull-que-dejo-a-perro-muerto-y-joven-herido-en-barranquilla/</t>
+          <t>https://prosperidadsocial.gov.co/Noticias/prosperidad-social-amplia-el-periodo-de-transferencias-de-renta-joven-en-modalidad-de-giro/</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>El hecho ocurrió en un conjunto residencial de Barranquilla y quedó registrado en cámaras de seguridad.</t>
+          <t>La ampliación del plazo permitirá que más de 27.000 participantes reciban sus subsidios, incluyendo transferencias pendientes de 2025. La transferencia monetaria condicionada se podrá reclamar en los puntos autorizados de SuRed y SuperGIROS. Bogotá...</t>
         </is>
       </c>
     </row>
@@ -8357,12 +8353,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Prosperidad Social amplía el periodo de transferencias de Renta Joven en modalidad de giro</t>
+          <t>Nueva convocatoria dirigida a jóvenes interesados en formarse en el sector de gastronomía</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Prosperidad Social</t>
+          <t>SDIS - Juventud</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -8372,7 +8368,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Política pública</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -8387,59 +8383,59 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>https://prosperidadsocial.gov.co/Noticias/prosperidad-social-amplia-el-periodo-de-transferencias-de-renta-joven-en-modalidad-de-giro/</t>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#e5d592a6d5</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>La ampliación del plazo permitirá que más de 27.000 participantes reciban sus subsidios, incluyendo transferencias pendientes de 2025. La transferencia monetaria condicionada se podrá reclamar en los puntos autorizados de SuRed y SuperGIROS. Bogotá...</t>
+          <t>• El Distrito, en alianza con la Fundación Gastronomía Social, lanzan una nueva convocatoria dirigida a jóvenes de 18 a 30 años, principalmente de la localidad de Kennedy, para formarse en servicio para el sector de la gastronomía. • Esta formación...</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Nueva convocatoria dirigida a jóvenes interesados en formarse en el sector de gastronomía</t>
+          <t>La incoherente decisión de Petro de abrirle la Casa de Nariño a Westcol decepcionó a quienes respaldaban su gobierno</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>SDIS - Juventud</t>
+          <t>Las2orillas</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#e5d592a6d5</t>
+          <t>https://www.las2orillas.co/la-incoherente-decision-de-petro-de-abrirle-la-casa-de-narino-a-westcol-decepciono-a-quienes-respaldaban-su-gobierno/</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>• El Distrito, en alianza con la Fundación Gastronomía Social, lanzan una nueva convocatoria dirigida a jóvenes de 18 a 30 años, principalmente de la localidad de Kennedy, para formarse en servicio para el sector de la gastronomía. • Esta formación...</t>
+          <t>Recibir a Westcol tras la tragedia del Hércules y sus discursos de odio es un golpe a la coherencia progresista. ¿Vale todo por llegarle a los jóvenes?El artículoLa incoherente decisión de Petro de abrirle la Casa de Nariño a Westcol decepcionó a...</t>
         </is>
       </c>
     </row>
@@ -8451,12 +8447,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>La incoherente decisión de Petro de abrirle la Casa de Nariño a Westcol decepcionó a quienes respaldaban su gobierno</t>
+          <t>Primero Petro luego Uribe: Westcol, el streamer que entrevista presidentes</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Las2orillas</t>
+          <t>La Silla Vacía</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -8481,12 +8477,12 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>https://www.las2orillas.co/la-incoherente-decision-de-petro-de-abrirle-la-casa-de-narino-a-westcol-decepciono-a-quienes-respaldaban-su-gobierno/</t>
+          <t>https://www.lasillavacia.com/silla-nacional/primero-petro-luego-uribe-westcol-el-streamer-que-entrevista-presidentes/</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>Recibir a Westcol tras la tragedia del Hércules y sus discursos de odio es un golpe a la coherencia progresista. ¿Vale todo por llegarle a los jóvenes?El artículoLa incoherente decisión de Petro de abrirle la Casa de Nariño a Westcol decepcionó a...</t>
+          <t>El influencer se convierte en interlocutor de los dos políticos más poderosos de Colombia. Ambos van detrás de su audiencia joven y masiva en época electoral.The postPrimero Petro luego Uribe: Westcol, el streamer que entrevista presidentesappeared...</t>
         </is>
       </c>
     </row>
@@ -8498,27 +8494,27 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Primero Petro luego Uribe: Westcol, el streamer que entrevista presidentes</t>
+          <t>Asesinaron a joven futbolista en Barranquilla; le dispararon en la cabeza</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>La Silla Vacía</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Barranquilla</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
@@ -8528,24 +8524,24 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>https://www.lasillavacia.com/silla-nacional/primero-petro-luego-uribe-westcol-el-streamer-que-entrevista-presidentes/</t>
+          <t>https://www.elespectador.com/colombia/barranquilla/asesinaron-a-joven-futbolista-en-barranquilla-le-dispararon-en-la-cabeza/</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>El influencer se convierte en interlocutor de los dos políticos más poderosos de Colombia. Ambos van detrás de su audiencia joven y masiva en época electoral.The postPrimero Petro luego Uribe: Westcol, el streamer que entrevista presidentesappeared...</t>
+          <t>Asesinaron a una joven promesa del fútbol en el barrio El Santuario de Barranquilla. Le dispararon en la cabeza en medio de una riña.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Asesinaron a joven futbolista en Barranquilla; le dispararon en la cabeza</t>
+          <t>Asesinaron a dos jóvenes en ataque sicarial en una discoteca de Riohacha</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -8565,7 +8561,7 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Barranquilla</t>
+          <t>Riohacha</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -8575,12 +8571,12 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/barranquilla/asesinaron-a-joven-futbolista-en-barranquilla-le-dispararon-en-la-cabeza/</t>
+          <t>https://www.elespectador.com/colombia/mas-regiones/tres-sicarios-abrieron-fuego-en-una-discoteca-de-riohacha-y-asesinaron-dos-jovenes/</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>Asesinaron a una joven promesa del fútbol en el barrio El Santuario de Barranquilla. Le dispararon en la cabeza en medio de una riña.</t>
+          <t>¿Qué sucedió en el ataque de tres sicarios ocurrido en una discoteca de Riohacha?</t>
         </is>
       </c>
     </row>
@@ -8592,69 +8588,69 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Asesinaron a dos jóvenes en ataque sicarial en una discoteca de Riohacha</t>
+          <t>Así fue la participación de los jóvenes en el primer Fest de las Oportunidades del año</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>SDIS - Juventud</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Riohacha</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/mas-regiones/tres-sicarios-abrieron-fuego-en-una-discoteca-de-riohacha-y-asesinaron-dos-jovenes/</t>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#9690ed7762</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>¿Qué sucedió en el ataque de tres sicarios ocurrido en una discoteca de Riohacha?</t>
+          <t>•El primer Fest de las Oportunidades 2026 reunió a más de 130 jóvenes en Usme, conectándolos con oferta en empleo, educación, emprendimiento y bienestar. •Más de 20 entidades y aliados participaron acercando oportunidades reales y orientación...</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Así fue la participación de los jóvenes en el primer Fest de las Oportunidades del año</t>
+          <t>Conductor atropelló y mató a un joven en Bogotá tras invadir el carril exclusivo de Transmilenio</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>SDIS - Juventud</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -8669,12 +8665,12 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#9690ed7762</t>
+          <t>https://www.infobae.com/colombia/2026/03/28/conductor-atropello-y-mato-a-un-joven-en-bogota-tras-invadir-el-carril-exclusivo-de-transmilenio/</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>•El primer Fest de las Oportunidades 2026 reunió a más de 130 jóvenes en Usme, conectándolos con oferta en empleo, educación, emprendimiento y bienestar. •Más de 20 entidades y aliados participaron acercando oportunidades reales y orientación...</t>
+          <t>La muerte de Juan Sebastián Triviño y las lesiones sufridas por su acompañante mantienen en alerta a la ciudad, mientras los familiares reclaman las grabaciones de cámaras de seguridad como elemento determinante para identificar al conductor...</t>
         </is>
       </c>
     </row>
@@ -8686,22 +8682,22 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Conductor atropelló y mató a un joven en Bogotá tras invadir el carril exclusivo de Transmilenio</t>
+          <t>Sobre la entrega de transferencias monetarias condicionadas de Jóvenes en Paz</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Prosperidad Social</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -8716,12 +8712,12 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/03/28/conductor-atropello-y-mato-a-un-joven-en-bogota-tras-invadir-el-carril-exclusivo-de-transmilenio/</t>
+          <t>https://prosperidadsocial.gov.co/Noticias/sobre-la-entrega-de-transferencias-monetarias-condicionadas-de-jovenes-en-paz/</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>La muerte de Juan Sebastián Triviño y las lesiones sufridas por su acompañante mantienen en alerta a la ciudad, mientras los familiares reclaman las grabaciones de cámaras de seguridad como elemento determinante para identificar al conductor...</t>
+          <t>Bogotá D.C., 27 de marzo de 2026. Prosperidad Social informa a los participantes del programa Jóvenes en Paz que se adelanta la última etapa del procedimiento para disponer de los recursos de los próximos ciclos del año. En consecuencia: La entrega...</t>
         </is>
       </c>
     </row>
@@ -8733,54 +8729,54 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Sobre la entrega de transferencias monetarias condicionadas de Jóvenes en Paz</t>
+          <t>Continúa la búsqueda de cuatro jóvenes desaparecidos en Coromoro, Santander</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Prosperidad Social</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Protección</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>https://prosperidadsocial.gov.co/Noticias/sobre-la-entrega-de-transferencias-monetarias-condicionadas-de-jovenes-en-paz/</t>
+          <t>https://www.elespectador.com/colombia/mas-regiones/buscan-a-cuatro-jovenes-desaparecidos-en-coromoro-santander-noticias-hoy/</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>Bogotá D.C., 27 de marzo de 2026. Prosperidad Social informa a los participantes del programa Jóvenes en Paz que se adelanta la última etapa del procedimiento para disponer de los recursos de los próximos ciclos del año. En consecuencia: La entrega...</t>
+          <t>Inicialmente eran seis los reportados como desaparecidos.</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Continúa la búsqueda de cuatro jóvenes desaparecidos en Coromoro, Santander</t>
+          <t>La historia de Luis Fernando Hostia y la meta de abrir caminos a personas con discapacidad</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -8795,7 +8791,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Protección</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -8810,24 +8806,24 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/mas-regiones/buscan-a-cuatro-jovenes-desaparecidos-en-coromoro-santander-noticias-hoy/</t>
+          <t>https://www.elespectador.com/colombia/mas-regiones/la-historia-de-luis-fernando-hostia-y-la-meta-de-romper-barreras-a-personas-con-discapacidad/</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>Inicialmente eran seis los reportados como desaparecidos.</t>
+          <t>Desde San Sebastián de Buenavista, un joven en condición de discapacidad rompió décadas de barreras educativas.</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>La historia de Luis Fernando Hostia y la meta de abrir caminos a personas con discapacidad</t>
+          <t>Lo que se sabe de la muerte de joven dentro de Univalle; hay varias preguntas</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -8842,12 +8838,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -8857,24 +8853,24 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/mas-regiones/la-historia-de-luis-fernando-hostia-y-la-meta-de-romper-barreras-a-personas-con-discapacidad/</t>
+          <t>https://www.elespectador.com/colombia/cali/lo-que-se-sabe-de-la-muerte-de-joven-dentro-de-univalle-hay-varias-preguntas/</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>Desde San Sebastián de Buenavista, un joven en condición de discapacidad rompió décadas de barreras educativas.</t>
+          <t>El caso ocurrió durante el fin de semana en la sede Meléndez de la Universidad del Valle, en Cali. La Secretaría de Movilidad se pronunció.</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Lo que se sabe de la muerte de joven dentro de Univalle; hay varias preguntas</t>
+          <t>Buscan a joven que desapareció en río Lebrija en Santander en medio de fuertes lluvias</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -8889,12 +8885,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -8904,24 +8900,24 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/cali/lo-que-se-sabe-de-la-muerte-de-joven-dentro-de-univalle-hay-varias-preguntas/</t>
+          <t>https://www.elespectador.com/colombia/buscan-a-joven-que-desaparecio-en-rio-lebrija-en-santander-en-medio-de-fuertes-lluvias/</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>El caso ocurrió durante el fin de semana en la sede Meléndez de la Universidad del Valle, en Cali. La Secretaría de Movilidad se pronunció.</t>
+          <t>Un joven de 24 años desapareció en el río Lebrija tras ser arrastrado por corriente. Las lluvias dejan más de 140 familias damnificadas.</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Buscan a joven que desapareció en río Lebrija en Santander en medio de fuertes lluvias</t>
+          <t>Balacera en Barranquilla dejó tres personas heridas y tres capturadas</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -8936,12 +8932,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Barranquilla</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
@@ -8951,71 +8947,67 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/buscan-a-joven-que-desaparecio-en-rio-lebrija-en-santander-en-medio-de-fuertes-lluvias/</t>
+          <t>https://www.elespectador.com/colombia/barranquilla/balacera-en-barranquilla-dejo-tres-personas-heridas-y-tres-capturadas/</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>Un joven de 24 años desapareció en el río Lebrija tras ser arrastrado por corriente. Las lluvias dejan más de 140 familias damnificadas.</t>
+          <t>Una balacera, al parecer entre miembros de Pepes y Costeños, dejó tres heridos y tres capturados, entre ellos un menor de edad.</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Balacera en Barranquilla dejó tres personas heridas y tres capturadas</t>
+          <t>Insólito pedido de familia de David Acosta luego de que el joven apareciera con vida en Bogotá</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Pulzo</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Barranquilla</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/barranquilla/balacera-en-barranquilla-dejo-tres-personas-heridas-y-tres-capturadas/</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr">
-        <is>
-          <t>Una balacera, al parecer entre miembros de Pepes y Costeños, dejó tres heridos y tres capturados, entre ellos un menor de edad.</t>
-        </is>
-      </c>
+          <t>https://www.pulzo.com/nacion/bogota/caso-david-acosta-familia-pide-cerrar-investigacion-falsa-desaparicion-PP5103111</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Insólito pedido de familia de David Acosta luego de que el joven apareciera con vida en Bogotá</t>
+          <t>Colombia tendrá más viejos que jóvenes a partir de esta fecha; hay alerta por las pensiones</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -9035,17 +9027,17 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>https://www.pulzo.com/nacion/bogota/caso-david-acosta-familia-pide-cerrar-investigacion-falsa-desaparicion-PP5103111</t>
+          <t>https://www.pulzo.com/economia/colombia-tendra-mas-viejos-que-jovenes-partir-esta-fecha-hay-alerta-PP5100998A</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -9058,27 +9050,27 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Colombia tendrá más viejos que jóvenes a partir de esta fecha; hay alerta por las pensiones</t>
+          <t>Adolescente de 14 años murió en riña entre menores de edad fuera de un colegio en Cali</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Pulzo</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
@@ -9088,30 +9080,34 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>https://www.pulzo.com/economia/colombia-tendra-mas-viejos-que-jovenes-partir-esta-fecha-hay-alerta-PP5100998A</t>
-        </is>
-      </c>
-      <c r="I187" t="inlineStr"/>
+          <t>https://www.elespectador.com/colombia/cali/adolescente-de-14-anos-murio-en-rina-entre-menores-de-edad-fuera-de-un-colegio-en-cali/</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>Adolescente de 14 años murió en riña entre menores afuera de un colegio en Cali. ¿Qué dicen las autoridades?</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Adolescente de 14 años murió en riña entre menores de edad fuera de un colegio en Cali</t>
+          <t>Mafe Carrascal explicó por qué la bancada del Pacto Histórico por Bogotá no asistió a encuentro con el alcalde Carlos Fernando Galán</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -9121,81 +9117,81 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/cali/adolescente-de-14-anos-murio-en-rina-entre-menores-de-edad-fuera-de-un-colegio-en-cali/</t>
+          <t>https://www.infobae.com/colombia/2026/03/17/mafe-carrascal-explico-por-que-la-bancada-del-pacto-historico-por-bogota-no-asistio-a-encuentro-con-el-alcalde-carlos-fernando-galan/</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>Adolescente de 14 años murió en riña entre menores afuera de un colegio en Cali. ¿Qué dicen las autoridades?</t>
+          <t>La representante indicó que la reunión se realizaría a puerta cerrada y que esta decisión contradice los intereses de su partido. Además, afirmó que al gobierno local le falta implementar políticas dirigidas a los jóvenes y a la prevención de...</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Mafe Carrascal explicó por qué la bancada del Pacto Histórico por Bogotá no asistió a encuentro con el alcalde Carlos Fernando Galán</t>
+          <t>Asesinan a joven de 15 años en Cartagena; su padre resultó herido al intentar defenderlo</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Seguridad</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/03/17/mafe-carrascal-explico-por-que-la-bancada-del-pacto-historico-por-bogota-no-asistio-a-encuentro-con-el-alcalde-carlos-fernando-galan/</t>
+          <t>https://www.elespectador.com/colombia/asesinan-a-menor-de-15-anos-en-cartagena-su-padre-resulto-herido-al-intentar-defenderlo/</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>La representante indicó que la reunión se realizaría a puerta cerrada y que esta decisión contradice los intereses de su partido. Además, afirmó que al gobierno local le falta implementar políticas dirigidas a los jóvenes y a la prevención de...</t>
+          <t>El presunto homicida ya fue localizado y detenido.</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Asesinan a joven de 15 años en Cartagena; su padre resultó herido al intentar defenderlo</t>
+          <t>Hallan el cuerpo de una adolescente en vivienda de Sahagún, Córdoba; autoridades investigan</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -9210,12 +9206,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Seguridad</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
@@ -9225,12 +9221,12 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/asesinan-a-menor-de-15-anos-en-cartagena-su-padre-resulto-herido-al-intentar-defenderlo/</t>
+          <t>https://www.elespectador.com/colombia/mas-regiones/hallan-el-cuerpo-de-una-menor-en-una-vivienda-de-sahagun-cordoba-autoridades-investigan/</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>El presunto homicida ya fue localizado y detenido.</t>
+          <t>En lo que va de este año, este sería el tercer caso de una mujer asesinada en el municipio y el cuarto en el departamento.</t>
         </is>
       </c>
     </row>
@@ -9242,7 +9238,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Hallan el cuerpo de una adolescente en vivienda de Sahagún, Córdoba; autoridades investigan</t>
+          <t>Dos jóvenes fueron detenidos por presunta extorsión en Santo Tomás, Atlántico</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -9257,7 +9253,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Seguridad</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -9272,44 +9268,44 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/mas-regiones/hallan-el-cuerpo-de-una-menor-en-una-vivienda-de-sahagun-cordoba-autoridades-investigan/</t>
+          <t>https://www.elespectador.com/colombia/mas-regiones/dos-jovenes-fueron-detenidos-por-presunta-extorsion-en-santo-tomas-atlantico/</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>En lo que va de este año, este sería el tercer caso de una mujer asesinada en el municipio y el cuarto en el departamento.</t>
+          <t>La investigación señala que los implicados habrían intimidado a un conductor de furgón.</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Dos jóvenes fueron detenidos por presunta extorsión en Santo Tomás, Atlántico</t>
+          <t>Con $86 mil millones de regalías, Bolívar construirá universidad en Montes de María y otros dos proyectos educativos</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Las2orillas</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Seguridad</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
@@ -9319,29 +9315,29 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/mas-regiones/dos-jovenes-fueron-detenidos-por-presunta-extorsion-en-santo-tomas-atlantico/</t>
+          <t>https://www.las2orillas.co/con-86-mil-millones-de-regalias-bolivar-construira-universidad-en-montes-de-maria-y-otros-dos-proyectos-educativos/</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>La investigación señala que los implicados habrían intimidado a un conductor de furgón.</t>
+          <t>Los proyectos impulsados por Yamil Arana buscan, entre otras cosas, abrir más de 4 mil cupos para jóvenes de una región que durante años fue escenario de conflictoEl artículoCon $86 mil millones de regalías, Bolívar construirá universidad en Montes...</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Con $86 mil millones de regalías, Bolívar construirá universidad en Montes de María y otros dos proyectos educativos</t>
+          <t>Nuevo giro en el caso de Tatiana Hernández, joven desaparecida en Cartagena: la buscan en el mar</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Las2orillas</t>
+          <t>Pulzo</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -9351,12 +9347,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Protección</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Cartagena</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
@@ -9366,57 +9362,57 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>https://www.las2orillas.co/con-86-mil-millones-de-regalias-bolivar-construira-universidad-en-montes-de-maria-y-otros-dos-proyectos-educativos/</t>
-        </is>
-      </c>
-      <c r="I193" t="inlineStr">
-        <is>
-          <t>Los proyectos impulsados por Yamil Arana buscan, entre otras cosas, abrir más de 4 mil cupos para jóvenes de una región que durante años fue escenario de conflictoEl artículoCon $86 mil millones de regalías, Bolívar construirá universidad en Montes...</t>
-        </is>
-      </c>
+          <t>https://www.pulzo.com/nacion/caso-tatiana-hernandez-da-giro-autoridades-intensifican-busqueda-mar-PP5091130</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Nuevo giro en el caso de Tatiana Hernández, joven desaparecida en Cartagena: la buscan en el mar</t>
+          <t>Prosperidad Social responde a inquietudes sobre Renta Joven</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Pulzo</t>
+          <t>Prosperidad Social</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Protección</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Cartagena</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>https://www.pulzo.com/nacion/caso-tatiana-hernandez-da-giro-autoridades-intensifican-busqueda-mar-PP5091130</t>
-        </is>
-      </c>
-      <c r="I194" t="inlineStr"/>
+          <t>https://prosperidadsocial.gov.co/Noticias/prosperidad-social-responde-a-inquietudes-sobre-renta-joven/</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>Bogotá D. C, 4 de marzo de 2026. Prosperidad Social se permite aclarar a la ciudadanía y, especialmente, a los participantes de Renta Joven algunas dudas e inquietudes que han expresado los beneficiarios en las redes sociales. Prosperidad Social...</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -9426,7 +9422,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Prosperidad Social responde a inquietudes sobre Renta Joven</t>
+          <t>Maratón por las generaciones atendió a más de 38.000 jóvenes y personas mayores beneficiarias de Prosperidad Social</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -9456,12 +9452,12 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>https://prosperidadsocial.gov.co/Noticias/prosperidad-social-responde-a-inquietudes-sobre-renta-joven/</t>
+          <t>https://prosperidadsocial.gov.co/Noticias/maraton-por-las-generaciones-atendio-a-mas-de-38-000-jovenes-y-personas-mayores-beneficiarias-de-prosperidad-social/</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>Bogotá D. C, 4 de marzo de 2026. Prosperidad Social se permite aclarar a la ciudadanía y, especialmente, a los participantes de Renta Joven algunas dudas e inquietudes que han expresado los beneficiarios en las redes sociales. Prosperidad Social...</t>
+          <t>Durante 38 horas continuas, se resolvieron inquietudes y dudas a beneficiarias y beneficiarios de los programas Renta Joven y Colombia Mayor. Nueve de cada 10 personas afirmaron haber recibido información clara y efectiva para resolver sus...</t>
         </is>
       </c>
     </row>
@@ -9473,42 +9469,42 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Maratón por las generaciones atendió a más de 38.000 jóvenes y personas mayores beneficiarias de Prosperidad Social</t>
+          <t>Joven rompió el silencio y reveló desgarradores detalles de los feminicidios más brutales del Valle del Cauca</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Prosperidad Social</t>
+          <t>Las2orillas</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>https://prosperidadsocial.gov.co/Noticias/maraton-por-las-generaciones-atendio-a-mas-de-38-000-jovenes-y-personas-mayores-beneficiarias-de-prosperidad-social/</t>
+          <t>https://www.las2orillas.co/joven-rompio-el-silencio-y-revelo-desgarradores-detalles-de-los-feminicidios-mas-brutales-del-valle-del-cauca/</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>Durante 38 horas continuas, se resolvieron inquietudes y dudas a beneficiarias y beneficiarios de los programas Renta Joven y Colombia Mayor. Nueve de cada 10 personas afirmaron haber recibido información clara y efectiva para resolver sus...</t>
+          <t>Mientras la Fiscalía la señala de disparar contra las víctimas, Angy Pérez asegura que fue obligada a desmembrar los cuerpos bajo la amenaza de perder a su bebéEl artículoJoven rompió el silencio y reveló desgarradores detalles de los feminicidios...</t>
         </is>
       </c>
     </row>
@@ -9520,42 +9516,42 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Joven rompió el silencio y reveló desgarradores detalles de los feminicidios más brutales del Valle del Cauca</t>
+          <t>Colombia Mayor y Renta Joven: Prosperidad Social realizará la Maratón por las Generaciones</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Las2orillas</t>
+          <t>Prosperidad Social</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Protección</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>https://www.las2orillas.co/joven-rompio-el-silencio-y-revelo-desgarradores-detalles-de-los-feminicidios-mas-brutales-del-valle-del-cauca/</t>
+          <t>https://prosperidadsocial.gov.co/Noticias/colombia-mayor-y-renta-joven-prosperidad-social-realizara-la-maraton-por-las-generaciones/</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>Mientras la Fiscalía la señala de disparar contra las víctimas, Angy Pérez asegura que fue obligada a desmembrar los cuerpos bajo la amenaza de perder a su bebéEl artículoJoven rompió el silencio y reveló desgarradores detalles de los feminicidios...</t>
+          <t>Se trata de una jornada continua de atención telefónica, en la que se resolverán inquietudes que tengan beneficiarias y beneficiarios de estos dos programas de la entidad. El canal telefónico tendrá atención continua por más de 36 horas, mientras...</t>
         </is>
       </c>
     </row>
@@ -9567,101 +9563,101 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Colombia Mayor y Renta Joven: Prosperidad Social realizará la Maratón por las Generaciones</t>
+          <t>Así fue la despedida de Iván Zuleta a su sobrina Daniela: la joven fue encontrada sin signos vitales en su habitación</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Prosperidad Social</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Protección</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Valledupar</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>https://prosperidadsocial.gov.co/Noticias/colombia-mayor-y-renta-joven-prosperidad-social-realizara-la-maraton-por-las-generaciones/</t>
+          <t>https://www.infobae.com/colombia/2026/03/11/asi-fue-la-despedida-de-ivan-zuleta-a-su-sobrina-daniela-que-habria-sido-encontrada-sin-signos-vitales-en-su-habitacion/</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>Se trata de una jornada continua de atención telefónica, en la que se resolverán inquietudes que tengan beneficiarias y beneficiarios de estos dos programas de la entidad. El canal telefónico tendrá atención continua por más de 36 horas, mientras...</t>
+          <t>La partida de la joven Zuleta Gnecco, hija de Fabián Zuleta y nieta de Fabio Zuleta, ha conmovido al mundo del vallenato, reuniendo a familiares y músicos icónicos para despedirla en Valledupar con emotivas muestras de cariño</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Así fue la despedida de Iván Zuleta a su sobrina Daniela: la joven fue encontrada sin signos vitales en su habitación</t>
+          <t>Jóvenes en San Cristóbal inician su formación en servicio para el sector de la gastronomía</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>SDIS - Juventud</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Valledupar</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/03/11/asi-fue-la-despedida-de-ivan-zuleta-a-su-sobrina-daniela-que-habria-sido-encontrada-sin-signos-vitales-en-su-habitacion/</t>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#79ade27adc</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>La partida de la joven Zuleta Gnecco, hija de Fabián Zuleta y nieta de Fabio Zuleta, ha conmovido al mundo del vallenato, reuniendo a familiares y músicos icónicos para despedirla en Valledupar con emotivas muestras de cariño</t>
+          <t>•24 chicos y chicas iniciaron su camino en la Academia Ñam, en donde se formarán en servicio a la mesa para mejorar sus oportunidades de empleabilidad en el sector de la gastronomía. •La inducción, que tuvo lugar en el Centro de Desarrollo...</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Jóvenes en San Cristóbal inician su formación en servicio para el sector de la gastronomía</t>
+          <t>La Academia Ñam llega a San Cristóbal con oportunidades para los jóvenes interesados en el sector de la gastronomía</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -9691,24 +9687,24 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#79ade27adc</t>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#1e64cd90aa</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>•24 chicos y chicas iniciaron su camino en la Academia Ñam, en donde se formarán en servicio a la mesa para mejorar sus oportunidades de empleabilidad en el sector de la gastronomía. •La inducción, que tuvo lugar en el Centro de Desarrollo...</t>
+          <t>•El Distrito, en alianza con la Fundación Gastronomía Social, lanzan una nueva convocatoria dirigida a jóvenes de 18 a 30 años interesados en formarse en servicio para el sector de la gastronomía. •Esta formación gratuita ofrece capacitación a...</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Bogotá presenta estudio que analiza los factores asociados a la vinculación de adolescentes a conductas punibles</t>
+          <t>El deporte abrió la puerta a nuevas oportunidades y conexión para los jóvenes de Bogotá</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -9723,7 +9719,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Cultura y deporte</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -9738,34 +9734,34 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#fb504c6e8d</t>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#8b36ede0c2</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>• La vinculación de adolescentes a conductas punibles no responde a una sola causa, sino a la convergencia de factores estructurales, familiares, territoriales y personales que requieren respuestas integrales y no únicamente punitivas. • El consumo...</t>
+          <t>• En la localidad de Kennedy se realizó una jornada deportiva con Futsala Colombia, que acercó a los jóvenes la oferta integral de servicios sociales, digitales y educativos en territorio. • En Jóvenes con Oportunidades, más de 18.000 jóvenes han...</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>La Academia Ñam llega a San Cristóbal con oportunidades para los jóvenes interesados en el sector de la gastronomía</t>
+          <t>Abre 320 becas a jóvenes con proyectos en sus comunidades o entornos, ¿cómo participar?</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>SDIS - Juventud</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -9785,86 +9781,86 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#1e64cd90aa</t>
+          <t>https://www.elespectador.com/colombia/mas-regiones/abre-320-becas-a-jovenes-con-proyectos-en-sus-comunidades-o-entornos-como-participar/</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>•El Distrito, en alianza con la Fundación Gastronomía Social, lanzan una nueva convocatoria dirigida a jóvenes de 18 a 30 años interesados en formarse en servicio para el sector de la gastronomía. •Esta formación gratuita ofrece capacitación a...</t>
+          <t>Abren becas para jóvenes en Medellín, Santa Marta, Cartagena y Bogotá. Tendrán formación, mentorías y acceso a redes de liderazgo.</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>El deporte abrió la puerta a nuevas oportunidades y conexión para los jóvenes de Bogotá</t>
+          <t>La primera guardia afro urbana liderada por mujeres surge en Cali</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>SDIS - Juventud</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Cultura y deporte</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#8b36ede0c2</t>
+          <t>https://www.elespectador.com/colombia/cali/la-primera-guardia-afro-urbana-liderada-por-mujeres-surge-en-cali/</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>• En la localidad de Kennedy se realizó una jornada deportiva con Futsala Colombia, que acercó a los jóvenes la oferta integral de servicios sociales, digitales y educativos en territorio. • En Jóvenes con Oportunidades, más de 18.000 jóvenes han...</t>
+          <t>En Llano Verde, mujeres desplazadas crearon la primera guardia afro urbana del país para prevenir violencia y proteger a jóvenes.</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Abre 320 becas a jóvenes con proyectos en sus comunidades o entornos, ¿cómo participar?</t>
+          <t>Bogotá fortalece el proceso de preinscripción de Jóvenes con Oportunidades 2026 y habilita nuevo enlace</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>SDIS - Juventud</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -9879,24 +9875,24 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/mas-regiones/abre-320-becas-a-jovenes-con-proyectos-en-sus-comunidades-o-entornos-como-participar/</t>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#6c31bba0c9</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>Abren becas para jóvenes en Medellín, Santa Marta, Cartagena y Bogotá. Tendrán formación, mentorías y acceso a redes de liderazgo.</t>
+          <t>•El Distrito habilitó un nuevo enlace mejorado para garantizar una experiencia más ágil, estable y segura en la convocatoria 2026 de Jóvenes con Oportunidades. •Las y los jóvenes entre 14 y 28 años que vivan en Bogotá y estén clasificados en Sisbén...</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>La primera guardia afro urbana liderada por mujeres surge en Cali</t>
+          <t>Aumenta el número de desaparecidos en Córdoba, dos jóvenes arrastrados por un arroyo</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -9911,12 +9907,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Protección</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
@@ -9926,24 +9922,24 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/cali/la-primera-guardia-afro-urbana-liderada-por-mujeres-surge-en-cali/</t>
+          <t>https://www.elespectador.com/colombia/mas-regiones/dos-campesinos-en-cordoba-desaparecen-tras-intentar-cruzar-un-arroyo/</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>En Llano Verde, mujeres desplazadas crearon la primera guardia afro urbana del país para prevenir violencia y proteger a jóvenes.</t>
+          <t>Dos jóvenes campesinos permanecen desaparecidos en Córdoba, luego de que una corriente los arrastrara en cuanto intentaban cruzar un arroyo</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Bogotá fortalece el proceso de preinscripción de Jóvenes con Oportunidades 2026 y habilita nuevo enlace</t>
+          <t>Bogotá abre convocatoria 2026 del programa Jóvenes con Oportunidades con más de 12.000 nuevos cupos</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -9973,81 +9969,77 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#6c31bba0c9</t>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#9a0f0687f3</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>•El Distrito habilitó un nuevo enlace mejorado para garantizar una experiencia más ágil, estable y segura en la convocatoria 2026 de Jóvenes con Oportunidades. •Las y los jóvenes entre 14 y 28 años que vivan en Bogotá y estén clasificados en Sisbén...</t>
+          <t>• El Distrito abre estaconvocatoria de Jóvenes con Oportunidades con más de 8.000 nuevos cupos, en su primera etapa, para jóvenes entre 14 y 28 años de Bogotá, fortaleciendo su acceso a rutas de formación, acompañamiento psicosocial y transferencias...</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Aumenta el número de desaparecidos en Córdoba, dos jóvenes arrastrados por un arroyo</t>
+          <t>Menores de edad mataron de 17 puñaladas a un hombre que iba de polizón en un camión de carga en la vía Bogotá-Villavicencio: quedó en video - Infobae</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Protección</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/mas-regiones/dos-campesinos-en-cordoba-desaparecen-tras-intentar-cruzar-un-arroyo/</t>
-        </is>
-      </c>
-      <c r="I207" t="inlineStr">
-        <is>
-          <t>Dos jóvenes campesinos permanecen desaparecidos en Córdoba, luego de que una corriente los arrastrara en cuanto intentaban cruzar un arroyo</t>
-        </is>
-      </c>
+          <t>https://news.google.com/rss/articles/CBMikAJBVV95cUxNYWQxNTA1UWhDOUtWS2dSWXNNQ19idDVRNXV4aktnZzFERmdBaFg0c2lrT2plR0tXcDN1dlFhd0J0Q1BUVmJEVU1YYTR3N0NtQUx2LTQ3amhNR2pNc0tvcjR6X1FfbkIwczFROFJTaFotclVpRGxId2h1eWtqbHMzSkNXc0JCeU1DWjkxOG5qekx4YjZGRlVVckdyX1gyT0luR2Nkd3ZQUTNFM1d1LUlvMzNSSGxiQUZ5V2pqT2E4WXhZWWRpY2JheDhpaWhwOTQwLThDWFlXU1p0N0lZVk5nSHdVZU8zWVlKNE9GTVJKaUxYTkxDMUt1MTF0NzN5MVUxXzBNUjZtZVJsWm9zMkNNdg?oc=5</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Bogotá abre convocatoria 2026 del programa Jóvenes con Oportunidades con más de 12.000 nuevos cupos</t>
+          <t>Menores de edad mataron de 17 puñaladas a un hombre que iba de polizón en un camión de carga en la vía Bogotá-Villavicencio: quedó en video - Infobae</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>SDIS - Juventud</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -10067,24 +10059,20 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#9a0f0687f3</t>
-        </is>
-      </c>
-      <c r="I208" t="inlineStr">
-        <is>
-          <t>• El Distrito abre estaconvocatoria de Jóvenes con Oportunidades con más de 8.000 nuevos cupos, en su primera etapa, para jóvenes entre 14 y 28 años de Bogotá, fortaleciendo su acceso a rutas de formación, acompañamiento psicosocial y transferencias...</t>
-        </is>
-      </c>
+          <t>https://news.google.com/rss/articles/CBMikAJBVV95cUxNYWQxNTA1UWhDOUtWS2dSWXNNQ19idDVRNXV4aktnZzFERmdBaFg0c2lrT2plR0tXcDN1dlFhd0J0Q1BUVmJEVU1YYTR3N0NtQUx2LTQ3amhNR2pNc0tvcjR6X1FfbkIwczFROFJTaFotclVpRGxId2h1eWtqbHMzSkNXc0JCeU1DWjkxOG5qekx4YjZGRlVVckdyX1gyT0luR2Nkd3ZQUTNFM1d1LUlvMzNSSGxiQUZ5V2pqT2E4WXhZWWRpY2JheDhpaWhwOTQwLThDWFlXU1p0N0lZVk5nSHdVZU8zWVlKNE9GTVJKaUxYTkxDMUt1MTF0NzN5MVUxXzBNUjZtZVJsWm9zMkNNdtIBqwJBVV95cUxPZnpNT2FPSmdUeFl0UmFScGh6MzVlYm9tVWhQekJjVTdRcHM2ZDlEbWFhVUJBX3dudVF2V01OaDdSRWN6c1FXV2thM0VJOHppRWhaWEVpbTVPOTVTd3RKcmJLT1NHa2MwVlR5SzE2TzlHM0RLS3k2VzFKRDdtaTd2M3RCNENTeXByY1BBTjR1SFE3STJQS3JBWURBRER1cTBKQmx2MVR6Sk5xYlpwbTdpNGRyWVBYdmkxTU9JaWNtRlZVM2JzTGtMQUhxaHFnUmVPQlNPbkNYWGlBX2ttc0Y4cjVzR0dVaFBER3lSMWxRZGVGVTRhTFZ6RE82ZzFKeWJnQ0U0bWlINmlXRE9KdUJvbzdpSEg1NURXMzZKeVNHWTd4b0puVldnbFlscw?oc=5</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Menores de edad mataron de 17 puñaladas a un hombre que iba de polizón en un camión de carga en la vía Bogotá-Villavicencio: quedó en video - Infobae</t>
+          <t>Jóvenes narraron el calvario sufrido cuando fueron víctimas de presunto abuso en la Universidad de Cartagena: “Causó un gran sangrado”</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -10099,22 +10087,22 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Cartagena</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAJBVV95cUxNYWQxNTA1UWhDOUtWS2dSWXNNQ19idDVRNXV4aktnZzFERmdBaFg0c2lrT2plR0tXcDN1dlFhd0J0Q1BUVmJEVU1YYTR3N0NtQUx2LTQ3amhNR2pNc0tvcjR6X1FfbkIwczFROFJTaFotclVpRGxId2h1eWtqbHMzSkNXc0JCeU1DWjkxOG5qekx4YjZGRlVVckdyX1gyT0luR2Nkd3ZQUTNFM1d1LUlvMzNSSGxiQUZ5V2pqT2E4WXhZWWRpY2JheDhpaWhwOTQwLThDWFlXU1p0N0lZVk5nSHdVZU8zWVlKNE9GTVJKaUxYTkxDMUt1MTF0NzN5MVUxXzBNUjZtZVJsWm9zMkNNdg?oc=5</t>
+          <t>https://www.infobae.com/colombia/2026/02/02/jovenes-narraron-el-calvario-sufrido-cuando-fueron-victimas-de-presunto-abuso-en-la-universidad-de-cartagena-causo-un-gran-sangrado/</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
@@ -10122,27 +10110,27 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Menores de edad mataron de 17 puñaladas a un hombre que iba de polizón en un camión de carga en la vía Bogotá-Villavicencio: quedó en video - Infobae</t>
+          <t>Bogotá abre nueva convocatoria de Academia Ñam para fortalecer la empleabilidad juvenil en el sector gastronómico</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>SDIS - Juventud</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -10157,20 +10145,24 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAJBVV95cUxNYWQxNTA1UWhDOUtWS2dSWXNNQ19idDVRNXV4aktnZzFERmdBaFg0c2lrT2plR0tXcDN1dlFhd0J0Q1BUVmJEVU1YYTR3N0NtQUx2LTQ3amhNR2pNc0tvcjR6X1FfbkIwczFROFJTaFotclVpRGxId2h1eWtqbHMzSkNXc0JCeU1DWjkxOG5qekx4YjZGRlVVckdyX1gyT0luR2Nkd3ZQUTNFM1d1LUlvMzNSSGxiQUZ5V2pqT2E4WXhZWWRpY2JheDhpaWhwOTQwLThDWFlXU1p0N0lZVk5nSHdVZU8zWVlKNE9GTVJKaUxYTkxDMUt1MTF0NzN5MVUxXzBNUjZtZVJsWm9zMkNNdtIBqwJBVV95cUxPZnpNT2FPSmdUeFl0UmFScGh6MzVlYm9tVWhQekJjVTdRcHM2ZDlEbWFhVUJBX3dudVF2V01OaDdSRWN6c1FXV2thM0VJOHppRWhaWEVpbTVPOTVTd3RKcmJLT1NHa2MwVlR5SzE2TzlHM0RLS3k2VzFKRDdtaTd2M3RCNENTeXByY1BBTjR1SFE3STJQS3JBWURBRER1cTBKQmx2MVR6Sk5xYlpwbTdpNGRyWVBYdmkxTU9JaWNtRlZVM2JzTGtMQUhxaHFnUmVPQlNPbkNYWGlBX2ttc0Y4cjVzR0dVaFBER3lSMWxRZGVGVTRhTFZ6RE82ZzFKeWJnQ0U0bWlINmlXRE9KdUJvbzdpSEg1NURXMzZKeVNHWTd4b0puVldnbFlscw?oc=5</t>
-        </is>
-      </c>
-      <c r="I210" t="inlineStr"/>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#85a520b8bc</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>• La Secretaría Distrital de Integración Social, en alianza con la Fundación Gastronomía Social, abre una nueva convocatoria de Academia Ñam, un programa gratuito de formación y práctica laboral en servicio gastronómico dirigido a jóvenes de 18 a 30...</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Jóvenes narraron el calvario sufrido cuando fueron víctimas de presunto abuso en la Universidad de Cartagena: “Causó un gran sangrado”</t>
+          <t>Frustraron robo en un restaurante en Bosa, Bogotá: un hombre de 23 años y dos menores de edad fueron capturados</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -10185,22 +10177,22 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Seguridad</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Cartagena</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/02/02/jovenes-narraron-el-calvario-sufrido-cuando-fueron-victimas-de-presunto-abuso-en-la-universidad-de-cartagena-causo-un-gran-sangrado/</t>
+          <t>https://www.infobae.com/colombia/2026/01/27/frustraron-robo-en-un-restaurante-en-bosa-bogota-un-hombre-de-23-anos-y-dos-menores-de-edad-fueron-capturados/</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -10208,74 +10200,70 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Bogotá abre nueva convocatoria de Academia Ñam para fortalecer la empleabilidad juvenil en el sector gastronómico</t>
+          <t>Alerta en Tolima: ya son 4 los muertos por fiebre amarilla en 2026, entre ellos un menor de edad</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>SDIS - Juventud</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#85a520b8bc</t>
-        </is>
-      </c>
-      <c r="I212" t="inlineStr">
-        <is>
-          <t>• La Secretaría Distrital de Integración Social, en alianza con la Fundación Gastronomía Social, abre una nueva convocatoria de Academia Ñam, un programa gratuito de formación y práctica laboral en servicio gastronómico dirigido a jóvenes de 18 a 30...</t>
-        </is>
-      </c>
+          <t>https://www.bluradio.com/nacion/alerta-en-tolima-ya-son-4-los-muertos-por-fiebre-amarilla-en-2026-entre-ellos-un-menor-de-edad-rg10</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Frustraron robo en un restaurante en Bosa, Bogotá: un hombre de 23 años y dos menores de edad fueron capturados</t>
+          <t>Distrito Joven acompañó a más de 50 mil jóvenes en la construcción de sus proyectos de vida durante 2025</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>SDIS - Juventud</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Seguridad</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -10290,25 +10278,29 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/27/frustraron-robo-en-un-restaurante-en-bosa-bogota-un-hombre-de-23-anos-y-dos-menores-de-edad-fueron-capturados/</t>
-        </is>
-      </c>
-      <c r="I213" t="inlineStr"/>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#729a4b8e04</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>• Durante 2025, la Subdirección para la Juventud acompañó a más de 50 mil jóvenes en Bogotá, fortaleciendo sus proyectos de vida a través de una atención integral. • Los servicios y estrategias implementados promovieron la inclusión social,...</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Alerta en Tolima: ya son 4 los muertos por fiebre amarilla en 2026, entre ellos un menor de edad</t>
+          <t>Radiografía de los ‘ninis’ en Colombia: 2,26 millones de jóvenes están desconectados del estudio y el empleo - Infobae</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -10318,12 +10310,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Empleo</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
@@ -10333,7 +10325,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/nacion/alerta-en-tolima-ya-son-4-los-muertos-por-fiebre-amarilla-en-2026-entre-ellos-un-menor-de-edad-rg10</t>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxQQzU0U2tHY3lvTUVKRmR2SExOeUdySS0ycnZSVWd3MlhIQmJmYVZxNm9NNVZ2YU8wZ1MtcUJiOXRPLWZhWUNLcUtVdG1uUVVUd0VfYU5sQWVNSjlDVWdDUTc2ZG8yajJIUlk0bVJxTTR3clhjd0wwRl9wSTRSUlk0UnZtY2FZTWZ2QUhQbjJ1TkdibEw4YmU4YXNTMEJUeV85V0dfSzdUQ0hSSk5DbFdZUk5VV2dnaGdabHhVQ1p2bjlCTlVKNHJNV3NoNmQtcG9CUkZaMWVDVXZmWDFXSTIxVi00UdIB_gFBVV95cUxQQXJkUXE5UnM4ZVhIZHo3UFJuSU0xVllueWt3Unk2aC03YllYdDBfc0FvalRGMDNsWjBRNmZfNUV1bTlsbWM3dFlLOGNCajVqcXQ5Z2hVRzdROXlpTUdrWEtLdVNyaDFqRGlnckQ3OUhfTjVNVk53YklESGhMMlRCcUVkNFRYMS04RUUwR2hvdERISVdENVlydzZhOGpfaU1yX0xkSkg0S3laV3E2MVV1UHRDN05aRU1iMlBiS2lRcXNWYTdMTlhVTzI2VkJkeFZTXzhqbS1adkpFa1RiX2dBaDJDaWhVYXVsM1psSV9jWjZGdy1QUXJ1d0xCdUxMdw?oc=5</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
@@ -10346,7 +10338,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Distrito Joven acompañó a más de 50 mil jóvenes en la construcción de sus proyectos de vida durante 2025</t>
+          <t>Casas de Juventud lanzan nuevos Semilleros Distritales para potenciar el talento juvenil en Bogotá</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -10361,7 +10353,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Cultura y deporte</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
@@ -10376,24 +10368,24 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#729a4b8e04</t>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#f8686f5026</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>• Durante 2025, la Subdirección para la Juventud acompañó a más de 50 mil jóvenes en Bogotá, fortaleciendo sus proyectos de vida a través de una atención integral. • Los servicios y estrategias implementados promovieron la inclusión social,...</t>
+          <t>•Bogotá abre la convocatoria a semilleros gratuitos en artes, deporte y cultura urbana, dirigidos a jóvenes entre 14 y 28 años de todas las localidades, como una estrategia distrital para fortalecer la expresión, la participación y el desarrollo de...</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Radiografía de los ‘ninis’ en Colombia: 2,26 millones de jóvenes están desconectados del estudio y el empleo - Infobae</t>
+          <t>Estudio reveló las principales problemáticas que preocupan a los jóvenes en Colombia, previo a las elecciones de Congreso y Presidencia - Infobae</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -10408,7 +10400,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Empleo</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -10423,7 +10415,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxQQzU0U2tHY3lvTUVKRmR2SExOeUdySS0ycnZSVWd3MlhIQmJmYVZxNm9NNVZ2YU8wZ1MtcUJiOXRPLWZhWUNLcUtVdG1uUVVUd0VfYU5sQWVNSjlDVWdDUTc2ZG8yajJIUlk0bVJxTTR3clhjd0wwRl9wSTRSUlk0UnZtY2FZTWZ2QUhQbjJ1TkdibEw4YmU4YXNTMEJUeV85V0dfSzdUQ0hSSk5DbFdZUk5VV2dnaGdabHhVQ1p2bjlCTlVKNHJNV3NoNmQtcG9CUkZaMWVDVXZmWDFXSTIxVi00UdIB_gFBVV95cUxQQXJkUXE5UnM4ZVhIZHo3UFJuSU0xVllueWt3Unk2aC03YllYdDBfc0FvalRGMDNsWjBRNmZfNUV1bTlsbWM3dFlLOGNCajVqcXQ5Z2hVRzdROXlpTUdrWEtLdVNyaDFqRGlnckQ3OUhfTjVNVk53YklESGhMMlRCcUVkNFRYMS04RUUwR2hvdERISVdENVlydzZhOGpfaU1yX0xkSkg0S3laV3E2MVV1UHRDN05aRU1iMlBiS2lRcXNWYTdMTlhVTzI2VkJkeFZTXzhqbS1adkpFa1RiX2dBaDJDaWhVYXVsM1psSV9jWjZGdy1QUXJ1d0xCdUxMdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwJBVV95cUxNYXdTSFVia3cwbnV6Y050TzB5M2JQckhpbDVVajdoRnZnZG1yTThKbVF0bFhsUWN0ZnFuM1h5M0VYWmxiUGZjaHN3WV85OFpwWlFaWkFkanlsSmcwNFhJQk5PTjJBZ3RXcTgzNHFCQU5qTGlUZlB3WTkxZmx3SVIwV05jblIwUFNNUUdBTkU2M2FZSHNlTUgyb2ZhZWsyMktyc0UtR2k2Z001NkUxZ01xSkxoei1uMUZqaGJfV0k2MWktaDVNRGtGOS1nNXlGTEdSZ1VSdEJGRDRkbkNPM3R1aURVbl9ZR3FYcC1aMkI4T0k4bDJaT0Jmb1dLNktqQVVOeHVpUGpkUGd3TmvSAaYCQVVfeXFMTl9Uc2p1OEVpYzZaLUFYOERNUjVQVjVSaHJtTEhhT1BibW1BMkVwQ0VVUFc3d2RsaWNtNHdTZm0tbDRlMHBPLWVES0Vyd3hKZHRQUmExYmVmaXNrZE5rTGhEWmd0YXQ5cjdPOGIyeVdEYUV5NHplUnFMX2pYWkRXdEFxbVB1UGhEOENhTWM3S2NCVnJQbDg4clVoSUhIWENVSUh1VE54MjZKUjF3OWdpUDZjdld4WU1BLTA2dWR2ZEwxQUpnLUNXS3JZZ2hWUkFQN2taQktacVNhM3NMOS1ZR1g2dkhmYmVmU0Q4Q0o2dWNCZUNMQnJsaDFjQlRXQUp5NUpEYllxWlhVQVVfbVlBdmVBa2RJRjVqNUNfTGxHMnFRaGhYMnN3?oc=5</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
@@ -10431,59 +10423,55 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Casas de Juventud lanzan nuevos Semilleros Distritales para potenciar el talento juvenil en Bogotá</t>
+          <t>Menor de edad colombiano fue baleado frente a su escuela en Chicago, la familia exige justicia</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>SDIS - Juventud</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Cultura y deporte</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#f8686f5026</t>
-        </is>
-      </c>
-      <c r="I217" t="inlineStr">
-        <is>
-          <t>•Bogotá abre la convocatoria a semilleros gratuitos en artes, deporte y cultura urbana, dirigidos a jóvenes entre 14 y 28 años de todas las localidades, como una estrategia distrital para fortalecer la expresión, la participación y el desarrollo de...</t>
-        </is>
-      </c>
+          <t>https://www.infobae.com/colombia/2026/01/14/menor-de-edad-colombiano-fue-baleado-frente-a-su-escuela-en-chicago-la-familia-exige-justicia/</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Estudio reveló las principales problemáticas que preocupan a los jóvenes en Colombia, previo a las elecciones de Congreso y Presidencia - Infobae</t>
+          <t>El particular castigo de Policía en Barranquilla a un grupo de jóvenes quedó en video: “El cuerpo sufre”</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -10498,12 +10486,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Seguridad</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Barranquilla</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
@@ -10513,7 +10501,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwJBVV95cUxNYXdTSFVia3cwbnV6Y050TzB5M2JQckhpbDVVajdoRnZnZG1yTThKbVF0bFhsUWN0ZnFuM1h5M0VYWmxiUGZjaHN3WV85OFpwWlFaWkFkanlsSmcwNFhJQk5PTjJBZ3RXcTgzNHFCQU5qTGlUZlB3WTkxZmx3SVIwV05jblIwUFNNUUdBTkU2M2FZSHNlTUgyb2ZhZWsyMktyc0UtR2k2Z001NkUxZ01xSkxoei1uMUZqaGJfV0k2MWktaDVNRGtGOS1nNXlGTEdSZ1VSdEJGRDRkbkNPM3R1aURVbl9ZR3FYcC1aMkI4T0k4bDJaT0Jmb1dLNktqQVVOeHVpUGpkUGd3TmvSAaYCQVVfeXFMTl9Uc2p1OEVpYzZaLUFYOERNUjVQVjVSaHJtTEhhT1BibW1BMkVwQ0VVUFc3d2RsaWNtNHdTZm0tbDRlMHBPLWVES0Vyd3hKZHRQUmExYmVmaXNrZE5rTGhEWmd0YXQ5cjdPOGIyeVdEYUV5NHplUnFMX2pYWkRXdEFxbVB1UGhEOENhTWM3S2NCVnJQbDg4clVoSUhIWENVSUh1VE54MjZKUjF3OWdpUDZjdld4WU1BLTA2dWR2ZEwxQUpnLUNXS3JZZ2hWUkFQN2taQktacVNhM3NMOS1ZR1g2dkhmYmVmU0Q4Q0o2dWNCZUNMQnJsaDFjQlRXQUp5NUpEYllxWlhVQVVfbVlBdmVBa2RJRjVqNUNfTGxHMnFRaGhYMnN3?oc=5</t>
+          <t>https://www.infobae.com/colombia/2026/01/09/el-particular-castigo-de-policia-en-barranquilla-a-un-grupo-de-jovenes-quedo-en-video-el-cuerpo-sufre/</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
@@ -10521,12 +10509,12 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Menor de edad colombiano fue baleado frente a su escuela en Chicago, la familia exige justicia</t>
+          <t>Aumenta a 1.419 el número de lesionados por pólvora en Colombia; 428 son menores de edad - Infobae</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -10541,7 +10529,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -10556,7 +10544,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/14/menor-de-edad-colombiano-fue-baleado-frente-a-su-escuela-en-chicago-la-familia-exige-justicia/</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxOY1FwS0xiWWVaYl9saTQ5X0xRYnVoR0lwNE5XYUVaaUl3LW8yN0hEZGFnckI5VVlrVnBPSFJpeDNkU1JIaC01dVJVdFJYbEtSVTFXRTBCdTFDSDJ6TXZjc2t5N0t0cVFUY2JGbGZ1NDB5R1FJVG1RX25hREVIMjZlYktrdHc2QUFiZXNQTXFGZk9zeWNJRUl1aWNCbG9OXzZRQVA2dFFUZ1J3UnJrZzU4Qnk5TVBMajBPenJOU0ZBekNheEl2SkV3QVRUc9IB5gFBVV95cUxQeDZfb0gzZm9CTTRpYWx1ZTBielQ1TVgtaHNBOXRVRjBDcVd2V3M2anR3VTJaLU8zUEFkbEJkdDFEcHdHQUlpNGVORDZXV1Jxdzl4YmdPN3F1bk10ODZ1MnpOUjVSRTZscUUzYl80MDVpaHROOXdBNlhoQkFFR3RyVVJ1MWw1WTVZZVcwWnZ6THBEYWkxR1hEMTQzRGIzRWJvWlVUOFFBU2duZE5MRnRoRnQyZDl0ajd2SEpUVVM5ZW5POEpzLUZIcTV1c3RaaHlvanRUcG1oU3REVFVVQk5xTnhuLWk1UQ?oc=5</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
@@ -10564,12 +10552,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>El particular castigo de Policía en Barranquilla a un grupo de jóvenes quedó en video: “El cuerpo sufre”</t>
+          <t>Gobierno condonará créditos del Icetex a más de mil jóvenes en Colombia: quiénes se beneficiarán - Infobae</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -10584,12 +10572,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Seguridad</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Barranquilla</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
@@ -10599,7 +10587,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/09/el-particular-castigo-de-policia-en-barranquilla-a-un-grupo-de-jovenes-quedo-en-video-el-cuerpo-sufre/</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxOZlVSRmszbERPaGNNNjhFRXY3VGVlUjc0eXo5R002RDZTbk15NWlUb1pLeWtWdmtObV9fY2ZxUmQ3cHNacWJoMExhZVZDRjlJM0lYZ2VfUVJOTEJnOXhGeXhtOFdlX3BmdFZTWXNJWHpXSDJsREdSaXJHSmFfY0RCcV8xSFVTLThuS1M4eUwxYTMxdWU2WTY3YUVTaWtLWHJFRUhlM0EtQzFNdDQwNy1wU2NyMDIzSk5rZGI4ZExtcmx1b2R2d01DNzdZT29LanFzXzBaNjluZ0rSAfMBQVVfeXFMT3pmVy1QSHJLaTJmREJmLVNLano0XzdpeW1VemRocGF5eHBVZktPRnNkTnNBUElFMDk1UUQ4MTZRNENCVWpZQVhTRmNrV1dwbDhCQnFvemZKTmZyT2cwdV96a2xOUWZDZEloWEFKcjJ2QkJsX0h3bFZDTkNRNGJOY1U5UGZaN0x6YU1EQlN5ZlFLb0hYQkM1MDdKNWl5TS1OcVNYWHRGXzl5NFp1WnQ2YWJqcWZzZDlDTk5FQ19Sa2lZOXRpOEJ4LV9DUnVOenhkQ3FJUGhkZkExNkNOYlV2Z21iLUQxUmF0eDJ5c3NyekcxTFlF?oc=5</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
@@ -10607,98 +10595,106 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Aumenta a 1.419 el número de lesionados por pólvora en Colombia; 428 son menores de edad - Infobae</t>
+          <t>Más de 40 jóvenes de Bogotá fueron reconocidos por su talento, creatividad y liderazgo en la Semana de la Juventud y la Semana Andina 2025</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>SDIS - Juventud</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Cultura y deporte</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxOY1FwS0xiWWVaYl9saTQ5X0xRYnVoR0lwNE5XYUVaaUl3LW8yN0hEZGFnckI5VVlrVnBPSFJpeDNkU1JIaC01dVJVdFJYbEtSVTFXRTBCdTFDSDJ6TXZjc2t5N0t0cVFUY2JGbGZ1NDB5R1FJVG1RX25hREVIMjZlYktrdHc2QUFiZXNQTXFGZk9zeWNJRUl1aWNCbG9OXzZRQVA2dFFUZ1J3UnJrZzU4Qnk5TVBMajBPenJOU0ZBekNheEl2SkV3QVRUc9IB5gFBVV95cUxQeDZfb0gzZm9CTTRpYWx1ZTBielQ1TVgtaHNBOXRVRjBDcVd2V3M2anR3VTJaLU8zUEFkbEJkdDFEcHdHQUlpNGVORDZXV1Jxdzl4YmdPN3F1bk10ODZ1MnpOUjVSRTZscUUzYl80MDVpaHROOXdBNlhoQkFFR3RyVVJ1MWw1WTVZZVcwWnZ6THBEYWkxR1hEMTQzRGIzRWJvWlVUOFFBU2duZE5MRnRoRnQyZDl0ajd2SEpUVVM5ZW5POEpzLUZIcTV1c3RaaHlvanRUcG1oU3REVFVVQk5xTnhuLWk1UQ?oc=5</t>
-        </is>
-      </c>
-      <c r="I221" t="inlineStr"/>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#c68de3a13a</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>• Más de 40 jóvenes y colectivos fueron premiados por su creatividad, liderazgo y compromiso social durante la Semana de la Juventud y la Semana Andina 2025. • La Subdirección para la Juventud de la Secretaría Distrital de Integración Social abrió...</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Gobierno condonará créditos del Icetex a más de mil jóvenes en Colombia: quiénes se beneficiarán - Infobae</t>
+          <t>Jóvenes con Oportunidades abre convocatoria para su ruta de formación en cursos cortos</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>SDIS - Juventud</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Empleo</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxOZlVSRmszbERPaGNNNjhFRXY3VGVlUjc0eXo5R002RDZTbk15NWlUb1pLeWtWdmtObV9fY2ZxUmQ3cHNacWJoMExhZVZDRjlJM0lYZ2VfUVJOTEJnOXhGeXhtOFdlX3BmdFZTWXNJWHpXSDJsREdSaXJHSmFfY0RCcV8xSFVTLThuS1M4eUwxYTMxdWU2WTY3YUVTaWtLWHJFRUhlM0EtQzFNdDQwNy1wU2NyMDIzSk5rZGI4ZExtcmx1b2R2d01DNzdZT29LanFzXzBaNjluZ0rSAfMBQVVfeXFMT3pmVy1QSHJLaTJmREJmLVNLano0XzdpeW1VemRocGF5eHBVZktPRnNkTnNBUElFMDk1UUQ4MTZRNENCVWpZQVhTRmNrV1dwbDhCQnFvemZKTmZyT2cwdV96a2xOUWZDZEloWEFKcjJ2QkJsX0h3bFZDTkNRNGJOY1U5UGZaN0x6YU1EQlN5ZlFLb0hYQkM1MDdKNWl5TS1OcVNYWHRGXzl5NFp1WnQ2YWJqcWZzZDlDTk5FQ19Sa2lZOXRpOEJ4LV9DUnVOenhkQ3FJUGhkZkExNkNOYlV2Z21iLUQxUmF0eDJ5c3NyekcxTFlF?oc=5</t>
-        </is>
-      </c>
-      <c r="I222" t="inlineStr"/>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#28dd65106b</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>•La Subdirección para la Juventud anunció la apertura de nuevos cupos en la ruta de formación en cursos cortos, dirigida a jóvenes entre 18 y 28 años que vivan en Bogotá y cuenten con Sisbén IV (A1 a C09). • La ruta combina proyecto de vida, cursos...</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Más de 40 jóvenes de Bogotá fueron reconocidos por su talento, creatividad y liderazgo en la Semana de la Juventud y la Semana Andina 2025</t>
+          <t>La Academia Ñam busca jóvenes interesados en el sector de la gastronomía</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -10713,7 +10709,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Cultura y deporte</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -10728,24 +10724,24 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#c68de3a13a</t>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#8622ae2557</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>• Más de 40 jóvenes y colectivos fueron premiados por su creatividad, liderazgo y compromiso social durante la Semana de la Juventud y la Semana Andina 2025. • La Subdirección para la Juventud de la Secretaría Distrital de Integración Social abrió...</t>
+          <t>• El Distrito, en alianza con la Fundación Gastronomía Social, lanzan una nueva convocatoria dirigida a jóvenes de 18 a 30 años de las localidades de La Candelaria y Santa Fe interesados en formarse en servicio en gastronomía. • Esta formación...</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Jóvenes con Oportunidades abre convocatoria para su ruta de formación en cursos cortos</t>
+          <t>La Escuela Distrital de Emprendimiento ya está en marcha en Kennedy</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -10760,7 +10756,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Empleo</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -10775,24 +10771,24 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#28dd65106b</t>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#09b7d9045f</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>•La Subdirección para la Juventud anunció la apertura de nuevos cupos en la ruta de formación en cursos cortos, dirigida a jóvenes entre 18 y 28 años que vivan en Bogotá y cuenten con Sisbén IV (A1 a C09). • La ruta combina proyecto de vida, cursos...</t>
+          <t>• 50 jóvenes emprendedores fortalecerán sus proyectos de negocios de la mano de expertos y líderes empresariales. • La Escuela Distrital de Emprendimiento, que llega a su quinta edición, nace de la alianza del Distrito con la ANDI y la Fundación...</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>La Academia Ñam busca jóvenes interesados en el sector de la gastronomía</t>
+          <t>La Academia Ñam abre una nueva convocatoria para jóvenes interesados en el sector de la gastronomía</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -10822,24 +10818,24 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#8622ae2557</t>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#17e48d890a</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>• El Distrito, en alianza con la Fundación Gastronomía Social, lanzan una nueva convocatoria dirigida a jóvenes de 18 a 30 años de las localidades de La Candelaria y Santa Fe interesados en formarse en servicio en gastronomía. • Esta formación...</t>
+          <t>• El Distrito, en alianza con la Fundación Gastronomía Social, lanzan convocatoria dirigida a jóvenes de 18 a 30 años interesados en formarse en servicio en el sector de la gastronomía. • Esta formación gratuita ofrece capacitación a través de...</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>La Escuela Distrital de Emprendimiento ya está en marcha en Kennedy</t>
+          <t>Bogotá ofrece más de 1.500 becas para que jóvenes estudien programas técnicos laborales</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -10869,24 +10865,24 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#09b7d9045f</t>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#e22c14d73a</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>• 50 jóvenes emprendedores fortalecerán sus proyectos de negocios de la mano de expertos y líderes empresariales. • La Escuela Distrital de Emprendimiento, que llega a su quinta edición, nace de la alianza del Distrito con la ANDI y la Fundación...</t>
+          <t>•Se trata de la convocatoria Formación y Educación para el trabajo que les permitirá a los jóvenes de la ciudad formarse en una ocupación que requiere el mercado laboral. •Losbeneficiarios podrán estudiar mercadeo y ventas, mecánica dental, cocina,...</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>La Academia Ñam abre una nueva convocatoria para jóvenes interesados en el sector de la gastronomía</t>
+          <t>Jóvenes de la Casa de la Juventud de Suba aprenden sobre medio ambiente y navegan el río Bogotá</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -10901,7 +10897,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
@@ -10916,24 +10912,24 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#17e48d890a</t>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#ba7949b3a9</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>• El Distrito, en alianza con la Fundación Gastronomía Social, lanzan convocatoria dirigida a jóvenes de 18 a 30 años interesados en formarse en servicio en el sector de la gastronomía. • Esta formación gratuita ofrece capacitación a través de...</t>
+          <t>•Los navegantes confirmaron que los malos olores quedaron en el pasado y hoy se aprecian algunas especies de fauna que han comenzado a retornar a lo largo del cauce. • Gracias a la Corporación Autónoma Regional de Cundinamarca (CAR), encargada de...</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Bogotá ofrece más de 1.500 becas para que jóvenes estudien programas técnicos laborales</t>
+          <t>Está abierta la convocatoria para la Escuela Distrital de Emprendimiento en Kennedy</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -10963,24 +10959,24 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#e22c14d73a</t>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#2acaf10b23</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>•Se trata de la convocatoria Formación y Educación para el trabajo que les permitirá a los jóvenes de la ciudad formarse en una ocupación que requiere el mercado laboral. •Losbeneficiarios podrán estudiar mercadeo y ventas, mecánica dental, cocina,...</t>
+          <t>• Jóvenes emprendedores podrán fortalecer sus proyectos de la mano de expertos y líderes empresariales. • La Escuela Distrital de Emprendimiento nace de la alianza del Distrito con la ANDI y la Fundación ANDI.</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Jóvenes de la Casa de la Juventud de Suba aprenden sobre medio ambiente y navegan el río Bogotá</t>
+          <t>El Frailejón abre sus puertas: Usme estrena nueva Casa de la Juventud</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -11010,104 +11006,10 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#ba7949b3a9</t>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#c7eca5d4bd</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
-        <is>
-          <t>•Los navegantes confirmaron que los malos olores quedaron en el pasado y hoy se aprecian algunas especies de fauna que han comenzado a retornar a lo largo del cauce. • Gracias a la Corporación Autónoma Regional de Cundinamarca (CAR), encargada de...</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="inlineStr">
-        <is>
-          <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>Está abierta la convocatoria para la Escuela Distrital de Emprendimiento en Kennedy</t>
-        </is>
-      </c>
-      <c r="C230" t="inlineStr">
-        <is>
-          <t>SDIS - Juventud</t>
-        </is>
-      </c>
-      <c r="D230" t="inlineStr">
-        <is>
-          <t>institucional</t>
-        </is>
-      </c>
-      <c r="E230" t="inlineStr">
-        <is>
-          <t>Educación</t>
-        </is>
-      </c>
-      <c r="F230" t="inlineStr">
-        <is>
-          <t>Bogotá</t>
-        </is>
-      </c>
-      <c r="G230" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="H230" t="inlineStr">
-        <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#2acaf10b23</t>
-        </is>
-      </c>
-      <c r="I230" t="inlineStr">
-        <is>
-          <t>• Jóvenes emprendedores podrán fortalecer sus proyectos de la mano de expertos y líderes empresariales. • La Escuela Distrital de Emprendimiento nace de la alianza del Distrito con la ANDI y la Fundación ANDI.</t>
-        </is>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="inlineStr">
-        <is>
-          <t>2025-09-06</t>
-        </is>
-      </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>El Frailejón abre sus puertas: Usme estrena nueva Casa de la Juventud</t>
-        </is>
-      </c>
-      <c r="C231" t="inlineStr">
-        <is>
-          <t>SDIS - Juventud</t>
-        </is>
-      </c>
-      <c r="D231" t="inlineStr">
-        <is>
-          <t>institucional</t>
-        </is>
-      </c>
-      <c r="E231" t="inlineStr">
-        <is>
-          <t>Otra</t>
-        </is>
-      </c>
-      <c r="F231" t="inlineStr">
-        <is>
-          <t>Bogotá</t>
-        </is>
-      </c>
-      <c r="G231" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="H231" t="inlineStr">
-        <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#c7eca5d4bd</t>
-        </is>
-      </c>
-      <c r="I231" t="inlineStr">
         <is>
           <t>• Aunque ya existía una Casa de la Juventud en Usme, la sede se traslada y reinaugura para ofrecer mejores condiciones, ampliar servicios y fortalecer la atención a los jóvenes. • La reapertura se desarrolló con el acompañamiento de la Plataforma...</t>
         </is>

--- a/data/noticias.xlsx
+++ b/data/noticias.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I229"/>
+  <dimension ref="A1:I232"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,45 +466,49 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Los jovenes en colombia estan leyendo peor: lo que dicen las pruebas pisa 2025 sobre los trabajadores del futuro</t>
+          <t>Prosperidad Social entregará transferencias a beneficiarios afectados por el terremoto sin verificación de condicionalidades y corresponsabilidades</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Portafolio</t>
+          <t>Prosperidad Social</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Política pública</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.portafolio.co/economia/los-jovenes-en-colombia-estan-leyendo-peor-lo-que-dicen-las-pruebas-pisa-2025-sobre-los-trabajadores-del-futuro-503346</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>https://prosperidadsocial.gov.co/Noticias/prosperidad-social-entregara-transferencias-a-beneficiarios-afectados-por-el-terremoto-sin-verificacion-de-condicionalidades-y-corresponsabilidades/</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>El Gobierno nacional autorizó a Prosperidad Social a suspender temporalmente las verificaciones de corresponsabilidades que no puedan realizarse por las afectaciones del terremoto. La medida busca evitar que beneficiarios pierdan o retrasen sus...</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -514,44 +518,40 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Prosperidad Social entregará transferencias a beneficiarios afectados por el terremoto sin verificación de condicionalidades y corresponsabilidades</t>
+          <t>Los jovenes en colombia estan leyendo peor: lo que dicen las pruebas pisa 2025 sobre los trabajadores del futuro</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Prosperidad Social</t>
+          <t>Portafolio</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Política pública</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://prosperidadsocial.gov.co/Noticias/prosperidad-social-entregara-transferencias-a-beneficiarios-afectados-por-el-terremoto-sin-verificacion-de-condicionalidades-y-corresponsabilidades/</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>El Gobierno nacional autorizó a Prosperidad Social a suspender temporalmente las verificaciones de corresponsabilidades que no puedan realizarse por las afectaciones del terremoto. La medida busca evitar que beneficiarios pierdan o retrasen sus...</t>
-        </is>
-      </c>
+          <t>https://www.portafolio.co/economia/los-jovenes-en-colombia-estan-leyendo-peor-lo-que-dicen-las-pruebas-pisa-2025-sobre-los-trabajadores-del-futuro-503346</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3567,27 +3567,27 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Joven de 18 años fue asesinado en Bogotá luego de pelea por una gorra</t>
+          <t>‘Comidas Compartidas’: cuando los alimentos conectan a las personas y derriban prejuicios</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Pulzo</t>
+          <t>SDIS - Juventud</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Cultura y deporte</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3602,10 +3602,14 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://www.pulzo.com/nacion/bogota/joven-18-anos-fue-asesinado-bogota-luego-pelea-por-gorra-PP5253435</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#548ecae5f8</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C, 24 de julio de 2026.Los alimentos, además de ser indispensables para los seres vivos, tienen el poder de conectar a las personas. Así lo demostró una nueva versión de ‘Comidas Compartidas’, una actividad en la que voluntarios de...</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3615,7 +3619,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Dos jóvenes murieron en balacera en Bucaramanga: atentado no iba contra ellos</t>
+          <t>Joven de 18 años fue asesinado en Bogotá luego de pelea por una gorra</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3635,17 +3639,17 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Bucaramanga</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://www.pulzo.com/nacion/dos-jovenes-murieron-balacera-bucaramanga-atentado-no-iba-contra-ellos-PP5252872A</t>
+          <t>https://www.pulzo.com/nacion/bogota/joven-18-anos-fue-asesinado-bogota-luego-pelea-por-gorra-PP5253435</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -3658,12 +3662,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>El cuerpo de María Camila Potosí, la joven embarazada de ocho meses que fue hallada sin vida en Cali, no tenía al bebé, denunció su familia</t>
+          <t>Dos jóvenes murieron en balacera en Bucaramanga: atentado no iba contra ellos</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Pulzo</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3678,7 +3682,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Bucaramanga</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -3688,39 +3692,35 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/07/23/el-cuerpo-de-maria-camila-potosi-la-joven-embarazada-de-ocho-meses-que-fue-hallada-sin-vida-en-cali-no-tenia-al-bebe-denuncio-su-familia/</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>La joven fue vista con vida por última vez cuando subió a una motocicleta junto a otra mujer, que ahora es el principal foco de las investigaciones. El cadáver presentaba signos de tortura y múltiples heridas con arma blanca</t>
-        </is>
-      </c>
+          <t>https://www.pulzo.com/nacion/dos-jovenes-murieron-balacera-bucaramanga-atentado-no-iba-contra-ellos-PP5252872A</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Hallan sin vida a joven embarazada que estaba desaparecida en Cali</t>
+          <t>El cuerpo de María Camila Potosí, la joven embarazada de ocho meses que fue hallada sin vida en Cali, no tenía al bebé, denunció su familia</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Protección</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3735,44 +3735,44 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/cali/hallan-sin-vida-a-joven-embarazada-que-estaba-desaparecida-en-cali-investigan-el-crimen/</t>
+          <t>https://www.infobae.com/colombia/2026/07/23/el-cuerpo-de-maria-camila-potosi-la-joven-embarazada-de-ocho-meses-que-fue-hallada-sin-vida-en-cali-no-tenia-al-bebe-denuncio-su-familia/</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>La joven de 21 años y con ocho meses de embarazo, fue encontrada en una zona rural de Cali. La Fiscalía asumió la investigación.</t>
+          <t>La joven fue vista con vida por última vez cuando subió a una motocicleta junto a otra mujer, que ahora es el principal foco de las investigaciones. El cadáver presentaba signos de tortura y múltiples heridas con arma blanca</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Los jugadores que más aumentaron su valor tras el gran torneo de selecciones, un colombiano dio el golpe</t>
+          <t>Hallan sin vida a joven embarazada que estaba desaparecida en Cali</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Las2orillas</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Cultura y deporte</t>
+          <t>Protección</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -3782,44 +3782,44 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://www.las2orillas.co/los-jugadores-que-mas-aumentaron-su-valor-tras-el-gran-torneo-de-selecciones-un-colombiano-dio-el-golpe/</t>
+          <t>https://www.elespectador.com/colombia/cali/hallan-sin-vida-a-joven-embarazada-que-estaba-desaparecida-en-cali-investigan-el-crimen/</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Cada partido cambia el mercado de fichajes. Jóvenes figuras dispararon su cotización y un colombiano terminó entre las grandes revelaciones del certamen.El artículoLos jugadores que más aumentaron su valor tras el gran torneo de selecciones, un...</t>
+          <t>La joven de 21 años y con ocho meses de embarazo, fue encontrada en una zona rural de Cali. La Fiscalía asumió la investigación.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Dos adolescentes murieron electrocutadas tras vendaval en Montería</t>
+          <t>Los jugadores que más aumentaron su valor tras el gran torneo de selecciones, un colombiano dio el golpe</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Las2orillas</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Cultura y deporte</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Montería</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -3829,24 +3829,24 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/mas-regiones/dos-adolescentes-murieron-electrocutadas-tras-vendaval-en-monteria/</t>
+          <t>https://www.las2orillas.co/los-jugadores-que-mas-aumentaron-su-valor-tras-el-gran-torneo-de-selecciones-un-colombiano-dio-el-golpe/</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Vendaval en Montería deja como saldo la muerte de dos adolescentes que fueron alcanzadas por un cable de alta tensión.</t>
+          <t>Cada partido cambia el mercado de fichajes. Jóvenes figuras dispararon su cotización y un colombiano terminó entre las grandes revelaciones del certamen.El artículoLos jugadores que más aumentaron su valor tras el gran torneo de selecciones, un...</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Turista bogotano y dos jóvenes murieron ahogados en playas del Parque Tayrona</t>
+          <t>Dos adolescentes murieron electrocutadas tras vendaval en Montería</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3861,54 +3861,54 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Montería</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/mas-regiones/turista-bogotano-y-dos-jovenes-murieron-ahogados-en-playas-del-parque-tayrona/</t>
+          <t>https://www.elespectador.com/colombia/mas-regiones/dos-adolescentes-murieron-electrocutadas-tras-vendaval-en-monteria/</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>En menos de 24 horas, las tres víctimas fueron arrastradas por el fuerte oleaje entre Mendihuaca y Los Naranjos, en el parque Tayrona.</t>
+          <t>Vendaval en Montería deja como saldo la muerte de dos adolescentes que fueron alcanzadas por un cable de alta tensión.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Apareció muerto joven que estaba desaparecido en Bogotá: lo hallaron en un caño</t>
+          <t>Turista bogotano y dos jóvenes murieron ahogados en playas del Parque Tayrona</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Pulzo</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3923,20 +3923,24 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://www.pulzo.com/nacion/aparecio-muerto-joven-que-estaba-desaparecido-bogota-que-paso-PP5247140</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>https://www.elespectador.com/colombia/mas-regiones/turista-bogotano-y-dos-jovenes-murieron-ahogados-en-playas-del-parque-tayrona/</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>En menos de 24 horas, las tres víctimas fueron arrastradas por el fuerte oleaje entre Mendihuaca y Los Naranjos, en el parque Tayrona.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Joven contó cómo la robaron con '"violencia psicológica" en Bogotá: vivió gran susto</t>
+          <t>Apareció muerto joven que estaba desaparecido en Bogotá: lo hallaron en un caño</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3966,7 +3970,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>https://www.pulzo.com/nacion/bogota/joven-conto-como-robaron-con-violencia-psicologica-bogota-PP5246025</t>
+          <t>https://www.pulzo.com/nacion/aparecio-muerto-joven-que-estaba-desaparecido-bogota-que-paso-PP5247140</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -3979,12 +3983,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Una joven presentadora de televisión y un viejo amigo del Tigre cercano a Uribe serán los voceros oficiales</t>
+          <t>Joven contó cómo la robaron con '"violencia psicológica" en Bogotá: vivió gran susto</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Las2orillas</t>
+          <t>Pulzo</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -3994,7 +3998,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -4009,29 +4013,25 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>https://www.las2orillas.co/una-joven-presentadora-de-television-y-un-viejo-amigo-del-tigre-cercano-a-uribe-seran-los-voceros-oficiales/</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>Carolina Gómez, con lazos con el movimiento cristiano que pesó en la elección y quien trabajaba en Red+ estará en Bogotá y Miller Soto actuará desde BarranquillaEl artículoUna joven presentadora de televisión y un viejo amigo del Tigre cercano a...</t>
-        </is>
-      </c>
+          <t>https://www.pulzo.com/nacion/bogota/joven-conto-como-robaron-con-violencia-psicologica-bogota-PP5246025</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Joven de Cartagena se hizo viral por pintar a la selección Colombia con sus pies: hizo los doce retratos en simultáneo</t>
+          <t>Una joven presentadora de televisión y un viejo amigo del Tigre cercano a Uribe serán los voceros oficiales</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Las2orillas</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -4046,34 +4046,34 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Cartagena</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/07/12/joven-de-cartagena-se-hizo-viral-por-pintar-a-la-seleccion-colombia-con-sus-pies-hizo-los-doce-retratos-en-simultaneo/</t>
+          <t>https://www.las2orillas.co/una-joven-presentadora-de-television-y-un-viejo-amigo-del-tigre-cercano-a-uribe-seran-los-voceros-oficiales/</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>En un video de 38 segundos mostró el proceso que le tomó más de 10 horas en terminar</t>
+          <t>Carolina Gómez, con lazos con el movimiento cristiano que pesó en la elección y quien trabajaba en Red+ estará en Bogotá y Miller Soto actuará desde BarranquillaEl artículoUna joven presentadora de televisión y un viejo amigo del Tigre cercano a...</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Gustavo Petro tendrá que detener bombardeos contra grupos ilegales en Arauca: juzgado ordenó revisar los protocolos para proteger a menores de edad</t>
+          <t>Joven de Cartagena se hizo viral por pintar a la selección Colombia con sus pies: hizo los doce retratos en simultáneo</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -4093,7 +4093,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Arauca</t>
+          <t>Cartagena</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -4103,12 +4103,12 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/07/06/gustavo-petro-tendra-que-detener-bombardeos-contra-grupos-ilegales-en-arauca-juzgado-ordeno-revisar-los-protocolos-para-proteger-a-menores-de-edad/</t>
+          <t>https://www.infobae.com/colombia/2026/07/12/joven-de-cartagena-se-hizo-viral-por-pintar-a-la-seleccion-colombia-con-sus-pies-hizo-los-doce-retratos-en-simultaneo/</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>La decisión judicial ordena suspender provisionalmente este tipo de operaciones mientras el Gobierno ajusta los protocolos de inteligencia y actuación para garantizar la protección de niños, niñas y adolescentes que puedan estar en zonas de combate</t>
+          <t>En un video de 38 segundos mostró el proceso que le tomó más de 10 horas en terminar</t>
         </is>
       </c>
     </row>
@@ -4120,17 +4120,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Jóvenes en Paz: Prosperidad Social inicia la entrega de la sexta transferencia monetaria de 2026</t>
+          <t>Gustavo Petro tendrá que detener bombardeos contra grupos ilegales en Arauca: juzgado ordenó revisar los protocolos para proteger a menores de edad</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Prosperidad Social</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -4140,22 +4140,22 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Arauca</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>https://prosperidadsocial.gov.co/Noticias/jovenes-en-paz-prosperidad-social-inicia-la-entrega-de-la-sexta-transferencia-monetaria-de-2026/</t>
+          <t>https://www.infobae.com/colombia/2026/07/06/gustavo-petro-tendra-que-detener-bombardeos-contra-grupos-ilegales-en-arauca-juzgado-ordeno-revisar-los-protocolos-para-proteger-a-menores-de-edad/</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>La transferencia será abonada desde el 3 de junio a 5.704 beneficiarios del programa.</t>
+          <t>La decisión judicial ordena suspender provisionalmente este tipo de operaciones mientras el Gobierno ajusta los protocolos de inteligencia y actuación para garantizar la protección de niños, niñas y adolescentes que puedan estar en zonas de combate</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Bogotá se suma al Fondo Internacional de Juventud y Acción Climática para impulsar el liderazgo juvenil frente al cambio climático</t>
+          <t>Jóvenes en Paz: Prosperidad Social inicia la entrega de la sexta transferencia monetaria de 2026</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>SDIS - Juventud</t>
+          <t>Prosperidad Social</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Cultura y deporte</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -4197,71 +4197,71 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#c5b69a2ace</t>
+          <t>https://prosperidadsocial.gov.co/Noticias/jovenes-en-paz-prosperidad-social-inicia-la-entrega-de-la-sexta-transferencia-monetaria-de-2026/</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>•La ciudad se convierte en parte de una red internacional de 300 ciudades que impulsan soluciones climáticas lideradas por jóvenes.A partir del 15 de agosto, Bogotá presentará la convocatoria para que organizaciones e iniciativas lideradas por...</t>
+          <t>La transferencia será abonada desde el 3 de junio a 5.704 beneficiarios del programa.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Abren postulaciones para el Premio Jorge Isaacs de escritores en el Valle del Cauca</t>
+          <t>Bogotá se suma al Fondo Internacional de Juventud y Acción Climática para impulsar el liderazgo juvenil frente al cambio climático</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>SDIS - Juventud</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Cultura y deporte</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Popayán</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/cali/abren-postulaciones-para-el-premio-jorge-isaacs-de-escritores-en-el-valle-del-cauca/</t>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#c5b69a2ace</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>La convocatoria estará abierta hasta el 18 de septiembre e incluye por primera vez una categoría para Jóvenes Creadores.</t>
+          <t>•La ciudad se convierte en parte de una red internacional de 300 ciudades que impulsan soluciones climáticas lideradas por jóvenes.A partir del 15 de agosto, Bogotá presentará la convocatoria para que organizaciones e iniciativas lideradas por...</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Hallaron a tres adolescentes consumiendo drogas en un hotel de Medellín</t>
+          <t>Abren postulaciones para el Premio Jorge Isaacs de escritores en el Valle del Cauca</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -4276,12 +4276,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Seguridad</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Popayán</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -4291,12 +4291,12 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/medellin/hallaron-a-tres-adolescentes-consumiendo-drogas-en-un-hotel-de-medellin/</t>
+          <t>https://www.elespectador.com/colombia/cali/abren-postulaciones-para-el-premio-jorge-isaacs-de-escritores-en-el-valle-del-cauca/</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>La Policía encontró a tres adolescentes, junto con tres adultos, consumiendo droga en la habitación de un hotel de Medellín, ¿qué se sabe?</t>
+          <t>La convocatoria estará abierta hasta el 18 de septiembre e incluye por primera vez una categoría para Jóvenes Creadores.</t>
         </is>
       </c>
     </row>
@@ -4308,27 +4308,27 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Bolsa de valores de colombia, una joven de 25 anos, con la experiencia de casi un siglo en el mercado</t>
+          <t>Hallaron a tres adolescentes consumiendo drogas en un hotel de Medellín</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Portafolio</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Seguridad</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Medellín</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -4338,25 +4338,29 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>https://www.portafolio.co/economia/finanzas/bolsa-de-valores-de-colombia-una-joven-de-25-anos-con-la-experiencia-de-casi-un-siglo-en-el-mercado-497411</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+          <t>https://www.elespectador.com/colombia/medellin/hallaron-a-tres-adolescentes-consumiendo-drogas-en-un-hotel-de-medellin/</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>La Policía encontró a tres adolescentes, junto con tres adultos, consumiendo droga en la habitación de un hotel de Medellín, ¿qué se sabe?</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Tres menores quedaron bajo custodia tras ser hallados en un apartamento de Medellín mientras consumían sustancias estupefacientes</t>
+          <t>Bolsa de valores de colombia, una joven de 25 anos, con la experiencia de casi un siglo en el mercado</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Portafolio</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4366,12 +4370,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -4381,24 +4385,20 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/07/02/tres-menores-quedaron-bajo-custodia-tras-ser-hallados-en-un-apartamento-de-medellin-mientras-consumian-sustancias-estupefacientes/</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>Las autoridades hallaron a los adolescentes, uno de 14 años y dos de 16, en una habitación del sector de La Candelaria y sin la compañía de padres o representantes legales</t>
-        </is>
-      </c>
+          <t>https://www.portafolio.co/economia/finanzas/bolsa-de-valores-de-colombia-una-joven-de-25-anos-con-la-experiencia-de-casi-un-siglo-en-el-mercado-497411</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Alias Flaco, presunto miembro del frente 33 de las disidencias, fue detenido en operativo que salvó a menor reclutada en Meta</t>
+          <t>Tres menores quedaron bajo custodia tras ser hallados en un apartamento de Medellín mientras consumían sustancias estupefacientes</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Seguridad</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Villavicencio</t>
+          <t>Medellín</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -4428,24 +4428,24 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/07/01/alias-flaco-presunto-miembro-del-frente-33-de-las-disidencias-fue-detenido-en-operativo-que-salvo-a-menor-reclutada-en-meta/</t>
+          <t>https://www.infobae.com/colombia/2026/07/02/tres-menores-quedaron-bajo-custodia-tras-ser-hallados-en-un-apartamento-de-medellin-mientras-consumian-sustancias-estupefacientes/</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>La operación, apoyada por una denuncia a la #Línea147, permitió ubicar y poner bajo resguardo a una menor de edad, mientras el detenido enfrentará cargos por reclutamiento ilícito</t>
+          <t>Las autoridades hallaron a los adolescentes, uno de 14 años y dos de 16, en una habitación del sector de La Candelaria y sin la compañía de padres o representantes legales</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Detuvieron al hijo del presidente de Rosario Central con un revólver</t>
+          <t>Alias Flaco, presunto miembro del frente 33 de las disidencias, fue detenido en operativo que salvó a menor reclutada en Meta</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -4460,12 +4460,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Seguridad</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Villavicencio</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -4475,12 +4475,12 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/sociedad/policiales/2026/06/30/detuvieron-al-hijo-del-presidente-de-rosario-central-con-un-revolver/</t>
+          <t>https://www.infobae.com/colombia/2026/07/01/alias-flaco-presunto-miembro-del-frente-33-de-las-disidencias-fue-detenido-en-operativo-que-salvo-a-menor-reclutada-en-meta/</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Matías Belloso fue aprehendido junto a otros tres jóvenes en un procedimiento que realizó el Comando Radioeléctrico en Granadero Baigorria, ciudad vecina a Rosario. Tenían un calibre 22 largo en el Peugeot 208 en el que se desplazaban</t>
+          <t>La operación, apoyada por una denuncia a la #Línea147, permitió ubicar y poner bajo resguardo a una menor de edad, mientras el detenido enfrentará cargos por reclutamiento ilícito</t>
         </is>
       </c>
     </row>
@@ -4492,27 +4492,27 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Encontraron vivos a los jóvenes Luciana y Jerónimo, quienes habían desaparecido en Barú</t>
+          <t>Detuvieron al hijo del presidente de Rosario Central con un revólver</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Protección</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Sincelejo</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -4522,44 +4522,44 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/cartagena/encontraron-vivos-a-los-jovenes-luciana-dangond-y-jeronimo-ibarra-quienes-habian-desaparecido-en-baru/</t>
+          <t>https://www.infobae.com/sociedad/policiales/2026/06/30/detuvieron-al-hijo-del-presidente-de-rosario-central-con-un-revolver/</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Dangond y Jerónimo Ibarra fueron encontrados con vida en Sucre. Los jóvenes desaparecieron el domingo en una moto acuática.</t>
+          <t>Matías Belloso fue aprehendido junto a otros tres jóvenes en un procedimiento que realizó el Comando Radioeléctrico en Granadero Baigorria, ciudad vecina a Rosario. Tenían un calibre 22 largo en el Peugeot 208 en el que se desplazaban</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Al menos 51 menores de edad han sido reclutados este año por grupos armados en Colombia</t>
+          <t>Encontraron vivos a los jóvenes Luciana y Jerónimo, quienes habían desaparecido en Barú</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Protección</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sincelejo</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -4569,30 +4569,34 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/america/agencias/2026/06/26/al-menos-51-menores-de-edad-han-sido-reclutados-este-ano-por-grupos-armados-en-colombia/</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>https://www.elespectador.com/colombia/cartagena/encontraron-vivos-a-los-jovenes-luciana-dangond-y-jeronimo-ibarra-quienes-habian-desaparecido-en-baru/</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Dangond y Jerónimo Ibarra fueron encontrados con vida en Sucre. Los jóvenes desaparecieron el domingo en una moto acuática.</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Autoridades investigan el asesinato de un joven de 17 años en Barranquilla</t>
+          <t>Al menos 51 menores de edad han sido reclutados este año por grupos armados en Colombia</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -4602,7 +4606,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Barranquilla</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -4612,59 +4616,55 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/barranquilla/joven-de-17-anos-fue-asesinado-en-una-cancha-del-barrio-las-malvinas-barranquilla-autoridades-investigan-presuntos-cobros-extorsivos/</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>Las autoridades investigan si el crimen estaría relacionado con presuntos cobros extorsivos.</t>
-        </is>
-      </c>
+          <t>https://www.infobae.com/america/agencias/2026/06/26/al-menos-51-menores-de-edad-han-sido-reclutados-este-ano-por-grupos-armados-en-colombia/</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Revelan nuevos detalles del caso de la mujer que fue hallada muerta dentro de una maleta en Bogotá</t>
+          <t>Autoridades investigan el asesinato de un joven de 17 años en Barranquilla</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Barranquilla</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/06/23/revelan-nuevos-detalles-del-caso-de-la-mujer-que-fue-hallada-muerta-dentro-de-una-maleta-en-chapinero/</t>
+          <t>https://www.elespectador.com/colombia/barranquilla/joven-de-17-anos-fue-asesinado-en-una-cancha-del-barrio-las-malvinas-barranquilla-autoridades-investigan-presuntos-cobros-extorsivos/</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>El CTI analiza pasaportes, videos y movimientos alrededor del inmueble donde apareció el cuerpo, mientras reconstruye las fechas de hospedaje y el rastro de dos extranjeros que estuvieron con la joven</t>
+          <t>Las autoridades investigan si el crimen estaría relacionado con presuntos cobros extorsivos.</t>
         </is>
       </c>
     </row>
@@ -4676,7 +4676,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Una joven de 16 años fue hallada muerta en un río de Illinois dos días después de haber sido reportada como desaparecida</t>
+          <t>Revelan nuevos detalles del caso de la mujer que fue hallada muerta dentro de una maleta en Bogotá</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -4691,39 +4691,39 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Protección</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/estados-unidos/2026/06/23/una-joven-de-16-anos-fue-hallada-muerta-en-un-rio-de-illinois-dos-dias-despues-de-haber-sido-reportada-como-desaparecida/</t>
+          <t>https://www.infobae.com/colombia/2026/06/23/revelan-nuevos-detalles-del-caso-de-la-mujer-que-fue-hallada-muerta-dentro-de-una-maleta-en-chapinero/</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Destiny Neal era buscada desde la tarde del viernes 19 de junio y fue localizada el domingo 21 a las 15:51 al norte del puente de Kimball</t>
+          <t>El CTI analiza pasaportes, videos y movimientos alrededor del inmueble donde apareció el cuerpo, mientras reconstruye las fechas de hospedaje y el rastro de dos extranjeros que estuvieron con la joven</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Día del Padre: Hombre dona un riñón a su hija y le devuelve la esperanza de seguir viviendo para que cumpla sus metas</t>
+          <t>Una joven de 16 años fue hallada muerta en un río de Illinois dos días después de haber sido reportada como desaparecida</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>Protección</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Villavicencio</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/peru/2026/06/21/dia-del-padre-hombre-dona-un-rinon-a-su-hija-y-le-devuelve-la-esperanza-de-seguir-viviendo-para-que-cumpla-sus-metas/</t>
+          <t>https://www.infobae.com/estados-unidos/2026/06/23/una-joven-de-16-anos-fue-hallada-muerta-en-un-rio-de-illinois-dos-dias-despues-de-haber-sido-reportada-como-desaparecida/</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>El trasplante realizado en el Hospital Almenara marcó un antes y un después para una joven diagnosticada con insuficiencia renal terminal y para su familia</t>
+          <t>Destiny Neal era buscada desde la tarde del viernes 19 de junio y fue localizada el domingo 21 a las 15:51 al norte del puente de Kimball</t>
         </is>
       </c>
     </row>
@@ -4770,27 +4770,27 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Encontraron cuerpo de joven desaparecido en Puerto Colombia, Atlántico</t>
+          <t>Día del Padre: Hombre dona un riñón a su hija y le devuelve la esperanza de seguir viviendo para que cumpla sus metas</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Protección</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Barranquilla</t>
+          <t>Villavicencio</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -4800,12 +4800,12 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/barranquilla/encontraron-cuerpo-de-joven-desaparecido-en-puerto-colombia-atlantico/</t>
+          <t>https://www.infobae.com/peru/2026/06/21/dia-del-padre-hombre-dona-un-rinon-a-su-hija-y-le-devuelve-la-esperanza-de-seguir-viviendo-para-que-cumpla-sus-metas/</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Las autoridades confirmaron el hallazgo del cuerpo de Luis Jaimes Reyes, quien fue arrastrado por una corriente en Puerto Colombia.</t>
+          <t>El trasplante realizado en el Hospital Almenara marcó un antes y un después para una joven diagnosticada con insuficiencia renal terminal y para su familia</t>
         </is>
       </c>
     </row>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Investigan riña que terminó con una menor de edad herida en colegio de la ladera de Cali</t>
+          <t>Encontraron cuerpo de joven desaparecido en Puerto Colombia, Atlántico</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -4832,12 +4832,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Protección</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Barranquilla</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -4847,24 +4847,24 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/cali/investigan-rina-que-termino-con-una-menor-de-edad-herida-en-colegio-de-la-ladera-de-cali/</t>
+          <t>https://www.elespectador.com/colombia/barranquilla/encontraron-cuerpo-de-joven-desaparecido-en-puerto-colombia-atlantico/</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>La riña se registró en medio de un torneo deportivo de la Institución Educativa Juana de Caicedo y Cuero.</t>
+          <t>Las autoridades confirmaron el hallazgo del cuerpo de Luis Jaimes Reyes, quien fue arrastrado por una corriente en Puerto Colombia.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Dos menores de edad murieron ahogados en Santander durante el fin de semana</t>
+          <t>Investigan riña que terminó con una menor de edad herida en colegio de la ladera de Cali</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -4879,12 +4879,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Bucaramanga</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -4894,24 +4894,24 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/mas-regiones/dos-menores-de-edad-murieron-ahogados-en-santander-durante-el-fin-de-semana/</t>
+          <t>https://www.elespectador.com/colombia/cali/investigan-rina-que-termino-con-una-menor-de-edad-herida-en-colegio-de-la-ladera-de-cali/</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Dos menores murieron ahogados en ríos y quebradas de Santander: uno en San Vicente de Chucurí y otro en Coromoro.</t>
+          <t>La riña se registró en medio de un torneo deportivo de la Institución Educativa Juana de Caicedo y Cuero.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Hallan sin vida a joven de Soledad que desapareció en playas de Salgar, Atlántico</t>
+          <t>Dos menores de edad murieron ahogados en Santander durante el fin de semana</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Protección</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Barranquilla</t>
+          <t>Bucaramanga</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -4941,59 +4941,59 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/mas-regiones/hallan-sin-vida-a-joven-de-soledad-que-desaparecio-en-playas-de-salgar-atlantico/</t>
+          <t>https://www.elespectador.com/colombia/mas-regiones/dos-menores-de-edad-murieron-ahogados-en-santander-durante-el-fin-de-semana/</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>El joven de 19 años había desaparecido el lunes festivo mientras se bañaba en una playa del corregimiento de Salgar.</t>
+          <t>Dos menores murieron ahogados en ríos y quebradas de Santander: uno en San Vicente de Chucurí y otro en Coromoro.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Familia de joven de 18 años denuncia hurto y presunto abuso sexual cerca de una estación de TransMilenio en el centro de Bogotá</t>
+          <t>Hallan sin vida a joven de Soledad que desapareció en playas de Salgar, Atlántico</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Protección</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Barranquilla</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/06/10/familia-de-joven-de-18-anos-denuncia-hurto-y-presunto-abuso-sexual-cerca-de-una-estacion-de-transmilenio-en-el-centro-de-bogota/</t>
+          <t>https://www.elespectador.com/colombia/mas-regiones/hallan-sin-vida-a-joven-de-soledad-que-desaparecio-en-playas-de-salgar-atlantico/</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Una mujer permanece bajo observación médica luego de reportar que dos hombres armados la interceptaron cuando salía de trabajar en inmediaciones de la estación Concejo de Bogotá</t>
+          <t>El joven de 19 años había desaparecido el lunes festivo mientras se bañaba en una playa del corregimiento de Salgar.</t>
         </is>
       </c>
     </row>
@@ -5005,54 +5005,54 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Tractocamión arrolló a mujer y menor de edad que iban en bicicleta eléctrica en Ibagué</t>
+          <t>Familia de joven de 18 años denuncia hurto y presunto abuso sexual cerca de una estación de TransMilenio en el centro de Bogotá</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ibagué</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/mas-regiones/tractocamion-arrollo-bicicleta-electrica-en-ibague-dejo-dos-lesionados/</t>
+          <t>https://www.infobae.com/colombia/2026/06/10/familia-de-joven-de-18-anos-denuncia-hurto-y-presunto-abuso-sexual-cerca-de-una-estacion-de-transmilenio-en-el-centro-de-bogota/</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>El siniestro ocurrió en la avenida Mirolindo, a la altura de Picaleña. Las víctimas fueron trasladadas a un centro asistencial.</t>
+          <t>Una mujer permanece bajo observación médica luego de reportar que dos hombres armados la interceptaron cuando salía de trabajar en inmediaciones de la estación Concejo de Bogotá</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Asesinan a joven de 17 años en Santander; una mujer resultó herida por bala perdida</t>
+          <t>Tractocamión arrolló a mujer y menor de edad que iban en bicicleta eléctrica en Ibagué</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -5067,12 +5067,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Bucaramanga</t>
+          <t>Ibagué</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -5082,12 +5082,12 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/mas-regiones/asesinan-a-joven-de-17-anos-en-santander-una-mujer-resulto-herida-por-bala-perdida/</t>
+          <t>https://www.elespectador.com/colombia/mas-regiones/tractocamion-arrollo-bicicleta-electrica-en-ibague-dejo-dos-lesionados/</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>El adolescente fue atacado por hombres en motocicleta en Piedecuesta. Durante la balacera, una mujer resultó lesionada por un proyectil.</t>
+          <t>El siniestro ocurrió en la avenida Mirolindo, a la altura de Picaleña. Las víctimas fueron trasladadas a un centro asistencial.</t>
         </is>
       </c>
     </row>
@@ -5099,7 +5099,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Condenan a hombre que intentó matar a un adolescente con gaseosa envenenada en Santander</t>
+          <t>Asesinan a joven de 17 años en Santander; una mujer resultó herida por bala perdida</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -5129,24 +5129,24 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/mas-regiones/condenan-a-hombre-que-intento-matar-a-un-nino-con-gaseosa-envenenada-en-santander/</t>
+          <t>https://www.elespectador.com/colombia/mas-regiones/asesinan-a-joven-de-17-anos-en-santander-una-mujer-resulto-herida-por-bala-perdida/</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Luis Arturo Prieto fue condenado a 11 años y seis meses de prisión por intentar asesinar a un menor de edad. El caso ocurrió en 2012.</t>
+          <t>El adolescente fue atacado por hombres en motocicleta en Piedecuesta. Durante la balacera, una mujer resultó lesionada por un proyectil.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Murió Wendy Yohana Sepúlveda, la mujer que fue quemada con gasolina por su expareja en Neiva</t>
+          <t>Condenan a hombre que intentó matar a un adolescente con gaseosa envenenada en Santander</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -5161,12 +5161,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Neiva</t>
+          <t>Bucaramanga</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -5176,24 +5176,24 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/mas-regiones/murio-wendy-yohana-la-joven-madre-que-fue-quemada-con-gasolina-por-su-expareja-en-neiva/</t>
+          <t>https://www.elespectador.com/colombia/mas-regiones/condenan-a-hombre-que-intento-matar-a-un-nino-con-gaseosa-envenenada-en-santander/</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>La joven había sido rociada con gasolina por su expareja y falleció este 1 de junio.</t>
+          <t>Luis Arturo Prieto fue condenado a 11 años y seis meses de prisión por intentar asesinar a un menor de edad. El caso ocurrió en 2012.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Tarjeta de identidad en Colombia: para qué sirve y cómo tramitarla</t>
+          <t>Murió Wendy Yohana Sepúlveda, la mujer que fue quemada con gasolina por su expareja en Neiva</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Neiva</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -5223,12 +5223,12 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/tarjeta-de-identidad-en-colombia-como-sacarla-requisitos-costos-y-para-que-sirve/</t>
+          <t>https://www.elespectador.com/colombia/mas-regiones/murio-wendy-yohana-la-joven-madre-que-fue-quemada-con-gasolina-por-su-expareja-en-neiva/</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Este documento es obligatorio para menores de edad. Así puede solicitarlo.</t>
+          <t>La joven había sido rociada con gasolina por su expareja y falleció este 1 de junio.</t>
         </is>
       </c>
     </row>
@@ -5240,17 +5240,17 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Prosperidad Social inicia la entrega del ciclo 5 de Jóvenes en Paz</t>
+          <t>Tarjeta de identidad en Colombia: para qué sirve y cómo tramitarla</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Prosperidad Social</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -5260,82 +5260,86 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>https://prosperidadsocial.gov.co/Noticias/prosperidad-social-inicia-la-entrega-del-ciclo-5-de-jovenes-en-paz/</t>
+          <t>https://www.elespectador.com/colombia/tarjeta-de-identidad-en-colombia-como-sacarla-requisitos-costos-y-para-que-sirve/</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>La transferencia será abonada desde el 3 de junio a 5.704 beneficiarios del programa.</t>
+          <t>Este documento es obligatorio para menores de edad. Así puede solicitarlo.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Mujer perdió el control de su camioneta y chocó contra una tienda: hay un joven muerto</t>
+          <t>Prosperidad Social inicia la entrega del ciclo 5 de Jóvenes en Paz</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Pulzo</t>
+          <t>Prosperidad Social</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Quibdó</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>https://www.pulzo.com/nacion/quindio-mujer-perdio-control-su-camioneta-choco-contra-tienda-PP5201135A</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr"/>
+          <t>https://prosperidadsocial.gov.co/Noticias/prosperidad-social-inicia-la-entrega-del-ciclo-5-de-jovenes-en-paz/</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>La transferencia será abonada desde el 3 de junio a 5.704 beneficiarios del programa.</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Quién es quién en el caso Agostina Vega: la madre, el fiscal, la amante y el principal sospechoso</t>
+          <t>Mujer perdió el control de su camioneta y chocó contra una tienda: hay un joven muerto</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Pulzo</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -5345,12 +5349,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Seguridad</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Montería</t>
+          <t>Quibdó</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -5360,14 +5364,10 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/sociedad/policiales/2026/05/31/quien-es-quien-en-el-caso-agostina-vega-la-madre-el-fiscal-la-amante-y-el-principal-sospechoso/</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>El cuerpo de la adolescente de 14 años fue hallado en un descampado del barrio Ampliación Ferreyra de la ciudad de Córdoba. El único detenido es Claudio Barrelier, amigo de la madre de la víctima</t>
-        </is>
-      </c>
+          <t>https://www.pulzo.com/nacion/quindio-mujer-perdio-control-su-camioneta-choco-contra-tienda-PP5201135A</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -5377,7 +5377,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Crimen de Agostina Vega en Córdoba: las tres preguntas clave que la investigación todavía no pudo responder</t>
+          <t>Quién es quién en el caso Agostina Vega: la madre, el fiscal, la amante y el principal sospechoso</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -5392,7 +5392,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Seguridad</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -5407,12 +5407,12 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/sociedad/policiales/2026/05/31/crimen-de-agostina-vega-en-cordoba-las-tres-preguntas-clave-que-la-investigacion-todavia-no-pudo-responder/</t>
+          <t>https://www.infobae.com/sociedad/policiales/2026/05/31/quien-es-quien-en-el-caso-agostina-vega-la-madre-el-fiscal-la-amante-y-el-principal-sospechoso/</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>La fiscalía ya tiene un detenido y reconstruyó parte de los movimientos de la adolescente antes de su muerte. Sin embargo, todavía quedan incógnitas centrales por resolver</t>
+          <t>El cuerpo de la adolescente de 14 años fue hallado en un descampado del barrio Ampliación Ferreyra de la ciudad de Córdoba. El único detenido es Claudio Barrelier, amigo de la madre de la víctima</t>
         </is>
       </c>
     </row>
@@ -5424,27 +5424,27 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>⁠Familia de Yenny Nohava, joven asesinada en Quindío, denunció amenazas a testigos</t>
+          <t>Crimen de Agostina Vega en Córdoba: las tres preguntas clave que la investigación todavía no pudo responder</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Armenia</t>
+          <t>Montería</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -5454,44 +5454,44 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/mas-regiones/familia-de-yenny-nohava-joven-asesinada-en-quindio-denuncio-amenazas-y-exposicion-de-testigos-condenado-sigue-libre/</t>
+          <t>https://www.infobae.com/sociedad/policiales/2026/05/31/crimen-de-agostina-vega-en-cordoba-las-tres-preguntas-clave-que-la-investigacion-todavia-no-pudo-responder/</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>El caso ocurrió en marzo de 2022. El condenado es el exnovio de la víctima, que sigue en libertad.</t>
+          <t>La fiscalía ya tiene un detenido y reconstruyó parte de los movimientos de la adolescente antes de su muerte. Sin embargo, todavía quedan incógnitas centrales por resolver</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Caso Agostina Vega, en vivo: retomaron los rastrillajes en el barrio donde la adolescente habría estado por última vez</t>
+          <t>⁠Familia de Yenny Nohava, joven asesinada en Quindío, denunció amenazas a testigos</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Seguridad</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Montería</t>
+          <t>Armenia</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -5501,24 +5501,24 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/sociedad/policiales/2026/05/30/caso-agostina-vega-volvieron-a-allanar-la-casa-del-unico-detenido-luego-de-que-cambiara-su-version-de-los-hechos/</t>
+          <t>https://www.elespectador.com/colombia/mas-regiones/familia-de-yenny-nohava-joven-asesinada-en-quindio-denuncio-amenazas-y-exposicion-de-testigos-condenado-sigue-libre/</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>La búsqueda de la menor de 14 años desaparecida en Córdoba cumplirá siete días y tiene en el blanco de las sospechas a Claudio Barrelier. Durante su segunda indagatoria, el detenido afirmó que la adolescente había ingresado a su casa y que había...</t>
+          <t>El caso ocurrió en marzo de 2022. El condenado es el exnovio de la víctima, que sigue en libertad.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Caso Agostina Vega, en vivo: trasladan a tres mujeres que estaban en la casa del detenido por la desaparición de la adolescente en Córdoba</t>
+          <t>Caso Agostina Vega, en vivo: retomaron los rastrillajes en el barrio donde la adolescente habría estado por última vez</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -5548,29 +5548,29 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/sociedad/policiales/2026/05/29/caso-agostina-vega-en-vivo-la-policia-allana-la-casa-del-unico-detenido-por-la-desaparicion-de-la-adolescente-en-cordoba/</t>
+          <t>https://www.infobae.com/sociedad/policiales/2026/05/30/caso-agostina-vega-volvieron-a-allanar-la-casa-del-unico-detenido-luego-de-que-cambiara-su-version-de-los-hechos/</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>La fiscalía ordenó un nuevo operativo en la vivienda de Claudio Gabriel Barrelier tras detectar movimientos sospechosos durante la madrugada. Peritos trabajan en el lugar en busca de huellas y otras pruebas, mientras la investigación suma nuevas...</t>
+          <t>La búsqueda de la menor de 14 años desaparecida en Córdoba cumplirá siete días y tiene en el blanco de las sospechas a Claudio Barrelier. Durante su segunda indagatoria, el detenido afirmó que la adolescente había ingresado a su casa y que había...</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Identifican a joven que murió en colegio de Bogotá cuando practicaba boxeo con un compañero</t>
+          <t>Caso Agostina Vega, en vivo: trasladan a tres mujeres que estaban en la casa del detenido por la desaparición de la adolescente en Córdoba</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Pulzo</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -5580,25 +5580,29 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Seguridad</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Montería</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>https://www.pulzo.com/nacion/bogota/muerte-estudiante-colegio-prado-veraniego-suba-bogota-PP5196509</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr"/>
+          <t>https://www.infobae.com/sociedad/policiales/2026/05/29/caso-agostina-vega-en-vivo-la-policia-allana-la-casa-del-unico-detenido-por-la-desaparicion-de-la-adolescente-en-cordoba/</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>La fiscalía ordenó un nuevo operativo en la vivienda de Claudio Gabriel Barrelier tras detectar movimientos sospechosos durante la madrugada. Peritos trabajan en el lugar en busca de huellas y otras pruebas, mientras la investigación suma nuevas...</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -5608,12 +5612,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Búsqueda de Agostina Vega, en vivo: el abogado de la madre dijo que la adolescente “estaría con vida y en Córdoba”</t>
+          <t>Identifican a joven que murió en colegio de Bogotá cuando practicaba boxeo con un compañero</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Pulzo</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -5623,29 +5627,25 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Montería</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/sociedad/policiales/2026/05/28/busqueda-de-agostina-vega-en-vivo-las-ultimas-noticias-de-la-desaparicion-de-la-joven-de-14-anos-en-cordoba/</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>La adolescente salió de su casa el sábado por la noche y fue vista por última vez junto a un hombre que hoy está bajo arresto</t>
-        </is>
-      </c>
+          <t>https://www.pulzo.com/nacion/bogota/muerte-estudiante-colegio-prado-veraniego-suba-bogota-PP5196509</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -5655,27 +5655,27 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Ataque sicarial en una cancha de Soledad dejó dos muertos, entre ellos un menor de edad</t>
+          <t>Búsqueda de Agostina Vega, en vivo: el abogado de la madre dijo que la adolescente “estaría con vida y en Córdoba”</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Barranquilla</t>
+          <t>Montería</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -5685,12 +5685,12 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/barranquilla/ataque-sicarial-en-una-cancha-de-soledad-deja-dos-muertos-entre-ellos-un-menor-de-edad/</t>
+          <t>https://www.infobae.com/sociedad/policiales/2026/05/28/busqueda-de-agostina-vega-en-vivo-las-ultimas-noticias-de-la-desaparicion-de-la-joven-de-14-anos-en-cordoba/</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Sicarios atacaron una cancha de fútbol en Soledad, Atlántico, dejando dos muertos y dos menores de edad heridos.</t>
+          <t>La adolescente salió de su casa el sábado por la noche y fue vista por última vez junto a un hombre que hoy está bajo arresto</t>
         </is>
       </c>
     </row>
@@ -5702,89 +5702,89 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>El programa Jóvenes con Oportunidades avanza con más de 5.800 vinculados en 2026 y encuentros territoriales de bienvenida</t>
+          <t>Ataque sicarial en una cancha de Soledad dejó dos muertos, entre ellos un menor de edad</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>SDIS - Juventud</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Cultura y deporte</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Barranquilla</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#ad74570fbf</t>
+          <t>https://www.elespectador.com/colombia/barranquilla/ataque-sicarial-en-una-cancha-de-soledad-deja-dos-muertos-entre-ellos-un-menor-de-edad/</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Bogotá D.C., mayo 28 de 2026.Jóvenes con Oportunidades continúa avanzando en Bogotá con la formalización y vinculación de jóvenes que hicieron parte de la convocatoria 2026 a sus diferentes rutas de formación, consolidando una apuesta distrital que...</t>
+          <t>Sicarios atacaron una cancha de fútbol en Soledad, Atlántico, dejando dos muertos y dos menores de edad heridos.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>La valorización y el prestigio de la salud mental dentro del gremio médico colombiano</t>
+          <t>El programa Jóvenes con Oportunidades avanza con más de 5.800 vinculados en 2026 y encuentros territoriales de bienvenida</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Las2orillas</t>
+          <t>SDIS - Juventud</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>Cultura y deporte</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>https://www.las2orillas.co/la-valorizacion-y-el-prestigio-de-la-salud-mental-dentro-del-gremio-medico-colombiano/</t>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#ad74570fbf</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Tras la pandemia, la salud mental revolucionó las facultades de medicina en el país: hoy los jóvenes eligen la psiquiatría por auténtica vocaciónEl artículoLa valorización y el prestigio de la salud mental dentro del gremio médico colombianofue...</t>
+          <t>Bogotá D.C., mayo 28 de 2026.Jóvenes con Oportunidades continúa avanzando en Bogotá con la formalización y vinculación de jóvenes que hicieron parte de la convocatoria 2026 a sus diferentes rutas de formación, consolidando una apuesta distrital que...</t>
         </is>
       </c>
     </row>
@@ -5796,7 +5796,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>El día que un par de adolescentes convencieron a Diomedes Díaz para que cantara en un pueblo minero</t>
+          <t>La valorización y el prestigio de la salud mental dentro del gremio médico colombiano</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -5811,12 +5811,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Popayán</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -5826,44 +5826,44 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>https://www.las2orillas.co/el-dia-que-un-par-de-adolescentes-convencieron-a-diomedes-diaz-para-que-cantara-en-un-pueblo-minero/</t>
+          <t>https://www.las2orillas.co/la-valorizacion-y-el-prestigio-de-la-salud-mental-dentro-del-gremio-medico-colombiano/</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>La histórica noche en que Diomedes Díaz y el Cocha Molina paralizaron al pueblo minero de El Bagre, Bajo Cauca, con un concierto que quedó en la memoriaEl artículoEl día que un par de adolescentes convencieron a Diomedes Díaz para que cantara en un...</t>
+          <t>Tras la pandemia, la salud mental revolucionó las facultades de medicina en el país: hoy los jóvenes eligen la psiquiatría por auténtica vocaciónEl artículoLa valorización y el prestigio de la salud mental dentro del gremio médico colombianofue...</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Fiesta clandestina en Circasia, Quindío, deja un muerto y dos jóvenes heridos</t>
+          <t>El día que un par de adolescentes convencieron a Diomedes Díaz para que cantara en un pueblo minero</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Las2orillas</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Armenia</t>
+          <t>Popayán</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -5873,24 +5873,24 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/mas-regiones/fiesta-clandestina-en-circasia-quindio-deja-un-muerto-y-dos-jovenes-heridos/</t>
+          <t>https://www.las2orillas.co/el-dia-que-un-par-de-adolescentes-convencieron-a-diomedes-diaz-para-que-cantara-en-un-pueblo-minero/</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>¿Qué se sabe del ataque en una fiesta clandestina en Circasia que dejó un muerto y dos heridos?</t>
+          <t>La histórica noche en que Diomedes Díaz y el Cocha Molina paralizaron al pueblo minero de El Bagre, Bajo Cauca, con un concierto que quedó en la memoriaEl artículoEl día que un par de adolescentes convencieron a Diomedes Díaz para que cantara en un...</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Lo que se sabe del asesinato de dos jóvenes en Girón, Santander; investigan retaliación</t>
+          <t>Fiesta clandestina en Circasia, Quindío, deja un muerto y dos jóvenes heridos</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -5910,7 +5910,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Bucaramanga</t>
+          <t>Armenia</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/mas-regiones/lo-que-se-sabe-del-asesinato-de-dos-jovenes-en-giron-santander-policia-investigan-retaliacion/</t>
+          <t>https://www.elespectador.com/colombia/mas-regiones/fiesta-clandestina-en-circasia-quindio-deja-un-muerto-y-dos-jovenes-heridos/</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Se conocen nuevos detalles del asesinato de Karen Valentina Vega y Nicol Cristiana Amaya, en Girón, Santander.</t>
+          <t>¿Qué se sabe del ataque en una fiesta clandestina en Circasia que dejó un muerto y dos heridos?</t>
         </is>
       </c>
     </row>
@@ -5937,27 +5937,27 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Aprenda cómo funciona la democracia en Colombia</t>
+          <t>Lo que se sabe del asesinato de dos jóvenes en Girón, Santander; investigan retaliación</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>La Silla Vacía</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bucaramanga</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -5967,29 +5967,29 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>https://www.lasillavacia.com/en-vivo/aprenda-como-funciona-la-democracia-en-colombia/</t>
+          <t>https://www.elespectador.com/colombia/mas-regiones/lo-que-se-sabe-del-asesinato-de-dos-jovenes-en-giron-santander-policia-investigan-retaliacion/</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Más de mil jóvenes ya aprendieron a entender las elecciones y frenar la desinformación con ABC de la Democracia.The postAprenda cómo funciona la democracia en Colombiaappeared first onLa Silla Vacía.</t>
+          <t>Se conocen nuevos detalles del asesinato de Karen Valentina Vega y Nicol Cristiana Amaya, en Girón, Santander.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Lejos de la política la hija de Germán Vargas Lleras vive el duelo a su manera</t>
+          <t>Aprenda cómo funciona la democracia en Colombia</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Las2orillas</t>
+          <t>La Silla Vacía</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -5999,7 +5999,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -6014,34 +6014,34 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>https://www.las2orillas.co/lejos-de-la-politica-la-hija-de-german-vargas-lleras-vive-el-duelo-a-su-manera/</t>
+          <t>https://www.lasillavacia.com/en-vivo/aprenda-como-funciona-la-democracia-en-colombia/</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Clemencia Vargas encontró en la danza un sentido de vida y en Colombia creó la Fundación Vive Bailando para jóvenes víctimas de la violenciaEl artículoLejos de la política la hija de Germán Vargas Lleras vive el duelo a su manerafue publicado...</t>
+          <t>Más de mil jóvenes ya aprendieron a entender las elecciones y frenar la desinformación con ABC de la Democracia.The postAprenda cómo funciona la democracia en Colombiaappeared first onLa Silla Vacía.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Campero escolar cayó a un río en Villacarmelo, Cali; murió el conductor y hay niños heridos</t>
+          <t>Lejos de la política la hija de Germán Vargas Lleras vive el duelo a su manera</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Las2orillas</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -6061,44 +6061,44 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/cali/accidente-rio-en-villacarmelo-cali-vehiculo-escolar-se-volco-murio-el-conductor-y-hay-ninos-heridos/</t>
+          <t>https://www.las2orillas.co/lejos-de-la-politica-la-hija-de-german-vargas-lleras-vive-el-duelo-a-su-manera/</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Tres menores de edad y una auxiliar resultaron lesionados tras la caída.</t>
+          <t>Clemencia Vargas encontró en la danza un sentido de vida y en Colombia creó la Fundación Vive Bailando para jóvenes víctimas de la violenciaEl artículoLejos de la política la hija de Germán Vargas Lleras vive el duelo a su manerafue publicado...</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Mientras el mundo celebra el Día Internacional de las Familias, en Colombia más de 26.000 niños crecen lejos de una</t>
+          <t>Campero escolar cayó a un río en Villacarmelo, Cali; murió el conductor y hay niños heridos</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Las2orillas</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -6108,24 +6108,24 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>https://www.las2orillas.co/mientras-el-mundo-celebra-el-dia-internacional-de-las-familias-en-colombia-mas-de-26-000-ninos-crecen-lejos-de-una/</t>
+          <t>https://www.elespectador.com/colombia/cali/accidente-rio-en-villacarmelo-cali-vehiculo-escolar-se-volco-murio-el-conductor-y-hay-ninos-heridos/</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Casi el 50 % de los niños, niñas y adolescentes separados de sus familias terminan creciendo en instituciones de cuidado y no en entornos familiaresEl artículoMientras el mundo celebra el Día Internacional de las Familias, en Colombia más de 26.000...</t>
+          <t>Tres menores de edad y una auxiliar resultaron lesionados tras la caída.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Cómo este caleño se convirtió en socio y amigo de Marc Anthony y hoy manda en el mundo de los eventos</t>
+          <t>Mientras el mundo celebra el Día Internacional de las Familias, en Colombia más de 26.000 niños crecen lejos de una</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -6145,7 +6145,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -6155,29 +6155,29 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>https://www.las2orillas.co/como-este-caleno-se-convirtio-en-socio-y-amigo-de-marc-anthony-y-hoy-manda-en-el-mundo-de-los-eventos/</t>
+          <t>https://www.las2orillas.co/mientras-el-mundo-celebra-el-dia-internacional-de-las-familias-en-colombia-mas-de-26-000-ninos-crecen-lejos-de-una/</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Henry Cárdenas salió muy joven de Cali rumbo a Chicago y terminó convirtiéndose en uno de los empresarios más influyentes del entretenimiento latinoEl artículoCómo este caleño se convirtió en socio y amigo de Marc Anthony y hoy manda en el mundo de...</t>
+          <t>Casi el 50 % de los niños, niñas y adolescentes separados de sus familias terminan creciendo en instituciones de cuidado y no en entornos familiaresEl artículoMientras el mundo celebra el Día Internacional de las Familias, en Colombia más de 26.000...</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Un alumno de 14 años llevó un arma a una escuela de Córdoba: “Tenía cuatro balas”</t>
+          <t>Cómo este caleño se convirtió en socio y amigo de Marc Anthony y hoy manda en el mundo de los eventos</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Las2orillas</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -6187,7 +6187,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -6202,106 +6202,106 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/sociedad/policiales/2026/05/20/un-alumno-de-14-anos-llevo-un-arma-a-una-escuela-de-cordoba-y-quedo-a-disposicion-de-la-justicia-tenia-cuatro-balas/</t>
+          <t>https://www.las2orillas.co/como-este-caleno-se-convirtio-en-socio-y-amigo-de-marc-anthony-y-hoy-manda-en-el-mundo-de-los-eventos/</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>El ministro de Seguridad de Córdoba confirmó que el adolescente llevó un revólver calibre 22 cargado al establecimiento y que el arma fue secuestrada tras la activación del protocolo escolar</t>
+          <t>Henry Cárdenas salió muy joven de Cali rumbo a Chicago y terminó convirtiéndose en uno de los empresarios más influyentes del entretenimiento latinoEl artículoCómo este caleño se convirtió en socio y amigo de Marc Anthony y hoy manda en el mundo de...</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Jóvenes de Engativá iniciaron su formación en la Escuela Distrital de Emprendimiento</t>
+          <t>Un alumno de 14 años llevó un arma a una escuela de Córdoba: “Tenía cuatro balas”</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>SDIS - Juventud</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#2811eb53ee</t>
+          <t>https://www.infobae.com/sociedad/policiales/2026/05/20/un-alumno-de-14-anos-llevo-un-arma-a-una-escuela-de-cordoba-y-quedo-a-disposicion-de-la-justicia-tenia-cuatro-balas/</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Bogotá, D.C., mayo 19 de 2026.Una nueva edición de la Escuela Distrital de Emprendimiento inició su formación el pasado viernes 16 de mayo —en la Casa de Juventud la localidad de Engativá— en la que 44 jóvenes se formarán de manera gratuita para...</t>
+          <t>El ministro de Seguridad de Córdoba confirmó que el adolescente llevó un revólver calibre 22 cargado al establecimiento y que el arma fue secuestrada tras la activación del protocolo escolar</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Asesinan a joven de 13 años por cruzar una ‘frontera invisible’ en Piedecuesta, Santander</t>
+          <t>Jóvenes de Engativá iniciaron su formación en la Escuela Distrital de Emprendimiento</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>SDIS - Juventud</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Bucaramanga</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/mas-regiones/asesinan-adolescente-de-13-anos-por-cruzar-presunta-frontera-invisible-en-piedecuesta-santander/</t>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#2811eb53ee</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>El asesinato de Cristian, un menor de edad apasionado por el deporte, volvió a encender las alarmas por las "fronteras invisibles".</t>
+          <t>Bogotá, D.C., mayo 19 de 2026.Una nueva edición de la Escuela Distrital de Emprendimiento inició su formación el pasado viernes 16 de mayo —en la Casa de Juventud la localidad de Engativá— en la que 44 jóvenes se formarán de manera gratuita para...</t>
         </is>
       </c>
     </row>
@@ -6313,7 +6313,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Investigan muerte de joven tras realizarse un tatuaje en el evento “Expotatuaje Medellín”</t>
+          <t>Asesinan a joven de 13 años por cruzar una ‘frontera invisible’ en Piedecuesta, Santander</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -6333,7 +6333,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Bucaramanga</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -6343,24 +6343,24 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/medellin/joven-murio-tras-tatuarse-en-feria-de-tatuadores-en-medellin-familia-anuncia-acciones-legales/</t>
+          <t>https://www.elespectador.com/colombia/mas-regiones/asesinan-adolescente-de-13-anos-por-cruzar-presunta-frontera-invisible-en-piedecuesta-santander/</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>La familia del joven anunció acciones legales al respecto.</t>
+          <t>El asesinato de Cristian, un menor de edad apasionado por el deporte, volvió a encender las alarmas por las "fronteras invisibles".</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Capturan en Cartagena a una mujer buscada por la Interpol por trata de personas</t>
+          <t>Investigan muerte de joven tras realizarse un tatuaje en el evento “Expotatuaje Medellín”</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -6375,12 +6375,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Seguridad</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Cartagena</t>
+          <t>Medellín</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -6390,12 +6390,12 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/cartagena/capturan-en-cartagena-a-una-mujer-buscada-por-la-interpol-por-red-de-trata-de-personas/</t>
+          <t>https://www.elespectador.com/colombia/medellin/joven-murio-tras-tatuarse-en-feria-de-tatuadores-en-medellin-familia-anuncia-acciones-legales/</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>La extranjera engañaba a jóvenes con falsas ofertas laborales para luego someterlas a explotación sexual.</t>
+          <t>La familia del joven anunció acciones legales al respecto.</t>
         </is>
       </c>
     </row>
@@ -6407,27 +6407,27 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Un vino joven producido por la familia portuguesa Alves logra vender más de 1.5 millones de botellas en D1</t>
+          <t>Capturan en Cartagena a una mujer buscada por la Interpol por trata de personas</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Las2orillas</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Seguridad</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Cartagena</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -6437,106 +6437,106 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>https://www.las2orillas.co/un-vino-joven-producido-por-la-familia-portuguesa-alves-logra-vender-mas-de-1-5-millones-de-botellas-en-d1/</t>
+          <t>https://www.elespectador.com/colombia/cartagena/capturan-en-cartagena-a-una-mujer-buscada-por-la-interpol-por-red-de-trata-de-personas/</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Su fortaleza estaba en el bacalao, pero desde hace 15 años le apostaron a un viñedo del que están sacando el vino Pinta Negra que desde 2018 llega a ColombiaEl artículoUn vino joven producido por la familia portuguesa Alves logra vender más de 1.5...</t>
+          <t>La extranjera engañaba a jóvenes con falsas ofertas laborales para luego someterlas a explotación sexual.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Bogotá fortalece la atención a jóvenes con ‘Parche Seguro’, estrategia para atender alertas y vulneraciones de derechos</t>
+          <t>Un vino joven producido por la familia portuguesa Alves logra vender más de 1.5 millones de botellas en D1</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>SDIS - Juventud</t>
+          <t>Las2orillas</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Protección</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#09eb371d59</t>
+          <t>https://www.las2orillas.co/un-vino-joven-producido-por-la-familia-portuguesa-alves-logra-vender-mas-de-1-5-millones-de-botellas-en-d1/</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Bogotá D.C., mayo 15 de 2026.La Secretaría Distrital de Integración Social, a través de la Subdirección para la Juventud, y en articulación con las secretarías distritales de Salud, Mujer y Seguridad, realizó el lanzamiento de Parche Seguro, una...</t>
+          <t>Su fortaleza estaba en el bacalao, pero desde hace 15 años le apostaron a un viñedo del que están sacando el vino Pinta Negra que desde 2018 llega a ColombiaEl artículoUn vino joven producido por la familia portuguesa Alves logra vender más de 1.5...</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Así operaba “La Virgen”, banda criminal que expendía drogas a menores de edad en Cali</t>
+          <t>Bogotá fortalece la atención a jóvenes con ‘Parche Seguro’, estrategia para atender alertas y vulneraciones de derechos</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>SDIS - Juventud</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Protección</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/cali/capturaron-a-los-integrantes-de-la-virgen-banda-que-se-dedicaba-al-expendio-de-drogas-a-menores-de-edad-en-cali/</t>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#09eb371d59</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>A través de empaques de colores, este grupo camuflaba dosis de marihuana, bazuco y cocaína.</t>
+          <t>Bogotá D.C., mayo 15 de 2026.La Secretaría Distrital de Integración Social, a través de la Subdirección para la Juventud, y en articulación con las secretarías distritales de Salud, Mujer y Seguridad, realizó el lanzamiento de Parche Seguro, una...</t>
         </is>
       </c>
     </row>
@@ -6548,27 +6548,27 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>El mercado laboral colombiano enfrenta una desconexion entre jovenes, seniors y tecnologia</t>
+          <t>Así operaba “La Virgen”, banda criminal que expendía drogas a menores de edad en Cali</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Portafolio</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Empleo</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -6578,40 +6578,44 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>https://www.portafolio.co/economia/empleo/el-mercado-laboral-colombiano-enfrenta-una-desconexion-entre-jovenes-seniors-y-tecnologia-493953</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr"/>
+          <t>https://www.elespectador.com/colombia/cali/capturaron-a-los-integrantes-de-la-virgen-banda-que-se-dedicaba-al-expendio-de-drogas-a-menores-de-edad-en-cali/</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>A través de empaques de colores, este grupo camuflaba dosis de marihuana, bazuco y cocaína.</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Hallan muertos a adolescente y a su padre en Casanare; investigan posible violencia vicaria</t>
+          <t>El mercado laboral colombiano enfrenta una desconexion entre jovenes, seniors y tecnologia</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Portafolio</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Empleo</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Yopal</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -6621,14 +6625,10 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/mas-regiones/hallan-muerto-a-un-menor-y-a-su-padre-en-casanare-investigan-posible-violencia-vicaria-noticias-hoy/</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>En la vivienda fue hallada un arma de propiedad instituciona</t>
-        </is>
-      </c>
+          <t>https://www.portafolio.co/economia/empleo/el-mercado-laboral-colombiano-enfrenta-una-desconexion-entre-jovenes-seniors-y-tecnologia-493953</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -6638,27 +6638,27 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Los nutrientes y beneficios que la carne pulpa le entrega a los niños</t>
+          <t>Hallan muertos a adolescente y a su padre en Casanare; investigan posible violencia vicaria</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Las2orillas</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Yopal</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -6668,44 +6668,44 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>https://www.las2orillas.co/los-nutrientes-y-beneficios-que-la-carne-pulpa-le-entrega-a-los-ninos/</t>
+          <t>https://www.elespectador.com/colombia/mas-regiones/hallan-muerto-a-un-menor-y-a-su-padre-en-casanare-investigan-posible-violencia-vicaria-noticias-hoy/</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Una nutricionista colombiana y BBC News coinciden: la carne magra aporta vitaminas que los vegetales no pueden reemplazar fácilmente en la dieta de niños y jóvenesEl artículoLos nutrientes y beneficios que la carne pulpa le entrega a los niñosfue...</t>
+          <t>En la vivienda fue hallada un arma de propiedad instituciona</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Quedó libre el joven señalado de vandalizar estaciones del MIO durante marcha en Cali</t>
+          <t>Los nutrientes y beneficios que la carne pulpa le entrega a los niños</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Las2orillas</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Seguridad</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -6715,24 +6715,24 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/cali/quedo-libre-el-joven-senalado-de-vandalizar-estaciones-del-mio-durante-marcha-en-cali/</t>
+          <t>https://www.las2orillas.co/los-nutrientes-y-beneficios-que-la-carne-pulpa-le-entrega-a-los-ninos/</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>El hombre, de 21 años, fue capturado tras un allanamiento en el barrio Panamericano.</t>
+          <t>Una nutricionista colombiana y BBC News coinciden: la carne magra aporta vitaminas que los vegetales no pueden reemplazar fácilmente en la dieta de niños y jóvenesEl artículoLos nutrientes y beneficios que la carne pulpa le entrega a los niñosfue...</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Turista de 18 años murió embestida por un taxi cuando salía de playa de Santa Marta</t>
+          <t>Quedó libre el joven señalado de vandalizar estaciones del MIO durante marcha en Cali</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -6747,39 +6747,39 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Seguridad</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/mas-regiones/turista-de-18-anos-murio-embestida-por-un-taxi-cuando-salia-de-la-playa-santa-marta/</t>
+          <t>https://www.elespectador.com/colombia/cali/quedo-libre-el-joven-senalado-de-vandalizar-estaciones-del-mio-durante-marcha-en-cali/</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>La joven turista había viajado desde Bogotá para reencontrarse con una amiga en la capital del Magdalena.</t>
+          <t>El hombre, de 21 años, fue capturado tras un allanamiento en el barrio Panamericano.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Hallaron sin vida a joven de 19 años que desapareció mientras nadaba en un humedal en Cali</t>
+          <t>Turista de 18 años murió embestida por un taxi cuando salía de playa de Santa Marta</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -6794,49 +6794,49 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/cali/hallaron-sin-vida-a-joven-de-19-anos-que-desaparecio-mientras-nadaba-en-un-humedal-en-cali-noticias-hoy/</t>
+          <t>https://www.elespectador.com/colombia/mas-regiones/turista-de-18-anos-murio-embestida-por-un-taxi-cuando-salia-de-la-playa-santa-marta/</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>El cuerpo fue localizado a dos metros de profundidad tras seis horas de labores de búsqueda.</t>
+          <t>La joven turista había viajado desde Bogotá para reencontrarse con una amiga en la capital del Magdalena.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Jóvenes de San Cristóbal toman el Congreso: Así se forjan los nuevos líderes de Bogotá</t>
+          <t>Hallaron sin vida a joven de 19 años que desapareció mientras nadaba en un humedal en Cali</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Pulzo</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -6846,20 +6846,24 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>https://www.pulzo.com/nacion/bogota/liderazgo-juvenil-y-participacion-estudiantil-en-bogota-jornada-pedagogica-en-el-congreso-de-colombia-PP5169613A</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr"/>
+          <t>https://www.elespectador.com/colombia/cali/hallaron-sin-vida-a-joven-de-19-anos-que-desaparecio-mientras-nadaba-en-un-humedal-en-cali-noticias-hoy/</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>El cuerpo fue localizado a dos metros de profundidad tras seis horas de labores de búsqueda.</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -6869,54 +6873,50 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Piden investigar muerte de adolescente en balacera en la que hubo policías, en Medellín</t>
+          <t>Jóvenes de San Cristóbal toman el Congreso: Así se forjan los nuevos líderes de Bogotá</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Pulzo</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/medellin/piden-investigar-muerte-de-adolescente-en-balacera-en-la-que-hubo-policias-en-medellin/</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>El alcalde de Medellín, Federico Gutiérrez, pidió investigar la muerte de joven de 17 años, en medio de balacera en la que hubo policías.</t>
-        </is>
-      </c>
+          <t>https://www.pulzo.com/nacion/bogota/liderazgo-juvenil-y-participacion-estudiantil-en-bogota-jornada-pedagogica-en-el-congreso-de-colombia-PP5169613A</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Confirman que hay dos muertos y al menos 37 heridos en accidente de monster truck en Popayán</t>
+          <t>Piden investigar muerte de adolescente en balacera en la que hubo policías, en Medellín</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -6936,7 +6936,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Popayán</t>
+          <t>Medellín</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/mas-regiones/confirman-que-hay-dos-muertos-y-al-menos-38-heridos-en-accidente-de-monster-truck-en-popayan/</t>
+          <t>https://www.elespectador.com/colombia/medellin/piden-investigar-muerte-de-adolescente-en-balacera-en-la-que-hubo-policias-en-medellin/</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Accidente de camión monster truck en Popayán dejó dos personas muertas, entre ellas una menor de edad.</t>
+          <t>El alcalde de Medellín, Federico Gutiérrez, pidió investigar la muerte de joven de 17 años, en medio de balacera en la que hubo policías.</t>
         </is>
       </c>
     </row>
@@ -6963,7 +6963,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Ataque sicarial dejó a un menor de edad muerto y otro herido en Piedecuesta, Santander</t>
+          <t>Confirman que hay dos muertos y al menos 37 heridos en accidente de monster truck en Popayán</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -6983,7 +6983,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Bucaramanga</t>
+          <t>Popayán</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -6993,12 +6993,12 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/mas-regiones/ataque-sicarial-dejo-a-un-menor-de-edad-muerto-y-otro-herido-en-piedecuesta-santander/</t>
+          <t>https://www.elespectador.com/colombia/mas-regiones/confirman-que-hay-dos-muertos-y-al-menos-38-heridos-en-accidente-de-monster-truck-en-popayan/</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Hombres armados persiguieron y asesinaron a un joven de 17 años en Piedecuesta, Santander.</t>
+          <t>Accidente de camión monster truck en Popayán dejó dos personas muertas, entre ellas una menor de edad.</t>
         </is>
       </c>
     </row>
@@ -7010,59 +7010,59 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>En Bogotá bajan las cifras de delitos, pero aumenta el miedo</t>
+          <t>Ataque sicarial dejó a un menor de edad muerto y otro herido en Piedecuesta, Santander</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>La Silla Vacía</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Bucaramanga</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>https://www.lasillavacia.com/red-de-expertos/red-cachaca/en-bogota-bajan-las-cifras-de-delitos-pero-aumenta-el-miedo/</t>
+          <t>https://www.elespectador.com/colombia/mas-regiones/ataque-sicarial-dejo-a-un-menor-de-edad-muerto-y-otro-herido-en-piedecuesta-santander/</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Aunque bajan los delitos en Bogotá, la inseguridad persiste, especialmente para niños y jóvenes, lo que revela una falla estructural en la protección de la ciudadanía.The postEn Bogotá bajan las cifras de delitos, pero aumenta el miedoappeared first...</t>
+          <t>Hombres armados persiguieron y asesinaron a un joven de 17 años en Piedecuesta, Santander.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Joven mató a su madre en Antioquia: lo que encontró la Policía cuando llegó a su vivienda fue aterrador</t>
+          <t>En Bogotá bajan las cifras de delitos, pero aumenta el miedo</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Pulzo</t>
+          <t>La Silla Vacía</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -7072,25 +7072,29 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Seguridad</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>https://www.pulzo.com/nacion/joven-26-anos-mato-su-madre-45-anos-antioquia-luego-ataco-policias-PP5165726</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr"/>
+          <t>https://www.lasillavacia.com/red-de-expertos/red-cachaca/en-bogota-bajan-las-cifras-de-delitos-pero-aumenta-el-miedo/</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>Aunque bajan los delitos en Bogotá, la inseguridad persiste, especialmente para niños y jóvenes, lo que revela una falla estructural en la protección de la ciudadanía.The postEn Bogotá bajan las cifras de delitos, pero aumenta el miedoappeared first...</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -7100,22 +7104,22 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Capturaron a hombre que habría asesinado a su mamá en Caldas, Antioquia; policía fue herido</t>
+          <t>Joven mató a su madre en Antioquia: lo que encontró la Policía cuando llegó a su vivienda fue aterrador</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Pulzo</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Seguridad</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -7130,14 +7134,10 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/medellin/capturaron-a-hombre-que-habria-asesinado-a-su-mama-en-caldas-antioquia-policia-fue-herido/</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>Autoridades capturaron a joven de 26 años que habría asesinado con arma blanca a su mamá. En el procedimiento, un policía resultó herido.</t>
-        </is>
-      </c>
+          <t>https://www.pulzo.com/nacion/joven-26-anos-mato-su-madre-45-anos-antioquia-luego-ataco-policias-PP5165726</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -7147,7 +7147,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>En ataque armado fue asesinada una joven en Vijes, Valle del Cauca; su mamá fue herida</t>
+          <t>Capturaron a hombre que habría asesinado a su mamá en Caldas, Antioquia; policía fue herido</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -7167,7 +7167,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Popayán</t>
+          <t>Medellín</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -7177,24 +7177,24 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/cali/en-ataque-armado-fue-asesinada-una-joven-en-vijes-valle-del-cauca-su-mama-fue-herida/</t>
+          <t>https://www.elespectador.com/colombia/medellin/capturaron-a-hombre-que-habria-asesinado-a-su-mama-en-caldas-antioquia-policia-fue-herido/</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Las autoridades ofrecieron COP 10 millones de recompensa por los responsables de ataque armado en el que murió una joven en Vijes, Valle.</t>
+          <t>Autoridades capturaron a joven de 26 años que habría asesinado con arma blanca a su mamá. En el procedimiento, un policía resultó herido.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Menor de 15 años murió arrastrado por corriente en Cartagena: guardas hallaron el cuerpo</t>
+          <t>En ataque armado fue asesinada una joven en Vijes, Valle del Cauca; su mamá fue herida</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -7214,7 +7214,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Cartagena</t>
+          <t>Popayán</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -7224,12 +7224,12 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/cartagena/menor-de-15-anos-murio-arrastrado-por-corriente-en-cartagena-guardas-hallaron-el-cuerpo/</t>
+          <t>https://www.elespectador.com/colombia/cali/en-ataque-armado-fue-asesinada-una-joven-en-vijes-valle-del-cauca-su-mama-fue-herida/</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>El joven desapareció tras lanzarse a un caño en medio de la lluvia.</t>
+          <t>Las autoridades ofrecieron COP 10 millones de recompensa por los responsables de ataque armado en el que murió una joven en Vijes, Valle.</t>
         </is>
       </c>
     </row>
@@ -7241,7 +7241,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Universitario fue asesinado en Manizales tras riña por presunta deuda de dinero</t>
+          <t>Menor de 15 años murió arrastrado por corriente en Cartagena: guardas hallaron el cuerpo</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -7261,7 +7261,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Manizales</t>
+          <t>Cartagena</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/mas-regiones/universitario-murio-tras-una-rina-en-manizales-investigan-presunta-deuda-de-dinero/</t>
+          <t>https://www.elespectador.com/colombia/cartagena/menor-de-15-anos-murio-arrastrado-por-corriente-en-cartagena-guardas-hallaron-el-cuerpo/</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>El joven fue herido dentro de un vehículo y trasladado a un hospital en donde falleció.</t>
+          <t>El joven desapareció tras lanzarse a un caño en medio de la lluvia.</t>
         </is>
       </c>
     </row>
@@ -7288,27 +7288,27 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Alerta en el mercado de la carne en colombia: gobierno propone limitar exportacion de ganado joven</t>
+          <t>Universitario fue asesinado en Manizales tras riña por presunta deuda de dinero</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Portafolio</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Manizales</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -7318,25 +7318,29 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>https://www.portafolio.co/economia/agro/alerta-en-el-mercado-de-la-carne-en-colombia-gobierno-propone-limitar-exportacion-de-ganado-joven-493075</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr"/>
+          <t>https://www.elespectador.com/colombia/mas-regiones/universitario-murio-tras-una-rina-en-manizales-investigan-presunta-deuda-de-dinero/</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>El joven fue herido dentro de un vehículo y trasladado a un hospital en donde falleció.</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Alerta Rosa, el nuevo mecanismo para búsqueda inmediata de mujeres, niños y adolescentes en Colombia</t>
+          <t>Alerta en el mercado de la carne en colombia: gobierno propone limitar exportacion de ganado joven</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>Portafolio</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -7361,7 +7365,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/nacion/alerta-rosa-el-nuevo-mecanismo-para-busqueda-inmediata-de-mujeres-ninos-y-adolescentes-en-colombia-rg10</t>
+          <t>https://www.portafolio.co/economia/agro/alerta-en-el-mercado-de-la-carne-en-colombia-gobierno-propone-limitar-exportacion-de-ganado-joven-493075</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -7374,54 +7378,50 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Los domingos también son para las juventudes: Bogotá amplía la atención en Casas de Juventud</t>
+          <t>Alerta Rosa, el nuevo mecanismo para búsqueda inmediata de mujeres, niños y adolescentes en Colombia</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>SDIS - Juventud</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Cultura y deporte</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#5d8561cf04</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>• Bogotá amplía el acceso a oportunidades para jóvenes con la apertura dominical de tres Casas de Juventud en Suba, Los Mártires y Kennedy, respondiendo a la necesidad de contar con más tiempo y espacios disponibles durante el fin de semana. • Las...</t>
-        </is>
-      </c>
+          <t>https://www.bluradio.com/nacion/alerta-rosa-el-nuevo-mecanismo-para-busqueda-inmediata-de-mujeres-ninos-y-adolescentes-en-colombia-rg10</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Abierta convocatoria para la Escuela Distrital de Emprendimiento para jóvenes en Engativá</t>
+          <t>Los domingos también son para las juventudes: Bogotá amplía la atención en Casas de Juventud</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -7436,7 +7436,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Cultura y deporte</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -7451,29 +7451,29 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#248fcdb8a0</t>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#5d8561cf04</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>• El Distrito abre la convocatoria para 50 jóvenes entre 18 y 28 años, que cuentan con un emprendimiento en marcha y buscan fortalecer sus capacidades para hacerlo crecer y consolidarlo. • La formación se realizará de manera presencial en la Casa de...</t>
+          <t>• Bogotá amplía el acceso a oportunidades para jóvenes con la apertura dominical de tres Casas de Juventud en Suba, Los Mártires y Kennedy, respondiendo a la necesidad de contar con más tiempo y espacios disponibles durante el fin de semana. • Las...</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Miles de jóvenes se toman Bogotá: Prosperidad Social acompaña el Festival Nacional de la Juventud</t>
+          <t>Voluntariado transformador: unidad de autocuidado para habitantes de calle en el Voto Nacional estrena ludoteca</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Prosperidad Social</t>
+          <t>SDIS - Juventud</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -7483,7 +7483,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -7498,133 +7498,133 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>https://prosperidadsocial.gov.co/Noticias/miles-de-jovenes-se-toman-bogota-prosperidad-social-acompana-el-festival-nacional-de-la-juventud/</t>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#364408dd32</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Más de 4.000 jóvenes de todo el país se reúnen del 24 al 26 de abril en la sede Aduanilla de Paiba de la Universidad Distrital</t>
+          <t>• 40 personas, entre voluntarios de empresas y habitantes de calle, unieron esfuerzos para adecuar un espacio que estimula el conocimiento y pone a volar a la imaginación. • Esta acción se enmarca en la estrategia ‘Más manos por Bogotá’, programa de...</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>El tío comunista de Paloma Valencia, la oveja negra que incomodó a su familia conservadora</t>
+          <t>Abierta convocatoria para la Escuela Distrital de Emprendimiento para jóvenes en Engativá</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Las2orillas</t>
+          <t>SDIS - Juventud</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Popayán</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>https://www.las2orillas.co/el-tio-comunista-de-paloma-valencia-la-oveja-negra-que-incomodo-a-su-familia-conservadora/</t>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#248fcdb8a0</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Álvaro Pío Valencia, hermano del expresidente Guillermo León, conoció de joven al papá de Iván Cepeda en Popayán e influyó para que él fuera un consagrado ComunistaEl artículoEl tío comunista de Paloma Valencia, la oveja negra que incomodó a su...</t>
+          <t>• El Distrito abre la convocatoria para 50 jóvenes entre 18 y 28 años, que cuentan con un emprendimiento en marcha y buscan fortalecer sus capacidades para hacerlo crecer y consolidarlo. • La formación se realizará de manera presencial en la Casa de...</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Masacre en Mocoa: asesinaron a cinco jóvenes en zona boscosa</t>
+          <t>Miles de jóvenes se toman Bogotá: Prosperidad Social acompaña el Festival Nacional de la Juventud</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Prosperidad Social</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Mocoa</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/mas-regiones/masacre-en-mocoa-asesinaron-a-cinco-jovenes-en-zona-boscosa/</t>
+          <t>https://prosperidadsocial.gov.co/Noticias/miles-de-jovenes-se-toman-bogota-prosperidad-social-acompana-el-festival-nacional-de-la-juventud/</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Cinco hombres fueron asesinados en Mocoa. El hecho se dio después de que se difundió un panfleto amenazante.</t>
+          <t>Más de 4.000 jóvenes de todo el país se reúnen del 24 al 26 de abril en la sede Aduanilla de Paiba de la Universidad Distrital</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Patinador de 14 años de la Liga Vallecaucana murió durante un entrenamiento: esto se sabe</t>
+          <t>El tío comunista de Paloma Valencia, la oveja negra que incomodó a su familia conservadora</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Las2orillas</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -7639,24 +7639,24 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/cali/muere-joven-patinador-en-cali-tras-accidente-durante-entrenamiento-en-patinodromo/</t>
+          <t>https://www.las2orillas.co/el-tio-comunista-de-paloma-valencia-la-oveja-negra-que-incomodo-a-su-familia-conservadora/</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>El joven hacía parte de la Liga Vallecaucana de Patinaje y del club Relámpago.</t>
+          <t>Álvaro Pío Valencia, hermano del expresidente Guillermo León, conoció de joven al papá de Iván Cepeda en Popayán e influyó para que él fuera un consagrado ComunistaEl artículoEl tío comunista de Paloma Valencia, la oveja negra que incomodó a su...</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Capturan a hombre que se hizo pasar por mototaxista y abusó de una joven de 14 años en Cali</t>
+          <t>Masacre en Mocoa: asesinaron a cinco jóvenes en zona boscosa</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Mocoa</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -7686,34 +7686,34 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/cali/capturan-a-hombre-que-se-hizo-pasar-por-mototaxista-y-abuso-de-una-joven-de-14-anos-en-cali/</t>
+          <t>https://www.elespectador.com/colombia/mas-regiones/masacre-en-mocoa-asesinaron-a-cinco-jovenes-en-zona-boscosa/</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>La víctima fue herida con arma cortopunzante y asfixiada hasta quedar inconsciente.</t>
+          <t>Cinco hombres fueron asesinados en Mocoa. El hecho se dio después de que se difundió un panfleto amenazante.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>La jueza que investiga el colapso de una pasarela en Santander imputa a un tercer técnico de Costas y aprecia indicios de seis homicidios por imprudencia grave</t>
+          <t>Patinador de 14 años de la Liga Vallecaucana murió durante un entrenamiento: esto se sabe</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -7723,7 +7723,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Bucaramanga</t>
+          <t>Popayán</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -7733,24 +7733,24 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/espana/2026/04/21/la-jueza-que-investiga-el-colapso-de-una-pasarela-en-santander-imputa-a-un-tercer-tecnico-de-costas-y-aprecia-indicios-de-seis-homicidios-por-imprudencia-grave/</t>
+          <t>https://www.elespectador.com/colombia/cali/muere-joven-patinador-en-cali-tras-accidente-durante-entrenamiento-en-patinodromo/</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>La instructora considera que la falta de inspección y mantenimiento durante años generó un riesgo no controlado que desembocó en el desplome de la estructura y en la muerte de seis jóvenes</t>
+          <t>El joven hacía parte de la Liga Vallecaucana de Patinaje y del club Relámpago.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Investigan el asesinato de adolescente de 15 años en campo de golf en Cartagena</t>
+          <t>Capturan a hombre que se hizo pasar por mototaxista y abusó de una joven de 14 años en Cali</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -7770,7 +7770,7 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Cartagena</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -7780,24 +7780,24 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/cartagena/investigan-el-asesinato-de-adolescente-de-17-anos-en-campo-de-golf-en-cartagena/</t>
+          <t>https://www.elespectador.com/colombia/cali/capturan-a-hombre-que-se-hizo-pasar-por-mototaxista-y-abuso-de-una-joven-de-14-anos-en-cali/</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>Las autoridades buscan esclarecer por qué un empleado de seguridad de un club de golf de Cartagena disparó contra un adolescente.</t>
+          <t>La víctima fue herida con arma cortopunzante y asfixiada hasta quedar inconsciente.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Filtran las primeras imágenes del doble asesinato contra miembros de la producción de ‘Sin senos sí hay paraíso 4′ en Bogotá: el agresor atacó por la espalda</t>
+          <t>La jueza que investiga el colapso de una pasarela en Santander imputa a un tercer técnico de Costas y aprecia indicios de seis homicidios por imprudencia grave</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -7817,44 +7817,44 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Bucaramanga</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/04/20/filtran-las-primeras-imagenes-del-doble-asesinato-contra-miembros-de-la-produccion-de-sin-senos-si-hay-paraiso-4-en-bogota-el-agresor-ataco-por-la-espalda/</t>
+          <t>https://www.infobae.com/espana/2026/04/21/la-jueza-que-investiga-el-colapso-de-una-pasarela-en-santander-imputa-a-un-tercer-tecnico-de-costas-y-aprecia-indicios-de-seis-homicidios-por-imprudencia-grave/</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>En el material fílmico se observa cuando el joven de 24 años diagnosticado con enfermedad mental se acercó al conductor de 45 años y, sin mediar palabra, lo tomó por el cuello y lo hirió mortalmente con arma blanca</t>
+          <t>La instructora considera que la falta de inspección y mantenimiento durante años generó un riesgo no controlado que desembocó en el desplome de la estructura y en la muerte de seis jóvenes</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Magnicidio Miguel Uribe Turbay: menor de edad que disparó al precandidato fue declarado como víctima en el proceso judicial</t>
+          <t>Investigan el asesinato de adolescente de 15 años en campo de golf en Cartagena</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -7864,7 +7864,7 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Cartagena</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -7874,29 +7874,29 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/04/18/magnicidio-miguel-uribe-turbay-menor-de-edad-que-disparo-al-precandidato-fue-declarado-como-victima-en-el-proceso-judicial/</t>
+          <t>https://www.elespectador.com/colombia/cartagena/investigan-el-asesinato-de-adolescente-de-17-anos-en-campo-de-golf-en-cartagena/</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>Alias Tianz confesó el crimen y cumple una sanción de siete años en un centro de atención especializada, bajo la custodia del Instituto Colombiano de Bienestar Familiar</t>
+          <t>Las autoridades buscan esclarecer por qué un empleado de seguridad de un club de golf de Cartagena disparó contra un adolescente.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Uno de cada cuatro jovenes en colombia no estudia ni trabaja y el mercado laboral da senales de debilidad</t>
+          <t>Filtran las primeras imágenes del doble asesinato contra miembros de la producción de ‘Sin senos sí hay paraíso 4′ en Bogotá: el agresor atacó por la espalda</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Portafolio</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -7906,87 +7906,91 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Empleo</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>https://www.portafolio.co/economia/empleo/uno-de-cada-cuatro-jovenes-en-colombia-no-estudia-ni-trabaja-y-el-mercado-laboral-da-senales-de-debilidad-492018</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr"/>
+          <t>https://www.infobae.com/colombia/2026/04/20/filtran-las-primeras-imagenes-del-doble-asesinato-contra-miembros-de-la-produccion-de-sin-senos-si-hay-paraiso-4-en-bogota-el-agresor-ataco-por-la-espalda/</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>En el material fílmico se observa cuando el joven de 24 años diagnosticado con enfermedad mental se acercó al conductor de 45 años y, sin mediar palabra, lo tomó por el cuello y lo hirió mortalmente con arma blanca</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>¡Atención, jóvenes! Bogotá abre formación gratuita para impulsar emprendimientos</t>
+          <t>Magnicidio Miguel Uribe Turbay: menor de edad que disparó al precandidato fue declarado como víctima en el proceso judicial</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>SDIS - Juventud</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#ee67a6f4f1</t>
+          <t>https://www.infobae.com/colombia/2026/04/18/magnicidio-miguel-uribe-turbay-menor-de-edad-que-disparo-al-precandidato-fue-declarado-como-victima-en-el-proceso-judicial/</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>•Bogotá abre la convocatoria de Innovers 2026, un programa gratuito para fortalecer el emprendimiento juvenil. • Dirigido a jóvenes entre 18 y 28 años, desde quienes tienen una idea hasta emprendimientos en crecimiento.</t>
+          <t>Alias Tianz confesó el crimen y cumple una sanción de siete años en un centro de atención especializada, bajo la custodia del Instituto Colombiano de Bienestar Familiar</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Asesinaron a dos jóvenes que habían sido secuestrados por la guerrilla hace un mes en Arauca</t>
+          <t>Uno de cada cuatro jovenes en colombia no estudia ni trabaja y el mercado laboral da senales de debilidad</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>Portafolio</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -7996,12 +8000,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Empleo</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Arauca</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -8011,7 +8015,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/nacion/asesinaron-a-dos-jovenes-que-habian-sido-secuestrados-por-la-guerrilla-hace-un-mes-en-arauca-rg10</t>
+          <t>https://www.portafolio.co/economia/empleo/uno-de-cada-cuatro-jovenes-en-colombia-no-estudia-ni-trabaja-y-el-mercado-laboral-da-senales-de-debilidad-492018</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -8019,22 +8023,22 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Bomberos rescataron a joven que le quedó atrapado el dedo en una banca del MIO en Cali</t>
+          <t>¡Atención, jóvenes! Bogotá abre formación gratuita para impulsar emprendimientos</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>SDIS - Juventud</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -8044,44 +8048,44 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/cali/bomberos-rescataron-a-joven-que-le-quedo-atrapado-el-dedo-en-una-banca-del-mio-en-cali/</t>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#ee67a6f4f1</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>El caso ocurrió en un paradero del sistema en el barrio Potrero Grande del MIO en Cali.</t>
+          <t>•Bogotá abre la convocatoria de Innovers 2026, un programa gratuito para fortalecer el emprendimiento juvenil. • Dirigido a jóvenes entre 18 y 28 años, desde quienes tienen una idea hasta emprendimientos en crecimiento.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Medellín abre convocatoria para impulsar emprendimientos rurales de jóvenes y mujeres</t>
+          <t>Asesinaron a dos jóvenes que habían sido secuestrados por la guerrilla hace un mes en Arauca</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -8091,7 +8095,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Arauca</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -8101,44 +8105,40 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/medellin/medellin-abre-convocatoria-para-impulsar-emprendimientos-rurales-de-jovenes-y-mujeres/</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr">
-        <is>
-          <t>Hasta 40 iniciativas podrán acceder a recursos y acompañamiento técnico. Las inscripciones estarán abiertas hasta el 10 de abril.</t>
-        </is>
-      </c>
+          <t>https://www.bluradio.com/nacion/asesinaron-a-dos-jovenes-que-habian-sido-secuestrados-por-la-guerrilla-hace-un-mes-en-arauca-rg10</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>MATAR MUJERES: LA VIOLENCIA INSTRUMENTAL COMO ESTRATEGIA DEL CONTROL ARMADO</t>
+          <t>Bomberos rescataron a joven que le quedó atrapado el dedo en una banca del MIO en Cali</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>La Silla Vacía</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -8148,24 +8148,24 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>https://www.lasillavacia.com/red-de-expertos/matar-mujeres-la-violencia-instrumental-como-estrategia-del-control-armado/</t>
+          <t>https://www.elespectador.com/colombia/cali/bomberos-rescataron-a-joven-que-le-quedo-atrapado-el-dedo-en-una-banca-del-mio-en-cali/</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>El asesinato de dos adolescentes en Malambo, Atlántico, es un crimen atroz que evidencia una lógica que se repite en distintos territorios y que consiste en matar mujeres para castigar, advertir e imponer control. Mientras sus familias recibían...</t>
+          <t>El caso ocurrió en un paradero del sistema en el barrio Potrero Grande del MIO en Cali.</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Capturan a joven de 19 años por asesinato de mujer y su hijo en Villavicencio</t>
+          <t>Medellín abre convocatoria para impulsar emprendimientos rurales de jóvenes y mujeres</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -8180,12 +8180,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Villavicencio</t>
+          <t>Medellín</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -8195,39 +8195,39 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/mas-regiones/capturan-a-joven-de-19-anos-por-asesinato-de-mujer-y-su-hijo-en-villavicencio/</t>
+          <t>https://www.elespectador.com/colombia/medellin/medellin-abre-convocatoria-para-impulsar-emprendimientos-rurales-de-jovenes-y-mujeres/</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>Las autoridades capturaron a un joven de 19 años señalado del doble homicidio ocurrido en el barrio San Antonio de Villavicencio.</t>
+          <t>Hasta 40 iniciativas podrán acceder a recursos y acompañamiento técnico. Las inscripciones estarán abiertas hasta el 10 de abril.</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Hallaron el cuerpo de una adolescente de 14 años que se ahogó en playa de Antioquia</t>
+          <t>MATAR MUJERES: LA VIOLENCIA INSTRUMENTAL COMO ESTRATEGIA DEL CONTROL ARMADO</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>La Silla Vacía</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -8242,24 +8242,24 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/mas-regiones/hallaron-el-cuerpo-de-una-adolescente-de-14-anos-que-se-ahogo-en-playa-de-san-juan-de-uraba-en-antioquia/</t>
+          <t>https://www.lasillavacia.com/red-de-expertos/matar-mujeres-la-violencia-instrumental-como-estrategia-del-control-armado/</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>La menor había ingresado al mar con una amiga en una zona con fuerte oleaje. Su cuerpo fue hallado horas después.</t>
+          <t>El asesinato de dos adolescentes en Malambo, Atlántico, es un crimen atroz que evidencia una lógica que se repite en distintos territorios y que consiste en matar mujeres para castigar, advertir e imponer control. Mientras sus familias recibían...</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Ataque de pitbull que dejó a perro muerto y joven herido en Barranquilla</t>
+          <t>Capturan a joven de 19 años por asesinato de mujer y su hijo en Villavicencio</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -8279,7 +8279,7 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Barranquilla</t>
+          <t>Villavicencio</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -8289,200 +8289,200 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/barranquilla/anuncian-acciones-tras-ataque-de-pitbull-que-dejo-a-perro-muerto-y-joven-herido-en-barranquilla/</t>
+          <t>https://www.elespectador.com/colombia/mas-regiones/capturan-a-joven-de-19-anos-por-asesinato-de-mujer-y-su-hijo-en-villavicencio/</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>El hecho ocurrió en un conjunto residencial de Barranquilla y quedó registrado en cámaras de seguridad.</t>
+          <t>Las autoridades capturaron a un joven de 19 años señalado del doble homicidio ocurrido en el barrio San Antonio de Villavicencio.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Prosperidad Social amplía el periodo de transferencias de Renta Joven en modalidad de giro</t>
+          <t>Hallaron el cuerpo de una adolescente de 14 años que se ahogó en playa de Antioquia</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Prosperidad Social</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Política pública</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>https://prosperidadsocial.gov.co/Noticias/prosperidad-social-amplia-el-periodo-de-transferencias-de-renta-joven-en-modalidad-de-giro/</t>
+          <t>https://www.elespectador.com/colombia/mas-regiones/hallaron-el-cuerpo-de-una-adolescente-de-14-anos-que-se-ahogo-en-playa-de-san-juan-de-uraba-en-antioquia/</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>La ampliación del plazo permitirá que más de 27.000 participantes reciban sus subsidios, incluyendo transferencias pendientes de 2025. La transferencia monetaria condicionada se podrá reclamar en los puntos autorizados de SuRed y SuperGIROS. Bogotá...</t>
+          <t>La menor había ingresado al mar con una amiga en una zona con fuerte oleaje. Su cuerpo fue hallado horas después.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Nueva convocatoria dirigida a jóvenes interesados en formarse en el sector de gastronomía</t>
+          <t>Ataque de pitbull que dejó a perro muerto y joven herido en Barranquilla</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>SDIS - Juventud</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Barranquilla</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#e5d592a6d5</t>
+          <t>https://www.elespectador.com/colombia/barranquilla/anuncian-acciones-tras-ataque-de-pitbull-que-dejo-a-perro-muerto-y-joven-herido-en-barranquilla/</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>• El Distrito, en alianza con la Fundación Gastronomía Social, lanzan una nueva convocatoria dirigida a jóvenes de 18 a 30 años, principalmente de la localidad de Kennedy, para formarse en servicio para el sector de la gastronomía. • Esta formación...</t>
+          <t>El hecho ocurrió en un conjunto residencial de Barranquilla y quedó registrado en cámaras de seguridad.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>La incoherente decisión de Petro de abrirle la Casa de Nariño a Westcol decepcionó a quienes respaldaban su gobierno</t>
+          <t>Prosperidad Social amplía el periodo de transferencias de Renta Joven en modalidad de giro</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Las2orillas</t>
+          <t>Prosperidad Social</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Política pública</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>https://www.las2orillas.co/la-incoherente-decision-de-petro-de-abrirle-la-casa-de-narino-a-westcol-decepciono-a-quienes-respaldaban-su-gobierno/</t>
+          <t>https://prosperidadsocial.gov.co/Noticias/prosperidad-social-amplia-el-periodo-de-transferencias-de-renta-joven-en-modalidad-de-giro/</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>Recibir a Westcol tras la tragedia del Hércules y sus discursos de odio es un golpe a la coherencia progresista. ¿Vale todo por llegarle a los jóvenes?El artículoLa incoherente decisión de Petro de abrirle la Casa de Nariño a Westcol decepcionó a...</t>
+          <t>La ampliación del plazo permitirá que más de 27.000 participantes reciban sus subsidios, incluyendo transferencias pendientes de 2025. La transferencia monetaria condicionada se podrá reclamar en los puntos autorizados de SuRed y SuperGIROS. Bogotá...</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Primero Petro luego Uribe: Westcol, el streamer que entrevista presidentes</t>
+          <t>Nueva convocatoria dirigida a jóvenes interesados en formarse en el sector de gastronomía</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>La Silla Vacía</t>
+          <t>SDIS - Juventud</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>https://www.lasillavacia.com/silla-nacional/primero-petro-luego-uribe-westcol-el-streamer-que-entrevista-presidentes/</t>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#e5d592a6d5</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>El influencer se convierte en interlocutor de los dos políticos más poderosos de Colombia. Ambos van detrás de su audiencia joven y masiva en época electoral.The postPrimero Petro luego Uribe: Westcol, el streamer que entrevista presidentesappeared...</t>
+          <t>• El Distrito, en alianza con la Fundación Gastronomía Social, lanzan una nueva convocatoria dirigida a jóvenes de 18 a 30 años, principalmente de la localidad de Kennedy, para formarse en servicio para el sector de la gastronomía. • Esta formación...</t>
         </is>
       </c>
     </row>
@@ -8494,27 +8494,27 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Asesinaron a joven futbolista en Barranquilla; le dispararon en la cabeza</t>
+          <t>La incoherente decisión de Petro de abrirle la Casa de Nariño a Westcol decepcionó a quienes respaldaban su gobierno</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Las2orillas</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Barranquilla</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
@@ -8524,44 +8524,44 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/barranquilla/asesinaron-a-joven-futbolista-en-barranquilla-le-dispararon-en-la-cabeza/</t>
+          <t>https://www.las2orillas.co/la-incoherente-decision-de-petro-de-abrirle-la-casa-de-narino-a-westcol-decepciono-a-quienes-respaldaban-su-gobierno/</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>Asesinaron a una joven promesa del fútbol en el barrio El Santuario de Barranquilla. Le dispararon en la cabeza en medio de una riña.</t>
+          <t>Recibir a Westcol tras la tragedia del Hércules y sus discursos de odio es un golpe a la coherencia progresista. ¿Vale todo por llegarle a los jóvenes?El artículoLa incoherente decisión de Petro de abrirle la Casa de Nariño a Westcol decepcionó a...</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Asesinaron a dos jóvenes en ataque sicarial en una discoteca de Riohacha</t>
+          <t>Primero Petro luego Uribe: Westcol, el streamer que entrevista presidentes</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>La Silla Vacía</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Riohacha</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -8571,81 +8571,81 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/mas-regiones/tres-sicarios-abrieron-fuego-en-una-discoteca-de-riohacha-y-asesinaron-dos-jovenes/</t>
+          <t>https://www.lasillavacia.com/silla-nacional/primero-petro-luego-uribe-westcol-el-streamer-que-entrevista-presidentes/</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>¿Qué sucedió en el ataque de tres sicarios ocurrido en una discoteca de Riohacha?</t>
+          <t>El influencer se convierte en interlocutor de los dos políticos más poderosos de Colombia. Ambos van detrás de su audiencia joven y masiva en época electoral.The postPrimero Petro luego Uribe: Westcol, el streamer que entrevista presidentesappeared...</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Así fue la participación de los jóvenes en el primer Fest de las Oportunidades del año</t>
+          <t>Asesinaron a joven futbolista en Barranquilla; le dispararon en la cabeza</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>SDIS - Juventud</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Barranquilla</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#9690ed7762</t>
+          <t>https://www.elespectador.com/colombia/barranquilla/asesinaron-a-joven-futbolista-en-barranquilla-le-dispararon-en-la-cabeza/</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>•El primer Fest de las Oportunidades 2026 reunió a más de 130 jóvenes en Usme, conectándolos con oferta en empleo, educación, emprendimiento y bienestar. •Más de 20 entidades y aliados participaron acercando oportunidades reales y orientación...</t>
+          <t>Asesinaron a una joven promesa del fútbol en el barrio El Santuario de Barranquilla. Le dispararon en la cabeza en medio de una riña.</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Conductor atropelló y mató a un joven en Bogotá tras invadir el carril exclusivo de Transmilenio</t>
+          <t>Asesinaron a dos jóvenes en ataque sicarial en una discoteca de Riohacha</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -8655,39 +8655,39 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Riohacha</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/03/28/conductor-atropello-y-mato-a-un-joven-en-bogota-tras-invadir-el-carril-exclusivo-de-transmilenio/</t>
+          <t>https://www.elespectador.com/colombia/mas-regiones/tres-sicarios-abrieron-fuego-en-una-discoteca-de-riohacha-y-asesinaron-dos-jovenes/</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>La muerte de Juan Sebastián Triviño y las lesiones sufridas por su acompañante mantienen en alerta a la ciudad, mientras los familiares reclaman las grabaciones de cámaras de seguridad como elemento determinante para identificar al conductor...</t>
+          <t>¿Qué sucedió en el ataque de tres sicarios ocurrido en una discoteca de Riohacha?</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Sobre la entrega de transferencias monetarias condicionadas de Jóvenes en Paz</t>
+          <t>Así fue la participación de los jóvenes en el primer Fest de las Oportunidades del año</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Prosperidad Social</t>
+          <t>SDIS - Juventud</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -8697,7 +8697,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -8712,12 +8712,12 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>https://prosperidadsocial.gov.co/Noticias/sobre-la-entrega-de-transferencias-monetarias-condicionadas-de-jovenes-en-paz/</t>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#9690ed7762</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>Bogotá D.C., 27 de marzo de 2026. Prosperidad Social informa a los participantes del programa Jóvenes en Paz que se adelanta la última etapa del procedimiento para disponer de los recursos de los próximos ciclos del año. En consecuencia: La entrega...</t>
+          <t>•El primer Fest de las Oportunidades 2026 reunió a más de 130 jóvenes en Usme, conectándolos con oferta en empleo, educación, emprendimiento y bienestar. •Más de 20 entidades y aliados participaron acercando oportunidades reales y orientación...</t>
         </is>
       </c>
     </row>
@@ -8729,101 +8729,101 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Continúa la búsqueda de cuatro jóvenes desaparecidos en Coromoro, Santander</t>
+          <t>Conductor atropelló y mató a un joven en Bogotá tras invadir el carril exclusivo de Transmilenio</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Protección</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/mas-regiones/buscan-a-cuatro-jovenes-desaparecidos-en-coromoro-santander-noticias-hoy/</t>
+          <t>https://www.infobae.com/colombia/2026/03/28/conductor-atropello-y-mato-a-un-joven-en-bogota-tras-invadir-el-carril-exclusivo-de-transmilenio/</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>Inicialmente eran seis los reportados como desaparecidos.</t>
+          <t>La muerte de Juan Sebastián Triviño y las lesiones sufridas por su acompañante mantienen en alerta a la ciudad, mientras los familiares reclaman las grabaciones de cámaras de seguridad como elemento determinante para identificar al conductor...</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>La historia de Luis Fernando Hostia y la meta de abrir caminos a personas con discapacidad</t>
+          <t>Sobre la entrega de transferencias monetarias condicionadas de Jóvenes en Paz</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Prosperidad Social</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/mas-regiones/la-historia-de-luis-fernando-hostia-y-la-meta-de-romper-barreras-a-personas-con-discapacidad/</t>
+          <t>https://prosperidadsocial.gov.co/Noticias/sobre-la-entrega-de-transferencias-monetarias-condicionadas-de-jovenes-en-paz/</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>Desde San Sebastián de Buenavista, un joven en condición de discapacidad rompió décadas de barreras educativas.</t>
+          <t>Bogotá D.C., 27 de marzo de 2026. Prosperidad Social informa a los participantes del programa Jóvenes en Paz que se adelanta la última etapa del procedimiento para disponer de los recursos de los próximos ciclos del año. En consecuencia: La entrega...</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Lo que se sabe de la muerte de joven dentro de Univalle; hay varias preguntas</t>
+          <t>Continúa la búsqueda de cuatro jóvenes desaparecidos en Coromoro, Santander</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -8838,12 +8838,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Protección</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -8853,24 +8853,24 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/cali/lo-que-se-sabe-de-la-muerte-de-joven-dentro-de-univalle-hay-varias-preguntas/</t>
+          <t>https://www.elespectador.com/colombia/mas-regiones/buscan-a-cuatro-jovenes-desaparecidos-en-coromoro-santander-noticias-hoy/</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>El caso ocurrió durante el fin de semana en la sede Meléndez de la Universidad del Valle, en Cali. La Secretaría de Movilidad se pronunció.</t>
+          <t>Inicialmente eran seis los reportados como desaparecidos.</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Buscan a joven que desapareció en río Lebrija en Santander en medio de fuertes lluvias</t>
+          <t>La historia de Luis Fernando Hostia y la meta de abrir caminos a personas con discapacidad</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -8885,7 +8885,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -8900,24 +8900,24 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/buscan-a-joven-que-desaparecio-en-rio-lebrija-en-santander-en-medio-de-fuertes-lluvias/</t>
+          <t>https://www.elespectador.com/colombia/mas-regiones/la-historia-de-luis-fernando-hostia-y-la-meta-de-romper-barreras-a-personas-con-discapacidad/</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>Un joven de 24 años desapareció en el río Lebrija tras ser arrastrado por corriente. Las lluvias dejan más de 140 familias damnificadas.</t>
+          <t>Desde San Sebastián de Buenavista, un joven en condición de discapacidad rompió décadas de barreras educativas.</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Balacera en Barranquilla dejó tres personas heridas y tres capturadas</t>
+          <t>Lo que se sabe de la muerte de joven dentro de Univalle; hay varias preguntas</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -8937,7 +8937,7 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Barranquilla</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
@@ -8947,34 +8947,34 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/barranquilla/balacera-en-barranquilla-dejo-tres-personas-heridas-y-tres-capturadas/</t>
+          <t>https://www.elespectador.com/colombia/cali/lo-que-se-sabe-de-la-muerte-de-joven-dentro-de-univalle-hay-varias-preguntas/</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>Una balacera, al parecer entre miembros de Pepes y Costeños, dejó tres heridos y tres capturados, entre ellos un menor de edad.</t>
+          <t>El caso ocurrió durante el fin de semana en la sede Meléndez de la Universidad del Valle, en Cali. La Secretaría de Movilidad se pronunció.</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Insólito pedido de familia de David Acosta luego de que el joven apareciera con vida en Bogotá</t>
+          <t>Buscan a joven que desapareció en río Lebrija en Santander en medio de fuertes lluvias</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Pulzo</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -8984,50 +8984,54 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>https://www.pulzo.com/nacion/bogota/caso-david-acosta-familia-pide-cerrar-investigacion-falsa-desaparicion-PP5103111</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr"/>
+          <t>https://www.elespectador.com/colombia/buscan-a-joven-que-desaparecio-en-rio-lebrija-en-santander-en-medio-de-fuertes-lluvias/</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>Un joven de 24 años desapareció en el río Lebrija tras ser arrastrado por corriente. Las lluvias dejan más de 140 familias damnificadas.</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Colombia tendrá más viejos que jóvenes a partir de esta fecha; hay alerta por las pensiones</t>
+          <t>Balacera en Barranquilla dejó tres personas heridas y tres capturadas</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Pulzo</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Barranquilla</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
@@ -9037,72 +9041,72 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>https://www.pulzo.com/economia/colombia-tendra-mas-viejos-que-jovenes-partir-esta-fecha-hay-alerta-PP5100998A</t>
-        </is>
-      </c>
-      <c r="I186" t="inlineStr"/>
+          <t>https://www.elespectador.com/colombia/barranquilla/balacera-en-barranquilla-dejo-tres-personas-heridas-y-tres-capturadas/</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>Una balacera, al parecer entre miembros de Pepes y Costeños, dejó tres heridos y tres capturados, entre ellos un menor de edad.</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Adolescente de 14 años murió en riña entre menores de edad fuera de un colegio en Cali</t>
+          <t>Insólito pedido de familia de David Acosta luego de que el joven apareciera con vida en Bogotá</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Pulzo</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/cali/adolescente-de-14-anos-murio-en-rina-entre-menores-de-edad-fuera-de-un-colegio-en-cali/</t>
-        </is>
-      </c>
-      <c r="I187" t="inlineStr">
-        <is>
-          <t>Adolescente de 14 años murió en riña entre menores afuera de un colegio en Cali. ¿Qué dicen las autoridades?</t>
-        </is>
-      </c>
+          <t>https://www.pulzo.com/nacion/bogota/caso-david-acosta-familia-pide-cerrar-investigacion-falsa-desaparicion-PP5103111</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Mafe Carrascal explicó por qué la bancada del Pacto Histórico por Bogotá no asistió a encuentro con el alcalde Carlos Fernando Galán</t>
+          <t>Colombia tendrá más viejos que jóvenes a partir de esta fecha; hay alerta por las pensiones</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Pulzo</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -9112,39 +9116,35 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/03/17/mafe-carrascal-explico-por-que-la-bancada-del-pacto-historico-por-bogota-no-asistio-a-encuentro-con-el-alcalde-carlos-fernando-galan/</t>
-        </is>
-      </c>
-      <c r="I188" t="inlineStr">
-        <is>
-          <t>La representante indicó que la reunión se realizaría a puerta cerrada y que esta decisión contradice los intereses de su partido. Además, afirmó que al gobierno local le falta implementar políticas dirigidas a los jóvenes y a la prevención de...</t>
-        </is>
-      </c>
+          <t>https://www.pulzo.com/economia/colombia-tendra-mas-viejos-que-jovenes-partir-esta-fecha-hay-alerta-PP5100998A</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Asesinan a joven de 15 años en Cartagena; su padre resultó herido al intentar defenderlo</t>
+          <t>Adolescente de 14 años murió en riña entre menores de edad fuera de un colegio en Cali</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -9159,7 +9159,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Seguridad</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -9174,71 +9174,71 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/asesinan-a-menor-de-15-anos-en-cartagena-su-padre-resulto-herido-al-intentar-defenderlo/</t>
+          <t>https://www.elespectador.com/colombia/cali/adolescente-de-14-anos-murio-en-rina-entre-menores-de-edad-fuera-de-un-colegio-en-cali/</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>El presunto homicida ya fue localizado y detenido.</t>
+          <t>Adolescente de 14 años murió en riña entre menores afuera de un colegio en Cali. ¿Qué dicen las autoridades?</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Hallan el cuerpo de una adolescente en vivienda de Sahagún, Córdoba; autoridades investigan</t>
+          <t>Mafe Carrascal explicó por qué la bancada del Pacto Histórico por Bogotá no asistió a encuentro con el alcalde Carlos Fernando Galán</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/mas-regiones/hallan-el-cuerpo-de-una-menor-en-una-vivienda-de-sahagun-cordoba-autoridades-investigan/</t>
+          <t>https://www.infobae.com/colombia/2026/03/17/mafe-carrascal-explico-por-que-la-bancada-del-pacto-historico-por-bogota-no-asistio-a-encuentro-con-el-alcalde-carlos-fernando-galan/</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>En lo que va de este año, este sería el tercer caso de una mujer asesinada en el municipio y el cuarto en el departamento.</t>
+          <t>La representante indicó que la reunión se realizaría a puerta cerrada y que esta decisión contradice los intereses de su partido. Además, afirmó que al gobierno local le falta implementar políticas dirigidas a los jóvenes y a la prevención de...</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Dos jóvenes fueron detenidos por presunta extorsión en Santo Tomás, Atlántico</t>
+          <t>Asesinan a joven de 15 años en Cartagena; su padre resultó herido al intentar defenderlo</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -9258,7 +9258,7 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
@@ -9268,44 +9268,44 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/mas-regiones/dos-jovenes-fueron-detenidos-por-presunta-extorsion-en-santo-tomas-atlantico/</t>
+          <t>https://www.elespectador.com/colombia/asesinan-a-menor-de-15-anos-en-cartagena-su-padre-resulto-herido-al-intentar-defenderlo/</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>La investigación señala que los implicados habrían intimidado a un conductor de furgón.</t>
+          <t>El presunto homicida ya fue localizado y detenido.</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Con $86 mil millones de regalías, Bolívar construirá universidad en Montes de María y otros dos proyectos educativos</t>
+          <t>Hallan el cuerpo de una adolescente en vivienda de Sahagún, Córdoba; autoridades investigan</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Las2orillas</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
@@ -9315,44 +9315,44 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>https://www.las2orillas.co/con-86-mil-millones-de-regalias-bolivar-construira-universidad-en-montes-de-maria-y-otros-dos-proyectos-educativos/</t>
+          <t>https://www.elespectador.com/colombia/mas-regiones/hallan-el-cuerpo-de-una-menor-en-una-vivienda-de-sahagun-cordoba-autoridades-investigan/</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>Los proyectos impulsados por Yamil Arana buscan, entre otras cosas, abrir más de 4 mil cupos para jóvenes de una región que durante años fue escenario de conflictoEl artículoCon $86 mil millones de regalías, Bolívar construirá universidad en Montes...</t>
+          <t>En lo que va de este año, este sería el tercer caso de una mujer asesinada en el municipio y el cuarto en el departamento.</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Nuevo giro en el caso de Tatiana Hernández, joven desaparecida en Cartagena: la buscan en el mar</t>
+          <t>Dos jóvenes fueron detenidos por presunta extorsión en Santo Tomás, Atlántico</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Pulzo</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Protección</t>
+          <t>Seguridad</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Cartagena</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
@@ -9362,104 +9362,104 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>https://www.pulzo.com/nacion/caso-tatiana-hernandez-da-giro-autoridades-intensifican-busqueda-mar-PP5091130</t>
-        </is>
-      </c>
-      <c r="I193" t="inlineStr"/>
+          <t>https://www.elespectador.com/colombia/mas-regiones/dos-jovenes-fueron-detenidos-por-presunta-extorsion-en-santo-tomas-atlantico/</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>La investigación señala que los implicados habrían intimidado a un conductor de furgón.</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Prosperidad Social responde a inquietudes sobre Renta Joven</t>
+          <t>Con $86 mil millones de regalías, Bolívar construirá universidad en Montes de María y otros dos proyectos educativos</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Prosperidad Social</t>
+          <t>Las2orillas</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>https://prosperidadsocial.gov.co/Noticias/prosperidad-social-responde-a-inquietudes-sobre-renta-joven/</t>
+          <t>https://www.las2orillas.co/con-86-mil-millones-de-regalias-bolivar-construira-universidad-en-montes-de-maria-y-otros-dos-proyectos-educativos/</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>Bogotá D. C, 4 de marzo de 2026. Prosperidad Social se permite aclarar a la ciudadanía y, especialmente, a los participantes de Renta Joven algunas dudas e inquietudes que han expresado los beneficiarios en las redes sociales. Prosperidad Social...</t>
+          <t>Los proyectos impulsados por Yamil Arana buscan, entre otras cosas, abrir más de 4 mil cupos para jóvenes de una región que durante años fue escenario de conflictoEl artículoCon $86 mil millones de regalías, Bolívar construirá universidad en Montes...</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Maratón por las generaciones atendió a más de 38.000 jóvenes y personas mayores beneficiarias de Prosperidad Social</t>
+          <t>Nuevo giro en el caso de Tatiana Hernández, joven desaparecida en Cartagena: la buscan en el mar</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Prosperidad Social</t>
+          <t>Pulzo</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Protección</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Cartagena</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>https://prosperidadsocial.gov.co/Noticias/maraton-por-las-generaciones-atendio-a-mas-de-38-000-jovenes-y-personas-mayores-beneficiarias-de-prosperidad-social/</t>
-        </is>
-      </c>
-      <c r="I195" t="inlineStr">
-        <is>
-          <t>Durante 38 horas continuas, se resolvieron inquietudes y dudas a beneficiarias y beneficiarios de los programas Renta Joven y Colombia Mayor. Nueve de cada 10 personas afirmaron haber recibido información clara y efectiva para resolver sus...</t>
-        </is>
-      </c>
+          <t>https://www.pulzo.com/nacion/caso-tatiana-hernandez-da-giro-autoridades-intensifican-busqueda-mar-PP5091130</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -9469,42 +9469,42 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Joven rompió el silencio y reveló desgarradores detalles de los feminicidios más brutales del Valle del Cauca</t>
+          <t>Prosperidad Social responde a inquietudes sobre Renta Joven</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Las2orillas</t>
+          <t>Prosperidad Social</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>https://www.las2orillas.co/joven-rompio-el-silencio-y-revelo-desgarradores-detalles-de-los-feminicidios-mas-brutales-del-valle-del-cauca/</t>
+          <t>https://prosperidadsocial.gov.co/Noticias/prosperidad-social-responde-a-inquietudes-sobre-renta-joven/</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>Mientras la Fiscalía la señala de disparar contra las víctimas, Angy Pérez asegura que fue obligada a desmembrar los cuerpos bajo la amenaza de perder a su bebéEl artículoJoven rompió el silencio y reveló desgarradores detalles de los feminicidios...</t>
+          <t>Bogotá D. C, 4 de marzo de 2026. Prosperidad Social se permite aclarar a la ciudadanía y, especialmente, a los participantes de Renta Joven algunas dudas e inquietudes que han expresado los beneficiarios en las redes sociales. Prosperidad Social...</t>
         </is>
       </c>
     </row>
@@ -9516,7 +9516,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Colombia Mayor y Renta Joven: Prosperidad Social realizará la Maratón por las Generaciones</t>
+          <t>Maratón por las generaciones atendió a más de 38.000 jóvenes y personas mayores beneficiarias de Prosperidad Social</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -9531,7 +9531,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Protección</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -9546,12 +9546,12 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>https://prosperidadsocial.gov.co/Noticias/colombia-mayor-y-renta-joven-prosperidad-social-realizara-la-maraton-por-las-generaciones/</t>
+          <t>https://prosperidadsocial.gov.co/Noticias/maraton-por-las-generaciones-atendio-a-mas-de-38-000-jovenes-y-personas-mayores-beneficiarias-de-prosperidad-social/</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>Se trata de una jornada continua de atención telefónica, en la que se resolverán inquietudes que tengan beneficiarias y beneficiarios de estos dos programas de la entidad. El canal telefónico tendrá atención continua por más de 36 horas, mientras...</t>
+          <t>Durante 38 horas continuas, se resolvieron inquietudes y dudas a beneficiarias y beneficiarios de los programas Renta Joven y Colombia Mayor. Nueve de cada 10 personas afirmaron haber recibido información clara y efectiva para resolver sus...</t>
         </is>
       </c>
     </row>
@@ -9563,12 +9563,12 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Así fue la despedida de Iván Zuleta a su sobrina Daniela: la joven fue encontrada sin signos vitales en su habitación</t>
+          <t>Joven rompió el silencio y reveló desgarradores detalles de los feminicidios más brutales del Valle del Cauca</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Las2orillas</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Valledupar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
@@ -9593,29 +9593,29 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/03/11/asi-fue-la-despedida-de-ivan-zuleta-a-su-sobrina-daniela-que-habria-sido-encontrada-sin-signos-vitales-en-su-habitacion/</t>
+          <t>https://www.las2orillas.co/joven-rompio-el-silencio-y-revelo-desgarradores-detalles-de-los-feminicidios-mas-brutales-del-valle-del-cauca/</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>La partida de la joven Zuleta Gnecco, hija de Fabián Zuleta y nieta de Fabio Zuleta, ha conmovido al mundo del vallenato, reuniendo a familiares y músicos icónicos para despedirla en Valledupar con emotivas muestras de cariño</t>
+          <t>Mientras la Fiscalía la señala de disparar contra las víctimas, Angy Pérez asegura que fue obligada a desmembrar los cuerpos bajo la amenaza de perder a su bebéEl artículoJoven rompió el silencio y reveló desgarradores detalles de los feminicidios...</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Jóvenes en San Cristóbal inician su formación en servicio para el sector de la gastronomía</t>
+          <t>Colombia Mayor y Renta Joven: Prosperidad Social realizará la Maratón por las Generaciones</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>SDIS - Juventud</t>
+          <t>Prosperidad Social</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -9625,7 +9625,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Protección</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -9640,71 +9640,71 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#79ade27adc</t>
+          <t>https://prosperidadsocial.gov.co/Noticias/colombia-mayor-y-renta-joven-prosperidad-social-realizara-la-maraton-por-las-generaciones/</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>•24 chicos y chicas iniciaron su camino en la Academia Ñam, en donde se formarán en servicio a la mesa para mejorar sus oportunidades de empleabilidad en el sector de la gastronomía. •La inducción, que tuvo lugar en el Centro de Desarrollo...</t>
+          <t>Se trata de una jornada continua de atención telefónica, en la que se resolverán inquietudes que tengan beneficiarias y beneficiarios de estos dos programas de la entidad. El canal telefónico tendrá atención continua por más de 36 horas, mientras...</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>La Academia Ñam llega a San Cristóbal con oportunidades para los jóvenes interesados en el sector de la gastronomía</t>
+          <t>Así fue la despedida de Iván Zuleta a su sobrina Daniela: la joven fue encontrada sin signos vitales en su habitación</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>SDIS - Juventud</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Valledupar</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#1e64cd90aa</t>
+          <t>https://www.infobae.com/colombia/2026/03/11/asi-fue-la-despedida-de-ivan-zuleta-a-su-sobrina-daniela-que-habria-sido-encontrada-sin-signos-vitales-en-su-habitacion/</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>•El Distrito, en alianza con la Fundación Gastronomía Social, lanzan una nueva convocatoria dirigida a jóvenes de 18 a 30 años interesados en formarse en servicio para el sector de la gastronomía. •Esta formación gratuita ofrece capacitación a...</t>
+          <t>La partida de la joven Zuleta Gnecco, hija de Fabián Zuleta y nieta de Fabio Zuleta, ha conmovido al mundo del vallenato, reuniendo a familiares y músicos icónicos para despedirla en Valledupar con emotivas muestras de cariño</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>El deporte abrió la puerta a nuevas oportunidades y conexión para los jóvenes de Bogotá</t>
+          <t>Jóvenes en San Cristóbal inician su formación en servicio para el sector de la gastronomía</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -9719,7 +9719,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Cultura y deporte</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -9734,34 +9734,34 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#8b36ede0c2</t>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#79ade27adc</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>• En la localidad de Kennedy se realizó una jornada deportiva con Futsala Colombia, que acercó a los jóvenes la oferta integral de servicios sociales, digitales y educativos en territorio. • En Jóvenes con Oportunidades, más de 18.000 jóvenes han...</t>
+          <t>•24 chicos y chicas iniciaron su camino en la Academia Ñam, en donde se formarán en servicio a la mesa para mejorar sus oportunidades de empleabilidad en el sector de la gastronomía. •La inducción, que tuvo lugar en el Centro de Desarrollo...</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Abre 320 becas a jóvenes con proyectos en sus comunidades o entornos, ¿cómo participar?</t>
+          <t>Bogotá presenta estudio que analiza los factores asociados a la vinculación de adolescentes a conductas punibles</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>SDIS - Juventud</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -9781,71 +9781,71 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/mas-regiones/abre-320-becas-a-jovenes-con-proyectos-en-sus-comunidades-o-entornos-como-participar/</t>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#fb504c6e8d</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>Abren becas para jóvenes en Medellín, Santa Marta, Cartagena y Bogotá. Tendrán formación, mentorías y acceso a redes de liderazgo.</t>
+          <t>• La vinculación de adolescentes a conductas punibles no responde a una sola causa, sino a la convergencia de factores estructurales, familiares, territoriales y personales que requieren respuestas integrales y no únicamente punitivas. • El consumo...</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>La primera guardia afro urbana liderada por mujeres surge en Cali</t>
+          <t>La Academia Ñam llega a San Cristóbal con oportunidades para los jóvenes interesados en el sector de la gastronomía</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>SDIS - Juventud</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/cali/la-primera-guardia-afro-urbana-liderada-por-mujeres-surge-en-cali/</t>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#1e64cd90aa</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>En Llano Verde, mujeres desplazadas crearon la primera guardia afro urbana del país para prevenir violencia y proteger a jóvenes.</t>
+          <t>•El Distrito, en alianza con la Fundación Gastronomía Social, lanzan una nueva convocatoria dirigida a jóvenes de 18 a 30 años interesados en formarse en servicio para el sector de la gastronomía. •Esta formación gratuita ofrece capacitación a...</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Bogotá fortalece el proceso de preinscripción de Jóvenes con Oportunidades 2026 y habilita nuevo enlace</t>
+          <t>El deporte abrió la puerta a nuevas oportunidades y conexión para los jóvenes de Bogotá</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -9860,7 +9860,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Cultura y deporte</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -9875,24 +9875,24 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#6c31bba0c9</t>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#8b36ede0c2</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>•El Distrito habilitó un nuevo enlace mejorado para garantizar una experiencia más ágil, estable y segura en la convocatoria 2026 de Jóvenes con Oportunidades. •Las y los jóvenes entre 14 y 28 años que vivan en Bogotá y estén clasificados en Sisbén...</t>
+          <t>• En la localidad de Kennedy se realizó una jornada deportiva con Futsala Colombia, que acercó a los jóvenes la oferta integral de servicios sociales, digitales y educativos en territorio. • En Jóvenes con Oportunidades, más de 18.000 jóvenes han...</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Aumenta el número de desaparecidos en Córdoba, dos jóvenes arrastrados por un arroyo</t>
+          <t>Abre 320 becas a jóvenes con proyectos en sus comunidades o entornos, ¿cómo participar?</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -9907,96 +9907,96 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Protección</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/mas-regiones/dos-campesinos-en-cordoba-desaparecen-tras-intentar-cruzar-un-arroyo/</t>
+          <t>https://www.elespectador.com/colombia/mas-regiones/abre-320-becas-a-jovenes-con-proyectos-en-sus-comunidades-o-entornos-como-participar/</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>Dos jóvenes campesinos permanecen desaparecidos en Córdoba, luego de que una corriente los arrastrara en cuanto intentaban cruzar un arroyo</t>
+          <t>Abren becas para jóvenes en Medellín, Santa Marta, Cartagena y Bogotá. Tendrán formación, mentorías y acceso a redes de liderazgo.</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Bogotá abre convocatoria 2026 del programa Jóvenes con Oportunidades con más de 12.000 nuevos cupos</t>
+          <t>La primera guardia afro urbana liderada por mujeres surge en Cali</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>SDIS - Juventud</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#9a0f0687f3</t>
+          <t>https://www.elespectador.com/colombia/cali/la-primera-guardia-afro-urbana-liderada-por-mujeres-surge-en-cali/</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>• El Distrito abre estaconvocatoria de Jóvenes con Oportunidades con más de 8.000 nuevos cupos, en su primera etapa, para jóvenes entre 14 y 28 años de Bogotá, fortaleciendo su acceso a rutas de formación, acompañamiento psicosocial y transferencias...</t>
+          <t>En Llano Verde, mujeres desplazadas crearon la primera guardia afro urbana del país para prevenir violencia y proteger a jóvenes.</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Menores de edad mataron de 17 puñaladas a un hombre que iba de polizón en un camión de carga en la vía Bogotá-Villavicencio: quedó en video - Infobae</t>
+          <t>Bogotá fortalece el proceso de preinscripción de Jóvenes con Oportunidades 2026 y habilita nuevo enlace</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>SDIS - Juventud</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -10016,121 +10016,133 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAJBVV95cUxNYWQxNTA1UWhDOUtWS2dSWXNNQ19idDVRNXV4aktnZzFERmdBaFg0c2lrT2plR0tXcDN1dlFhd0J0Q1BUVmJEVU1YYTR3N0NtQUx2LTQ3amhNR2pNc0tvcjR6X1FfbkIwczFROFJTaFotclVpRGxId2h1eWtqbHMzSkNXc0JCeU1DWjkxOG5qekx4YjZGRlVVckdyX1gyT0luR2Nkd3ZQUTNFM1d1LUlvMzNSSGxiQUZ5V2pqT2E4WXhZWWRpY2JheDhpaWhwOTQwLThDWFlXU1p0N0lZVk5nSHdVZU8zWVlKNE9GTVJKaUxYTkxDMUt1MTF0NzN5MVUxXzBNUjZtZVJsWm9zMkNNdg?oc=5</t>
-        </is>
-      </c>
-      <c r="I207" t="inlineStr"/>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#6c31bba0c9</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>•El Distrito habilitó un nuevo enlace mejorado para garantizar una experiencia más ágil, estable y segura en la convocatoria 2026 de Jóvenes con Oportunidades. •Las y los jóvenes entre 14 y 28 años que vivan en Bogotá y estén clasificados en Sisbén...</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Menores de edad mataron de 17 puñaladas a un hombre que iba de polizón en un camión de carga en la vía Bogotá-Villavicencio: quedó en video - Infobae</t>
+          <t>Aumenta el número de desaparecidos en Córdoba, dos jóvenes arrastrados por un arroyo</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Protección</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAJBVV95cUxNYWQxNTA1UWhDOUtWS2dSWXNNQ19idDVRNXV4aktnZzFERmdBaFg0c2lrT2plR0tXcDN1dlFhd0J0Q1BUVmJEVU1YYTR3N0NtQUx2LTQ3amhNR2pNc0tvcjR6X1FfbkIwczFROFJTaFotclVpRGxId2h1eWtqbHMzSkNXc0JCeU1DWjkxOG5qekx4YjZGRlVVckdyX1gyT0luR2Nkd3ZQUTNFM1d1LUlvMzNSSGxiQUZ5V2pqT2E4WXhZWWRpY2JheDhpaWhwOTQwLThDWFlXU1p0N0lZVk5nSHdVZU8zWVlKNE9GTVJKaUxYTkxDMUt1MTF0NzN5MVUxXzBNUjZtZVJsWm9zMkNNdtIBqwJBVV95cUxPZnpNT2FPSmdUeFl0UmFScGh6MzVlYm9tVWhQekJjVTdRcHM2ZDlEbWFhVUJBX3dudVF2V01OaDdSRWN6c1FXV2thM0VJOHppRWhaWEVpbTVPOTVTd3RKcmJLT1NHa2MwVlR5SzE2TzlHM0RLS3k2VzFKRDdtaTd2M3RCNENTeXByY1BBTjR1SFE3STJQS3JBWURBRER1cTBKQmx2MVR6Sk5xYlpwbTdpNGRyWVBYdmkxTU9JaWNtRlZVM2JzTGtMQUhxaHFnUmVPQlNPbkNYWGlBX2ttc0Y4cjVzR0dVaFBER3lSMWxRZGVGVTRhTFZ6RE82ZzFKeWJnQ0U0bWlINmlXRE9KdUJvbzdpSEg1NURXMzZKeVNHWTd4b0puVldnbFlscw?oc=5</t>
-        </is>
-      </c>
-      <c r="I208" t="inlineStr"/>
+          <t>https://www.elespectador.com/colombia/mas-regiones/dos-campesinos-en-cordoba-desaparecen-tras-intentar-cruzar-un-arroyo/</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>Dos jóvenes campesinos permanecen desaparecidos en Córdoba, luego de que una corriente los arrastrara en cuanto intentaban cruzar un arroyo</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Jóvenes narraron el calvario sufrido cuando fueron víctimas de presunto abuso en la Universidad de Cartagena: “Causó un gran sangrado”</t>
+          <t>Bogotá abre convocatoria 2026 del programa Jóvenes con Oportunidades con más de 12.000 nuevos cupos</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>SDIS - Juventud</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Cartagena</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/02/02/jovenes-narraron-el-calvario-sufrido-cuando-fueron-victimas-de-presunto-abuso-en-la-universidad-de-cartagena-causo-un-gran-sangrado/</t>
-        </is>
-      </c>
-      <c r="I209" t="inlineStr"/>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#9a0f0687f3</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>• El Distrito abre estaconvocatoria de Jóvenes con Oportunidades con más de 8.000 nuevos cupos, en su primera etapa, para jóvenes entre 14 y 28 años de Bogotá, fortaleciendo su acceso a rutas de formación, acompañamiento psicosocial y transferencias...</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Bogotá abre nueva convocatoria de Academia Ñam para fortalecer la empleabilidad juvenil en el sector gastronómico</t>
+          <t>Menores de edad mataron de 17 puñaladas a un hombre que iba de polizón en un camión de carga en la vía Bogotá-Villavicencio: quedó en video - Infobae</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>SDIS - Juventud</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -10145,24 +10157,20 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#85a520b8bc</t>
-        </is>
-      </c>
-      <c r="I210" t="inlineStr">
-        <is>
-          <t>• La Secretaría Distrital de Integración Social, en alianza con la Fundación Gastronomía Social, abre una nueva convocatoria de Academia Ñam, un programa gratuito de formación y práctica laboral en servicio gastronómico dirigido a jóvenes de 18 a 30...</t>
-        </is>
-      </c>
+          <t>https://news.google.com/rss/articles/CBMikAJBVV95cUxNYWQxNTA1UWhDOUtWS2dSWXNNQ19idDVRNXV4aktnZzFERmdBaFg0c2lrT2plR0tXcDN1dlFhd0J0Q1BUVmJEVU1YYTR3N0NtQUx2LTQ3amhNR2pNc0tvcjR6X1FfbkIwczFROFJTaFotclVpRGxId2h1eWtqbHMzSkNXc0JCeU1DWjkxOG5qekx4YjZGRlVVckdyX1gyT0luR2Nkd3ZQUTNFM1d1LUlvMzNSSGxiQUZ5V2pqT2E4WXhZWWRpY2JheDhpaWhwOTQwLThDWFlXU1p0N0lZVk5nSHdVZU8zWVlKNE9GTVJKaUxYTkxDMUt1MTF0NzN5MVUxXzBNUjZtZVJsWm9zMkNNdg?oc=5</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Frustraron robo en un restaurante en Bosa, Bogotá: un hombre de 23 años y dos menores de edad fueron capturados</t>
+          <t>Menores de edad mataron de 17 puñaladas a un hombre que iba de polizón en un camión de carga en la vía Bogotá-Villavicencio: quedó en video - Infobae</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -10177,7 +10185,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Seguridad</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
@@ -10192,7 +10200,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/27/frustraron-robo-en-un-restaurante-en-bosa-bogota-un-hombre-de-23-anos-y-dos-menores-de-edad-fueron-capturados/</t>
+          <t>https://news.google.com/rss/articles/CBMikAJBVV95cUxNYWQxNTA1UWhDOUtWS2dSWXNNQ19idDVRNXV4aktnZzFERmdBaFg0c2lrT2plR0tXcDN1dlFhd0J0Q1BUVmJEVU1YYTR3N0NtQUx2LTQ3amhNR2pNc0tvcjR6X1FfbkIwczFROFJTaFotclVpRGxId2h1eWtqbHMzSkNXc0JCeU1DWjkxOG5qekx4YjZGRlVVckdyX1gyT0luR2Nkd3ZQUTNFM1d1LUlvMzNSSGxiQUZ5V2pqT2E4WXhZWWRpY2JheDhpaWhwOTQwLThDWFlXU1p0N0lZVk5nSHdVZU8zWVlKNE9GTVJKaUxYTkxDMUt1MTF0NzN5MVUxXzBNUjZtZVJsWm9zMkNNdtIBqwJBVV95cUxPZnpNT2FPSmdUeFl0UmFScGh6MzVlYm9tVWhQekJjVTdRcHM2ZDlEbWFhVUJBX3dudVF2V01OaDdSRWN6c1FXV2thM0VJOHppRWhaWEVpbTVPOTVTd3RKcmJLT1NHa2MwVlR5SzE2TzlHM0RLS3k2VzFKRDdtaTd2M3RCNENTeXByY1BBTjR1SFE3STJQS3JBWURBRER1cTBKQmx2MVR6Sk5xYlpwbTdpNGRyWVBYdmkxTU9JaWNtRlZVM2JzTGtMQUhxaHFnUmVPQlNPbkNYWGlBX2ttc0Y4cjVzR0dVaFBER3lSMWxRZGVGVTRhTFZ6RE82ZzFKeWJnQ0U0bWlINmlXRE9KdUJvbzdpSEg1NURXMzZKeVNHWTd4b0puVldnbFlscw?oc=5</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -10200,17 +10208,17 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Alerta en Tolima: ya son 4 los muertos por fiebre amarilla en 2026, entre ellos un menor de edad</t>
+          <t>Jóvenes narraron el calvario sufrido cuando fueron víctimas de presunto abuso en la Universidad de Cartagena: “Causó un gran sangrado”</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -10220,12 +10228,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Cartagena</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
@@ -10235,7 +10243,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/nacion/alerta-en-tolima-ya-son-4-los-muertos-por-fiebre-amarilla-en-2026-entre-ellos-un-menor-de-edad-rg10</t>
+          <t>https://www.infobae.com/colombia/2026/02/02/jovenes-narraron-el-calvario-sufrido-cuando-fueron-victimas-de-presunto-abuso-en-la-universidad-de-cartagena-causo-un-gran-sangrado/</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
@@ -10243,12 +10251,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Distrito Joven acompañó a más de 50 mil jóvenes en la construcción de sus proyectos de vida durante 2025</t>
+          <t>Bogotá abre nueva convocatoria de Academia Ñam para fortalecer la empleabilidad juvenil en el sector gastronómico</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -10263,7 +10271,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -10278,24 +10286,24 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#729a4b8e04</t>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#85a520b8bc</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>• Durante 2025, la Subdirección para la Juventud acompañó a más de 50 mil jóvenes en Bogotá, fortaleciendo sus proyectos de vida a través de una atención integral. • Los servicios y estrategias implementados promovieron la inclusión social,...</t>
+          <t>• La Secretaría Distrital de Integración Social, en alianza con la Fundación Gastronomía Social, abre una nueva convocatoria de Academia Ñam, un programa gratuito de formación y práctica laboral en servicio gastronómico dirigido a jóvenes de 18 a 30...</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Radiografía de los ‘ninis’ en Colombia: 2,26 millones de jóvenes están desconectados del estudio y el empleo - Infobae</t>
+          <t>Frustraron robo en un restaurante en Bosa, Bogotá: un hombre de 23 años y dos menores de edad fueron capturados</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -10310,22 +10318,22 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Empleo</t>
+          <t>Seguridad</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxQQzU0U2tHY3lvTUVKRmR2SExOeUdySS0ycnZSVWd3MlhIQmJmYVZxNm9NNVZ2YU8wZ1MtcUJiOXRPLWZhWUNLcUtVdG1uUVVUd0VfYU5sQWVNSjlDVWdDUTc2ZG8yajJIUlk0bVJxTTR3clhjd0wwRl9wSTRSUlk0UnZtY2FZTWZ2QUhQbjJ1TkdibEw4YmU4YXNTMEJUeV85V0dfSzdUQ0hSSk5DbFdZUk5VV2dnaGdabHhVQ1p2bjlCTlVKNHJNV3NoNmQtcG9CUkZaMWVDVXZmWDFXSTIxVi00UdIB_gFBVV95cUxQQXJkUXE5UnM4ZVhIZHo3UFJuSU0xVllueWt3Unk2aC03YllYdDBfc0FvalRGMDNsWjBRNmZfNUV1bTlsbWM3dFlLOGNCajVqcXQ5Z2hVRzdROXlpTUdrWEtLdVNyaDFqRGlnckQ3OUhfTjVNVk53YklESGhMMlRCcUVkNFRYMS04RUUwR2hvdERISVdENVlydzZhOGpfaU1yX0xkSkg0S3laV3E2MVV1UHRDN05aRU1iMlBiS2lRcXNWYTdMTlhVTzI2VkJkeFZTXzhqbS1adkpFa1RiX2dBaDJDaWhVYXVsM1psSV9jWjZGdy1QUXJ1d0xCdUxMdw?oc=5</t>
+          <t>https://www.infobae.com/colombia/2026/01/27/frustraron-robo-en-un-restaurante-en-bosa-bogota-un-hombre-de-23-anos-y-dos-menores-de-edad-fueron-capturados/</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
@@ -10333,69 +10341,65 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Casas de Juventud lanzan nuevos Semilleros Distritales para potenciar el talento juvenil en Bogotá</t>
+          <t>Alerta en Tolima: ya son 4 los muertos por fiebre amarilla en 2026, entre ellos un menor de edad</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>SDIS - Juventud</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Cultura y deporte</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#f8686f5026</t>
-        </is>
-      </c>
-      <c r="I215" t="inlineStr">
-        <is>
-          <t>•Bogotá abre la convocatoria a semilleros gratuitos en artes, deporte y cultura urbana, dirigidos a jóvenes entre 14 y 28 años de todas las localidades, como una estrategia distrital para fortalecer la expresión, la participación y el desarrollo de...</t>
-        </is>
-      </c>
+          <t>https://www.bluradio.com/nacion/alerta-en-tolima-ya-son-4-los-muertos-por-fiebre-amarilla-en-2026-entre-ellos-un-menor-de-edad-rg10</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Estudio reveló las principales problemáticas que preocupan a los jóvenes en Colombia, previo a las elecciones de Congreso y Presidencia - Infobae</t>
+          <t>Distrito Joven acompañó a más de 50 mil jóvenes en la construcción de sus proyectos de vida durante 2025</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>SDIS - Juventud</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -10405,30 +10409,34 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwJBVV95cUxNYXdTSFVia3cwbnV6Y050TzB5M2JQckhpbDVVajdoRnZnZG1yTThKbVF0bFhsUWN0ZnFuM1h5M0VYWmxiUGZjaHN3WV85OFpwWlFaWkFkanlsSmcwNFhJQk5PTjJBZ3RXcTgzNHFCQU5qTGlUZlB3WTkxZmx3SVIwV05jblIwUFNNUUdBTkU2M2FZSHNlTUgyb2ZhZWsyMktyc0UtR2k2Z001NkUxZ01xSkxoei1uMUZqaGJfV0k2MWktaDVNRGtGOS1nNXlGTEdSZ1VSdEJGRDRkbkNPM3R1aURVbl9ZR3FYcC1aMkI4T0k4bDJaT0Jmb1dLNktqQVVOeHVpUGpkUGd3TmvSAaYCQVVfeXFMTl9Uc2p1OEVpYzZaLUFYOERNUjVQVjVSaHJtTEhhT1BibW1BMkVwQ0VVUFc3d2RsaWNtNHdTZm0tbDRlMHBPLWVES0Vyd3hKZHRQUmExYmVmaXNrZE5rTGhEWmd0YXQ5cjdPOGIyeVdEYUV5NHplUnFMX2pYWkRXdEFxbVB1UGhEOENhTWM3S2NCVnJQbDg4clVoSUhIWENVSUh1VE54MjZKUjF3OWdpUDZjdld4WU1BLTA2dWR2ZEwxQUpnLUNXS3JZZ2hWUkFQN2taQktacVNhM3NMOS1ZR1g2dkhmYmVmU0Q4Q0o2dWNCZUNMQnJsaDFjQlRXQUp5NUpEYllxWlhVQVVfbVlBdmVBa2RJRjVqNUNfTGxHMnFRaGhYMnN3?oc=5</t>
-        </is>
-      </c>
-      <c r="I216" t="inlineStr"/>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#729a4b8e04</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>• Durante 2025, la Subdirección para la Juventud acompañó a más de 50 mil jóvenes en Bogotá, fortaleciendo sus proyectos de vida a través de una atención integral. • Los servicios y estrategias implementados promovieron la inclusión social,...</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Menor de edad colombiano fue baleado frente a su escuela en Chicago, la familia exige justicia</t>
+          <t>Radiografía de los ‘ninis’ en Colombia: 2,26 millones de jóvenes están desconectados del estudio y el empleo - Infobae</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -10443,7 +10451,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Empleo</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -10458,7 +10466,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/14/menor-de-edad-colombiano-fue-baleado-frente-a-su-escuela-en-chicago-la-familia-exige-justicia/</t>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxQQzU0U2tHY3lvTUVKRmR2SExOeUdySS0ycnZSVWd3MlhIQmJmYVZxNm9NNVZ2YU8wZ1MtcUJiOXRPLWZhWUNLcUtVdG1uUVVUd0VfYU5sQWVNSjlDVWdDUTc2ZG8yajJIUlk0bVJxTTR3clhjd0wwRl9wSTRSUlk0UnZtY2FZTWZ2QUhQbjJ1TkdibEw4YmU4YXNTMEJUeV85V0dfSzdUQ0hSSk5DbFdZUk5VV2dnaGdabHhVQ1p2bjlCTlVKNHJNV3NoNmQtcG9CUkZaMWVDVXZmWDFXSTIxVi00UdIB_gFBVV95cUxQQXJkUXE5UnM4ZVhIZHo3UFJuSU0xVllueWt3Unk2aC03YllYdDBfc0FvalRGMDNsWjBRNmZfNUV1bTlsbWM3dFlLOGNCajVqcXQ5Z2hVRzdROXlpTUdrWEtLdVNyaDFqRGlnckQ3OUhfTjVNVk53YklESGhMMlRCcUVkNFRYMS04RUUwR2hvdERISVdENVlydzZhOGpfaU1yX0xkSkg0S3laV3E2MVV1UHRDN05aRU1iMlBiS2lRcXNWYTdMTlhVTzI2VkJkeFZTXzhqbS1adkpFa1RiX2dBaDJDaWhVYXVsM1psSV9jWjZGdy1QUXJ1d0xCdUxMdw?oc=5</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
@@ -10466,55 +10474,59 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>El particular castigo de Policía en Barranquilla a un grupo de jóvenes quedó en video: “El cuerpo sufre”</t>
+          <t>Casas de Juventud lanzan nuevos Semilleros Distritales para potenciar el talento juvenil en Bogotá</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>SDIS - Juventud</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Seguridad</t>
+          <t>Cultura y deporte</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Barranquilla</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/09/el-particular-castigo-de-policia-en-barranquilla-a-un-grupo-de-jovenes-quedo-en-video-el-cuerpo-sufre/</t>
-        </is>
-      </c>
-      <c r="I218" t="inlineStr"/>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#f8686f5026</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>•Bogotá abre la convocatoria a semilleros gratuitos en artes, deporte y cultura urbana, dirigidos a jóvenes entre 14 y 28 años de todas las localidades, como una estrategia distrital para fortalecer la expresión, la participación y el desarrollo de...</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Aumenta a 1.419 el número de lesionados por pólvora en Colombia; 428 son menores de edad - Infobae</t>
+          <t>Estudio reveló las principales problemáticas que preocupan a los jóvenes en Colombia, previo a las elecciones de Congreso y Presidencia - Infobae</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -10544,7 +10556,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxOY1FwS0xiWWVaYl9saTQ5X0xRYnVoR0lwNE5XYUVaaUl3LW8yN0hEZGFnckI5VVlrVnBPSFJpeDNkU1JIaC01dVJVdFJYbEtSVTFXRTBCdTFDSDJ6TXZjc2t5N0t0cVFUY2JGbGZ1NDB5R1FJVG1RX25hREVIMjZlYktrdHc2QUFiZXNQTXFGZk9zeWNJRUl1aWNCbG9OXzZRQVA2dFFUZ1J3UnJrZzU4Qnk5TVBMajBPenJOU0ZBekNheEl2SkV3QVRUc9IB5gFBVV95cUxQeDZfb0gzZm9CTTRpYWx1ZTBielQ1TVgtaHNBOXRVRjBDcVd2V3M2anR3VTJaLU8zUEFkbEJkdDFEcHdHQUlpNGVORDZXV1Jxdzl4YmdPN3F1bk10ODZ1MnpOUjVSRTZscUUzYl80MDVpaHROOXdBNlhoQkFFR3RyVVJ1MWw1WTVZZVcwWnZ6THBEYWkxR1hEMTQzRGIzRWJvWlVUOFFBU2duZE5MRnRoRnQyZDl0ajd2SEpUVVM5ZW5POEpzLUZIcTV1c3RaaHlvanRUcG1oU3REVFVVQk5xTnhuLWk1UQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwJBVV95cUxNYXdTSFVia3cwbnV6Y050TzB5M2JQckhpbDVVajdoRnZnZG1yTThKbVF0bFhsUWN0ZnFuM1h5M0VYWmxiUGZjaHN3WV85OFpwWlFaWkFkanlsSmcwNFhJQk5PTjJBZ3RXcTgzNHFCQU5qTGlUZlB3WTkxZmx3SVIwV05jblIwUFNNUUdBTkU2M2FZSHNlTUgyb2ZhZWsyMktyc0UtR2k2Z001NkUxZ01xSkxoei1uMUZqaGJfV0k2MWktaDVNRGtGOS1nNXlGTEdSZ1VSdEJGRDRkbkNPM3R1aURVbl9ZR3FYcC1aMkI4T0k4bDJaT0Jmb1dLNktqQVVOeHVpUGpkUGd3TmvSAaYCQVVfeXFMTl9Uc2p1OEVpYzZaLUFYOERNUjVQVjVSaHJtTEhhT1BibW1BMkVwQ0VVUFc3d2RsaWNtNHdTZm0tbDRlMHBPLWVES0Vyd3hKZHRQUmExYmVmaXNrZE5rTGhEWmd0YXQ5cjdPOGIyeVdEYUV5NHplUnFMX2pYWkRXdEFxbVB1UGhEOENhTWM3S2NCVnJQbDg4clVoSUhIWENVSUh1VE54MjZKUjF3OWdpUDZjdld4WU1BLTA2dWR2ZEwxQUpnLUNXS3JZZ2hWUkFQN2taQktacVNhM3NMOS1ZR1g2dkhmYmVmU0Q4Q0o2dWNCZUNMQnJsaDFjQlRXQUp5NUpEYllxWlhVQVVfbVlBdmVBa2RJRjVqNUNfTGxHMnFRaGhYMnN3?oc=5</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
@@ -10552,12 +10564,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Gobierno condonará créditos del Icetex a más de mil jóvenes en Colombia: quiénes se beneficiarán - Infobae</t>
+          <t>Menor de edad colombiano fue baleado frente a su escuela en Chicago, la familia exige justicia</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -10572,7 +10584,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
@@ -10587,7 +10599,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxOZlVSRmszbERPaGNNNjhFRXY3VGVlUjc0eXo5R002RDZTbk15NWlUb1pLeWtWdmtObV9fY2ZxUmQ3cHNacWJoMExhZVZDRjlJM0lYZ2VfUVJOTEJnOXhGeXhtOFdlX3BmdFZTWXNJWHpXSDJsREdSaXJHSmFfY0RCcV8xSFVTLThuS1M4eUwxYTMxdWU2WTY3YUVTaWtLWHJFRUhlM0EtQzFNdDQwNy1wU2NyMDIzSk5rZGI4ZExtcmx1b2R2d01DNzdZT29LanFzXzBaNjluZ0rSAfMBQVVfeXFMT3pmVy1QSHJLaTJmREJmLVNLano0XzdpeW1VemRocGF5eHBVZktPRnNkTnNBUElFMDk1UUQ4MTZRNENCVWpZQVhTRmNrV1dwbDhCQnFvemZKTmZyT2cwdV96a2xOUWZDZEloWEFKcjJ2QkJsX0h3bFZDTkNRNGJOY1U5UGZaN0x6YU1EQlN5ZlFLb0hYQkM1MDdKNWl5TS1OcVNYWHRGXzl5NFp1WnQ2YWJqcWZzZDlDTk5FQ19Sa2lZOXRpOEJ4LV9DUnVOenhkQ3FJUGhkZkExNkNOYlV2Z21iLUQxUmF0eDJ5c3NyekcxTFlF?oc=5</t>
+          <t>https://www.infobae.com/colombia/2026/01/14/menor-de-edad-colombiano-fue-baleado-frente-a-su-escuela-en-chicago-la-familia-exige-justicia/</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
@@ -10595,153 +10607,141 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Más de 40 jóvenes de Bogotá fueron reconocidos por su talento, creatividad y liderazgo en la Semana de la Juventud y la Semana Andina 2025</t>
+          <t>El particular castigo de Policía en Barranquilla a un grupo de jóvenes quedó en video: “El cuerpo sufre”</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>SDIS - Juventud</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Cultura y deporte</t>
+          <t>Seguridad</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Barranquilla</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#c68de3a13a</t>
-        </is>
-      </c>
-      <c r="I221" t="inlineStr">
-        <is>
-          <t>• Más de 40 jóvenes y colectivos fueron premiados por su creatividad, liderazgo y compromiso social durante la Semana de la Juventud y la Semana Andina 2025. • La Subdirección para la Juventud de la Secretaría Distrital de Integración Social abrió...</t>
-        </is>
-      </c>
+          <t>https://www.infobae.com/colombia/2026/01/09/el-particular-castigo-de-policia-en-barranquilla-a-un-grupo-de-jovenes-quedo-en-video-el-cuerpo-sufre/</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Jóvenes con Oportunidades abre convocatoria para su ruta de formación en cursos cortos</t>
+          <t>Aumenta a 1.419 el número de lesionados por pólvora en Colombia; 428 son menores de edad - Infobae</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>SDIS - Juventud</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Empleo</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#28dd65106b</t>
-        </is>
-      </c>
-      <c r="I222" t="inlineStr">
-        <is>
-          <t>•La Subdirección para la Juventud anunció la apertura de nuevos cupos en la ruta de formación en cursos cortos, dirigida a jóvenes entre 18 y 28 años que vivan en Bogotá y cuenten con Sisbén IV (A1 a C09). • La ruta combina proyecto de vida, cursos...</t>
-        </is>
-      </c>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxOY1FwS0xiWWVaYl9saTQ5X0xRYnVoR0lwNE5XYUVaaUl3LW8yN0hEZGFnckI5VVlrVnBPSFJpeDNkU1JIaC01dVJVdFJYbEtSVTFXRTBCdTFDSDJ6TXZjc2t5N0t0cVFUY2JGbGZ1NDB5R1FJVG1RX25hREVIMjZlYktrdHc2QUFiZXNQTXFGZk9zeWNJRUl1aWNCbG9OXzZRQVA2dFFUZ1J3UnJrZzU4Qnk5TVBMajBPenJOU0ZBekNheEl2SkV3QVRUc9IB5gFBVV95cUxQeDZfb0gzZm9CTTRpYWx1ZTBielQ1TVgtaHNBOXRVRjBDcVd2V3M2anR3VTJaLU8zUEFkbEJkdDFEcHdHQUlpNGVORDZXV1Jxdzl4YmdPN3F1bk10ODZ1MnpOUjVSRTZscUUzYl80MDVpaHROOXdBNlhoQkFFR3RyVVJ1MWw1WTVZZVcwWnZ6THBEYWkxR1hEMTQzRGIzRWJvWlVUOFFBU2duZE5MRnRoRnQyZDl0ajd2SEpUVVM5ZW5POEpzLUZIcTV1c3RaaHlvanRUcG1oU3REVFVVQk5xTnhuLWk1UQ?oc=5</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>La Academia Ñam busca jóvenes interesados en el sector de la gastronomía</t>
+          <t>Gobierno condonará créditos del Icetex a más de mil jóvenes en Colombia: quiénes se beneficiarán - Infobae</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>SDIS - Juventud</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#8622ae2557</t>
-        </is>
-      </c>
-      <c r="I223" t="inlineStr">
-        <is>
-          <t>• El Distrito, en alianza con la Fundación Gastronomía Social, lanzan una nueva convocatoria dirigida a jóvenes de 18 a 30 años de las localidades de La Candelaria y Santa Fe interesados en formarse en servicio en gastronomía. • Esta formación...</t>
-        </is>
-      </c>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxOZlVSRmszbERPaGNNNjhFRXY3VGVlUjc0eXo5R002RDZTbk15NWlUb1pLeWtWdmtObV9fY2ZxUmQ3cHNacWJoMExhZVZDRjlJM0lYZ2VfUVJOTEJnOXhGeXhtOFdlX3BmdFZTWXNJWHpXSDJsREdSaXJHSmFfY0RCcV8xSFVTLThuS1M4eUwxYTMxdWU2WTY3YUVTaWtLWHJFRUhlM0EtQzFNdDQwNy1wU2NyMDIzSk5rZGI4ZExtcmx1b2R2d01DNzdZT29LanFzXzBaNjluZ0rSAfMBQVVfeXFMT3pmVy1QSHJLaTJmREJmLVNLano0XzdpeW1VemRocGF5eHBVZktPRnNkTnNBUElFMDk1UUQ4MTZRNENCVWpZQVhTRmNrV1dwbDhCQnFvemZKTmZyT2cwdV96a2xOUWZDZEloWEFKcjJ2QkJsX0h3bFZDTkNRNGJOY1U5UGZaN0x6YU1EQlN5ZlFLb0hYQkM1MDdKNWl5TS1OcVNYWHRGXzl5NFp1WnQ2YWJqcWZzZDlDTk5FQ19Sa2lZOXRpOEJ4LV9DUnVOenhkQ3FJUGhkZkExNkNOYlV2Z21iLUQxUmF0eDJ5c3NyekcxTFlF?oc=5</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>La Escuela Distrital de Emprendimiento ya está en marcha en Kennedy</t>
+          <t>Más de 40 jóvenes de Bogotá fueron reconocidos por su talento, creatividad y liderazgo en la Semana de la Juventud y la Semana Andina 2025</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -10756,7 +10756,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Cultura y deporte</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -10771,24 +10771,24 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#09b7d9045f</t>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#c68de3a13a</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>• 50 jóvenes emprendedores fortalecerán sus proyectos de negocios de la mano de expertos y líderes empresariales. • La Escuela Distrital de Emprendimiento, que llega a su quinta edición, nace de la alianza del Distrito con la ANDI y la Fundación...</t>
+          <t>• Más de 40 jóvenes y colectivos fueron premiados por su creatividad, liderazgo y compromiso social durante la Semana de la Juventud y la Semana Andina 2025. • La Subdirección para la Juventud de la Secretaría Distrital de Integración Social abrió...</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>La Academia Ñam abre una nueva convocatoria para jóvenes interesados en el sector de la gastronomía</t>
+          <t>Jóvenes con Oportunidades abre convocatoria para su ruta de formación en cursos cortos</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -10803,7 +10803,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Empleo</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -10818,24 +10818,24 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#17e48d890a</t>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#28dd65106b</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>• El Distrito, en alianza con la Fundación Gastronomía Social, lanzan convocatoria dirigida a jóvenes de 18 a 30 años interesados en formarse en servicio en el sector de la gastronomía. • Esta formación gratuita ofrece capacitación a través de...</t>
+          <t>•La Subdirección para la Juventud anunció la apertura de nuevos cupos en la ruta de formación en cursos cortos, dirigida a jóvenes entre 18 y 28 años que vivan en Bogotá y cuenten con Sisbén IV (A1 a C09). • La ruta combina proyecto de vida, cursos...</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Bogotá ofrece más de 1.500 becas para que jóvenes estudien programas técnicos laborales</t>
+          <t>La Academia Ñam busca jóvenes interesados en el sector de la gastronomía</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -10865,24 +10865,24 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#e22c14d73a</t>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#8622ae2557</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>•Se trata de la convocatoria Formación y Educación para el trabajo que les permitirá a los jóvenes de la ciudad formarse en una ocupación que requiere el mercado laboral. •Losbeneficiarios podrán estudiar mercadeo y ventas, mecánica dental, cocina,...</t>
+          <t>• El Distrito, en alianza con la Fundación Gastronomía Social, lanzan una nueva convocatoria dirigida a jóvenes de 18 a 30 años de las localidades de La Candelaria y Santa Fe interesados en formarse en servicio en gastronomía. • Esta formación...</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Jóvenes de la Casa de la Juventud de Suba aprenden sobre medio ambiente y navegan el río Bogotá</t>
+          <t>La Escuela Distrital de Emprendimiento ya está en marcha en Kennedy</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -10897,7 +10897,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
@@ -10912,24 +10912,24 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#ba7949b3a9</t>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#09b7d9045f</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>•Los navegantes confirmaron que los malos olores quedaron en el pasado y hoy se aprecian algunas especies de fauna que han comenzado a retornar a lo largo del cauce. • Gracias a la Corporación Autónoma Regional de Cundinamarca (CAR), encargada de...</t>
+          <t>• 50 jóvenes emprendedores fortalecerán sus proyectos de negocios de la mano de expertos y líderes empresariales. • La Escuela Distrital de Emprendimiento, que llega a su quinta edición, nace de la alianza del Distrito con la ANDI y la Fundación...</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Está abierta la convocatoria para la Escuela Distrital de Emprendimiento en Kennedy</t>
+          <t>La Academia Ñam abre una nueva convocatoria para jóvenes interesados en el sector de la gastronomía</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -10959,57 +10959,198 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#2acaf10b23</t>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#17e48d890a</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>• Jóvenes emprendedores podrán fortalecer sus proyectos de la mano de expertos y líderes empresariales. • La Escuela Distrital de Emprendimiento nace de la alianza del Distrito con la ANDI y la Fundación ANDI.</t>
+          <t>• El Distrito, en alianza con la Fundación Gastronomía Social, lanzan convocatoria dirigida a jóvenes de 18 a 30 años interesados en formarse en servicio en el sector de la gastronomía. • Esta formación gratuita ofrece capacitación a través de...</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Bogotá ofrece más de 1.500 becas para que jóvenes estudien programas técnicos laborales</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>SDIS - Juventud</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>institucional</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#e22c14d73a</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>•Se trata de la convocatoria Formación y Educación para el trabajo que les permitirá a los jóvenes de la ciudad formarse en una ocupación que requiere el mercado laboral. •Losbeneficiarios podrán estudiar mercadeo y ventas, mecánica dental, cocina,...</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Jóvenes de la Casa de la Juventud de Suba aprenden sobre medio ambiente y navegan el río Bogotá</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>SDIS - Juventud</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>institucional</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>Otra</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#ba7949b3a9</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>•Los navegantes confirmaron que los malos olores quedaron en el pasado y hoy se aprecian algunas especies de fauna que han comenzado a retornar a lo largo del cauce. • Gracias a la Corporación Autónoma Regional de Cundinamarca (CAR), encargada de...</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Está abierta la convocatoria para la Escuela Distrital de Emprendimiento en Kennedy</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>SDIS - Juventud</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>institucional</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#2acaf10b23</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>• Jóvenes emprendedores podrán fortalecer sus proyectos de la mano de expertos y líderes empresariales. • La Escuela Distrital de Emprendimiento nace de la alianza del Distrito con la ANDI y la Fundación ANDI.</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
           <t>2025-09-06</t>
         </is>
       </c>
-      <c r="B229" t="inlineStr">
+      <c r="B232" t="inlineStr">
         <is>
           <t>El Frailejón abre sus puertas: Usme estrena nueva Casa de la Juventud</t>
         </is>
       </c>
-      <c r="C229" t="inlineStr">
+      <c r="C232" t="inlineStr">
         <is>
           <t>SDIS - Juventud</t>
         </is>
       </c>
-      <c r="D229" t="inlineStr">
+      <c r="D232" t="inlineStr">
         <is>
           <t>institucional</t>
         </is>
       </c>
-      <c r="E229" t="inlineStr">
+      <c r="E232" t="inlineStr">
         <is>
           <t>Otra</t>
         </is>
       </c>
-      <c r="F229" t="inlineStr">
+      <c r="F232" t="inlineStr">
         <is>
           <t>Bogotá</t>
         </is>
       </c>
-      <c r="G229" t="inlineStr">
+      <c r="G232" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="H229" t="inlineStr">
+      <c r="H232" t="inlineStr">
         <is>
           <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#c7eca5d4bd</t>
         </is>
       </c>
-      <c r="I229" t="inlineStr">
+      <c r="I232" t="inlineStr">
         <is>
           <t>• Aunque ya existía una Casa de la Juventud en Usme, la sede se traslada y reinaugura para ofrecer mejores condiciones, ampliar servicios y fortalecer la atención a los jóvenes. • La reapertura se desarrolló con el acompañamiento de la Plataforma...</t>
         </is>

--- a/data/noticias.xlsx
+++ b/data/noticias.xlsx
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/data/noticias.xlsx
+++ b/data/noticias.xlsx
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/data/noticias.xlsx
+++ b/data/noticias.xlsx
@@ -466,22 +466,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Colombia está entre los países en que las personas se pensionan más jóvenes, según la Ocde: esta es la comparación con otros lugares</t>
+          <t>Prosperidad Social entregará transferencias a beneficiarios afectados por el terremoto sin verificación de condicionalidades y corresponsabilidades</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Prosperidad Social</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -491,22 +491,22 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/10/01/colombia-esta-entre-los-paises-en-que-las-personas-se-pensionan-mas-jovenes-segun-la-ocde-esta-es-la-comparacion-con-otros-lugares/</t>
+          <t>https://prosperidadsocial.gov.co/Noticias/prosperidad-social-entregara-transferencias-a-beneficiarios-afectados-por-el-terremoto-sin-verificacion-de-condicionalidades-y-corresponsabilidades/</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>En el país las mujeres pueden acceder a la prestación desde los 57 años y los hombres desde los 62, frente a las referencias internacionales de 63,9 y 64,7 registradas en 2024 entre los países analizados</t>
+          <t>El Gobierno nacional autorizó a Prosperidad Social a suspender temporalmente las verificaciones de corresponsabilidades que no puedan realizarse por las afectaciones del terremoto. La medida busca evitar que beneficiarios pierdan o retrasen sus...</t>
         </is>
       </c>
     </row>
@@ -518,12 +518,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Uno de cada cuatro jovenes de 18 a 24 anos en colombia es 'nini', no estudia ni trabaja, el doble de la ocde</t>
+          <t>Colombia está entre los países en que las personas se pensionan más jóvenes, según la Ocde: esta es la comparación con otros lugares</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Portafolio</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -548,10 +548,14 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.portafolio.co/economia/uno-de-cada-cuatro-jovenes-de-18-a-24-anos-en-colombia-es-nini-no-estudia-ni-trabaja-el-doble-de-la-ocde-503651</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>https://www.infobae.com/colombia/2026/10/01/colombia-esta-entre-los-paises-en-que-las-personas-se-pensionan-mas-jovenes-segun-la-ocde-esta-es-la-comparacion-con-otros-lugares/</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>En el país las mujeres pueden acceder a la prestación desde los 57 años y los hombres desde los 62, frente a las referencias internacionales de 63,9 y 64,7 registradas en 2024 entre los países analizados</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -561,17 +565,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Prosperidad Social entregará transferencias a beneficiarios afectados por el terremoto sin verificación de condicionalidades y corresponsabilidades</t>
+          <t>Uno de cada cuatro jovenes de 18 a 24 anos en colombia es 'nini', no estudia ni trabaja, el doble de la ocde</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Prosperidad Social</t>
+          <t>Portafolio</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -581,24 +585,20 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://prosperidadsocial.gov.co/Noticias/prosperidad-social-entregara-transferencias-a-beneficiarios-afectados-por-el-terremoto-sin-verificacion-de-condicionalidades-y-corresponsabilidades/</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>El Gobierno nacional autorizó a Prosperidad Social a suspender temporalmente las verificaciones de corresponsabilidades que no puedan realizarse por las afectaciones del terremoto. La medida busca evitar que beneficiarios pierdan o retrasen sus...</t>
-        </is>
-      </c>
+          <t>https://www.portafolio.co/economia/uno-de-cada-cuatro-jovenes-de-18-a-24-anos-en-colombia-es-nini-no-estudia-ni-trabaja-el-doble-de-la-ocde-503651</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">

--- a/data/noticias.xlsx
+++ b/data/noticias.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I235"/>
+  <dimension ref="A1:I233"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,22 +466,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Asesinan a joven líder social en Tibú, Norte de Santander: el caso de Magnely Pallares Franco y el conflicto en Catatumbo</t>
+          <t>Prosperidad Social entregará transferencias a beneficiarios afectados por el terremoto sin verificación de condicionalidades y corresponsabilidades</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Pulzo</t>
+          <t>Prosperidad Social</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -491,20 +491,24 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Cúcuta</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.pulzo.com/nacion/magnely-pallares-franco-lider-social-asesinado-en-tibu-norte-de-santander-que-paso-PP5320707A</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>https://prosperidadsocial.gov.co/Noticias/prosperidad-social-entregara-transferencias-a-beneficiarios-afectados-por-el-terremoto-sin-verificacion-de-condicionalidades-y-corresponsabilidades/</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>El Gobierno nacional autorizó a Prosperidad Social a suspender temporalmente las verificaciones de corresponsabilidades que no puedan realizarse por las afectaciones del terremoto. La medida busca evitar que beneficiarios pierdan o retrasen sus...</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -514,17 +518,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Prosperidad Social entregará transferencias a beneficiarios afectados por el terremoto sin verificación de condicionalidades y corresponsabilidades</t>
+          <t>Asesinan a joven líder social en Tibú, Norte de Santander: el caso de Magnely Pallares Franco y el conflicto en Catatumbo</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Prosperidad Social</t>
+          <t>Pulzo</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -534,24 +538,20 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Cúcuta</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://prosperidadsocial.gov.co/Noticias/prosperidad-social-entregara-transferencias-a-beneficiarios-afectados-por-el-terremoto-sin-verificacion-de-condicionalidades-y-corresponsabilidades/</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>El Gobierno nacional autorizó a Prosperidad Social a suspender temporalmente las verificaciones de corresponsabilidades que no puedan realizarse por las afectaciones del terremoto. La medida busca evitar que beneficiarios pierdan o retrasen sus...</t>
-        </is>
-      </c>
+          <t>https://www.pulzo.com/nacion/magnely-pallares-franco-lider-social-asesinado-en-tibu-norte-de-santander-que-paso-PP5320707A</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -7596,12 +7596,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Voluntariado transformador: unidad de autocuidado para habitantes de calle en el Voto Nacional estrena ludoteca</t>
+          <t>Abierta convocatoria para la Escuela Distrital de Emprendimiento para jóvenes en Engativá</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -7616,7 +7616,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -7631,29 +7631,29 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#364408dd32</t>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#248fcdb8a0</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>• 40 personas, entre voluntarios de empresas y habitantes de calle, unieron esfuerzos para adecuar un espacio que estimula el conocimiento y pone a volar a la imaginación. • Esta acción se enmarca en la estrategia ‘Más manos por Bogotá’, programa de...</t>
+          <t>• El Distrito abre la convocatoria para 50 jóvenes entre 18 y 28 años, que cuentan con un emprendimiento en marcha y buscan fortalecer sus capacidades para hacerlo crecer y consolidarlo. • La formación se realizará de manera presencial en la Casa de...</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Abierta convocatoria para la Escuela Distrital de Emprendimiento para jóvenes en Engativá</t>
+          <t>Miles de jóvenes se toman Bogotá: Prosperidad Social acompaña el Festival Nacional de la Juventud</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>SDIS - Juventud</t>
+          <t>Prosperidad Social</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -7678,91 +7678,91 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#248fcdb8a0</t>
+          <t>https://prosperidadsocial.gov.co/Noticias/miles-de-jovenes-se-toman-bogota-prosperidad-social-acompana-el-festival-nacional-de-la-juventud/</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>• El Distrito abre la convocatoria para 50 jóvenes entre 18 y 28 años, que cuentan con un emprendimiento en marcha y buscan fortalecer sus capacidades para hacerlo crecer y consolidarlo. • La formación se realizará de manera presencial en la Casa de...</t>
+          <t>Más de 4.000 jóvenes de todo el país se reúnen del 24 al 26 de abril en la sede Aduanilla de Paiba de la Universidad Distrital</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Miles de jóvenes se toman Bogotá: Prosperidad Social acompaña el Festival Nacional de la Juventud</t>
+          <t>El tío comunista de Paloma Valencia, la oveja negra que incomodó a su familia conservadora</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Prosperidad Social</t>
+          <t>Las2orillas</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Popayán</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>https://prosperidadsocial.gov.co/Noticias/miles-de-jovenes-se-toman-bogota-prosperidad-social-acompana-el-festival-nacional-de-la-juventud/</t>
+          <t>https://www.las2orillas.co/el-tio-comunista-de-paloma-valencia-la-oveja-negra-que-incomodo-a-su-familia-conservadora/</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>Más de 4.000 jóvenes de todo el país se reúnen del 24 al 26 de abril en la sede Aduanilla de Paiba de la Universidad Distrital</t>
+          <t>Álvaro Pío Valencia, hermano del expresidente Guillermo León, conoció de joven al papá de Iván Cepeda en Popayán e influyó para que él fuera un consagrado ComunistaEl artículoEl tío comunista de Paloma Valencia, la oveja negra que incomodó a su...</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>El tío comunista de Paloma Valencia, la oveja negra que incomodó a su familia conservadora</t>
+          <t>Masacre en Mocoa: asesinaron a cinco jóvenes en zona boscosa</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Las2orillas</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Popayán</t>
+          <t>Mocoa</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>https://www.las2orillas.co/el-tio-comunista-de-paloma-valencia-la-oveja-negra-que-incomodo-a-su-familia-conservadora/</t>
+          <t>https://www.elespectador.com/colombia/mas-regiones/masacre-en-mocoa-asesinaron-a-cinco-jovenes-en-zona-boscosa/</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>Álvaro Pío Valencia, hermano del expresidente Guillermo León, conoció de joven al papá de Iván Cepeda en Popayán e influyó para que él fuera un consagrado ComunistaEl artículoEl tío comunista de Paloma Valencia, la oveja negra que incomodó a su...</t>
+          <t>Cinco hombres fueron asesinados en Mocoa. El hecho se dio después de que se difundió un panfleto amenazante.</t>
         </is>
       </c>
     </row>
@@ -7789,7 +7789,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Masacre en Mocoa: asesinaron a cinco jóvenes en zona boscosa</t>
+          <t>Patinador de 14 años de la Liga Vallecaucana murió durante un entrenamiento: esto se sabe</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -7809,7 +7809,7 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Mocoa</t>
+          <t>Popayán</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -7819,24 +7819,24 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/mas-regiones/masacre-en-mocoa-asesinaron-a-cinco-jovenes-en-zona-boscosa/</t>
+          <t>https://www.elespectador.com/colombia/cali/muere-joven-patinador-en-cali-tras-accidente-durante-entrenamiento-en-patinodromo/</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>Cinco hombres fueron asesinados en Mocoa. El hecho se dio después de que se difundió un panfleto amenazante.</t>
+          <t>El joven hacía parte de la Liga Vallecaucana de Patinaje y del club Relámpago.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Patinador de 14 años de la Liga Vallecaucana murió durante un entrenamiento: esto se sabe</t>
+          <t>Capturan a hombre que se hizo pasar por mototaxista y abusó de una joven de 14 años en Cali</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -7856,7 +7856,7 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Popayán</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -7866,34 +7866,34 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/cali/muere-joven-patinador-en-cali-tras-accidente-durante-entrenamiento-en-patinodromo/</t>
+          <t>https://www.elespectador.com/colombia/cali/capturan-a-hombre-que-se-hizo-pasar-por-mototaxista-y-abuso-de-una-joven-de-14-anos-en-cali/</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>El joven hacía parte de la Liga Vallecaucana de Patinaje y del club Relámpago.</t>
+          <t>La víctima fue herida con arma cortopunzante y asfixiada hasta quedar inconsciente.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Capturan a hombre que se hizo pasar por mototaxista y abusó de una joven de 14 años en Cali</t>
+          <t>La jueza que investiga el colapso de una pasarela en Santander imputa a un tercer técnico de Costas y aprecia indicios de seis homicidios por imprudencia grave</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -7903,7 +7903,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Bucaramanga</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -7913,12 +7913,12 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/cali/capturan-a-hombre-que-se-hizo-pasar-por-mototaxista-y-abuso-de-una-joven-de-14-anos-en-cali/</t>
+          <t>https://www.infobae.com/espana/2026/04/21/la-jueza-que-investiga-el-colapso-de-una-pasarela-en-santander-imputa-a-un-tercer-tecnico-de-costas-y-aprecia-indicios-de-seis-homicidios-por-imprudencia-grave/</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>La víctima fue herida con arma cortopunzante y asfixiada hasta quedar inconsciente.</t>
+          <t>La instructora considera que la falta de inspección y mantenimiento durante años generó un riesgo no controlado que desembocó en el desplome de la estructura y en la muerte de seis jóvenes</t>
         </is>
       </c>
     </row>
@@ -7930,17 +7930,17 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>La jueza que investiga el colapso de una pasarela en Santander imputa a un tercer técnico de Costas y aprecia indicios de seis homicidios por imprudencia grave</t>
+          <t>Investigan el asesinato de adolescente de 15 años en campo de golf en Cartagena</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -7950,7 +7950,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Bucaramanga</t>
+          <t>Cartagena</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -7960,34 +7960,34 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/espana/2026/04/21/la-jueza-que-investiga-el-colapso-de-una-pasarela-en-santander-imputa-a-un-tercer-tecnico-de-costas-y-aprecia-indicios-de-seis-homicidios-por-imprudencia-grave/</t>
+          <t>https://www.elespectador.com/colombia/cartagena/investigan-el-asesinato-de-adolescente-de-17-anos-en-campo-de-golf-en-cartagena/</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>La instructora considera que la falta de inspección y mantenimiento durante años generó un riesgo no controlado que desembocó en el desplome de la estructura y en la muerte de seis jóvenes</t>
+          <t>Las autoridades buscan esclarecer por qué un empleado de seguridad de un club de golf de Cartagena disparó contra un adolescente.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Investigan el asesinato de adolescente de 15 años en campo de golf en Cartagena</t>
+          <t>Filtran las primeras imágenes del doble asesinato contra miembros de la producción de ‘Sin senos sí hay paraíso 4′ en Bogotá: el agresor atacó por la espalda</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -7997,34 +7997,34 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Cartagena</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/cartagena/investigan-el-asesinato-de-adolescente-de-17-anos-en-campo-de-golf-en-cartagena/</t>
+          <t>https://www.infobae.com/colombia/2026/04/20/filtran-las-primeras-imagenes-del-doble-asesinato-contra-miembros-de-la-produccion-de-sin-senos-si-hay-paraiso-4-en-bogota-el-agresor-ataco-por-la-espalda/</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>Las autoridades buscan esclarecer por qué un empleado de seguridad de un club de golf de Cartagena disparó contra un adolescente.</t>
+          <t>En el material fílmico se observa cuando el joven de 24 años diagnosticado con enfermedad mental se acercó al conductor de 45 años y, sin mediar palabra, lo tomó por el cuello y lo hirió mortalmente con arma blanca</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Filtran las primeras imágenes del doble asesinato contra miembros de la producción de ‘Sin senos sí hay paraíso 4′ en Bogotá: el agresor atacó por la espalda</t>
+          <t>Magnicidio Miguel Uribe Turbay: menor de edad que disparó al precandidato fue declarado como víctima en el proceso judicial</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -8044,39 +8044,39 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/04/20/filtran-las-primeras-imagenes-del-doble-asesinato-contra-miembros-de-la-produccion-de-sin-senos-si-hay-paraiso-4-en-bogota-el-agresor-ataco-por-la-espalda/</t>
+          <t>https://www.infobae.com/colombia/2026/04/18/magnicidio-miguel-uribe-turbay-menor-de-edad-que-disparo-al-precandidato-fue-declarado-como-victima-en-el-proceso-judicial/</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>En el material fílmico se observa cuando el joven de 24 años diagnosticado con enfermedad mental se acercó al conductor de 45 años y, sin mediar palabra, lo tomó por el cuello y lo hirió mortalmente con arma blanca</t>
+          <t>Alias Tianz confesó el crimen y cumple una sanción de siete años en un centro de atención especializada, bajo la custodia del Instituto Colombiano de Bienestar Familiar</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Magnicidio Miguel Uribe Turbay: menor de edad que disparó al precandidato fue declarado como víctima en el proceso judicial</t>
+          <t>Uno de cada cuatro jovenes en colombia no estudia ni trabaja y el mercado laboral da senales de debilidad</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Portafolio</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -8086,7 +8086,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Empleo</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -8101,14 +8101,10 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/04/18/magnicidio-miguel-uribe-turbay-menor-de-edad-que-disparo-al-precandidato-fue-declarado-como-victima-en-el-proceso-judicial/</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr">
-        <is>
-          <t>Alias Tianz confesó el crimen y cumple una sanción de siete años en un centro de atención especializada, bajo la custodia del Instituto Colombiano de Bienestar Familiar</t>
-        </is>
-      </c>
+          <t>https://www.portafolio.co/economia/empleo/uno-de-cada-cuatro-jovenes-en-colombia-no-estudia-ni-trabaja-y-el-mercado-laboral-da-senales-de-debilidad-492018</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -8118,60 +8114,64 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Uno de cada cuatro jovenes en colombia no estudia ni trabaja y el mercado laboral da senales de debilidad</t>
+          <t>¡Atención, jóvenes! Bogotá abre formación gratuita para impulsar emprendimientos</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Portafolio</t>
+          <t>SDIS - Juventud</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Empleo</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>https://www.portafolio.co/economia/empleo/uno-de-cada-cuatro-jovenes-en-colombia-no-estudia-ni-trabaja-y-el-mercado-laboral-da-senales-de-debilidad-492018</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr"/>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#ee67a6f4f1</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>•Bogotá abre la convocatoria de Innovers 2026, un programa gratuito para fortalecer el emprendimiento juvenil. • Dirigido a jóvenes entre 18 y 28 años, desde quienes tienen una idea hasta emprendimientos en crecimiento.</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>¡Atención, jóvenes! Bogotá abre formación gratuita para impulsar emprendimientos</t>
+          <t>Asesinaron a dos jóvenes que habían sido secuestrados por la guerrilla hace un mes en Arauca</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>SDIS - Juventud</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -8181,44 +8181,40 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Arauca</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#ee67a6f4f1</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr">
-        <is>
-          <t>•Bogotá abre la convocatoria de Innovers 2026, un programa gratuito para fortalecer el emprendimiento juvenil. • Dirigido a jóvenes entre 18 y 28 años, desde quienes tienen una idea hasta emprendimientos en crecimiento.</t>
-        </is>
-      </c>
+          <t>https://www.bluradio.com/nacion/asesinaron-a-dos-jovenes-que-habian-sido-secuestrados-por-la-guerrilla-hace-un-mes-en-arauca-rg10</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Asesinaron a dos jóvenes que habían sido secuestrados por la guerrilla hace un mes en Arauca</t>
+          <t>Bomberos rescataron a joven que le quedó atrapado el dedo en una banca del MIO en Cali</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -8228,7 +8224,7 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Arauca</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -8238,20 +8234,24 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/nacion/asesinaron-a-dos-jovenes-que-habian-sido-secuestrados-por-la-guerrilla-hace-un-mes-en-arauca-rg10</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr"/>
+          <t>https://www.elespectador.com/colombia/cali/bomberos-rescataron-a-joven-que-le-quedo-atrapado-el-dedo-en-una-banca-del-mio-en-cali/</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>El caso ocurrió en un paradero del sistema en el barrio Potrero Grande del MIO en Cali.</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Bomberos rescataron a joven que le quedó atrapado el dedo en una banca del MIO en Cali</t>
+          <t>Medellín abre convocatoria para impulsar emprendimientos rurales de jóvenes y mujeres</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -8271,7 +8271,7 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Medellín</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -8281,12 +8281,12 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/cali/bomberos-rescataron-a-joven-que-le-quedo-atrapado-el-dedo-en-una-banca-del-mio-en-cali/</t>
+          <t>https://www.elespectador.com/colombia/medellin/medellin-abre-convocatoria-para-impulsar-emprendimientos-rurales-de-jovenes-y-mujeres/</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>El caso ocurrió en un paradero del sistema en el barrio Potrero Grande del MIO en Cali.</t>
+          <t>Hasta 40 iniciativas podrán acceder a recursos y acompañamiento técnico. Las inscripciones estarán abiertas hasta el 10 de abril.</t>
         </is>
       </c>
     </row>
@@ -8298,27 +8298,27 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Medellín abre convocatoria para impulsar emprendimientos rurales de jóvenes y mujeres</t>
+          <t>MATAR MUJERES: LA VIOLENCIA INSTRUMENTAL COMO ESTRATEGIA DEL CONTROL ARMADO</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>La Silla Vacía</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -8328,34 +8328,34 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/medellin/medellin-abre-convocatoria-para-impulsar-emprendimientos-rurales-de-jovenes-y-mujeres/</t>
+          <t>https://www.lasillavacia.com/red-de-expertos/matar-mujeres-la-violencia-instrumental-como-estrategia-del-control-armado/</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>Hasta 40 iniciativas podrán acceder a recursos y acompañamiento técnico. Las inscripciones estarán abiertas hasta el 10 de abril.</t>
+          <t>El asesinato de dos adolescentes en Malambo, Atlántico, es un crimen atroz que evidencia una lógica que se repite en distintos territorios y que consiste en matar mujeres para castigar, advertir e imponer control. Mientras sus familias recibían...</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>MATAR MUJERES: LA VIOLENCIA INSTRUMENTAL COMO ESTRATEGIA DEL CONTROL ARMADO</t>
+          <t>Capturan a joven de 19 años por asesinato de mujer y su hijo en Villavicencio</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>La Silla Vacía</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -8365,7 +8365,7 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Villavicencio</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -8375,12 +8375,12 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>https://www.lasillavacia.com/red-de-expertos/matar-mujeres-la-violencia-instrumental-como-estrategia-del-control-armado/</t>
+          <t>https://www.elespectador.com/colombia/mas-regiones/capturan-a-joven-de-19-anos-por-asesinato-de-mujer-y-su-hijo-en-villavicencio/</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>El asesinato de dos adolescentes en Malambo, Atlántico, es un crimen atroz que evidencia una lógica que se repite en distintos territorios y que consiste en matar mujeres para castigar, advertir e imponer control. Mientras sus familias recibían...</t>
+          <t>Las autoridades capturaron a un joven de 19 años señalado del doble homicidio ocurrido en el barrio San Antonio de Villavicencio.</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Capturan a joven de 19 años por asesinato de mujer y su hijo en Villavicencio</t>
+          <t>Hallaron el cuerpo de una adolescente de 14 años que se ahogó en playa de Antioquia</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -8407,12 +8407,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Villavicencio</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -8422,24 +8422,24 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/mas-regiones/capturan-a-joven-de-19-anos-por-asesinato-de-mujer-y-su-hijo-en-villavicencio/</t>
+          <t>https://www.elespectador.com/colombia/mas-regiones/hallaron-el-cuerpo-de-una-adolescente-de-14-anos-que-se-ahogo-en-playa-de-san-juan-de-uraba-en-antioquia/</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>Las autoridades capturaron a un joven de 19 años señalado del doble homicidio ocurrido en el barrio San Antonio de Villavicencio.</t>
+          <t>La menor había ingresado al mar con una amiga en una zona con fuerte oleaje. Su cuerpo fue hallado horas después.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Hallaron el cuerpo de una adolescente de 14 años que se ahogó en playa de Antioquia</t>
+          <t>Ataque de pitbull que dejó a perro muerto y joven herido en Barranquilla</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -8454,12 +8454,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Barranquilla</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -8469,59 +8469,59 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/mas-regiones/hallaron-el-cuerpo-de-una-adolescente-de-14-anos-que-se-ahogo-en-playa-de-san-juan-de-uraba-en-antioquia/</t>
+          <t>https://www.elespectador.com/colombia/barranquilla/anuncian-acciones-tras-ataque-de-pitbull-que-dejo-a-perro-muerto-y-joven-herido-en-barranquilla/</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>La menor había ingresado al mar con una amiga en una zona con fuerte oleaje. Su cuerpo fue hallado horas después.</t>
+          <t>El hecho ocurrió en un conjunto residencial de Barranquilla y quedó registrado en cámaras de seguridad.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Ataque de pitbull que dejó a perro muerto y joven herido en Barranquilla</t>
+          <t>Prosperidad Social amplía el periodo de transferencias de Renta Joven en modalidad de giro</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Prosperidad Social</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Política pública</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Barranquilla</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/barranquilla/anuncian-acciones-tras-ataque-de-pitbull-que-dejo-a-perro-muerto-y-joven-herido-en-barranquilla/</t>
+          <t>https://prosperidadsocial.gov.co/Noticias/prosperidad-social-amplia-el-periodo-de-transferencias-de-renta-joven-en-modalidad-de-giro/</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>El hecho ocurrió en un conjunto residencial de Barranquilla y quedó registrado en cámaras de seguridad.</t>
+          <t>La ampliación del plazo permitirá que más de 27.000 participantes reciban sus subsidios, incluyendo transferencias pendientes de 2025. La transferencia monetaria condicionada se podrá reclamar en los puntos autorizados de SuRed y SuperGIROS. Bogotá...</t>
         </is>
       </c>
     </row>
@@ -8533,12 +8533,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Prosperidad Social amplía el periodo de transferencias de Renta Joven en modalidad de giro</t>
+          <t>Nueva convocatoria dirigida a jóvenes interesados en formarse en el sector de gastronomía</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Prosperidad Social</t>
+          <t>SDIS - Juventud</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -8548,7 +8548,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Política pública</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -8563,59 +8563,59 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>https://prosperidadsocial.gov.co/Noticias/prosperidad-social-amplia-el-periodo-de-transferencias-de-renta-joven-en-modalidad-de-giro/</t>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#e5d592a6d5</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>La ampliación del plazo permitirá que más de 27.000 participantes reciban sus subsidios, incluyendo transferencias pendientes de 2025. La transferencia monetaria condicionada se podrá reclamar en los puntos autorizados de SuRed y SuperGIROS. Bogotá...</t>
+          <t>• El Distrito, en alianza con la Fundación Gastronomía Social, lanzan una nueva convocatoria dirigida a jóvenes de 18 a 30 años, principalmente de la localidad de Kennedy, para formarse en servicio para el sector de la gastronomía. • Esta formación...</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Nueva convocatoria dirigida a jóvenes interesados en formarse en el sector de gastronomía</t>
+          <t>La incoherente decisión de Petro de abrirle la Casa de Nariño a Westcol decepcionó a quienes respaldaban su gobierno</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>SDIS - Juventud</t>
+          <t>Las2orillas</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#e5d592a6d5</t>
+          <t>https://www.las2orillas.co/la-incoherente-decision-de-petro-de-abrirle-la-casa-de-narino-a-westcol-decepciono-a-quienes-respaldaban-su-gobierno/</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>• El Distrito, en alianza con la Fundación Gastronomía Social, lanzan una nueva convocatoria dirigida a jóvenes de 18 a 30 años, principalmente de la localidad de Kennedy, para formarse en servicio para el sector de la gastronomía. • Esta formación...</t>
+          <t>Recibir a Westcol tras la tragedia del Hércules y sus discursos de odio es un golpe a la coherencia progresista. ¿Vale todo por llegarle a los jóvenes?El artículoLa incoherente decisión de Petro de abrirle la Casa de Nariño a Westcol decepcionó a...</t>
         </is>
       </c>
     </row>
@@ -8627,12 +8627,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>La incoherente decisión de Petro de abrirle la Casa de Nariño a Westcol decepcionó a quienes respaldaban su gobierno</t>
+          <t>Primero Petro luego Uribe: Westcol, el streamer que entrevista presidentes</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Las2orillas</t>
+          <t>La Silla Vacía</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -8657,12 +8657,12 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>https://www.las2orillas.co/la-incoherente-decision-de-petro-de-abrirle-la-casa-de-narino-a-westcol-decepciono-a-quienes-respaldaban-su-gobierno/</t>
+          <t>https://www.lasillavacia.com/silla-nacional/primero-petro-luego-uribe-westcol-el-streamer-que-entrevista-presidentes/</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>Recibir a Westcol tras la tragedia del Hércules y sus discursos de odio es un golpe a la coherencia progresista. ¿Vale todo por llegarle a los jóvenes?El artículoLa incoherente decisión de Petro de abrirle la Casa de Nariño a Westcol decepcionó a...</t>
+          <t>El influencer se convierte en interlocutor de los dos políticos más poderosos de Colombia. Ambos van detrás de su audiencia joven y masiva en época electoral.The postPrimero Petro luego Uribe: Westcol, el streamer que entrevista presidentesappeared...</t>
         </is>
       </c>
     </row>
@@ -8674,27 +8674,27 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Primero Petro luego Uribe: Westcol, el streamer que entrevista presidentes</t>
+          <t>Asesinaron a joven futbolista en Barranquilla; le dispararon en la cabeza</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>La Silla Vacía</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Barranquilla</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -8704,24 +8704,24 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>https://www.lasillavacia.com/silla-nacional/primero-petro-luego-uribe-westcol-el-streamer-que-entrevista-presidentes/</t>
+          <t>https://www.elespectador.com/colombia/barranquilla/asesinaron-a-joven-futbolista-en-barranquilla-le-dispararon-en-la-cabeza/</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>El influencer se convierte en interlocutor de los dos políticos más poderosos de Colombia. Ambos van detrás de su audiencia joven y masiva en época electoral.The postPrimero Petro luego Uribe: Westcol, el streamer que entrevista presidentesappeared...</t>
+          <t>Asesinaron a una joven promesa del fútbol en el barrio El Santuario de Barranquilla. Le dispararon en la cabeza en medio de una riña.</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Asesinaron a joven futbolista en Barranquilla; le dispararon en la cabeza</t>
+          <t>Asesinaron a dos jóvenes en ataque sicarial en una discoteca de Riohacha</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Barranquilla</t>
+          <t>Riohacha</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
@@ -8751,12 +8751,12 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/barranquilla/asesinaron-a-joven-futbolista-en-barranquilla-le-dispararon-en-la-cabeza/</t>
+          <t>https://www.elespectador.com/colombia/mas-regiones/tres-sicarios-abrieron-fuego-en-una-discoteca-de-riohacha-y-asesinaron-dos-jovenes/</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>Asesinaron a una joven promesa del fútbol en el barrio El Santuario de Barranquilla. Le dispararon en la cabeza en medio de una riña.</t>
+          <t>¿Qué sucedió en el ataque de tres sicarios ocurrido en una discoteca de Riohacha?</t>
         </is>
       </c>
     </row>
@@ -8768,69 +8768,69 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Asesinaron a dos jóvenes en ataque sicarial en una discoteca de Riohacha</t>
+          <t>Así fue la participación de los jóvenes en el primer Fest de las Oportunidades del año</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>SDIS - Juventud</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Riohacha</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/mas-regiones/tres-sicarios-abrieron-fuego-en-una-discoteca-de-riohacha-y-asesinaron-dos-jovenes/</t>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#9690ed7762</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>¿Qué sucedió en el ataque de tres sicarios ocurrido en una discoteca de Riohacha?</t>
+          <t>•El primer Fest de las Oportunidades 2026 reunió a más de 130 jóvenes en Usme, conectándolos con oferta en empleo, educación, emprendimiento y bienestar. •Más de 20 entidades y aliados participaron acercando oportunidades reales y orientación...</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Así fue la participación de los jóvenes en el primer Fest de las Oportunidades del año</t>
+          <t>Conductor atropelló y mató a un joven en Bogotá tras invadir el carril exclusivo de Transmilenio</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>SDIS - Juventud</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -8845,12 +8845,12 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#9690ed7762</t>
+          <t>https://www.infobae.com/colombia/2026/03/28/conductor-atropello-y-mato-a-un-joven-en-bogota-tras-invadir-el-carril-exclusivo-de-transmilenio/</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>•El primer Fest de las Oportunidades 2026 reunió a más de 130 jóvenes en Usme, conectándolos con oferta en empleo, educación, emprendimiento y bienestar. •Más de 20 entidades y aliados participaron acercando oportunidades reales y orientación...</t>
+          <t>La muerte de Juan Sebastián Triviño y las lesiones sufridas por su acompañante mantienen en alerta a la ciudad, mientras los familiares reclaman las grabaciones de cámaras de seguridad como elemento determinante para identificar al conductor...</t>
         </is>
       </c>
     </row>
@@ -8862,22 +8862,22 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Conductor atropelló y mató a un joven en Bogotá tras invadir el carril exclusivo de Transmilenio</t>
+          <t>Sobre la entrega de transferencias monetarias condicionadas de Jóvenes en Paz</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Prosperidad Social</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -8892,12 +8892,12 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/03/28/conductor-atropello-y-mato-a-un-joven-en-bogota-tras-invadir-el-carril-exclusivo-de-transmilenio/</t>
+          <t>https://prosperidadsocial.gov.co/Noticias/sobre-la-entrega-de-transferencias-monetarias-condicionadas-de-jovenes-en-paz/</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>La muerte de Juan Sebastián Triviño y las lesiones sufridas por su acompañante mantienen en alerta a la ciudad, mientras los familiares reclaman las grabaciones de cámaras de seguridad como elemento determinante para identificar al conductor...</t>
+          <t>Bogotá D.C., 27 de marzo de 2026. Prosperidad Social informa a los participantes del programa Jóvenes en Paz que se adelanta la última etapa del procedimiento para disponer de los recursos de los próximos ciclos del año. En consecuencia: La entrega...</t>
         </is>
       </c>
     </row>
@@ -8909,54 +8909,54 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Sobre la entrega de transferencias monetarias condicionadas de Jóvenes en Paz</t>
+          <t>Continúa la búsqueda de cuatro jóvenes desaparecidos en Coromoro, Santander</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Prosperidad Social</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Protección</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>https://prosperidadsocial.gov.co/Noticias/sobre-la-entrega-de-transferencias-monetarias-condicionadas-de-jovenes-en-paz/</t>
+          <t>https://www.elespectador.com/colombia/mas-regiones/buscan-a-cuatro-jovenes-desaparecidos-en-coromoro-santander-noticias-hoy/</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>Bogotá D.C., 27 de marzo de 2026. Prosperidad Social informa a los participantes del programa Jóvenes en Paz que se adelanta la última etapa del procedimiento para disponer de los recursos de los próximos ciclos del año. En consecuencia: La entrega...</t>
+          <t>Inicialmente eran seis los reportados como desaparecidos.</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Continúa la búsqueda de cuatro jóvenes desaparecidos en Coromoro, Santander</t>
+          <t>La historia de Luis Fernando Hostia y la meta de abrir caminos a personas con discapacidad</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -8971,7 +8971,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Protección</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -8986,24 +8986,24 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/mas-regiones/buscan-a-cuatro-jovenes-desaparecidos-en-coromoro-santander-noticias-hoy/</t>
+          <t>https://www.elespectador.com/colombia/mas-regiones/la-historia-de-luis-fernando-hostia-y-la-meta-de-romper-barreras-a-personas-con-discapacidad/</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>Inicialmente eran seis los reportados como desaparecidos.</t>
+          <t>Desde San Sebastián de Buenavista, un joven en condición de discapacidad rompió décadas de barreras educativas.</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>La historia de Luis Fernando Hostia y la meta de abrir caminos a personas con discapacidad</t>
+          <t>Lo que se sabe de la muerte de joven dentro de Univalle; hay varias preguntas</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
@@ -9033,24 +9033,24 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/mas-regiones/la-historia-de-luis-fernando-hostia-y-la-meta-de-romper-barreras-a-personas-con-discapacidad/</t>
+          <t>https://www.elespectador.com/colombia/cali/lo-que-se-sabe-de-la-muerte-de-joven-dentro-de-univalle-hay-varias-preguntas/</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>Desde San Sebastián de Buenavista, un joven en condición de discapacidad rompió décadas de barreras educativas.</t>
+          <t>El caso ocurrió durante el fin de semana en la sede Meléndez de la Universidad del Valle, en Cali. La Secretaría de Movilidad se pronunció.</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Lo que se sabe de la muerte de joven dentro de Univalle; hay varias preguntas</t>
+          <t>Buscan a joven que desapareció en río Lebrija en Santander en medio de fuertes lluvias</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -9065,12 +9065,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
@@ -9080,24 +9080,24 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/cali/lo-que-se-sabe-de-la-muerte-de-joven-dentro-de-univalle-hay-varias-preguntas/</t>
+          <t>https://www.elespectador.com/colombia/buscan-a-joven-que-desaparecio-en-rio-lebrija-en-santander-en-medio-de-fuertes-lluvias/</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>El caso ocurrió durante el fin de semana en la sede Meléndez de la Universidad del Valle, en Cali. La Secretaría de Movilidad se pronunció.</t>
+          <t>Un joven de 24 años desapareció en el río Lebrija tras ser arrastrado por corriente. Las lluvias dejan más de 140 familias damnificadas.</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Buscan a joven que desapareció en río Lebrija en Santander en medio de fuertes lluvias</t>
+          <t>Balacera en Barranquilla dejó tres personas heridas y tres capturadas</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -9112,12 +9112,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Barranquilla</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -9127,71 +9127,67 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/buscan-a-joven-que-desaparecio-en-rio-lebrija-en-santander-en-medio-de-fuertes-lluvias/</t>
+          <t>https://www.elespectador.com/colombia/barranquilla/balacera-en-barranquilla-dejo-tres-personas-heridas-y-tres-capturadas/</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>Un joven de 24 años desapareció en el río Lebrija tras ser arrastrado por corriente. Las lluvias dejan más de 140 familias damnificadas.</t>
+          <t>Una balacera, al parecer entre miembros de Pepes y Costeños, dejó tres heridos y tres capturados, entre ellos un menor de edad.</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Balacera en Barranquilla dejó tres personas heridas y tres capturadas</t>
+          <t>Insólito pedido de familia de David Acosta luego de que el joven apareciera con vida en Bogotá</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Pulzo</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Barranquilla</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/barranquilla/balacera-en-barranquilla-dejo-tres-personas-heridas-y-tres-capturadas/</t>
-        </is>
-      </c>
-      <c r="I189" t="inlineStr">
-        <is>
-          <t>Una balacera, al parecer entre miembros de Pepes y Costeños, dejó tres heridos y tres capturados, entre ellos un menor de edad.</t>
-        </is>
-      </c>
+          <t>https://www.pulzo.com/nacion/bogota/caso-david-acosta-familia-pide-cerrar-investigacion-falsa-desaparicion-PP5103111</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Insólito pedido de familia de David Acosta luego de que el joven apareciera con vida en Bogotá</t>
+          <t>Colombia tendrá más viejos que jóvenes a partir de esta fecha; hay alerta por las pensiones</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -9211,17 +9207,17 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>https://www.pulzo.com/nacion/bogota/caso-david-acosta-familia-pide-cerrar-investigacion-falsa-desaparicion-PP5103111</t>
+          <t>https://www.pulzo.com/economia/colombia-tendra-mas-viejos-que-jovenes-partir-esta-fecha-hay-alerta-PP5100998A</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -9234,27 +9230,27 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Colombia tendrá más viejos que jóvenes a partir de esta fecha; hay alerta por las pensiones</t>
+          <t>Adolescente de 14 años murió en riña entre menores de edad fuera de un colegio en Cali</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Pulzo</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
@@ -9264,30 +9260,34 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>https://www.pulzo.com/economia/colombia-tendra-mas-viejos-que-jovenes-partir-esta-fecha-hay-alerta-PP5100998A</t>
-        </is>
-      </c>
-      <c r="I191" t="inlineStr"/>
+          <t>https://www.elespectador.com/colombia/cali/adolescente-de-14-anos-murio-en-rina-entre-menores-de-edad-fuera-de-un-colegio-en-cali/</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>Adolescente de 14 años murió en riña entre menores afuera de un colegio en Cali. ¿Qué dicen las autoridades?</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Adolescente de 14 años murió en riña entre menores de edad fuera de un colegio en Cali</t>
+          <t>Mafe Carrascal explicó por qué la bancada del Pacto Histórico por Bogotá no asistió a encuentro con el alcalde Carlos Fernando Galán</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -9297,81 +9297,81 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/cali/adolescente-de-14-anos-murio-en-rina-entre-menores-de-edad-fuera-de-un-colegio-en-cali/</t>
+          <t>https://www.infobae.com/colombia/2026/03/17/mafe-carrascal-explico-por-que-la-bancada-del-pacto-historico-por-bogota-no-asistio-a-encuentro-con-el-alcalde-carlos-fernando-galan/</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>Adolescente de 14 años murió en riña entre menores afuera de un colegio en Cali. ¿Qué dicen las autoridades?</t>
+          <t>La representante indicó que la reunión se realizaría a puerta cerrada y que esta decisión contradice los intereses de su partido. Además, afirmó que al gobierno local le falta implementar políticas dirigidas a los jóvenes y a la prevención de...</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Mafe Carrascal explicó por qué la bancada del Pacto Histórico por Bogotá no asistió a encuentro con el alcalde Carlos Fernando Galán</t>
+          <t>Asesinan a joven de 15 años en Cartagena; su padre resultó herido al intentar defenderlo</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Seguridad</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/03/17/mafe-carrascal-explico-por-que-la-bancada-del-pacto-historico-por-bogota-no-asistio-a-encuentro-con-el-alcalde-carlos-fernando-galan/</t>
+          <t>https://www.elespectador.com/colombia/asesinan-a-menor-de-15-anos-en-cartagena-su-padre-resulto-herido-al-intentar-defenderlo/</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>La representante indicó que la reunión se realizaría a puerta cerrada y que esta decisión contradice los intereses de su partido. Además, afirmó que al gobierno local le falta implementar políticas dirigidas a los jóvenes y a la prevención de...</t>
+          <t>El presunto homicida ya fue localizado y detenido.</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Asesinan a joven de 15 años en Cartagena; su padre resultó herido al intentar defenderlo</t>
+          <t>Hallan el cuerpo de una adolescente en vivienda de Sahagún, Córdoba; autoridades investigan</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -9386,12 +9386,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Seguridad</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
@@ -9401,12 +9401,12 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/asesinan-a-menor-de-15-anos-en-cartagena-su-padre-resulto-herido-al-intentar-defenderlo/</t>
+          <t>https://www.elespectador.com/colombia/mas-regiones/hallan-el-cuerpo-de-una-menor-en-una-vivienda-de-sahagun-cordoba-autoridades-investigan/</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>El presunto homicida ya fue localizado y detenido.</t>
+          <t>En lo que va de este año, este sería el tercer caso de una mujer asesinada en el municipio y el cuarto en el departamento.</t>
         </is>
       </c>
     </row>
@@ -9418,7 +9418,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Hallan el cuerpo de una adolescente en vivienda de Sahagún, Córdoba; autoridades investigan</t>
+          <t>Dos jóvenes fueron detenidos por presunta extorsión en Santo Tomás, Atlántico</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -9433,7 +9433,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Seguridad</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -9448,44 +9448,44 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/mas-regiones/hallan-el-cuerpo-de-una-menor-en-una-vivienda-de-sahagun-cordoba-autoridades-investigan/</t>
+          <t>https://www.elespectador.com/colombia/mas-regiones/dos-jovenes-fueron-detenidos-por-presunta-extorsion-en-santo-tomas-atlantico/</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>En lo que va de este año, este sería el tercer caso de una mujer asesinada en el municipio y el cuarto en el departamento.</t>
+          <t>La investigación señala que los implicados habrían intimidado a un conductor de furgón.</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Dos jóvenes fueron detenidos por presunta extorsión en Santo Tomás, Atlántico</t>
+          <t>Con $86 mil millones de regalías, Bolívar construirá universidad en Montes de María y otros dos proyectos educativos</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Las2orillas</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Seguridad</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
@@ -9495,29 +9495,29 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/mas-regiones/dos-jovenes-fueron-detenidos-por-presunta-extorsion-en-santo-tomas-atlantico/</t>
+          <t>https://www.las2orillas.co/con-86-mil-millones-de-regalias-bolivar-construira-universidad-en-montes-de-maria-y-otros-dos-proyectos-educativos/</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>La investigación señala que los implicados habrían intimidado a un conductor de furgón.</t>
+          <t>Los proyectos impulsados por Yamil Arana buscan, entre otras cosas, abrir más de 4 mil cupos para jóvenes de una región que durante años fue escenario de conflictoEl artículoCon $86 mil millones de regalías, Bolívar construirá universidad en Montes...</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Con $86 mil millones de regalías, Bolívar construirá universidad en Montes de María y otros dos proyectos educativos</t>
+          <t>Nuevo giro en el caso de Tatiana Hernández, joven desaparecida en Cartagena: la buscan en el mar</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Las2orillas</t>
+          <t>Pulzo</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -9527,12 +9527,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Protección</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Cartagena</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
@@ -9542,57 +9542,57 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>https://www.las2orillas.co/con-86-mil-millones-de-regalias-bolivar-construira-universidad-en-montes-de-maria-y-otros-dos-proyectos-educativos/</t>
-        </is>
-      </c>
-      <c r="I197" t="inlineStr">
-        <is>
-          <t>Los proyectos impulsados por Yamil Arana buscan, entre otras cosas, abrir más de 4 mil cupos para jóvenes de una región que durante años fue escenario de conflictoEl artículoCon $86 mil millones de regalías, Bolívar construirá universidad en Montes...</t>
-        </is>
-      </c>
+          <t>https://www.pulzo.com/nacion/caso-tatiana-hernandez-da-giro-autoridades-intensifican-busqueda-mar-PP5091130</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Nuevo giro en el caso de Tatiana Hernández, joven desaparecida en Cartagena: la buscan en el mar</t>
+          <t>Prosperidad Social responde a inquietudes sobre Renta Joven</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Pulzo</t>
+          <t>Prosperidad Social</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Protección</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Cartagena</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>https://www.pulzo.com/nacion/caso-tatiana-hernandez-da-giro-autoridades-intensifican-busqueda-mar-PP5091130</t>
-        </is>
-      </c>
-      <c r="I198" t="inlineStr"/>
+          <t>https://prosperidadsocial.gov.co/Noticias/prosperidad-social-responde-a-inquietudes-sobre-renta-joven/</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>Bogotá D. C, 4 de marzo de 2026. Prosperidad Social se permite aclarar a la ciudadanía y, especialmente, a los participantes de Renta Joven algunas dudas e inquietudes que han expresado los beneficiarios en las redes sociales. Prosperidad Social...</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -9602,7 +9602,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Prosperidad Social responde a inquietudes sobre Renta Joven</t>
+          <t>Maratón por las generaciones atendió a más de 38.000 jóvenes y personas mayores beneficiarias de Prosperidad Social</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -9632,12 +9632,12 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>https://prosperidadsocial.gov.co/Noticias/prosperidad-social-responde-a-inquietudes-sobre-renta-joven/</t>
+          <t>https://prosperidadsocial.gov.co/Noticias/maraton-por-las-generaciones-atendio-a-mas-de-38-000-jovenes-y-personas-mayores-beneficiarias-de-prosperidad-social/</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>Bogotá D. C, 4 de marzo de 2026. Prosperidad Social se permite aclarar a la ciudadanía y, especialmente, a los participantes de Renta Joven algunas dudas e inquietudes que han expresado los beneficiarios en las redes sociales. Prosperidad Social...</t>
+          <t>Durante 38 horas continuas, se resolvieron inquietudes y dudas a beneficiarias y beneficiarios de los programas Renta Joven y Colombia Mayor. Nueve de cada 10 personas afirmaron haber recibido información clara y efectiva para resolver sus...</t>
         </is>
       </c>
     </row>
@@ -9649,42 +9649,42 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Maratón por las generaciones atendió a más de 38.000 jóvenes y personas mayores beneficiarias de Prosperidad Social</t>
+          <t>Joven rompió el silencio y reveló desgarradores detalles de los feminicidios más brutales del Valle del Cauca</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Prosperidad Social</t>
+          <t>Las2orillas</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>https://prosperidadsocial.gov.co/Noticias/maraton-por-las-generaciones-atendio-a-mas-de-38-000-jovenes-y-personas-mayores-beneficiarias-de-prosperidad-social/</t>
+          <t>https://www.las2orillas.co/joven-rompio-el-silencio-y-revelo-desgarradores-detalles-de-los-feminicidios-mas-brutales-del-valle-del-cauca/</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>Durante 38 horas continuas, se resolvieron inquietudes y dudas a beneficiarias y beneficiarios de los programas Renta Joven y Colombia Mayor. Nueve de cada 10 personas afirmaron haber recibido información clara y efectiva para resolver sus...</t>
+          <t>Mientras la Fiscalía la señala de disparar contra las víctimas, Angy Pérez asegura que fue obligada a desmembrar los cuerpos bajo la amenaza de perder a su bebéEl artículoJoven rompió el silencio y reveló desgarradores detalles de los feminicidios...</t>
         </is>
       </c>
     </row>
@@ -9696,42 +9696,42 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Joven rompió el silencio y reveló desgarradores detalles de los feminicidios más brutales del Valle del Cauca</t>
+          <t>Colombia Mayor y Renta Joven: Prosperidad Social realizará la Maratón por las Generaciones</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Las2orillas</t>
+          <t>Prosperidad Social</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Protección</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>https://www.las2orillas.co/joven-rompio-el-silencio-y-revelo-desgarradores-detalles-de-los-feminicidios-mas-brutales-del-valle-del-cauca/</t>
+          <t>https://prosperidadsocial.gov.co/Noticias/colombia-mayor-y-renta-joven-prosperidad-social-realizara-la-maraton-por-las-generaciones/</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>Mientras la Fiscalía la señala de disparar contra las víctimas, Angy Pérez asegura que fue obligada a desmembrar los cuerpos bajo la amenaza de perder a su bebéEl artículoJoven rompió el silencio y reveló desgarradores detalles de los feminicidios...</t>
+          <t>Se trata de una jornada continua de atención telefónica, en la que se resolverán inquietudes que tengan beneficiarias y beneficiarios de estos dos programas de la entidad. El canal telefónico tendrá atención continua por más de 36 horas, mientras...</t>
         </is>
       </c>
     </row>
@@ -9743,101 +9743,101 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Colombia Mayor y Renta Joven: Prosperidad Social realizará la Maratón por las Generaciones</t>
+          <t>Así fue la despedida de Iván Zuleta a su sobrina Daniela: la joven fue encontrada sin signos vitales en su habitación</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Prosperidad Social</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Protección</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Valledupar</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>https://prosperidadsocial.gov.co/Noticias/colombia-mayor-y-renta-joven-prosperidad-social-realizara-la-maraton-por-las-generaciones/</t>
+          <t>https://www.infobae.com/colombia/2026/03/11/asi-fue-la-despedida-de-ivan-zuleta-a-su-sobrina-daniela-que-habria-sido-encontrada-sin-signos-vitales-en-su-habitacion/</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>Se trata de una jornada continua de atención telefónica, en la que se resolverán inquietudes que tengan beneficiarias y beneficiarios de estos dos programas de la entidad. El canal telefónico tendrá atención continua por más de 36 horas, mientras...</t>
+          <t>La partida de la joven Zuleta Gnecco, hija de Fabián Zuleta y nieta de Fabio Zuleta, ha conmovido al mundo del vallenato, reuniendo a familiares y músicos icónicos para despedirla en Valledupar con emotivas muestras de cariño</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Así fue la despedida de Iván Zuleta a su sobrina Daniela: la joven fue encontrada sin signos vitales en su habitación</t>
+          <t>Jóvenes en San Cristóbal inician su formación en servicio para el sector de la gastronomía</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>SDIS - Juventud</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Valledupar</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/03/11/asi-fue-la-despedida-de-ivan-zuleta-a-su-sobrina-daniela-que-habria-sido-encontrada-sin-signos-vitales-en-su-habitacion/</t>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#79ade27adc</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>La partida de la joven Zuleta Gnecco, hija de Fabián Zuleta y nieta de Fabio Zuleta, ha conmovido al mundo del vallenato, reuniendo a familiares y músicos icónicos para despedirla en Valledupar con emotivas muestras de cariño</t>
+          <t>•24 chicos y chicas iniciaron su camino en la Academia Ñam, en donde se formarán en servicio a la mesa para mejorar sus oportunidades de empleabilidad en el sector de la gastronomía. •La inducción, que tuvo lugar en el Centro de Desarrollo...</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Jóvenes en San Cristóbal inician su formación en servicio para el sector de la gastronomía</t>
+          <t>La Academia Ñam llega a San Cristóbal con oportunidades para los jóvenes interesados en el sector de la gastronomía</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -9867,24 +9867,24 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#79ade27adc</t>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#1e64cd90aa</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>•24 chicos y chicas iniciaron su camino en la Academia Ñam, en donde se formarán en servicio a la mesa para mejorar sus oportunidades de empleabilidad en el sector de la gastronomía. •La inducción, que tuvo lugar en el Centro de Desarrollo...</t>
+          <t>•El Distrito, en alianza con la Fundación Gastronomía Social, lanzan una nueva convocatoria dirigida a jóvenes de 18 a 30 años interesados en formarse en servicio para el sector de la gastronomía. •Esta formación gratuita ofrece capacitación a...</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Bogotá presenta estudio que analiza los factores asociados a la vinculación de adolescentes a conductas punibles</t>
+          <t>El deporte abrió la puerta a nuevas oportunidades y conexión para los jóvenes de Bogotá</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -9899,7 +9899,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Cultura y deporte</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -9914,34 +9914,34 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#fb504c6e8d</t>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#8b36ede0c2</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>• La vinculación de adolescentes a conductas punibles no responde a una sola causa, sino a la convergencia de factores estructurales, familiares, territoriales y personales que requieren respuestas integrales y no únicamente punitivas. • El consumo...</t>
+          <t>• En la localidad de Kennedy se realizó una jornada deportiva con Futsala Colombia, que acercó a los jóvenes la oferta integral de servicios sociales, digitales y educativos en territorio. • En Jóvenes con Oportunidades, más de 18.000 jóvenes han...</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>La Academia Ñam llega a San Cristóbal con oportunidades para los jóvenes interesados en el sector de la gastronomía</t>
+          <t>Abre 320 becas a jóvenes con proyectos en sus comunidades o entornos, ¿cómo participar?</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>SDIS - Juventud</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -9961,86 +9961,86 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#1e64cd90aa</t>
+          <t>https://www.elespectador.com/colombia/mas-regiones/abre-320-becas-a-jovenes-con-proyectos-en-sus-comunidades-o-entornos-como-participar/</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>•El Distrito, en alianza con la Fundación Gastronomía Social, lanzan una nueva convocatoria dirigida a jóvenes de 18 a 30 años interesados en formarse en servicio para el sector de la gastronomía. •Esta formación gratuita ofrece capacitación a...</t>
+          <t>Abren becas para jóvenes en Medellín, Santa Marta, Cartagena y Bogotá. Tendrán formación, mentorías y acceso a redes de liderazgo.</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>El deporte abrió la puerta a nuevas oportunidades y conexión para los jóvenes de Bogotá</t>
+          <t>La primera guardia afro urbana liderada por mujeres surge en Cali</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>SDIS - Juventud</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Cultura y deporte</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#8b36ede0c2</t>
+          <t>https://www.elespectador.com/colombia/cali/la-primera-guardia-afro-urbana-liderada-por-mujeres-surge-en-cali/</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>• En la localidad de Kennedy se realizó una jornada deportiva con Futsala Colombia, que acercó a los jóvenes la oferta integral de servicios sociales, digitales y educativos en territorio. • En Jóvenes con Oportunidades, más de 18.000 jóvenes han...</t>
+          <t>En Llano Verde, mujeres desplazadas crearon la primera guardia afro urbana del país para prevenir violencia y proteger a jóvenes.</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Abre 320 becas a jóvenes con proyectos en sus comunidades o entornos, ¿cómo participar?</t>
+          <t>Bogotá fortalece el proceso de preinscripción de Jóvenes con Oportunidades 2026 y habilita nuevo enlace</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>SDIS - Juventud</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -10055,24 +10055,24 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/mas-regiones/abre-320-becas-a-jovenes-con-proyectos-en-sus-comunidades-o-entornos-como-participar/</t>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#6c31bba0c9</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>Abren becas para jóvenes en Medellín, Santa Marta, Cartagena y Bogotá. Tendrán formación, mentorías y acceso a redes de liderazgo.</t>
+          <t>•El Distrito habilitó un nuevo enlace mejorado para garantizar una experiencia más ágil, estable y segura en la convocatoria 2026 de Jóvenes con Oportunidades. •Las y los jóvenes entre 14 y 28 años que vivan en Bogotá y estén clasificados en Sisbén...</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>La primera guardia afro urbana liderada por mujeres surge en Cali</t>
+          <t>Aumenta el número de desaparecidos en Córdoba, dos jóvenes arrastrados por un arroyo</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -10087,12 +10087,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Protección</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
@@ -10102,24 +10102,24 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/cali/la-primera-guardia-afro-urbana-liderada-por-mujeres-surge-en-cali/</t>
+          <t>https://www.elespectador.com/colombia/mas-regiones/dos-campesinos-en-cordoba-desaparecen-tras-intentar-cruzar-un-arroyo/</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>En Llano Verde, mujeres desplazadas crearon la primera guardia afro urbana del país para prevenir violencia y proteger a jóvenes.</t>
+          <t>Dos jóvenes campesinos permanecen desaparecidos en Córdoba, luego de que una corriente los arrastrara en cuanto intentaban cruzar un arroyo</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Bogotá fortalece el proceso de preinscripción de Jóvenes con Oportunidades 2026 y habilita nuevo enlace</t>
+          <t>Bogotá abre convocatoria 2026 del programa Jóvenes con Oportunidades con más de 12.000 nuevos cupos</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -10149,81 +10149,77 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#6c31bba0c9</t>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#9a0f0687f3</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>•El Distrito habilitó un nuevo enlace mejorado para garantizar una experiencia más ágil, estable y segura en la convocatoria 2026 de Jóvenes con Oportunidades. •Las y los jóvenes entre 14 y 28 años que vivan en Bogotá y estén clasificados en Sisbén...</t>
+          <t>• El Distrito abre estaconvocatoria de Jóvenes con Oportunidades con más de 8.000 nuevos cupos, en su primera etapa, para jóvenes entre 14 y 28 años de Bogotá, fortaleciendo su acceso a rutas de formación, acompañamiento psicosocial y transferencias...</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Aumenta el número de desaparecidos en Córdoba, dos jóvenes arrastrados por un arroyo</t>
+          <t>Menores de edad mataron de 17 puñaladas a un hombre que iba de polizón en un camión de carga en la vía Bogotá-Villavicencio: quedó en video - Infobae</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Protección</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/mas-regiones/dos-campesinos-en-cordoba-desaparecen-tras-intentar-cruzar-un-arroyo/</t>
-        </is>
-      </c>
-      <c r="I211" t="inlineStr">
-        <is>
-          <t>Dos jóvenes campesinos permanecen desaparecidos en Córdoba, luego de que una corriente los arrastrara en cuanto intentaban cruzar un arroyo</t>
-        </is>
-      </c>
+          <t>https://news.google.com/rss/articles/CBMikAJBVV95cUxNYWQxNTA1UWhDOUtWS2dSWXNNQ19idDVRNXV4aktnZzFERmdBaFg0c2lrT2plR0tXcDN1dlFhd0J0Q1BUVmJEVU1YYTR3N0NtQUx2LTQ3amhNR2pNc0tvcjR6X1FfbkIwczFROFJTaFotclVpRGxId2h1eWtqbHMzSkNXc0JCeU1DWjkxOG5qekx4YjZGRlVVckdyX1gyT0luR2Nkd3ZQUTNFM1d1LUlvMzNSSGxiQUZ5V2pqT2E4WXhZWWRpY2JheDhpaWhwOTQwLThDWFlXU1p0N0lZVk5nSHdVZU8zWVlKNE9GTVJKaUxYTkxDMUt1MTF0NzN5MVUxXzBNUjZtZVJsWm9zMkNNdg?oc=5</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Bogotá abre convocatoria 2026 del programa Jóvenes con Oportunidades con más de 12.000 nuevos cupos</t>
+          <t>Menores de edad mataron de 17 puñaladas a un hombre que iba de polizón en un camión de carga en la vía Bogotá-Villavicencio: quedó en video - Infobae</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>SDIS - Juventud</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -10243,24 +10239,20 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#9a0f0687f3</t>
-        </is>
-      </c>
-      <c r="I212" t="inlineStr">
-        <is>
-          <t>• El Distrito abre estaconvocatoria de Jóvenes con Oportunidades con más de 8.000 nuevos cupos, en su primera etapa, para jóvenes entre 14 y 28 años de Bogotá, fortaleciendo su acceso a rutas de formación, acompañamiento psicosocial y transferencias...</t>
-        </is>
-      </c>
+          <t>https://news.google.com/rss/articles/CBMikAJBVV95cUxNYWQxNTA1UWhDOUtWS2dSWXNNQ19idDVRNXV4aktnZzFERmdBaFg0c2lrT2plR0tXcDN1dlFhd0J0Q1BUVmJEVU1YYTR3N0NtQUx2LTQ3amhNR2pNc0tvcjR6X1FfbkIwczFROFJTaFotclVpRGxId2h1eWtqbHMzSkNXc0JCeU1DWjkxOG5qekx4YjZGRlVVckdyX1gyT0luR2Nkd3ZQUTNFM1d1LUlvMzNSSGxiQUZ5V2pqT2E4WXhZWWRpY2JheDhpaWhwOTQwLThDWFlXU1p0N0lZVk5nSHdVZU8zWVlKNE9GTVJKaUxYTkxDMUt1MTF0NzN5MVUxXzBNUjZtZVJsWm9zMkNNdtIBqwJBVV95cUxPZnpNT2FPSmdUeFl0UmFScGh6MzVlYm9tVWhQekJjVTdRcHM2ZDlEbWFhVUJBX3dudVF2V01OaDdSRWN6c1FXV2thM0VJOHppRWhaWEVpbTVPOTVTd3RKcmJLT1NHa2MwVlR5SzE2TzlHM0RLS3k2VzFKRDdtaTd2M3RCNENTeXByY1BBTjR1SFE3STJQS3JBWURBRER1cTBKQmx2MVR6Sk5xYlpwbTdpNGRyWVBYdmkxTU9JaWNtRlZVM2JzTGtMQUhxaHFnUmVPQlNPbkNYWGlBX2ttc0Y4cjVzR0dVaFBER3lSMWxRZGVGVTRhTFZ6RE82ZzFKeWJnQ0U0bWlINmlXRE9KdUJvbzdpSEg1NURXMzZKeVNHWTd4b0puVldnbFlscw?oc=5</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Menores de edad mataron de 17 puñaladas a un hombre que iba de polizón en un camión de carga en la vía Bogotá-Villavicencio: quedó en video - Infobae</t>
+          <t>Jóvenes narraron el calvario sufrido cuando fueron víctimas de presunto abuso en la Universidad de Cartagena: “Causó un gran sangrado”</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -10275,22 +10267,22 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Cartagena</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAJBVV95cUxNYWQxNTA1UWhDOUtWS2dSWXNNQ19idDVRNXV4aktnZzFERmdBaFg0c2lrT2plR0tXcDN1dlFhd0J0Q1BUVmJEVU1YYTR3N0NtQUx2LTQ3amhNR2pNc0tvcjR6X1FfbkIwczFROFJTaFotclVpRGxId2h1eWtqbHMzSkNXc0JCeU1DWjkxOG5qekx4YjZGRlVVckdyX1gyT0luR2Nkd3ZQUTNFM1d1LUlvMzNSSGxiQUZ5V2pqT2E4WXhZWWRpY2JheDhpaWhwOTQwLThDWFlXU1p0N0lZVk5nSHdVZU8zWVlKNE9GTVJKaUxYTkxDMUt1MTF0NzN5MVUxXzBNUjZtZVJsWm9zMkNNdg?oc=5</t>
+          <t>https://www.infobae.com/colombia/2026/02/02/jovenes-narraron-el-calvario-sufrido-cuando-fueron-victimas-de-presunto-abuso-en-la-universidad-de-cartagena-causo-un-gran-sangrado/</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
@@ -10298,27 +10290,27 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Menores de edad mataron de 17 puñaladas a un hombre que iba de polizón en un camión de carga en la vía Bogotá-Villavicencio: quedó en video - Infobae</t>
+          <t>Bogotá abre nueva convocatoria de Academia Ñam para fortalecer la empleabilidad juvenil en el sector gastronómico</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>SDIS - Juventud</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -10333,20 +10325,24 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAJBVV95cUxNYWQxNTA1UWhDOUtWS2dSWXNNQ19idDVRNXV4aktnZzFERmdBaFg0c2lrT2plR0tXcDN1dlFhd0J0Q1BUVmJEVU1YYTR3N0NtQUx2LTQ3amhNR2pNc0tvcjR6X1FfbkIwczFROFJTaFotclVpRGxId2h1eWtqbHMzSkNXc0JCeU1DWjkxOG5qekx4YjZGRlVVckdyX1gyT0luR2Nkd3ZQUTNFM1d1LUlvMzNSSGxiQUZ5V2pqT2E4WXhZWWRpY2JheDhpaWhwOTQwLThDWFlXU1p0N0lZVk5nSHdVZU8zWVlKNE9GTVJKaUxYTkxDMUt1MTF0NzN5MVUxXzBNUjZtZVJsWm9zMkNNdtIBqwJBVV95cUxPZnpNT2FPSmdUeFl0UmFScGh6MzVlYm9tVWhQekJjVTdRcHM2ZDlEbWFhVUJBX3dudVF2V01OaDdSRWN6c1FXV2thM0VJOHppRWhaWEVpbTVPOTVTd3RKcmJLT1NHa2MwVlR5SzE2TzlHM0RLS3k2VzFKRDdtaTd2M3RCNENTeXByY1BBTjR1SFE3STJQS3JBWURBRER1cTBKQmx2MVR6Sk5xYlpwbTdpNGRyWVBYdmkxTU9JaWNtRlZVM2JzTGtMQUhxaHFnUmVPQlNPbkNYWGlBX2ttc0Y4cjVzR0dVaFBER3lSMWxRZGVGVTRhTFZ6RE82ZzFKeWJnQ0U0bWlINmlXRE9KdUJvbzdpSEg1NURXMzZKeVNHWTd4b0puVldnbFlscw?oc=5</t>
-        </is>
-      </c>
-      <c r="I214" t="inlineStr"/>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#85a520b8bc</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>• La Secretaría Distrital de Integración Social, en alianza con la Fundación Gastronomía Social, abre una nueva convocatoria de Academia Ñam, un programa gratuito de formación y práctica laboral en servicio gastronómico dirigido a jóvenes de 18 a 30...</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Jóvenes narraron el calvario sufrido cuando fueron víctimas de presunto abuso en la Universidad de Cartagena: “Causó un gran sangrado”</t>
+          <t>Frustraron robo en un restaurante en Bosa, Bogotá: un hombre de 23 años y dos menores de edad fueron capturados</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -10361,22 +10357,22 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Seguridad</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Cartagena</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/02/02/jovenes-narraron-el-calvario-sufrido-cuando-fueron-victimas-de-presunto-abuso-en-la-universidad-de-cartagena-causo-un-gran-sangrado/</t>
+          <t>https://www.infobae.com/colombia/2026/01/27/frustraron-robo-en-un-restaurante-en-bosa-bogota-un-hombre-de-23-anos-y-dos-menores-de-edad-fueron-capturados/</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
@@ -10384,74 +10380,70 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Bogotá abre nueva convocatoria de Academia Ñam para fortalecer la empleabilidad juvenil en el sector gastronómico</t>
+          <t>Alerta en Tolima: ya son 4 los muertos por fiebre amarilla en 2026, entre ellos un menor de edad</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>SDIS - Juventud</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#85a520b8bc</t>
-        </is>
-      </c>
-      <c r="I216" t="inlineStr">
-        <is>
-          <t>• La Secretaría Distrital de Integración Social, en alianza con la Fundación Gastronomía Social, abre una nueva convocatoria de Academia Ñam, un programa gratuito de formación y práctica laboral en servicio gastronómico dirigido a jóvenes de 18 a 30...</t>
-        </is>
-      </c>
+          <t>https://www.bluradio.com/nacion/alerta-en-tolima-ya-son-4-los-muertos-por-fiebre-amarilla-en-2026-entre-ellos-un-menor-de-edad-rg10</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Frustraron robo en un restaurante en Bosa, Bogotá: un hombre de 23 años y dos menores de edad fueron capturados</t>
+          <t>Distrito Joven acompañó a más de 50 mil jóvenes en la construcción de sus proyectos de vida durante 2025</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>SDIS - Juventud</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Seguridad</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -10466,25 +10458,29 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/27/frustraron-robo-en-un-restaurante-en-bosa-bogota-un-hombre-de-23-anos-y-dos-menores-de-edad-fueron-capturados/</t>
-        </is>
-      </c>
-      <c r="I217" t="inlineStr"/>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#729a4b8e04</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>• Durante 2025, la Subdirección para la Juventud acompañó a más de 50 mil jóvenes en Bogotá, fortaleciendo sus proyectos de vida a través de una atención integral. • Los servicios y estrategias implementados promovieron la inclusión social,...</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Alerta en Tolima: ya son 4 los muertos por fiebre amarilla en 2026, entre ellos un menor de edad</t>
+          <t>Radiografía de los ‘ninis’ en Colombia: 2,26 millones de jóvenes están desconectados del estudio y el empleo - Infobae</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -10494,12 +10490,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Empleo</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
@@ -10509,7 +10505,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/nacion/alerta-en-tolima-ya-son-4-los-muertos-por-fiebre-amarilla-en-2026-entre-ellos-un-menor-de-edad-rg10</t>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxQQzU0U2tHY3lvTUVKRmR2SExOeUdySS0ycnZSVWd3MlhIQmJmYVZxNm9NNVZ2YU8wZ1MtcUJiOXRPLWZhWUNLcUtVdG1uUVVUd0VfYU5sQWVNSjlDVWdDUTc2ZG8yajJIUlk0bVJxTTR3clhjd0wwRl9wSTRSUlk0UnZtY2FZTWZ2QUhQbjJ1TkdibEw4YmU4YXNTMEJUeV85V0dfSzdUQ0hSSk5DbFdZUk5VV2dnaGdabHhVQ1p2bjlCTlVKNHJNV3NoNmQtcG9CUkZaMWVDVXZmWDFXSTIxVi00UdIB_gFBVV95cUxQQXJkUXE5UnM4ZVhIZHo3UFJuSU0xVllueWt3Unk2aC03YllYdDBfc0FvalRGMDNsWjBRNmZfNUV1bTlsbWM3dFlLOGNCajVqcXQ5Z2hVRzdROXlpTUdrWEtLdVNyaDFqRGlnckQ3OUhfTjVNVk53YklESGhMMlRCcUVkNFRYMS04RUUwR2hvdERISVdENVlydzZhOGpfaU1yX0xkSkg0S3laV3E2MVV1UHRDN05aRU1iMlBiS2lRcXNWYTdMTlhVTzI2VkJkeFZTXzhqbS1adkpFa1RiX2dBaDJDaWhVYXVsM1psSV9jWjZGdy1QUXJ1d0xCdUxMdw?oc=5</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
@@ -10522,7 +10518,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Distrito Joven acompañó a más de 50 mil jóvenes en la construcción de sus proyectos de vida durante 2025</t>
+          <t>Casas de Juventud lanzan nuevos Semilleros Distritales para potenciar el talento juvenil en Bogotá</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -10537,7 +10533,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Cultura y deporte</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -10552,24 +10548,24 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#729a4b8e04</t>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#f8686f5026</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>• Durante 2025, la Subdirección para la Juventud acompañó a más de 50 mil jóvenes en Bogotá, fortaleciendo sus proyectos de vida a través de una atención integral. • Los servicios y estrategias implementados promovieron la inclusión social,...</t>
+          <t>•Bogotá abre la convocatoria a semilleros gratuitos en artes, deporte y cultura urbana, dirigidos a jóvenes entre 14 y 28 años de todas las localidades, como una estrategia distrital para fortalecer la expresión, la participación y el desarrollo de...</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Radiografía de los ‘ninis’ en Colombia: 2,26 millones de jóvenes están desconectados del estudio y el empleo - Infobae</t>
+          <t>Estudio reveló las principales problemáticas que preocupan a los jóvenes en Colombia, previo a las elecciones de Congreso y Presidencia - Infobae</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -10584,7 +10580,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Empleo</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
@@ -10599,7 +10595,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxQQzU0U2tHY3lvTUVKRmR2SExOeUdySS0ycnZSVWd3MlhIQmJmYVZxNm9NNVZ2YU8wZ1MtcUJiOXRPLWZhWUNLcUtVdG1uUVVUd0VfYU5sQWVNSjlDVWdDUTc2ZG8yajJIUlk0bVJxTTR3clhjd0wwRl9wSTRSUlk0UnZtY2FZTWZ2QUhQbjJ1TkdibEw4YmU4YXNTMEJUeV85V0dfSzdUQ0hSSk5DbFdZUk5VV2dnaGdabHhVQ1p2bjlCTlVKNHJNV3NoNmQtcG9CUkZaMWVDVXZmWDFXSTIxVi00UdIB_gFBVV95cUxQQXJkUXE5UnM4ZVhIZHo3UFJuSU0xVllueWt3Unk2aC03YllYdDBfc0FvalRGMDNsWjBRNmZfNUV1bTlsbWM3dFlLOGNCajVqcXQ5Z2hVRzdROXlpTUdrWEtLdVNyaDFqRGlnckQ3OUhfTjVNVk53YklESGhMMlRCcUVkNFRYMS04RUUwR2hvdERISVdENVlydzZhOGpfaU1yX0xkSkg0S3laV3E2MVV1UHRDN05aRU1iMlBiS2lRcXNWYTdMTlhVTzI2VkJkeFZTXzhqbS1adkpFa1RiX2dBaDJDaWhVYXVsM1psSV9jWjZGdy1QUXJ1d0xCdUxMdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwJBVV95cUxNYXdTSFVia3cwbnV6Y050TzB5M2JQckhpbDVVajdoRnZnZG1yTThKbVF0bFhsUWN0ZnFuM1h5M0VYWmxiUGZjaHN3WV85OFpwWlFaWkFkanlsSmcwNFhJQk5PTjJBZ3RXcTgzNHFCQU5qTGlUZlB3WTkxZmx3SVIwV05jblIwUFNNUUdBTkU2M2FZSHNlTUgyb2ZhZWsyMktyc0UtR2k2Z001NkUxZ01xSkxoei1uMUZqaGJfV0k2MWktaDVNRGtGOS1nNXlGTEdSZ1VSdEJGRDRkbkNPM3R1aURVbl9ZR3FYcC1aMkI4T0k4bDJaT0Jmb1dLNktqQVVOeHVpUGpkUGd3TmvSAaYCQVVfeXFMTl9Uc2p1OEVpYzZaLUFYOERNUjVQVjVSaHJtTEhhT1BibW1BMkVwQ0VVUFc3d2RsaWNtNHdTZm0tbDRlMHBPLWVES0Vyd3hKZHRQUmExYmVmaXNrZE5rTGhEWmd0YXQ5cjdPOGIyeVdEYUV5NHplUnFMX2pYWkRXdEFxbVB1UGhEOENhTWM3S2NCVnJQbDg4clVoSUhIWENVSUh1VE54MjZKUjF3OWdpUDZjdld4WU1BLTA2dWR2ZEwxQUpnLUNXS3JZZ2hWUkFQN2taQktacVNhM3NMOS1ZR1g2dkhmYmVmU0Q4Q0o2dWNCZUNMQnJsaDFjQlRXQUp5NUpEYllxWlhVQVVfbVlBdmVBa2RJRjVqNUNfTGxHMnFRaGhYMnN3?oc=5</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
@@ -10607,59 +10603,55 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Casas de Juventud lanzan nuevos Semilleros Distritales para potenciar el talento juvenil en Bogotá</t>
+          <t>Menor de edad colombiano fue baleado frente a su escuela en Chicago, la familia exige justicia</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>SDIS - Juventud</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Cultura y deporte</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#f8686f5026</t>
-        </is>
-      </c>
-      <c r="I221" t="inlineStr">
-        <is>
-          <t>•Bogotá abre la convocatoria a semilleros gratuitos en artes, deporte y cultura urbana, dirigidos a jóvenes entre 14 y 28 años de todas las localidades, como una estrategia distrital para fortalecer la expresión, la participación y el desarrollo de...</t>
-        </is>
-      </c>
+          <t>https://www.infobae.com/colombia/2026/01/14/menor-de-edad-colombiano-fue-baleado-frente-a-su-escuela-en-chicago-la-familia-exige-justicia/</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Estudio reveló las principales problemáticas que preocupan a los jóvenes en Colombia, previo a las elecciones de Congreso y Presidencia - Infobae</t>
+          <t>El particular castigo de Policía en Barranquilla a un grupo de jóvenes quedó en video: “El cuerpo sufre”</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -10674,12 +10666,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Seguridad</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Barranquilla</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
@@ -10689,7 +10681,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwJBVV95cUxNYXdTSFVia3cwbnV6Y050TzB5M2JQckhpbDVVajdoRnZnZG1yTThKbVF0bFhsUWN0ZnFuM1h5M0VYWmxiUGZjaHN3WV85OFpwWlFaWkFkanlsSmcwNFhJQk5PTjJBZ3RXcTgzNHFCQU5qTGlUZlB3WTkxZmx3SVIwV05jblIwUFNNUUdBTkU2M2FZSHNlTUgyb2ZhZWsyMktyc0UtR2k2Z001NkUxZ01xSkxoei1uMUZqaGJfV0k2MWktaDVNRGtGOS1nNXlGTEdSZ1VSdEJGRDRkbkNPM3R1aURVbl9ZR3FYcC1aMkI4T0k4bDJaT0Jmb1dLNktqQVVOeHVpUGpkUGd3TmvSAaYCQVVfeXFMTl9Uc2p1OEVpYzZaLUFYOERNUjVQVjVSaHJtTEhhT1BibW1BMkVwQ0VVUFc3d2RsaWNtNHdTZm0tbDRlMHBPLWVES0Vyd3hKZHRQUmExYmVmaXNrZE5rTGhEWmd0YXQ5cjdPOGIyeVdEYUV5NHplUnFMX2pYWkRXdEFxbVB1UGhEOENhTWM3S2NCVnJQbDg4clVoSUhIWENVSUh1VE54MjZKUjF3OWdpUDZjdld4WU1BLTA2dWR2ZEwxQUpnLUNXS3JZZ2hWUkFQN2taQktacVNhM3NMOS1ZR1g2dkhmYmVmU0Q4Q0o2dWNCZUNMQnJsaDFjQlRXQUp5NUpEYllxWlhVQVVfbVlBdmVBa2RJRjVqNUNfTGxHMnFRaGhYMnN3?oc=5</t>
+          <t>https://www.infobae.com/colombia/2026/01/09/el-particular-castigo-de-policia-en-barranquilla-a-un-grupo-de-jovenes-quedo-en-video-el-cuerpo-sufre/</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
@@ -10697,12 +10689,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Menor de edad colombiano fue baleado frente a su escuela en Chicago, la familia exige justicia</t>
+          <t>Aumenta a 1.419 el número de lesionados por pólvora en Colombia; 428 son menores de edad - Infobae</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -10717,7 +10709,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -10732,7 +10724,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/14/menor-de-edad-colombiano-fue-baleado-frente-a-su-escuela-en-chicago-la-familia-exige-justicia/</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxOY1FwS0xiWWVaYl9saTQ5X0xRYnVoR0lwNE5XYUVaaUl3LW8yN0hEZGFnckI5VVlrVnBPSFJpeDNkU1JIaC01dVJVdFJYbEtSVTFXRTBCdTFDSDJ6TXZjc2t5N0t0cVFUY2JGbGZ1NDB5R1FJVG1RX25hREVIMjZlYktrdHc2QUFiZXNQTXFGZk9zeWNJRUl1aWNCbG9OXzZRQVA2dFFUZ1J3UnJrZzU4Qnk5TVBMajBPenJOU0ZBekNheEl2SkV3QVRUc9IB5gFBVV95cUxQeDZfb0gzZm9CTTRpYWx1ZTBielQ1TVgtaHNBOXRVRjBDcVd2V3M2anR3VTJaLU8zUEFkbEJkdDFEcHdHQUlpNGVORDZXV1Jxdzl4YmdPN3F1bk10ODZ1MnpOUjVSRTZscUUzYl80MDVpaHROOXdBNlhoQkFFR3RyVVJ1MWw1WTVZZVcwWnZ6THBEYWkxR1hEMTQzRGIzRWJvWlVUOFFBU2duZE5MRnRoRnQyZDl0ajd2SEpUVVM5ZW5POEpzLUZIcTV1c3RaaHlvanRUcG1oU3REVFVVQk5xTnhuLWk1UQ?oc=5</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
@@ -10740,12 +10732,12 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>El particular castigo de Policía en Barranquilla a un grupo de jóvenes quedó en video: “El cuerpo sufre”</t>
+          <t>Gobierno condonará créditos del Icetex a más de mil jóvenes en Colombia: quiénes se beneficiarán - Infobae</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -10760,12 +10752,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Seguridad</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Barranquilla</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
@@ -10775,7 +10767,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/09/el-particular-castigo-de-policia-en-barranquilla-a-un-grupo-de-jovenes-quedo-en-video-el-cuerpo-sufre/</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxOZlVSRmszbERPaGNNNjhFRXY3VGVlUjc0eXo5R002RDZTbk15NWlUb1pLeWtWdmtObV9fY2ZxUmQ3cHNacWJoMExhZVZDRjlJM0lYZ2VfUVJOTEJnOXhGeXhtOFdlX3BmdFZTWXNJWHpXSDJsREdSaXJHSmFfY0RCcV8xSFVTLThuS1M4eUwxYTMxdWU2WTY3YUVTaWtLWHJFRUhlM0EtQzFNdDQwNy1wU2NyMDIzSk5rZGI4ZExtcmx1b2R2d01DNzdZT29LanFzXzBaNjluZ0rSAfMBQVVfeXFMT3pmVy1QSHJLaTJmREJmLVNLano0XzdpeW1VemRocGF5eHBVZktPRnNkTnNBUElFMDk1UUQ4MTZRNENCVWpZQVhTRmNrV1dwbDhCQnFvemZKTmZyT2cwdV96a2xOUWZDZEloWEFKcjJ2QkJsX0h3bFZDTkNRNGJOY1U5UGZaN0x6YU1EQlN5ZlFLb0hYQkM1MDdKNWl5TS1OcVNYWHRGXzl5NFp1WnQ2YWJqcWZzZDlDTk5FQ19Sa2lZOXRpOEJ4LV9DUnVOenhkQ3FJUGhkZkExNkNOYlV2Z21iLUQxUmF0eDJ5c3NyekcxTFlF?oc=5</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
@@ -10783,98 +10775,106 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Aumenta a 1.419 el número de lesionados por pólvora en Colombia; 428 son menores de edad - Infobae</t>
+          <t>Más de 40 jóvenes de Bogotá fueron reconocidos por su talento, creatividad y liderazgo en la Semana de la Juventud y la Semana Andina 2025</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>SDIS - Juventud</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Cultura y deporte</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxOY1FwS0xiWWVaYl9saTQ5X0xRYnVoR0lwNE5XYUVaaUl3LW8yN0hEZGFnckI5VVlrVnBPSFJpeDNkU1JIaC01dVJVdFJYbEtSVTFXRTBCdTFDSDJ6TXZjc2t5N0t0cVFUY2JGbGZ1NDB5R1FJVG1RX25hREVIMjZlYktrdHc2QUFiZXNQTXFGZk9zeWNJRUl1aWNCbG9OXzZRQVA2dFFUZ1J3UnJrZzU4Qnk5TVBMajBPenJOU0ZBekNheEl2SkV3QVRUc9IB5gFBVV95cUxQeDZfb0gzZm9CTTRpYWx1ZTBielQ1TVgtaHNBOXRVRjBDcVd2V3M2anR3VTJaLU8zUEFkbEJkdDFEcHdHQUlpNGVORDZXV1Jxdzl4YmdPN3F1bk10ODZ1MnpOUjVSRTZscUUzYl80MDVpaHROOXdBNlhoQkFFR3RyVVJ1MWw1WTVZZVcwWnZ6THBEYWkxR1hEMTQzRGIzRWJvWlVUOFFBU2duZE5MRnRoRnQyZDl0ajd2SEpUVVM5ZW5POEpzLUZIcTV1c3RaaHlvanRUcG1oU3REVFVVQk5xTnhuLWk1UQ?oc=5</t>
-        </is>
-      </c>
-      <c r="I225" t="inlineStr"/>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#c68de3a13a</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>• Más de 40 jóvenes y colectivos fueron premiados por su creatividad, liderazgo y compromiso social durante la Semana de la Juventud y la Semana Andina 2025. • La Subdirección para la Juventud de la Secretaría Distrital de Integración Social abrió...</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Gobierno condonará créditos del Icetex a más de mil jóvenes en Colombia: quiénes se beneficiarán - Infobae</t>
+          <t>Jóvenes con Oportunidades abre convocatoria para su ruta de formación en cursos cortos</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>SDIS - Juventud</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Empleo</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxOZlVSRmszbERPaGNNNjhFRXY3VGVlUjc0eXo5R002RDZTbk15NWlUb1pLeWtWdmtObV9fY2ZxUmQ3cHNacWJoMExhZVZDRjlJM0lYZ2VfUVJOTEJnOXhGeXhtOFdlX3BmdFZTWXNJWHpXSDJsREdSaXJHSmFfY0RCcV8xSFVTLThuS1M4eUwxYTMxdWU2WTY3YUVTaWtLWHJFRUhlM0EtQzFNdDQwNy1wU2NyMDIzSk5rZGI4ZExtcmx1b2R2d01DNzdZT29LanFzXzBaNjluZ0rSAfMBQVVfeXFMT3pmVy1QSHJLaTJmREJmLVNLano0XzdpeW1VemRocGF5eHBVZktPRnNkTnNBUElFMDk1UUQ4MTZRNENCVWpZQVhTRmNrV1dwbDhCQnFvemZKTmZyT2cwdV96a2xOUWZDZEloWEFKcjJ2QkJsX0h3bFZDTkNRNGJOY1U5UGZaN0x6YU1EQlN5ZlFLb0hYQkM1MDdKNWl5TS1OcVNYWHRGXzl5NFp1WnQ2YWJqcWZzZDlDTk5FQ19Sa2lZOXRpOEJ4LV9DUnVOenhkQ3FJUGhkZkExNkNOYlV2Z21iLUQxUmF0eDJ5c3NyekcxTFlF?oc=5</t>
-        </is>
-      </c>
-      <c r="I226" t="inlineStr"/>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#28dd65106b</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>•La Subdirección para la Juventud anunció la apertura de nuevos cupos en la ruta de formación en cursos cortos, dirigida a jóvenes entre 18 y 28 años que vivan en Bogotá y cuenten con Sisbén IV (A1 a C09). • La ruta combina proyecto de vida, cursos...</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Más de 40 jóvenes de Bogotá fueron reconocidos por su talento, creatividad y liderazgo en la Semana de la Juventud y la Semana Andina 2025</t>
+          <t>La Academia Ñam busca jóvenes interesados en el sector de la gastronomía</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -10889,7 +10889,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Cultura y deporte</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
@@ -10904,24 +10904,24 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#c68de3a13a</t>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#8622ae2557</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>• Más de 40 jóvenes y colectivos fueron premiados por su creatividad, liderazgo y compromiso social durante la Semana de la Juventud y la Semana Andina 2025. • La Subdirección para la Juventud de la Secretaría Distrital de Integración Social abrió...</t>
+          <t>• El Distrito, en alianza con la Fundación Gastronomía Social, lanzan una nueva convocatoria dirigida a jóvenes de 18 a 30 años de las localidades de La Candelaria y Santa Fe interesados en formarse en servicio en gastronomía. • Esta formación...</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Jóvenes con Oportunidades abre convocatoria para su ruta de formación en cursos cortos</t>
+          <t>La Escuela Distrital de Emprendimiento ya está en marcha en Kennedy</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -10936,7 +10936,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Empleo</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
@@ -10951,24 +10951,24 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#28dd65106b</t>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#09b7d9045f</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>•La Subdirección para la Juventud anunció la apertura de nuevos cupos en la ruta de formación en cursos cortos, dirigida a jóvenes entre 18 y 28 años que vivan en Bogotá y cuenten con Sisbén IV (A1 a C09). • La ruta combina proyecto de vida, cursos...</t>
+          <t>• 50 jóvenes emprendedores fortalecerán sus proyectos de negocios de la mano de expertos y líderes empresariales. • La Escuela Distrital de Emprendimiento, que llega a su quinta edición, nace de la alianza del Distrito con la ANDI y la Fundación...</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>La Academia Ñam busca jóvenes interesados en el sector de la gastronomía</t>
+          <t>La Academia Ñam abre una nueva convocatoria para jóvenes interesados en el sector de la gastronomía</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -10998,24 +10998,24 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#8622ae2557</t>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#17e48d890a</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>• El Distrito, en alianza con la Fundación Gastronomía Social, lanzan una nueva convocatoria dirigida a jóvenes de 18 a 30 años de las localidades de La Candelaria y Santa Fe interesados en formarse en servicio en gastronomía. • Esta formación...</t>
+          <t>• El Distrito, en alianza con la Fundación Gastronomía Social, lanzan convocatoria dirigida a jóvenes de 18 a 30 años interesados en formarse en servicio en el sector de la gastronomía. • Esta formación gratuita ofrece capacitación a través de...</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>La Escuela Distrital de Emprendimiento ya está en marcha en Kennedy</t>
+          <t>Bogotá ofrece más de 1.500 becas para que jóvenes estudien programas técnicos laborales</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -11045,24 +11045,24 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#09b7d9045f</t>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#e22c14d73a</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>• 50 jóvenes emprendedores fortalecerán sus proyectos de negocios de la mano de expertos y líderes empresariales. • La Escuela Distrital de Emprendimiento, que llega a su quinta edición, nace de la alianza del Distrito con la ANDI y la Fundación...</t>
+          <t>•Se trata de la convocatoria Formación y Educación para el trabajo que les permitirá a los jóvenes de la ciudad formarse en una ocupación que requiere el mercado laboral. •Losbeneficiarios podrán estudiar mercadeo y ventas, mecánica dental, cocina,...</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>La Academia Ñam abre una nueva convocatoria para jóvenes interesados en el sector de la gastronomía</t>
+          <t>Jóvenes de la Casa de la Juventud de Suba aprenden sobre medio ambiente y navegan el río Bogotá</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -11077,7 +11077,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
@@ -11092,24 +11092,24 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#17e48d890a</t>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#ba7949b3a9</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>• El Distrito, en alianza con la Fundación Gastronomía Social, lanzan convocatoria dirigida a jóvenes de 18 a 30 años interesados en formarse en servicio en el sector de la gastronomía. • Esta formación gratuita ofrece capacitación a través de...</t>
+          <t>•Los navegantes confirmaron que los malos olores quedaron en el pasado y hoy se aprecian algunas especies de fauna que han comenzado a retornar a lo largo del cauce. • Gracias a la Corporación Autónoma Regional de Cundinamarca (CAR), encargada de...</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Bogotá ofrece más de 1.500 becas para que jóvenes estudien programas técnicos laborales</t>
+          <t>Está abierta la convocatoria para la Escuela Distrital de Emprendimiento en Kennedy</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -11139,24 +11139,24 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#e22c14d73a</t>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#2acaf10b23</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>•Se trata de la convocatoria Formación y Educación para el trabajo que les permitirá a los jóvenes de la ciudad formarse en una ocupación que requiere el mercado laboral. •Losbeneficiarios podrán estudiar mercadeo y ventas, mecánica dental, cocina,...</t>
+          <t>• Jóvenes emprendedores podrán fortalecer sus proyectos de la mano de expertos y líderes empresariales. • La Escuela Distrital de Emprendimiento nace de la alianza del Distrito con la ANDI y la Fundación ANDI.</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Jóvenes de la Casa de la Juventud de Suba aprenden sobre medio ambiente y navegan el río Bogotá</t>
+          <t>El Frailejón abre sus puertas: Usme estrena nueva Casa de la Juventud</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -11186,104 +11186,10 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#ba7949b3a9</t>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#c7eca5d4bd</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
-        <is>
-          <t>•Los navegantes confirmaron que los malos olores quedaron en el pasado y hoy se aprecian algunas especies de fauna que han comenzado a retornar a lo largo del cauce. • Gracias a la Corporación Autónoma Regional de Cundinamarca (CAR), encargada de...</t>
-        </is>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" t="inlineStr">
-        <is>
-          <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>Está abierta la convocatoria para la Escuela Distrital de Emprendimiento en Kennedy</t>
-        </is>
-      </c>
-      <c r="C234" t="inlineStr">
-        <is>
-          <t>SDIS - Juventud</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr">
-        <is>
-          <t>institucional</t>
-        </is>
-      </c>
-      <c r="E234" t="inlineStr">
-        <is>
-          <t>Educación</t>
-        </is>
-      </c>
-      <c r="F234" t="inlineStr">
-        <is>
-          <t>Bogotá</t>
-        </is>
-      </c>
-      <c r="G234" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="H234" t="inlineStr">
-        <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#2acaf10b23</t>
-        </is>
-      </c>
-      <c r="I234" t="inlineStr">
-        <is>
-          <t>• Jóvenes emprendedores podrán fortalecer sus proyectos de la mano de expertos y líderes empresariales. • La Escuela Distrital de Emprendimiento nace de la alianza del Distrito con la ANDI y la Fundación ANDI.</t>
-        </is>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" t="inlineStr">
-        <is>
-          <t>2025-09-06</t>
-        </is>
-      </c>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>El Frailejón abre sus puertas: Usme estrena nueva Casa de la Juventud</t>
-        </is>
-      </c>
-      <c r="C235" t="inlineStr">
-        <is>
-          <t>SDIS - Juventud</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr">
-        <is>
-          <t>institucional</t>
-        </is>
-      </c>
-      <c r="E235" t="inlineStr">
-        <is>
-          <t>Otra</t>
-        </is>
-      </c>
-      <c r="F235" t="inlineStr">
-        <is>
-          <t>Bogotá</t>
-        </is>
-      </c>
-      <c r="G235" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="H235" t="inlineStr">
-        <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#c7eca5d4bd</t>
-        </is>
-      </c>
-      <c r="I235" t="inlineStr">
         <is>
           <t>• Aunque ya existía una Casa de la Juventud en Usme, la sede se traslada y reinaugura para ofrecer mejores condiciones, ampliar servicios y fortalecer la atención a los jóvenes. • La reapertura se desarrolló con el acompañamiento de la Plataforma...</t>
         </is>

--- a/data/noticias.xlsx
+++ b/data/noticias.xlsx
@@ -466,17 +466,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>“La matan por ser mujer”: a diez años del crimen de Lucía Pérez, su madre insiste en que la Justicia lo califique como femicidio</t>
+          <t>La balcanización criminal de Haití</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Las2orillas</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -491,7 +491,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -501,59 +501,59 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/sociedad/policiales/2026/10/06/la-matan-por-ser-mujer-a-diez-anos-del-crimen-de-lucia-perez-su-madre-insiste-en-que-la-justicia-lo-califique-como-femicidio/</t>
+          <t>https://www.las2orillas.co/la-balcanizacion-criminal-de-haiti/</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Marta Montero, la mamá de la joven asesinada en 2016 en Mar del Plata, atraviesa un nuevo aniversario del hecho mientras espera a que la Suprema Corte Bonaerense resuelva si el asesinato fue o no motivado por la cuestión de género</t>
+          <t>Puerto Príncipe su capital, es la ciudad más violenta del mundo. 200 pandillas ejercen una tenebrosa gobernanza criminalEl artículoLa balcanización criminal de Haitífue publicado originalmente enLas2orillas.co: Historias, voces y noticias de...</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>La balcanización criminal de Haití</t>
+          <t>Prosperidad Social entregará transferencias a beneficiarios afectados por el terremoto sin verificación de condicionalidades y corresponsabilidades</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Las2orillas</t>
+          <t>Prosperidad Social</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.las2orillas.co/la-balcanizacion-criminal-de-haiti/</t>
+          <t>https://prosperidadsocial.gov.co/Noticias/prosperidad-social-entregara-transferencias-a-beneficiarios-afectados-por-el-terremoto-sin-verificacion-de-condicionalidades-y-corresponsabilidades/</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Puerto Príncipe su capital, es la ciudad más violenta del mundo. 200 pandillas ejercen una tenebrosa gobernanza criminalEl artículoLa balcanización criminal de Haitífue publicado originalmente enLas2orillas.co: Historias, voces y noticias de...</t>
+          <t>El Gobierno nacional autorizó a Prosperidad Social a suspender temporalmente las verificaciones de corresponsabilidades que no puedan realizarse por las afectaciones del terremoto. La medida busca evitar que beneficiarios pierdan o retrasen sus...</t>
         </is>
       </c>
     </row>
@@ -565,42 +565,42 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Prosperidad Social entregará transferencias a beneficiarios afectados por el terremoto sin verificación de condicionalidades y corresponsabilidades</t>
+          <t>“La matan por ser mujer”: a diez años del crimen de Lucía Pérez, su madre insiste en que la Justicia lo califique como femicidio</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Prosperidad Social</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://prosperidadsocial.gov.co/Noticias/prosperidad-social-entregara-transferencias-a-beneficiarios-afectados-por-el-terremoto-sin-verificacion-de-condicionalidades-y-corresponsabilidades/</t>
+          <t>https://www.infobae.com/sociedad/policiales/2026/10/06/la-matan-por-ser-mujer-a-diez-anos-del-crimen-de-lucia-perez-su-madre-insiste-en-que-la-justicia-lo-califique-como-femicidio/</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>El Gobierno nacional autorizó a Prosperidad Social a suspender temporalmente las verificaciones de corresponsabilidades que no puedan realizarse por las afectaciones del terremoto. La medida busca evitar que beneficiarios pierdan o retrasen sus...</t>
+          <t>Marta Montero, la mamá de la joven asesinada en 2016 en Mar del Plata, atraviesa un nuevo aniversario del hecho mientras espera a que la Suprema Corte Bonaerense resuelva si el asesinato fue o no motivado por la cuestión de género</t>
         </is>
       </c>
     </row>

--- a/data/noticias.xlsx
+++ b/data/noticias.xlsx
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -513,7 +513,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">

--- a/data/noticias.xlsx
+++ b/data/noticias.xlsx
@@ -466,17 +466,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ocho clubes se consagran campeones en la Valledupar Cup 2026, que reunió a más de 3.500 jóvenes futbolistas</t>
+          <t>Gobierno anticipa anuncio sobre talento colombia: el plan para los jovenes que no estudian ni trabajan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Pulzo</t>
+          <t>Portafolio</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -491,7 +491,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Valledupar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -501,7 +501,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.pulzo.com/deportes/futbol/valledupar-cup-2026-equipos-campeones-impacto-deportivo-y-economico-en-valledupar-colombia-PP5327651A</t>
+          <t>https://www.portafolio.co/economia/gobierno/gobierno-anticipa-anuncio-sobre-talento-colombia-el-plan-para-los-jovenes-que-no-estudian-ni-trabajan-504298</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -509,22 +509,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Polémica en Cúcuta por concejal que se peleó con un joven en un local comercial: “Vaya y mire quién soy yo”</t>
+          <t>Prosperidad Social entregará transferencias a beneficiarios afectados por el terremoto sin verificación de condicionalidades y corresponsabilidades</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Prosperidad Social</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -534,22 +534,22 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Cúcuta</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/10/11/polemica-en-cucuta-por-concejal-que-se-peleo-con-un-joven-en-un-local-comercial-vaya-y-mire-quien-soy-yo/</t>
+          <t>https://prosperidadsocial.gov.co/Noticias/prosperidad-social-entregara-transferencias-a-beneficiarios-afectados-por-el-terremoto-sin-verificacion-de-condicionalidades-y-corresponsabilidades/</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>La secuencia difundida en redes sociales muestra un intercambio verbal entre el cabildante Carlos Dueñas y un hombre al interior de un supermercado de la capital de Norte de Santander</t>
+          <t>El Gobierno nacional autorizó a Prosperidad Social a suspender temporalmente las verificaciones de corresponsabilidades que no puedan realizarse por las afectaciones del terremoto. La medida busca evitar que beneficiarios pierdan o retrasen sus...</t>
         </is>
       </c>
     </row>
@@ -561,12 +561,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Sin el celular en los colegios, los jóvenes tendrán que enfrentarse a nueve horas de soledad</t>
+          <t>Ocho clubes se consagran campeones en la Valledupar Cup 2026, que reunió a más de 3.500 jóvenes futbolistas</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Las2orillas</t>
+          <t>Pulzo</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -576,12 +576,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Valledupar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -591,14 +591,10 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.las2orillas.co/sin-el-celular-en-los-colegios-los-jovenes-tendran-que-enfrentarse-a-nueve-horas-de-soledad/</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Limitar las pantallas en las escuelas es acertado, pero el debate de fondo es reconstruir los vínculos reales que hoy faltan en la adolescenciaEl artículoSin el celular en los colegios, los jóvenes tendrán que enfrentarse a nueve horas de soledadfue...</t>
-        </is>
-      </c>
+          <t>https://www.pulzo.com/deportes/futbol/valledupar-cup-2026-equipos-campeones-impacto-deportivo-y-economico-en-valledupar-colombia-PP5327651A</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -608,17 +604,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Prosperidad Social entregará transferencias a beneficiarios afectados por el terremoto sin verificación de condicionalidades y corresponsabilidades</t>
+          <t>Polémica en Cúcuta por concejal que se peleó con un joven en un local comercial: “Vaya y mire quién soy yo”</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Prosperidad Social</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -628,22 +624,22 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Cúcuta</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://prosperidadsocial.gov.co/Noticias/prosperidad-social-entregara-transferencias-a-beneficiarios-afectados-por-el-terremoto-sin-verificacion-de-condicionalidades-y-corresponsabilidades/</t>
+          <t>https://www.infobae.com/colombia/2026/10/11/polemica-en-cucuta-por-concejal-que-se-peleo-con-un-joven-en-un-local-comercial-vaya-y-mire-quien-soy-yo/</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>El Gobierno nacional autorizó a Prosperidad Social a suspender temporalmente las verificaciones de corresponsabilidades que no puedan realizarse por las afectaciones del terremoto. La medida busca evitar que beneficiarios pierdan o retrasen sus...</t>
+          <t>La secuencia difundida en redes sociales muestra un intercambio verbal entre el cabildante Carlos Dueñas y un hombre al interior de un supermercado de la capital de Norte de Santander</t>
         </is>
       </c>
     </row>

--- a/data/noticias.xlsx
+++ b/data/noticias.xlsx
@@ -466,22 +466,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Gobierno anticipa anuncio sobre talento colombia: el plan para los jovenes que no estudian ni trabajan</t>
+          <t>Prosperidad Social entregará transferencias a beneficiarios afectados por el terremoto sin verificación de condicionalidades y corresponsabilidades</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Portafolio</t>
+          <t>Prosperidad Social</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -491,20 +491,24 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.portafolio.co/economia/gobierno/gobierno-anticipa-anuncio-sobre-talento-colombia-el-plan-para-los-jovenes-que-no-estudian-ni-trabajan-504298</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>https://prosperidadsocial.gov.co/Noticias/prosperidad-social-entregara-transferencias-a-beneficiarios-afectados-por-el-terremoto-sin-verificacion-de-condicionalidades-y-corresponsabilidades/</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>El Gobierno nacional autorizó a Prosperidad Social a suspender temporalmente las verificaciones de corresponsabilidades que no puedan realizarse por las afectaciones del terremoto. La medida busca evitar que beneficiarios pierdan o retrasen sus...</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -514,17 +518,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Prosperidad Social entregará transferencias a beneficiarios afectados por el terremoto sin verificación de condicionalidades y corresponsabilidades</t>
+          <t>Gobierno anticipa anuncio sobre talento colombia: el plan para los jovenes que no estudian ni trabajan</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Prosperidad Social</t>
+          <t>Portafolio</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -534,24 +538,20 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://prosperidadsocial.gov.co/Noticias/prosperidad-social-entregara-transferencias-a-beneficiarios-afectados-por-el-terremoto-sin-verificacion-de-condicionalidades-y-corresponsabilidades/</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>El Gobierno nacional autorizó a Prosperidad Social a suspender temporalmente las verificaciones de corresponsabilidades que no puedan realizarse por las afectaciones del terremoto. La medida busca evitar que beneficiarios pierdan o retrasen sus...</t>
-        </is>
-      </c>
+          <t>https://www.portafolio.co/economia/gobierno/gobierno-anticipa-anuncio-sobre-talento-colombia-el-plan-para-los-jovenes-que-no-estudian-ni-trabajan-504298</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">

--- a/data/noticias.xlsx
+++ b/data/noticias.xlsx
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/data/noticias.xlsx
+++ b/data/noticias.xlsx
@@ -466,22 +466,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Menor de edad rescatada tras quedar atrapada en accidente de tránsito en la variante Bogotá-Melgar, Cundinamarca</t>
+          <t>Prosperidad Social entregará transferencias a beneficiarios afectados por el terremoto sin verificación de condicionalidades y corresponsabilidades</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Pulzo</t>
+          <t>Prosperidad Social</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -501,10 +501,14 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.pulzo.com/nacion/accidente-en-variante-bogota-melgar-menor-atrapada-en-vehiculo-rescata-bomberos-en-melgar-cundinamarca-PP5333484A</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>https://prosperidadsocial.gov.co/Noticias/prosperidad-social-entregara-transferencias-a-beneficiarios-afectados-por-el-terremoto-sin-verificacion-de-condicionalidades-y-corresponsabilidades/</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>El Gobierno nacional autorizó a Prosperidad Social a suspender temporalmente las verificaciones de corresponsabilidades que no puedan realizarse por las afectaciones del terremoto. La medida busca evitar que beneficiarios pierdan o retrasen sus...</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -514,17 +518,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Prosperidad Social entregará transferencias a beneficiarios afectados por el terremoto sin verificación de condicionalidades y corresponsabilidades</t>
+          <t>Menor de edad rescatada tras quedar atrapada en accidente de tránsito en la variante Bogotá-Melgar, Cundinamarca</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Prosperidad Social</t>
+          <t>Pulzo</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -544,14 +548,10 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://prosperidadsocial.gov.co/Noticias/prosperidad-social-entregara-transferencias-a-beneficiarios-afectados-por-el-terremoto-sin-verificacion-de-condicionalidades-y-corresponsabilidades/</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>El Gobierno nacional autorizó a Prosperidad Social a suspender temporalmente las verificaciones de corresponsabilidades que no puedan realizarse por las afectaciones del terremoto. La medida busca evitar que beneficiarios pierdan o retrasen sus...</t>
-        </is>
-      </c>
+          <t>https://www.pulzo.com/nacion/accidente-en-variante-bogota-melgar-menor-atrapada-en-vehiculo-rescata-bomberos-en-melgar-cundinamarca-PP5333484A</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">

--- a/data/noticias.xlsx
+++ b/data/noticias.xlsx
@@ -466,12 +466,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>¿Por qué los colombianos caemos siempre en los mismos errores políticos?</t>
+          <t>Con 110 participantes en el Capitolio Nacional, el Congreso Juvenil pide espacio en la escena política</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,59 +501,59 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.las2orillas.co/por-que-los-colombianos-caemos-siempre-en-los-mismos-errores-politicos/</t>
+          <t>https://www.las2orillas.co/con-110-participantes-en-el-capitolio-nacional-el-congreso-juvenil-pide-espacio-en-la-escena-politica/</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Una llamada a los jóvenes a conocer la historia política colombiana para evitar repetir errores del pasado y votar con verdadero sentido críticoEl artículo¿Por qué los colombianos caemos siempre en los mismos errores políticos?fue publicado...</t>
+          <t>Jóvenes colombianos simularon el ejercicio parlamentario en el Capitolio y abren el debate sobre las curules especiales para las nuevas generacionesEl artículoCon 110 participantes en el Capitolio Nacional, el Congreso Juvenil pide espacio en la...</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Por qué la llamada de su mamá que tardó 21 años en recibir salvó al humorista Iván Marín del suicidio</t>
+          <t>Prosperidad Social entregará transferencias a beneficiarios afectados por el terremoto sin verificación de condicionalidades y corresponsabilidades</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Las2orillas</t>
+          <t>Prosperidad Social</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.las2orillas.co/por-que-la-llamada-de-su-mama-que-tardo-21-anos-en-recibir-salvo-al-humorista-ivan-marin-del-suicidio/</t>
+          <t>https://prosperidadsocial.gov.co/Noticias/prosperidad-social-entregara-transferencias-a-beneficiarios-afectados-por-el-terremoto-sin-verificacion-de-condicionalidades-y-corresponsabilidades/</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>En el pódcast ‘La Habitación Invisible’, el comediante recordó la crisis existencial de la juventud y su recuperación en la que la comedia es protagonistaEl artículoPor qué la llamada de su mamá que tardó 21 años en recibir salvó al humorista Iván...</t>
+          <t>El Gobierno nacional autorizó a Prosperidad Social a suspender temporalmente las verificaciones de corresponsabilidades que no puedan realizarse por las afectaciones del terremoto. La medida busca evitar que beneficiarios pierdan o retrasen sus...</t>
         </is>
       </c>
     </row>
@@ -565,17 +565,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Prosperidad Social entregará transferencias a beneficiarios afectados por el terremoto sin verificación de condicionalidades y corresponsabilidades</t>
+          <t>¿Por qué los colombianos caemos siempre en los mismos errores políticos?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Prosperidad Social</t>
+          <t>Las2orillas</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -585,22 +585,22 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://prosperidadsocial.gov.co/Noticias/prosperidad-social-entregara-transferencias-a-beneficiarios-afectados-por-el-terremoto-sin-verificacion-de-condicionalidades-y-corresponsabilidades/</t>
+          <t>https://www.las2orillas.co/por-que-los-colombianos-caemos-siempre-en-los-mismos-errores-politicos/</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>El Gobierno nacional autorizó a Prosperidad Social a suspender temporalmente las verificaciones de corresponsabilidades que no puedan realizarse por las afectaciones del terremoto. La medida busca evitar que beneficiarios pierdan o retrasen sus...</t>
+          <t>Una llamada a los jóvenes a conocer la historia política colombiana para evitar repetir errores del pasado y votar con verdadero sentido críticoEl artículo¿Por qué los colombianos caemos siempre en los mismos errores políticos?fue publicado...</t>
         </is>
       </c>
     </row>

--- a/data/noticias.xlsx
+++ b/data/noticias.xlsx
@@ -466,22 +466,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Con 110 participantes en el Capitolio Nacional, el Congreso Juvenil pide espacio en la escena política</t>
+          <t>Prosperidad Social entregará transferencias a beneficiarios afectados por el terremoto sin verificación de condicionalidades y corresponsabilidades</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Las2orillas</t>
+          <t>Prosperidad Social</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -491,22 +491,22 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.las2orillas.co/con-110-participantes-en-el-capitolio-nacional-el-congreso-juvenil-pide-espacio-en-la-escena-politica/</t>
+          <t>https://prosperidadsocial.gov.co/Noticias/prosperidad-social-entregara-transferencias-a-beneficiarios-afectados-por-el-terremoto-sin-verificacion-de-condicionalidades-y-corresponsabilidades/</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Jóvenes colombianos simularon el ejercicio parlamentario en el Capitolio y abren el debate sobre las curules especiales para las nuevas generacionesEl artículoCon 110 participantes en el Capitolio Nacional, el Congreso Juvenil pide espacio en la...</t>
+          <t>El Gobierno nacional autorizó a Prosperidad Social a suspender temporalmente las verificaciones de corresponsabilidades que no puedan realizarse por las afectaciones del terremoto. La medida busca evitar que beneficiarios pierdan o retrasen sus...</t>
         </is>
       </c>
     </row>
@@ -518,17 +518,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Prosperidad Social entregará transferencias a beneficiarios afectados por el terremoto sin verificación de condicionalidades y corresponsabilidades</t>
+          <t>Con 110 participantes en el Capitolio Nacional, el Congreso Juvenil pide espacio en la escena política</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Prosperidad Social</t>
+          <t>Las2orillas</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -538,22 +538,22 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://prosperidadsocial.gov.co/Noticias/prosperidad-social-entregara-transferencias-a-beneficiarios-afectados-por-el-terremoto-sin-verificacion-de-condicionalidades-y-corresponsabilidades/</t>
+          <t>https://www.las2orillas.co/con-110-participantes-en-el-capitolio-nacional-el-congreso-juvenil-pide-espacio-en-la-escena-politica/</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>El Gobierno nacional autorizó a Prosperidad Social a suspender temporalmente las verificaciones de corresponsabilidades que no puedan realizarse por las afectaciones del terremoto. La medida busca evitar que beneficiarios pierdan o retrasen sus...</t>
+          <t>Jóvenes colombianos simularon el ejercicio parlamentario en el Capitolio y abren el debate sobre las curules especiales para las nuevas generacionesEl artículoCon 110 participantes en el Capitolio Nacional, el Congreso Juvenil pide espacio en la...</t>
         </is>
       </c>
     </row>

--- a/data/noticias.xlsx
+++ b/data/noticias.xlsx
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/data/noticias.xlsx
+++ b/data/noticias.xlsx
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/data/noticias.xlsx
+++ b/data/noticias.xlsx
@@ -466,27 +466,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Festival de Libros para Niños y Jóvenes celebra su edición 20 en La Milla Encantada del Bronx Distrito Creativo en Bogotá</t>
+          <t>Prosperidad Social entregará transferencias a beneficiarios afectados por el terremoto sin verificación de condicionalidades y corresponsabilidades</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Pulzo</t>
+          <t>Prosperidad Social</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Cultura y deporte</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -501,10 +501,14 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.pulzo.com/nacion/bogota/festival-de-libros-para-ninos-y-jovenes-2026-en-bogota-actividades-fecha-y-lugar-PP5345083A</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>https://prosperidadsocial.gov.co/Noticias/prosperidad-social-entregara-transferencias-a-beneficiarios-afectados-por-el-terremoto-sin-verificacion-de-condicionalidades-y-corresponsabilidades/</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>El Gobierno nacional autorizó a Prosperidad Social a suspender temporalmente las verificaciones de corresponsabilidades que no puedan realizarse por las afectaciones del terremoto. La medida busca evitar que beneficiarios pierdan o retrasen sus...</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -514,12 +518,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Guapi: donde navegar se convierte en liderazgo juvenil para transformar el Pacífico colombiano</t>
+          <t>Festival de Libros para Niños y Jóvenes celebra su edición 20 en La Milla Encantada del Bronx Distrito Creativo en Bogotá</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Las2orillas</t>
+          <t>Pulzo</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -529,29 +533,25 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Protección</t>
+          <t>Cultura y deporte</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.las2orillas.co/guapi-donde-navegar-se-convierte-en-liderazgo-juvenil-para-transformar-el-pacifico-colombiano/</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Desde Guapi hasta Cali, Angie Vanessa Montaño demuestra que la distancia geográfica y el abandono estatal no pueden seguir frenando a la juventud afroEl artículoGuapi: donde navegar se convierte en liderazgo juvenil para transformar el Pacífico...</t>
-        </is>
-      </c>
+          <t>https://www.pulzo.com/nacion/bogota/festival-de-libros-para-ninos-y-jovenes-2026-en-bogota-actividades-fecha-y-lugar-PP5345083A</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -561,7 +561,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>De huir del conflicto a llevar agua segura y sostenible a las aulas: el liderazgo de Mabel Garcés en el Cauca</t>
+          <t>Guapi: donde navegar se convierte en liderazgo juvenil para transformar el Pacífico colombiano</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -576,12 +576,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Protección</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Popayán</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -591,12 +591,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.las2orillas.co/de-huir-del-conflicto-a-llevar-agua-segura-y-sostenible-a-las-aulas-el-liderazgo-de-mabel-garces-en-el-cauca/</t>
+          <t>https://www.las2orillas.co/guapi-donde-navegar-se-convierte-en-liderazgo-juvenil-para-transformar-el-pacifico-colombiano/</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Desplazada en su niñez por la violencia, esta joven llevó a un colegio de Puerto Tejada un sistema de agua limpia pensado y cuidado por la propia comunidaEl artículoDe huir del conflicto a llevar agua segura y sostenible a las aulas: el liderazgo de...</t>
+          <t>Desde Guapi hasta Cali, Angie Vanessa Montaño demuestra que la distancia geográfica y el abandono estatal no pueden seguir frenando a la juventud afroEl artículoGuapi: donde navegar se convierte en liderazgo juvenil para transformar el Pacífico...</t>
         </is>
       </c>
     </row>
@@ -608,42 +608,42 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Prosperidad Social entregará transferencias a beneficiarios afectados por el terremoto sin verificación de condicionalidades y corresponsabilidades</t>
+          <t>De huir del conflicto a llevar agua segura y sostenible a las aulas: el liderazgo de Mabel Garcés en el Cauca</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Prosperidad Social</t>
+          <t>Las2orillas</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Popayán</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://prosperidadsocial.gov.co/Noticias/prosperidad-social-entregara-transferencias-a-beneficiarios-afectados-por-el-terremoto-sin-verificacion-de-condicionalidades-y-corresponsabilidades/</t>
+          <t>https://www.las2orillas.co/de-huir-del-conflicto-a-llevar-agua-segura-y-sostenible-a-las-aulas-el-liderazgo-de-mabel-garces-en-el-cauca/</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>El Gobierno nacional autorizó a Prosperidad Social a suspender temporalmente las verificaciones de corresponsabilidades que no puedan realizarse por las afectaciones del terremoto. La medida busca evitar que beneficiarios pierdan o retrasen sus...</t>
+          <t>Desplazada en su niñez por la violencia, esta joven llevó a un colegio de Puerto Tejada un sistema de agua limpia pensado y cuidado por la propia comunidaEl artículoDe huir del conflicto a llevar agua segura y sostenible a las aulas: el liderazgo de...</t>
         </is>
       </c>
     </row>
